--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF2FC24-8428-43AE-920B-1F71F78F97F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AD3BCB-6882-40CB-BE56-C90C1CB4DE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="234">
   <si>
     <t>№ п/п</t>
   </si>
@@ -54,21 +54,21 @@
     <t>ЛГУП-7511</t>
   </si>
   <si>
+    <t>ЛГУП-7564</t>
+  </si>
+  <si>
+    <t>м</t>
+  </si>
+  <si>
     <t>кг</t>
   </si>
   <si>
-    <t>ЛГУП-7564</t>
-  </si>
-  <si>
     <t>м2</t>
   </si>
   <si>
     <t>Лист S=6 Ст.09Г2С ГОСТ 19281-89</t>
   </si>
   <si>
-    <t>м</t>
-  </si>
-  <si>
     <t>Ящик пластиковый396х297х280</t>
   </si>
   <si>
@@ -96,15 +96,21 @@
     <t>Ремонт двери 1900х1000мм(уст.ка вент. решеток, установка цепи и фиксатора, покраска)</t>
   </si>
   <si>
+    <t>Лампа индикации ADDS D22 LED белая 220В AC/DC ЛK-22 IP55 25152DEK Dekraft</t>
+  </si>
+  <si>
+    <t>ЛГУП-7654</t>
+  </si>
+  <si>
     <t>Резьбовой крепежный элемент с наружной резьбой РКН-20 У2 IP54 ЗЭТА</t>
   </si>
   <si>
-    <t>ЛГУП-7654</t>
-  </si>
-  <si>
     <t>Электроприв четвер.взры. ГЗ-ОФВ-300/28М 1х220 DN80PN63 L=452 УХЛ (исп. фл. J)</t>
   </si>
   <si>
+    <t>Аварийное освещение Вега 60 с БАП 2Ex Тех 1ExmbIIC T6 Gb X, IP65</t>
+  </si>
+  <si>
     <t>Пломба 1-6х10-АД-1М ГОСТ 18677-73</t>
   </si>
   <si>
@@ -120,24 +126,21 @@
     <t>мм</t>
   </si>
   <si>
+    <t>Извещатель пожарный тепловой взрывозащищенный 101-07е 1Ex db [ia Ga] IIC Т4 Gb Х IP66</t>
+  </si>
+  <si>
     <t>Винт для обеспечения электрического контакта крышек ( М 5 х 8) арт.CM030508</t>
   </si>
   <si>
-    <t>Аварийное освещение Вега 60 с БАП 2Ex Тех 1ExmbIIC T6 Gb X, IP65</t>
-  </si>
-  <si>
-    <t>Извещатель пожарный тепловой взрывозащищенный 101-07е 1Ex db [ia Ga] IIC Т4 Gb Х IP66</t>
-  </si>
-  <si>
-    <t>Лампа индикации ADDS D22 LED белая 220В AC/DC ЛK-22 IP55 25152DEK Dekraft</t>
+    <t>Рулетка  7,5м х 25мм обрезиненный корпус (3 фиксатора, зацеп с магнитом)</t>
+  </si>
+  <si>
+    <t>ЛГУП-7867</t>
   </si>
   <si>
     <t>Бита (вставка) Spline М 8  L=30мм</t>
   </si>
   <si>
-    <t>ЛГУП-7867</t>
-  </si>
-  <si>
     <t>Ветошь /рул./</t>
   </si>
   <si>
@@ -165,27 +168,27 @@
     <t>Перчатки 4нит. 10кл. (черные) (пара)</t>
   </si>
   <si>
-    <t>Рулетка  7,5м х 25мм обрезиненный корпус (3 фиксатора, зацеп с магнитом)</t>
+    <t>Маркер по металлу черный тонкий</t>
+  </si>
+  <si>
+    <t>НТУП-018192</t>
+  </si>
+  <si>
+    <t>Маркер по металлу белый</t>
   </si>
   <si>
     <t>Маркер по металлу красный</t>
   </si>
   <si>
-    <t>НТУП-018192</t>
-  </si>
-  <si>
-    <t>Маркер по металлу белый</t>
-  </si>
-  <si>
-    <t>Маркер по металлу черный тонкий</t>
+    <t>Паронит 3 мм</t>
+  </si>
+  <si>
+    <t>лист</t>
   </si>
   <si>
     <t>Паронит 2мм</t>
   </si>
   <si>
-    <t>лист</t>
-  </si>
-  <si>
     <t>Ключи обмедненные</t>
   </si>
   <si>
@@ -195,9 +198,6 @@
     <t>Мел сварщика белый</t>
   </si>
   <si>
-    <t>Паронит 3 мм</t>
-  </si>
-  <si>
     <t>ЛГУП-7998</t>
   </si>
   <si>
@@ -216,84 +216,21 @@
     <t>ЛГУП-8015</t>
   </si>
   <si>
-    <t>Пластина R390-11 11т308 М -РМ 1130</t>
-  </si>
-  <si>
-    <t>ЛГУП-8023</t>
-  </si>
-  <si>
-    <t>НТУП-018253</t>
-  </si>
-  <si>
-    <t>Отвод 57х6, 09Г2С ГОСТ 17375-2001</t>
-  </si>
-  <si>
-    <t>отвод 89х8, 09Г2С ГОСТ 17375-2001</t>
-  </si>
-  <si>
-    <t>Отвод 114х8 ст 09Г2с</t>
-  </si>
-  <si>
-    <t>Отвод 159х8, 09Г2С ГОСТ 17375-2001</t>
-  </si>
-  <si>
-    <t>Заглушка 114х8 09Г2С ГОСТ 17379-2001</t>
-  </si>
-  <si>
-    <t>Отвод 219х8</t>
-  </si>
-  <si>
-    <t>Заглушка 57х6 ст.09Г2С ГОСТ 17379-01</t>
-  </si>
-  <si>
-    <t>Отвод 76х8, ст09г2с ГОСТ 17375-2001</t>
-  </si>
-  <si>
-    <t>НТУП-018254</t>
-  </si>
-  <si>
-    <t>Швеллер 16П (12м) ГОСТ  8240-97</t>
-  </si>
-  <si>
-    <t>Труба 159x8,0 ГОСТ 8732-78/09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба 114x8,0 ГОСТ 8732-78/09Г2С ГОСТ 8731-74</t>
+    <t>Шестиграник 27-h12 ГОСТ 8560-78/(ст.13ХФА)</t>
+  </si>
+  <si>
+    <t>ЛГ00-000047</t>
+  </si>
+  <si>
+    <t>ЛГ00-000048</t>
+  </si>
+  <si>
+    <t>Смеси асфальтобетонные плотные мелкозернистые, тип А, марка 1</t>
   </si>
   <si>
     <t>т</t>
   </si>
   <si>
-    <t>Труба 76х8 ст. 09Г2С ГОСТ 8732-78</t>
-  </si>
-  <si>
-    <t>т</t>
-  </si>
-  <si>
-    <t>Шестиграник 27-h12 ГОСТ 8560-78/(ст.13ХФА)</t>
-  </si>
-  <si>
-    <t>ЛГ00-000047</t>
-  </si>
-  <si>
-    <t>Ноутбук</t>
-  </si>
-  <si>
-    <t>НТУП-018276</t>
-  </si>
-  <si>
-    <t>Мышь проводная</t>
-  </si>
-  <si>
-    <t>ЛГУП-8039</t>
-  </si>
-  <si>
-    <t>ЛГ00-000048</t>
-  </si>
-  <si>
-    <t>Смеси асфальтобетонные плотные мелкозернистые, тип А, марка 1</t>
-  </si>
-  <si>
     <t>ЛГУП-8043</t>
   </si>
   <si>
@@ -303,126 +240,156 @@
     <t>ЛГУП-8046</t>
   </si>
   <si>
-    <t>Отвод 90-32х4 ст.12Х18Н10Т ГОСТ 17375-2001</t>
-  </si>
-  <si>
-    <t>ЛГУП-8049</t>
-  </si>
-  <si>
-    <t>Труба D32х4 ГОСТ 8732-78/ 12Х18Н10Т ГОСТ 5632-2014</t>
+    <t>Индустриальное масло  Gazpromneft  Industrial 40 ( И-40А ) 205л</t>
+  </si>
+  <si>
+    <t>ЛГУП-8058</t>
+  </si>
+  <si>
+    <t>Кран шаровый ДУ80 Ру 40 под приварку</t>
+  </si>
+  <si>
+    <t>НТУП-018299</t>
+  </si>
+  <si>
+    <t>ЛГУП-8060</t>
+  </si>
+  <si>
+    <t>ЛГУП-8061</t>
+  </si>
+  <si>
+    <t>(не исп1) шт</t>
+  </si>
+  <si>
+    <t>Шайба 5Л ГОСТ 6402-70</t>
+  </si>
+  <si>
+    <t>ЛГУП-8062</t>
+  </si>
+  <si>
+    <t>Коробка соединительно-разветвительная взрывозащищенная КСРВ-2-2/0-К</t>
+  </si>
+  <si>
+    <t>Текстолит 4мм (90х60)</t>
+  </si>
+  <si>
+    <t>Саморез-шуруп острый (оцинк.) 2,2х4,5 ГОСТ 1144-80</t>
+  </si>
+  <si>
+    <t>Стойка для печатных плат (шестигр., латунь) М4, 27мм ГОСТ 20862-81</t>
+  </si>
+  <si>
+    <t>Гофрокороб 395*155*155</t>
+  </si>
+  <si>
+    <t>Проволока КО 1,0 ГОСТ 792-67</t>
+  </si>
+  <si>
+    <t>Лента упаковочная полипропиленовая 12х0,6мм</t>
+  </si>
+  <si>
+    <t>Круг D30 Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D24 Ст.45 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D20 Ст.35 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D32 Ст. 45 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Сетка полутомпаковая 008Н Л80 ГОСТ 6613-86</t>
+  </si>
+  <si>
+    <t>Проволока D1.8 Ст.60C2А ГОСТ14963-78</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-5 ГОСТ 19903/20-ТВ1-М1-КИ-ТО ГОСТ1577</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-5 ГОСТ 19903-74 / 2-IV-Н Ст.3кп ГОСТ 16523-97 (кг)</t>
   </si>
   <si>
     <t>Лист Б-ПН-10 ГОСТ 19903-74 / 2-IV-Н Ст.3кп ГОСТ 16523-97 (кг)</t>
   </si>
   <si>
-    <t>Лист Б-ПН-5 ГОСТ 19903-74 / 2-IV-Н Ст.3кп ГОСТ 16523-97 (кг)</t>
-  </si>
-  <si>
-    <t>Лист Б-ПН-5 ГОСТ 19903/20-ТВ1-М1-КИ-ТО ГОСТ1577</t>
-  </si>
-  <si>
-    <t>Сетка полутомпаковая 008Н Л80 ГОСТ 6613-86</t>
-  </si>
-  <si>
-    <t>Проволока D1.8 Ст.60C2А ГОСТ14963-78</t>
-  </si>
-  <si>
-    <t>Круг D20 Ст.35 ГОСТ 1050-88</t>
+    <t>Лист алюм. анод. сатин (черн/бел) 1,0</t>
   </si>
   <si>
     <t>Круг D90 Ст.35 ГОСт1050-88</t>
   </si>
   <si>
-    <t>Круг D24 Ст.45 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Круг D30 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Круг D32 Ст. 45 ГОСТ 1050-88</t>
+    <t>Круг D90 Ст.20Х13 ГОСТ 5632-72</t>
+  </si>
+  <si>
+    <t>Круг D80 Ст.45 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D18 Ст.20Х13 ГОСТ 5949-75</t>
+  </si>
+  <si>
+    <t>Круг D110 Ст.12Х18Н10Т ГОСТ 5949-75</t>
+  </si>
+  <si>
+    <t>Круг D100 Ст.35 ГOСТ 1050-2013</t>
+  </si>
+  <si>
+    <t>Круг D75 Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D70 Ст.20Х13 ГОСТ5632-72</t>
+  </si>
+  <si>
+    <t>Круг D65 Ст.35 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D65 Ст.3 ГОСТ 535-2005</t>
+  </si>
+  <si>
+    <t>Круг D60 Ст.35 ГОСТ 1050-88</t>
   </si>
   <si>
     <t>Круг D4 Ст.10 ГОСТ 1050-88</t>
   </si>
   <si>
-    <t>Гофрокороб 395*155*155</t>
+    <t>Круг D45 Ст.45 ГОСТ 1050-2013</t>
+  </si>
+  <si>
+    <t>Круг D45 Ст.3 ГОСТ 535-2005</t>
+  </si>
+  <si>
+    <t>Круг D80 Ст.35 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D75 Ст.35 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D75 Ст.20Х13 ГОСТ 5632-72</t>
   </si>
   <si>
     <t>Круг D42 Ст.14Х17Н2 ГОСТ 5949-75</t>
   </si>
   <si>
-    <t>Круг D80 Ст.45 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Круг D90 Ст.20Х13 ГОСТ 5632-72</t>
-  </si>
-  <si>
-    <t>Круг D18 Ст.20Х13 ГОСТ 5949-75</t>
-  </si>
-  <si>
-    <t>Круг D110 Ст.12Х18Н10Т ГОСТ 5949-75</t>
-  </si>
-  <si>
-    <t>Круг D100 Ст.35 ГOСТ 1050-2013</t>
-  </si>
-  <si>
-    <t>Круг D75 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Лист алюм. анод. сатин (черн/бел) 1,0</t>
-  </si>
-  <si>
     <t>Круг D20 Ст.20 ГОСТ 1050-88</t>
   </si>
   <si>
-    <t>Круг D75 Ст.20Х13 ГОСТ 5632-72</t>
-  </si>
-  <si>
-    <t>Круг D75 Ст.35 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Проволока КО 1,0 ГОСТ 792-67</t>
-  </si>
-  <si>
-    <t>Лента упаковочная полипропиленовая 12х0,6мм</t>
-  </si>
-  <si>
-    <t>Круг D80 Ст.35 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Круг D45 Ст.3 ГОСТ 535-2005</t>
-  </si>
-  <si>
-    <t>Круг D45 Ст.45 ГОСТ 1050-2013</t>
-  </si>
-  <si>
-    <t>Круг D60 Ст.35 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Круг D65 Ст.3 ГОСТ 535-2005</t>
-  </si>
-  <si>
-    <t>Круг D65 Ст.35 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Круг D70 Ст.20Х13 ГОСТ5632-72</t>
+    <t>Днище 377х12-09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Днище 219х4-25 16ГС-3 ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Днище 1020х14-09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Днище 820х12-09Г2С ГОСТ 6533-78</t>
   </si>
   <si>
     <t>Днище 530х12-09Г2С ГОСТ 6533-78</t>
   </si>
   <si>
-    <t>Днище 820х12-09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Днище 377х12-09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Днище 219х4-25 16ГС-3 ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Днище 1020х14-09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
     <t>Днище 720х12-09Г2С ГОСТ 6533-78</t>
   </si>
   <si>
@@ -459,6 +426,72 @@
     <t>Пластина анкерная 120</t>
   </si>
   <si>
+    <t>Пластина для заземления PTCE арт. 37501</t>
+  </si>
+  <si>
+    <t>Плата печатная ПСМ.11.00.01.01-02</t>
+  </si>
+  <si>
+    <t>Плата питания ПСМ.11.00.00.01-02</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Уплотнительный модуль МКС 20/О 5-14мм</t>
+  </si>
+  <si>
+    <t>Уплотнительный модуль МКС 40/Ø 17-34 мм</t>
+  </si>
+  <si>
+    <t>Наконечник НВИ 2-5 вилка 1,5-2,5мм SQ0503-0005 TDM</t>
+  </si>
+  <si>
+    <t>Припой с канифолью ПОС 61 d=1,0мм ГОСТ 21931-76 (Sn61; Pb39)</t>
+  </si>
+  <si>
+    <t>Держатель проводника Rd8, DEHNGRIP NIRO h20 с отв.8мм М6</t>
+  </si>
+  <si>
+    <t>Диод КД209А ТТЗ.362.008 ТУ</t>
+  </si>
+  <si>
+    <t>Заглушка  25х25 для трубы профильной ПВД черная</t>
+  </si>
+  <si>
+    <t>Заглушка 10707 Legrand DPL 65х195</t>
+  </si>
+  <si>
+    <t>Лента самоклеящаяся уплотнительная ППЭ 5х15 МКС</t>
+  </si>
+  <si>
+    <t>Трубка для фильтра 1/4" Гейзер</t>
+  </si>
+  <si>
+    <t>MV-клемма проводника Rd8</t>
+  </si>
+  <si>
+    <t>Кабель-канал 10453 Legrand DPL 195х65 (2м)</t>
+  </si>
+  <si>
+    <t>Компрессионный блок МКС КБ 120</t>
+  </si>
+  <si>
+    <t>Консоль с опорой ML 300мм (шт)</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р307(-60+40) 2-6х20НК(А)-1х20НК(В)-6х20НК(С)-4х26(П) 1ЕхеLLCGbXT6, ip66</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р402(-60+40)12-2х20НК(А)-2х20НК(С)-1,5х11(П), 1ЕхеLLCGbXT6, ip66, 110х75х55</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р403(-60+40) 2-4х20НК(А)-4х20НК(С)-2,5х20(П),1ЕхеLLCGbXT6, ip66, 160х175х55</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р407(-60+40) 2-8х20НК(А)-8х20НК(С)-2,5х31(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
+  </si>
+  <si>
     <t>Короб ПВХ 40х40 мм</t>
   </si>
   <si>
@@ -513,61 +546,34 @@
     <t>Металлорукав в ПВХ изоляции РЗ-ЦП-15</t>
   </si>
   <si>
-    <t>Наконечник НВИ 2-5 вилка 1,5-2,5мм SQ0503-0005 TDM</t>
-  </si>
-  <si>
-    <t>MV-клемма проводника Rd8</t>
-  </si>
-  <si>
-    <t>Припой с канифолью ПОС 61 d=1,0мм ГОСТ 21931-76 (Sn61; Pb39)</t>
-  </si>
-  <si>
-    <t>Лента самоклеящаяся уплотнительная ППЭ 5х15 МКС</t>
-  </si>
-  <si>
-    <t>Трубка для фильтра 1/4" Гейзер</t>
-  </si>
-  <si>
-    <t>Угол горизонтальный CPO 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Уплотнительный модуль МКС 20/О 5-14мм</t>
-  </si>
-  <si>
-    <t>Уплотнительный модуль МКС 40/Ø 17-34 мм</t>
-  </si>
-  <si>
-    <t>Держатель проводника Rd8, DEHNGRIP NIRO h20 с отв.8мм М6</t>
-  </si>
-  <si>
-    <t>Диод КД209А ТТЗ.362.008 ТУ</t>
-  </si>
-  <si>
-    <t>Заглушка  25х25 для трубы профильной ПВД черная</t>
-  </si>
-  <si>
-    <t>Заглушка 10707 Legrand DPL 65х195</t>
-  </si>
-  <si>
-    <t>Кабель-канал 10453 Legrand DPL 195х65 (2м)</t>
-  </si>
-  <si>
-    <t>Компрессионный блок МКС КБ 120</t>
-  </si>
-  <si>
-    <t>Консоль с опорой ML 300мм (шт)</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р307(-60+40) 2-6х20НК(А)-1х20НК(В)-6х20НК(С)-4х26(П) 1ЕхеLLCGbXT6, ip66</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р402(-60+40)12-2х20НК(А)-2х20НК(С)-1,5х11(П), 1ЕхеLLCGbXT6, ip66, 110х75х55</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р403(-60+40) 2-4х20НК(А)-4х20НК(С)-2,5х20(П),1ЕхеLLCGbXT6, ip66, 160х175х55</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р407(-60+40) 2-8х20НК(А)-8х20НК(С)-2,5х31(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
+    <t>Выключатель двухклавишный IP55</t>
+  </si>
+  <si>
+    <t>Геркон КЭМ-2</t>
+  </si>
+  <si>
+    <t>Держатель для полосы заземления К-188 У2 (цинк)</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (100 х 50)</t>
+  </si>
+  <si>
+    <t>Считыватель бесконтактный для proxi-карт, RD 26-REH-КМ АЯКС Ex mb IIC T5 Gb X , IP67</t>
+  </si>
+  <si>
+    <t>Считыватель бесконтактный для proxi-карт, Proxy-3МA IP20</t>
+  </si>
+  <si>
+    <t>Скоба металлическая СМО 16-17 49152 КВТ</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с наружной резьбой РКН-15 (ММРн-15)</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
+  </si>
+  <si>
+    <t>Профиль PSM (3000) арт. 34181</t>
   </si>
   <si>
     <t>Коробка клеммная МТ Р407(-60+40) 2-8х20НК(А)-8х20НК(С)-4х26(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
@@ -576,60 +582,21 @@
     <t>Коробка распаячная КМ41242 IP55</t>
   </si>
   <si>
+    <t>Крышка Угол горизонтальный CPO 90 (100х50)</t>
+  </si>
+  <si>
+    <t>Крышка на Угол вертикальный внешний CD 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Крышка (50х15х3000)</t>
+  </si>
+  <si>
+    <t>Крышка (100х15х3000)</t>
+  </si>
+  <si>
     <t>Крепление для труб ПВХ с защелкой, 16 мм</t>
   </si>
   <si>
-    <t>Крышка (100х15х3000)</t>
-  </si>
-  <si>
-    <t>Крышка (50х15х3000)</t>
-  </si>
-  <si>
-    <t>Крышка на Угол вертикальный внешний CD 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Крышка Угол горизонтальный CPO 90 (100х50)</t>
-  </si>
-  <si>
-    <t>Профиль PSM (3000) арт. 34181</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с наружной резьбой РКН-15 (ММРн-15)</t>
-  </si>
-  <si>
-    <t>Скоба металлическая СМО 16-17 49152 КВТ</t>
-  </si>
-  <si>
-    <t>Считыватель бесконтактный для proxi-карт, Proxy-3МA IP20</t>
-  </si>
-  <si>
-    <t>Считыватель бесконтактный для proxi-карт, RD 26-REH-КМ АЯКС Ex mb IIC T5 Gb X , IP67</t>
-  </si>
-  <si>
-    <t>Угол горизонтальный CPO 90 (100 х 50)</t>
-  </si>
-  <si>
-    <t>Выключатель двухклавишный IP55</t>
-  </si>
-  <si>
-    <t>Геркон КЭМ-2</t>
-  </si>
-  <si>
-    <t>Держатель для полосы заземления К-188 У2 (цинк)</t>
-  </si>
-  <si>
-    <t>Плата питания ПСМ.11.00.00.01-02</t>
-  </si>
-  <si>
-    <t>Плата печатная ПСМ.11.00.01.01-02</t>
-  </si>
-  <si>
-    <t>Пластина для заземления PTCE арт. 37501</t>
-  </si>
-  <si>
     <t>Очки защитные для токарей.О15.</t>
   </si>
   <si>
@@ -642,93 +609,57 @@
     <t>Пост аварийной сигнализации загазованности в/защ.ПАСВ1-П-75-1Ж1К-В1 (=24В, -60..+40С) 1ExsIICT6</t>
   </si>
   <si>
+    <t>Магнит МС3 ЦО 14,5/4 ТУ 3498-005-12591667-2014</t>
+  </si>
+  <si>
+    <t>Пружина №442 НТ.110.000.007.0</t>
+  </si>
+  <si>
+    <t>Пружина крышки НТ.200.004.003.0</t>
+  </si>
+  <si>
+    <t>Пружина №467 НТ.200.000.029.0</t>
+  </si>
+  <si>
     <t>Пружина НТ.3.02.00.00.002-01</t>
   </si>
   <si>
-    <t>Пружина №467 НТ.200.000.029.0</t>
-  </si>
-  <si>
-    <t>Пружина крышки НТ.200.004.003.0</t>
-  </si>
-  <si>
-    <t>Пружина №442 НТ.110.000.007.0</t>
-  </si>
-  <si>
-    <t>Магнит МС3 ЦО 14,5/4 ТУ 3498-005-12591667-2014</t>
+    <t>Грунт-эмаль Дюропокс ДТМ 80 (внутрянка)</t>
+  </si>
+  <si>
+    <t>Дверь левс доводчиком2000х1000мм(ВхШ) полотно RAL 9003(белый)/коробка(RAL 9003)(белый)с цепью</t>
+  </si>
+  <si>
+    <t>Клапан обратный поворотный КОП 80-40 УХЛ1 19лс53нж (исп. фл. 3)</t>
+  </si>
+  <si>
+    <t>Задвижка клиновая литая ЗКЛ 80-40 УХЛ1 30лс15нж, класс герм.А (ряд 2, исп.фл.3)</t>
+  </si>
+  <si>
+    <t>Легкосбрасываемое окнная конструкция 1200х1100 мм / ПВХ-профили морозост. исп, RAL 9003 белый</t>
+  </si>
+  <si>
+    <t>Задвижка клиновая литая ЗКЛ 50-40 УХЛ1 30С15нж, класс герм.А (ряд 2, исп.фл.3)</t>
   </si>
   <si>
     <t>Задвижка ЗКС 31лс77нж Ду 15 Ру 40 МПа (соединение муфтовое Rc 1/2)</t>
   </si>
   <si>
-    <t>Задвижка клиновая литая ЗКЛ 50-40 УХЛ1 30С15нж, класс герм.А (ряд 2, исп.фл.3)</t>
-  </si>
-  <si>
-    <t>Задвижка клиновая литая ЗКЛ 80-40 УХЛ1 30лс15нж, класс герм.А (ряд 2, исп.фл.3)</t>
-  </si>
-  <si>
-    <t>Клапан обратный поворотный КОП 80-40 УХЛ1 19лс53нж (исп. фл. 3)</t>
-  </si>
-  <si>
-    <t>Дверь левс доводчиком2000х1000мм(ВхШ) полотно RAL 9003(белый)/коробка(RAL 9003)(белый)с цепью</t>
-  </si>
-  <si>
-    <t>Легкосбрасываемое окнная конструкция 1200х1100 мм / ПВХ-профили морозост. исп, RAL 9003 белый</t>
-  </si>
-  <si>
-    <t>Грунт-эмаль Дюропокс ДТМ 80 (внутрянка)</t>
+    <t>Болт М8-6gх25.58.019 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Гайка М10-6Н ГОСТ 5927-70 (размер под ключ S=17)</t>
+  </si>
+  <si>
+    <t>Гайка М10.5 019 ГОСТ 5927-70</t>
+  </si>
+  <si>
+    <t>Гайка М14х1,5 ГОСТ 15522-70</t>
   </si>
   <si>
     <t>Гайка М16-6Н.8.20.019 ГОСТ 15523-70</t>
   </si>
   <si>
-    <t>Гайка М14х1,5 ГОСТ 15522-70</t>
-  </si>
-  <si>
-    <t>Гайка М10.5 019 ГОСТ 5927-70</t>
-  </si>
-  <si>
-    <t>Гайка М10-6Н ГОСТ 5927-70 (размер под ключ S=17)</t>
-  </si>
-  <si>
-    <t>Болт М8-6gх25.58.019 ГОСТ 7798-70</t>
-  </si>
-  <si>
-    <t>Заглушка 219х8 ГОСТ 09Г2С 17379-2001</t>
-  </si>
-  <si>
-    <t>Переход 57х6-89х8 09Г2С ГОСТ 17378-2001</t>
-  </si>
-  <si>
-    <t>Переход 89х8-76х8 ст. 09Г2С ГОСТ 17378-01</t>
-  </si>
-  <si>
-    <t>Переход 114х8-89х8 Ст.09Г2С ГОСТ 17378-01</t>
-  </si>
-  <si>
-    <t>Переход 159х8-114х8 09Г2С ГОСТ 17378-01</t>
-  </si>
-  <si>
-    <t>Заглушка 89х8 ст.09Г2С ГОСТ 17379-2001</t>
-  </si>
-  <si>
-    <t>Заглушка 159х8 ст.09Г2С ГОСТ 17379-2001</t>
-  </si>
-  <si>
-    <t>Заглушка 76х8 ст.09Г2С ГОСТ 17379-2001</t>
-  </si>
-  <si>
-    <t>Уголок 50х50х3 ГОСТ 8509-93/09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Труба D57х6 ГОСТ 8732-78/ 09Г2С ГОСТ 4543-2016</t>
-  </si>
-  <si>
-    <t>Труба D219х8 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Круг D45 Ст.40Х ГОСТ 4543-71</t>
-  </si>
-  <si>
     <t>Лист чечевица В-К-ПУ-3,0 Ст.09Г2С ГОСТ 8568-77</t>
   </si>
   <si>
@@ -766,6 +697,33 @@
   </si>
   <si>
     <t>Кольцо уплотнительное НТ 202.003.004.0</t>
+  </si>
+  <si>
+    <t>Пластина WNMG 080408-GP GM3225 GESAC</t>
+  </si>
+  <si>
+    <t>Пластина CCMT09T308-GP GM3225 GESAC</t>
+  </si>
+  <si>
+    <t>Пластина SPGT060204-DG AT9030</t>
+  </si>
+  <si>
+    <t>Фреза концевая твердосплавная GE-D10.0-25L-4F-10D-75L</t>
+  </si>
+  <si>
+    <t>Пластина R390-11 T3 08M-PM 1130 SANDVIK (кратно12 для корпуса ПСМ, кратно 2 -для верх.корп.КМР)</t>
+  </si>
+  <si>
+    <t>Фреза концевая твердосплавная D5*HRC55*L100*25*4F</t>
+  </si>
+  <si>
+    <t>Винт М4х6 ГОСТ 17473-80</t>
+  </si>
+  <si>
+    <t>Болт М5х40 оцинк. ГОСТ 7805-70</t>
+  </si>
+  <si>
+    <t>Шайба 5.01.019 ГОСТ 11371-78</t>
   </si>
   <si>
     <t>Кольцо А75х1,7 ГОСТ 13943-86_</t>
@@ -1205,14 +1163,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F210"/>
+  <dimension ref="A1:F198"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="46.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="74.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1260,16 +1218,16 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="8" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D3" s="5">
-        <v>36.9</v>
+        <v>15</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1278,16 +1236,16 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="8" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D4" s="5">
-        <v>3.6</v>
+        <v>9</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1296,16 +1254,16 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="8" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D5" s="5">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="E5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1314,16 +1272,16 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="8" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D6" s="5">
-        <v>0.33</v>
+        <v>60</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1332,16 +1290,16 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="8" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D7" s="5">
-        <v>0.15</v>
+        <v>6</v>
       </c>
       <c r="E7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1350,16 +1308,16 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="8" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="D8" s="5">
         <v>0.75</v>
       </c>
       <c r="E8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1368,16 +1326,16 @@
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="8" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D9" s="5">
-        <v>52.05</v>
+        <v>5.4</v>
       </c>
       <c r="E9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1386,16 +1344,16 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="8" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D10" s="5">
-        <v>6</v>
+        <v>0.33</v>
       </c>
       <c r="E10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1404,16 +1362,16 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="8" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D11" s="5">
-        <v>60</v>
+        <v>0.15</v>
       </c>
       <c r="E11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1422,16 +1380,16 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="8" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D12" s="5">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="E12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1440,16 +1398,16 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="8" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D13" s="5">
-        <v>0.09</v>
+        <v>3.6</v>
       </c>
       <c r="E13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1458,16 +1416,16 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="8" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="D14" s="5">
-        <v>15</v>
+        <v>36.9</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1476,16 +1434,16 @@
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="8" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D15" s="5">
-        <v>38.700000000000003</v>
+        <v>0.3</v>
       </c>
       <c r="E15" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1494,16 +1452,16 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="8" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D16" s="5">
-        <v>47.4</v>
+        <v>52.05</v>
       </c>
       <c r="E16" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1512,16 +1470,16 @@
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="8" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D17" s="5">
         <v>90</v>
       </c>
       <c r="E17" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1530,16 +1488,16 @@
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="8" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D18" s="5">
-        <v>15.9</v>
+        <v>47.4</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1548,16 +1506,16 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="8" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="D19" s="5">
-        <v>472.8</v>
+        <v>15.9</v>
       </c>
       <c r="E19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1566,16 +1524,16 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="8" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D20" s="5">
-        <v>112.8</v>
+        <v>472.8</v>
       </c>
       <c r="E20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1584,16 +1542,16 @@
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="8" t="s">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="D21" s="5">
-        <v>28.2</v>
+        <v>112.8</v>
       </c>
       <c r="E21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1602,16 +1560,16 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="8" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="D22" s="5">
-        <v>20.7</v>
+        <v>28.2</v>
       </c>
       <c r="E22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1620,16 +1578,16 @@
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="8" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D23" s="5">
-        <v>0.3</v>
+        <v>20.7</v>
       </c>
       <c r="E23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1638,16 +1596,16 @@
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="8" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D24" s="5">
-        <v>1.05</v>
+        <v>22.5</v>
       </c>
       <c r="E24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1656,16 +1614,16 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="8" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D25" s="5">
-        <v>20.7</v>
+        <v>13.65</v>
       </c>
       <c r="E25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1674,16 +1632,16 @@
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="8" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D26" s="5">
-        <v>33.15</v>
+        <v>21.9</v>
       </c>
       <c r="E26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1692,16 +1650,16 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="8" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D27" s="5">
+        <v>6.6</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1710,16 +1668,16 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="8" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D28" s="5">
-        <v>21</v>
+        <v>0.09</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1728,16 +1686,16 @@
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="8" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D29" s="5">
-        <v>40.5</v>
+        <v>55.8</v>
       </c>
       <c r="E29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1746,16 +1704,16 @@
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="8" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D30" s="5">
         <v>20.399999999999999</v>
       </c>
       <c r="E30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1764,16 +1722,16 @@
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="8" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="D31" s="5">
-        <v>55.8</v>
+        <v>40.5</v>
       </c>
       <c r="E31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1782,16 +1740,16 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="8" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="D32" s="5">
-        <v>6.6</v>
+        <v>33.15</v>
       </c>
       <c r="E32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1800,16 +1758,16 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="8" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D33" s="5">
-        <v>21.9</v>
+        <v>20.7</v>
       </c>
       <c r="E33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1818,16 +1776,16 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="8" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D34" s="5">
-        <v>13.65</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1836,16 +1794,16 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="8" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D35" s="5">
-        <v>22.5</v>
+        <v>1.05</v>
       </c>
       <c r="E35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1890,7 +1848,7 @@
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="8" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D38" s="5">
         <v>200</v>
@@ -1908,7 +1866,7 @@
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="8" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D39" s="5">
         <v>200</v>
@@ -1926,7 +1884,7 @@
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="8" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D40" s="5">
         <v>200</v>
@@ -1944,7 +1902,7 @@
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="8" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="D41" s="5">
         <v>200</v>
@@ -1962,7 +1920,7 @@
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="8" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D42" s="5">
         <v>200</v>
@@ -1980,7 +1938,7 @@
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="8" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D43" s="5">
         <v>200</v>
@@ -1998,7 +1956,7 @@
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="8" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="D44" s="5">
         <v>1</v>
@@ -2055,7 +2013,7 @@
         <v>23</v>
       </c>
       <c r="D47" s="5">
-        <v>42</v>
+        <v>153</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>7</v>
@@ -2070,10 +2028,10 @@
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="8" t="s">
-        <v>134</v>
+        <v>25</v>
       </c>
       <c r="D48" s="5">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>7</v>
@@ -2088,10 +2046,10 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="8" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="D49" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>7</v>
@@ -2106,10 +2064,10 @@
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="8" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="D50" s="5">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>7</v>
@@ -2124,10 +2082,10 @@
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="8" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="D51" s="5">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>7</v>
@@ -2142,10 +2100,10 @@
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="8" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="D52" s="5">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>7</v>
@@ -2160,10 +2118,10 @@
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="8" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="D53" s="5">
-        <v>8</v>
+        <v>144</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>7</v>
@@ -2178,10 +2136,10 @@
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="8" t="s">
-        <v>140</v>
+        <v>26</v>
       </c>
       <c r="D54" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>7</v>
@@ -2196,7 +2154,7 @@
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="8" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="D55" s="5">
         <v>8</v>
@@ -2214,7 +2172,7 @@
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="8" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="D56" s="5">
         <v>8</v>
@@ -2232,10 +2190,10 @@
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="8" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="D57" s="5">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>7</v>
@@ -2250,13 +2208,13 @@
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="8" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="D58" s="5">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>24</v>
@@ -2268,13 +2226,13 @@
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="8" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="D59" s="5">
-        <v>320</v>
+        <v>56</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>24</v>
@@ -2286,13 +2244,13 @@
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="8" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="D60" s="5">
-        <v>100.8</v>
+        <v>200</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>24</v>
@@ -2304,13 +2262,13 @@
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="D61" s="7">
-        <v>1199</v>
+        <v>134</v>
+      </c>
+      <c r="D61" s="5">
+        <v>8</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>24</v>
@@ -2322,13 +2280,13 @@
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="8" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="D62" s="5">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>24</v>
@@ -2340,13 +2298,13 @@
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="8" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="D63" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>24</v>
@@ -2358,13 +2316,13 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="8" t="s">
-        <v>150</v>
+        <v>28</v>
       </c>
       <c r="D64" s="5">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>24</v>
@@ -2376,13 +2334,13 @@
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="8" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="D65" s="5">
-        <v>861.2</v>
+        <v>64</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>24</v>
@@ -2394,13 +2352,13 @@
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="8" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="D66" s="5">
-        <v>98</v>
+        <v>240</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>24</v>
@@ -2412,13 +2370,13 @@
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="8" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="D67" s="5">
-        <v>288</v>
+        <v>48</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>24</v>
@@ -2430,13 +2388,13 @@
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="8" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="D68" s="5">
-        <v>989</v>
+        <v>40</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>24</v>
@@ -2448,13 +2406,13 @@
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="8" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="D69" s="5">
-        <v>396.5</v>
+        <v>88</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>24</v>
@@ -2466,13 +2424,13 @@
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="8" t="s">
-        <v>156</v>
+        <v>30</v>
       </c>
       <c r="D70" s="5">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>24</v>
@@ -2484,13 +2442,13 @@
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="8" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="D71" s="5">
-        <v>16</v>
+        <v>560</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>24</v>
@@ -2502,13 +2460,13 @@
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="8" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="D72" s="5">
-        <v>274.8</v>
+        <v>192</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>24</v>
@@ -2520,13 +2478,13 @@
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="8" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="D73" s="5">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>24</v>
@@ -2538,13 +2496,13 @@
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="8" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="D74" s="5">
-        <v>259</v>
+        <v>10</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>24</v>
@@ -2556,13 +2514,13 @@
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="D75" s="7">
-        <v>1040</v>
+        <v>145</v>
+      </c>
+      <c r="D75" s="5">
+        <v>16.8</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>24</v>
@@ -2574,13 +2532,13 @@
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="8" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="D76" s="5">
-        <v>602.20000000000005</v>
+        <v>48</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>24</v>
@@ -2592,10 +2550,10 @@
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="8" t="s">
-        <v>25</v>
+        <v>147</v>
       </c>
       <c r="D77" s="5">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>7</v>
@@ -2610,13 +2568,13 @@
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="8" t="s">
-        <v>26</v>
+        <v>148</v>
       </c>
       <c r="D78" s="5">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>24</v>
@@ -2628,13 +2586,13 @@
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="8" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="D79" s="5">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>24</v>
@@ -2646,10 +2604,10 @@
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="8" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="D80" s="5">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>7</v>
@@ -2658,73 +2616,73 @@
         <v>24</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
         <v>80</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="8" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="D81" s="5">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>81</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="8" t="s">
-        <v>28</v>
+        <v>152</v>
       </c>
       <c r="D82" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
         <v>82</v>
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="8" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D83" s="5">
-        <v>16.8</v>
+        <v>10</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
         <v>83</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="8" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D84" s="5">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>24</v>
@@ -2736,13 +2694,13 @@
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="8" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D85" s="5">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>24</v>
@@ -2754,13 +2712,13 @@
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="8" t="s">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c r="D86" s="5">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>24</v>
@@ -2772,13 +2730,13 @@
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="8" t="s">
-        <v>32</v>
+        <v>157</v>
       </c>
       <c r="D87" s="5">
-        <v>6</v>
+        <v>100.8</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>24</v>
@@ -2790,13 +2748,13 @@
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="D88" s="5">
-        <v>240</v>
+        <v>158</v>
+      </c>
+      <c r="D88" s="7">
+        <v>1199</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>24</v>
@@ -2808,13 +2766,13 @@
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="8" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="D89" s="5">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>24</v>
@@ -2826,13 +2784,13 @@
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="8" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D90" s="5">
-        <v>560</v>
+        <v>10</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>24</v>
@@ -2844,13 +2802,13 @@
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="8" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D91" s="5">
-        <v>192</v>
+        <v>30</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>24</v>
@@ -2862,13 +2820,13 @@
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="8" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D92" s="5">
-        <v>76</v>
+        <v>861.2</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>24</v>
@@ -2880,13 +2838,13 @@
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="8" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="D93" s="5">
+        <v>98</v>
+      </c>
+      <c r="E93" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>7</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>24</v>
@@ -2898,13 +2856,13 @@
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="8" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="D94" s="5">
-        <v>40</v>
+        <v>288</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>24</v>
@@ -2916,13 +2874,13 @@
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="8" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="D95" s="5">
-        <v>16</v>
+        <v>989</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>24</v>
@@ -2934,103 +2892,103 @@
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="8" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D96" s="5">
-        <v>112</v>
+        <v>396.5</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
         <v>96</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="8" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="D97" s="5">
-        <v>18</v>
+        <v>0.6</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
         <v>97</v>
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="8" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="D98" s="5">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F98" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
         <v>98</v>
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="8" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D99" s="5">
+        <v>274.8</v>
+      </c>
+      <c r="E99" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E99" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="F99" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
         <v>99</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="8" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D100" s="5">
+        <v>48</v>
+      </c>
+      <c r="E100" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E100" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="F100" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
         <v>100</v>
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="8" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="D101" s="5">
-        <v>5</v>
+        <v>259</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>24</v>
@@ -3042,13 +3000,13 @@
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="D102" s="5">
-        <v>8</v>
+        <v>172</v>
+      </c>
+      <c r="D102" s="7">
+        <v>1040</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>24</v>
@@ -3060,28 +3018,28 @@
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="8" t="s">
-        <v>183</v>
+        <v>86</v>
       </c>
       <c r="D103" s="5">
-        <v>75</v>
+        <v>602.20000000000005</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
         <v>103</v>
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="8" t="s">
-        <v>184</v>
+        <v>33</v>
       </c>
       <c r="D104" s="5">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>7</v>
@@ -3096,10 +3054,10 @@
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="8" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D105" s="5">
-        <v>144</v>
+        <v>8</v>
       </c>
       <c r="E105" s="6" t="s">
         <v>7</v>
@@ -3114,10 +3072,10 @@
       </c>
       <c r="B106" s="4"/>
       <c r="C106" s="8" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="D106" s="5">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>7</v>
@@ -3132,10 +3090,10 @@
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="8" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D107" s="5">
-        <v>32</v>
+        <v>400</v>
       </c>
       <c r="E107" s="6" t="s">
         <v>7</v>
@@ -3150,10 +3108,10 @@
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="8" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="D108" s="5">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>7</v>
@@ -3168,10 +3126,10 @@
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="8" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="D109" s="5">
-        <v>298</v>
+        <v>32</v>
       </c>
       <c r="E109" s="6" t="s">
         <v>7</v>
@@ -3180,16 +3138,16 @@
         <v>24</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
         <v>109</v>
       </c>
       <c r="B110" s="4"/>
       <c r="C110" s="8" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D110" s="5">
-        <v>422</v>
+        <v>8</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>7</v>
@@ -3204,10 +3162,10 @@
       </c>
       <c r="B111" s="4"/>
       <c r="C111" s="8" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D111" s="5">
-        <v>900</v>
+        <v>8</v>
       </c>
       <c r="E111" s="6" t="s">
         <v>7</v>
@@ -3222,10 +3180,10 @@
       </c>
       <c r="B112" s="4"/>
       <c r="C112" s="8" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D112" s="5">
-        <v>8</v>
+        <v>900</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>7</v>
@@ -3234,16 +3192,16 @@
         <v>24</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
         <v>112</v>
       </c>
       <c r="B113" s="4"/>
       <c r="C113" s="8" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="D113" s="5">
-        <v>8</v>
+        <v>422</v>
       </c>
       <c r="E113" s="6" t="s">
         <v>7</v>
@@ -3258,10 +3216,10 @@
       </c>
       <c r="B114" s="4"/>
       <c r="C114" s="8" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="D114" s="5">
-        <v>32</v>
+        <v>298</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>7</v>
@@ -3276,10 +3234,10 @@
       </c>
       <c r="B115" s="4"/>
       <c r="C115" s="8" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="D115" s="5">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E115" s="6" t="s">
         <v>7</v>
@@ -3288,16 +3246,16 @@
         <v>24</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
         <v>115</v>
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="8" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="D116" s="5">
-        <v>112</v>
+        <v>5</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>7</v>
@@ -3312,10 +3270,10 @@
       </c>
       <c r="B117" s="4"/>
       <c r="C117" s="8" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="D117" s="5">
-        <v>400</v>
+        <v>8</v>
       </c>
       <c r="E117" s="6" t="s">
         <v>7</v>
@@ -3324,16 +3282,16 @@
         <v>24</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
         <v>117</v>
       </c>
       <c r="B118" s="4"/>
       <c r="C118" s="8" t="s">
-        <v>33</v>
+        <v>185</v>
       </c>
       <c r="D118" s="5">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>7</v>
@@ -3348,10 +3306,10 @@
       </c>
       <c r="B119" s="4"/>
       <c r="C119" s="8" t="s">
-        <v>34</v>
+        <v>186</v>
       </c>
       <c r="D119" s="5">
-        <v>153</v>
+        <v>32</v>
       </c>
       <c r="E119" s="6" t="s">
         <v>7</v>
@@ -3366,10 +3324,10 @@
       </c>
       <c r="B120" s="4"/>
       <c r="C120" s="8" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="D120" s="5">
-        <v>8</v>
+        <v>144</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>7</v>
@@ -3384,10 +3342,10 @@
       </c>
       <c r="B121" s="4"/>
       <c r="C121" s="8" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="D121" s="5">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="E121" s="6" t="s">
         <v>7</v>
@@ -3402,10 +3360,10 @@
       </c>
       <c r="B122" s="4"/>
       <c r="C122" s="8" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="D122" s="5">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>7</v>
@@ -3423,10 +3381,10 @@
         <v>35</v>
       </c>
       <c r="D123" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>36</v>
@@ -3438,13 +3396,13 @@
       </c>
       <c r="B124" s="4"/>
       <c r="C124" s="8" t="s">
-        <v>37</v>
+        <v>190</v>
       </c>
       <c r="D124" s="5">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>36</v>
@@ -3456,10 +3414,10 @@
       </c>
       <c r="B125" s="4"/>
       <c r="C125" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D125" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E125" s="6" t="s">
         <v>15</v>
@@ -3474,10 +3432,10 @@
       </c>
       <c r="B126" s="4"/>
       <c r="C126" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D126" s="5">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>15</v>
@@ -3492,13 +3450,13 @@
       </c>
       <c r="B127" s="4"/>
       <c r="C127" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D127" s="5">
         <v>10</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>36</v>
@@ -3510,13 +3468,13 @@
       </c>
       <c r="B128" s="4"/>
       <c r="C128" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D128" s="5">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>36</v>
@@ -3528,10 +3486,10 @@
       </c>
       <c r="B129" s="4"/>
       <c r="C129" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D129" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E129" s="6" t="s">
         <v>7</v>
@@ -3546,7 +3504,7 @@
       </c>
       <c r="B130" s="4"/>
       <c r="C130" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D130" s="5">
         <v>20</v>
@@ -3564,10 +3522,10 @@
       </c>
       <c r="B131" s="4"/>
       <c r="C131" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D131" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E131" s="6" t="s">
         <v>7</v>
@@ -3582,10 +3540,10 @@
       </c>
       <c r="B132" s="4"/>
       <c r="C132" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D132" s="7">
-        <v>1000</v>
+        <v>44</v>
+      </c>
+      <c r="D132" s="5">
+        <v>20</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>7</v>
@@ -3600,10 +3558,10 @@
       </c>
       <c r="B133" s="4"/>
       <c r="C133" s="8" t="s">
-        <v>201</v>
+        <v>45</v>
       </c>
       <c r="D133" s="5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E133" s="6" t="s">
         <v>7</v>
@@ -3620,8 +3578,8 @@
       <c r="C134" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D134" s="5">
-        <v>10</v>
+      <c r="D134" s="7">
+        <v>1000</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>7</v>
@@ -3639,7 +3597,7 @@
         <v>47</v>
       </c>
       <c r="D135" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E135" s="6" t="s">
         <v>15</v>
@@ -3654,10 +3612,10 @@
       </c>
       <c r="B136" s="4"/>
       <c r="C136" s="8" t="s">
-        <v>49</v>
+        <v>191</v>
       </c>
       <c r="D136" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>15</v>
@@ -3690,10 +3648,10 @@
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D138" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>15</v>
@@ -3708,10 +3666,10 @@
       </c>
       <c r="B139" s="4"/>
       <c r="C139" s="8" t="s">
-        <v>202</v>
+        <v>50</v>
       </c>
       <c r="D139" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E139" s="6" t="s">
         <v>15</v>
@@ -3744,7 +3702,7 @@
       </c>
       <c r="B141" s="4"/>
       <c r="C141" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D141" s="5">
         <v>6</v>
@@ -3765,7 +3723,7 @@
         <v>51</v>
       </c>
       <c r="D142" s="5">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>52</v>
@@ -3783,10 +3741,10 @@
         <v>53</v>
       </c>
       <c r="D143" s="5">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F143" s="4" t="s">
         <v>48</v>
@@ -3798,13 +3756,13 @@
       </c>
       <c r="B144" s="4"/>
       <c r="C144" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D144" s="5">
         <v>10</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>48</v>
@@ -3819,10 +3777,10 @@
         <v>56</v>
       </c>
       <c r="D145" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F145" s="4" t="s">
         <v>48</v>
@@ -3834,7 +3792,7 @@
       </c>
       <c r="B146" s="4"/>
       <c r="C146" s="8" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="D146" s="5">
         <v>2</v>
@@ -3852,7 +3810,7 @@
       </c>
       <c r="B147" s="4"/>
       <c r="C147" s="8" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="D147" s="5">
         <v>6</v>
@@ -3870,10 +3828,10 @@
       </c>
       <c r="B148" s="4"/>
       <c r="C148" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="D148" s="5">
-        <v>100</v>
+        <v>194</v>
+      </c>
+      <c r="D148" s="7">
+        <v>4000</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>7</v>
@@ -3888,7 +3846,7 @@
       </c>
       <c r="B149" s="4"/>
       <c r="C149" s="8" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="D149" s="5">
         <v>100</v>
@@ -3906,7 +3864,7 @@
       </c>
       <c r="B150" s="4"/>
       <c r="C150" s="8" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="D150" s="5">
         <v>200</v>
@@ -3924,7 +3882,7 @@
       </c>
       <c r="B151" s="4"/>
       <c r="C151" s="8" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="D151" s="5">
         <v>100</v>
@@ -3942,10 +3900,10 @@
       </c>
       <c r="B152" s="4"/>
       <c r="C152" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="D152" s="7">
-        <v>4000</v>
+        <v>198</v>
+      </c>
+      <c r="D152" s="5">
+        <v>100</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>7</v>
@@ -3960,13 +3918,13 @@
       </c>
       <c r="B153" s="4"/>
       <c r="C153" s="8" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D153" s="5">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F153" s="4" t="s">
         <v>59</v>
@@ -3978,10 +3936,10 @@
       </c>
       <c r="B154" s="4"/>
       <c r="C154" s="8" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="D154" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>7</v>
@@ -3996,10 +3954,10 @@
       </c>
       <c r="B155" s="4"/>
       <c r="C155" s="8" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="D155" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E155" s="6" t="s">
         <v>7</v>
@@ -4014,10 +3972,10 @@
       </c>
       <c r="B156" s="4"/>
       <c r="C156" s="8" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="D156" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>7</v>
@@ -4032,10 +3990,10 @@
       </c>
       <c r="B157" s="4"/>
       <c r="C157" s="8" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="D157" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E157" s="6" t="s">
         <v>7</v>
@@ -4050,10 +4008,10 @@
       </c>
       <c r="B158" s="4"/>
       <c r="C158" s="8" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="D158" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>7</v>
@@ -4068,13 +4026,13 @@
       </c>
       <c r="B159" s="4"/>
       <c r="C159" s="8" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="D159" s="5">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F159" s="4" t="s">
         <v>59</v>
@@ -4104,7 +4062,7 @@
       </c>
       <c r="B161" s="4"/>
       <c r="C161" s="8" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="D161" s="5">
         <v>800</v>
@@ -4122,10 +4080,10 @@
       </c>
       <c r="B162" s="4"/>
       <c r="C162" s="8" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="D162" s="5">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>7</v>
@@ -4140,7 +4098,7 @@
       </c>
       <c r="B163" s="4"/>
       <c r="C163" s="8" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="D163" s="5">
         <v>300</v>
@@ -4158,10 +4116,10 @@
       </c>
       <c r="B164" s="4"/>
       <c r="C164" s="8" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D164" s="5">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>7</v>
@@ -4176,7 +4134,7 @@
       </c>
       <c r="B165" s="4"/>
       <c r="C165" s="8" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="D165" s="5">
         <v>800</v>
@@ -4197,10 +4155,10 @@
         <v>63</v>
       </c>
       <c r="D166" s="5">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F166" s="4" t="s">
         <v>64</v>
@@ -4212,13 +4170,13 @@
       </c>
       <c r="B167" s="4"/>
       <c r="C167" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="D167" s="5">
-        <v>3</v>
+        <v>211</v>
+      </c>
+      <c r="D167" s="7">
+        <v>2713.44</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F167" s="4" t="s">
         <v>65</v>
@@ -4230,13 +4188,13 @@
       </c>
       <c r="B168" s="4"/>
       <c r="C168" s="8" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="D168" s="5">
-        <v>48</v>
+        <v>35.28</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F168" s="4" t="s">
         <v>65</v>
@@ -4248,13 +4206,13 @@
       </c>
       <c r="B169" s="4"/>
       <c r="C169" s="8" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="D169" s="5">
-        <v>450</v>
+        <v>66</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F169" s="4" t="s">
         <v>65</v>
@@ -4266,13 +4224,13 @@
       </c>
       <c r="B170" s="4"/>
       <c r="C170" s="8" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="D170" s="5">
-        <v>48</v>
+        <v>5.82</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F170" s="4" t="s">
         <v>65</v>
@@ -4284,13 +4242,13 @@
       </c>
       <c r="B171" s="4"/>
       <c r="C171" s="8" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="D171" s="5">
-        <v>35</v>
+        <v>103.74</v>
       </c>
       <c r="E171" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F171" s="4" t="s">
         <v>65</v>
@@ -4302,34 +4260,34 @@
       </c>
       <c r="B172" s="4"/>
       <c r="C172" s="8" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="D172" s="5">
-        <v>25</v>
+        <v>20.22</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F172" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="173" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="3">
         <v>172</v>
       </c>
       <c r="B173" s="4"/>
       <c r="C173" s="8" t="s">
-        <v>228</v>
+        <v>66</v>
       </c>
       <c r="D173" s="5">
-        <v>12</v>
+        <v>612</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="174" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4338,16 +4296,16 @@
       </c>
       <c r="B174" s="4"/>
       <c r="C174" s="8" t="s">
-        <v>66</v>
+        <v>217</v>
       </c>
       <c r="D174" s="5">
-        <v>180</v>
+        <v>19.5</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4356,16 +4314,16 @@
       </c>
       <c r="B175" s="4"/>
       <c r="C175" s="8" t="s">
-        <v>67</v>
+        <v>218</v>
       </c>
       <c r="D175" s="5">
-        <v>450</v>
+        <v>1.8</v>
       </c>
       <c r="E175" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="176" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4374,16 +4332,16 @@
       </c>
       <c r="B176" s="4"/>
       <c r="C176" s="8" t="s">
-        <v>68</v>
+        <v>219</v>
       </c>
       <c r="D176" s="5">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4392,16 +4350,16 @@
       </c>
       <c r="B177" s="4"/>
       <c r="C177" s="8" t="s">
-        <v>69</v>
+        <v>220</v>
       </c>
       <c r="D177" s="5">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E177" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="178" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4410,16 +4368,16 @@
       </c>
       <c r="B178" s="4"/>
       <c r="C178" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="D178" s="5">
+        <v>6</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F178" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="D178" s="5">
-        <v>10</v>
-      </c>
-      <c r="E178" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F178" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="179" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4428,16 +4386,16 @@
       </c>
       <c r="B179" s="4"/>
       <c r="C179" s="8" t="s">
-        <v>71</v>
+        <v>222</v>
       </c>
       <c r="D179" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E179" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="180" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4446,16 +4404,16 @@
       </c>
       <c r="B180" s="4"/>
       <c r="C180" s="8" t="s">
-        <v>72</v>
+        <v>233</v>
       </c>
       <c r="D180" s="5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4464,16 +4422,16 @@
       </c>
       <c r="B181" s="4"/>
       <c r="C181" s="8" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D181" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E181" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4482,16 +4440,16 @@
       </c>
       <c r="B182" s="4"/>
       <c r="C182" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D182" s="5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="183" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4500,106 +4458,106 @@
       </c>
       <c r="B183" s="4"/>
       <c r="C183" s="8" t="s">
-        <v>230</v>
+        <v>73</v>
       </c>
       <c r="D183" s="5">
-        <v>32.799999999999997</v>
+        <v>3</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F183" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="184" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="3">
         <v>183</v>
       </c>
       <c r="B184" s="4"/>
       <c r="C184" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D184" s="5">
+        <v>2</v>
+      </c>
+      <c r="E184" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F184" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D184" s="5">
-        <v>200</v>
-      </c>
-      <c r="E184" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F184" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="185" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="3">
         <v>184</v>
       </c>
       <c r="B185" s="4"/>
       <c r="C185" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="D185" s="7">
-        <v>1000</v>
+        <v>224</v>
+      </c>
+      <c r="D185" s="5">
+        <v>100</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="3">
         <v>185</v>
       </c>
       <c r="B186" s="4"/>
       <c r="C186" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="D186" s="5">
+        <v>100</v>
+      </c>
+      <c r="E186" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F186" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D186" s="7">
-        <v>3300</v>
-      </c>
-      <c r="E186" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F186" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="187" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="3">
         <v>186</v>
       </c>
       <c r="B187" s="4"/>
       <c r="C187" s="8" t="s">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="D187" s="5">
-        <v>1.1000000000000001</v>
+        <v>20</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="3">
         <v>187</v>
       </c>
       <c r="B188" s="4"/>
       <c r="C188" s="8" t="s">
-        <v>79</v>
+        <v>227</v>
       </c>
       <c r="D188" s="5">
-        <v>0.7</v>
+        <v>10</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="189" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4608,70 +4566,70 @@
       </c>
       <c r="B189" s="4"/>
       <c r="C189" s="8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D189" s="5">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E189" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="3">
         <v>189</v>
       </c>
       <c r="B190" s="4"/>
       <c r="C190" s="8" t="s">
-        <v>81</v>
+        <v>229</v>
       </c>
       <c r="D190" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="3">
         <v>190</v>
       </c>
       <c r="B191" s="4"/>
       <c r="C191" s="8" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D191" s="5">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="E191" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="3">
         <v>191</v>
       </c>
       <c r="B192" s="4"/>
       <c r="C192" s="8" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D192" s="5">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4680,322 +4638,106 @@
       </c>
       <c r="B193" s="4"/>
       <c r="C193" s="8" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D193" s="5">
-        <v>157.19999999999999</v>
+        <v>36</v>
       </c>
       <c r="E193" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="3">
         <v>193</v>
       </c>
       <c r="B194" s="4"/>
       <c r="C194" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="D194" s="7">
-        <v>2713.44</v>
+        <v>81</v>
+      </c>
+      <c r="D194" s="5">
+        <v>18</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="3">
         <v>194</v>
       </c>
       <c r="B195" s="4"/>
       <c r="C195" s="8" t="s">
-        <v>235</v>
+        <v>82</v>
       </c>
       <c r="D195" s="5">
-        <v>35.28</v>
+        <v>36</v>
       </c>
       <c r="E195" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="3">
         <v>195</v>
       </c>
       <c r="B196" s="4"/>
       <c r="C196" s="8" t="s">
-        <v>236</v>
+        <v>83</v>
       </c>
       <c r="D196" s="5">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="3">
         <v>196</v>
       </c>
       <c r="B197" s="4"/>
       <c r="C197" s="8" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D197" s="5">
-        <v>5.82</v>
+        <v>36</v>
       </c>
       <c r="E197" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="3">
         <v>197</v>
       </c>
       <c r="B198" s="4"/>
       <c r="C198" s="8" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D198" s="5">
-        <v>103.74</v>
+        <v>36</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="3">
-        <v>198</v>
-      </c>
-      <c r="B199" s="4"/>
-      <c r="C199" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="D199" s="5">
-        <v>20.22</v>
-      </c>
-      <c r="E199" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F199" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="3">
-        <v>199</v>
-      </c>
-      <c r="B200" s="4"/>
-      <c r="C200" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D200" s="5">
-        <v>612</v>
-      </c>
-      <c r="E200" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F200" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A201" s="3">
-        <v>200</v>
-      </c>
-      <c r="B201" s="4"/>
-      <c r="C201" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D201" s="5">
-        <v>19.5</v>
-      </c>
-      <c r="E201" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F201" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="3">
-        <v>201</v>
-      </c>
-      <c r="B202" s="4"/>
-      <c r="C202" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="D202" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="E202" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F202" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="3">
-        <v>202</v>
-      </c>
-      <c r="B203" s="4"/>
-      <c r="C203" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="D203" s="5">
-        <v>4</v>
-      </c>
-      <c r="E203" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F203" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="3">
-        <v>203</v>
-      </c>
-      <c r="B204" s="4"/>
-      <c r="C204" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="D204" s="5">
-        <v>4</v>
-      </c>
-      <c r="E204" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F204" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A205" s="3">
-        <v>204</v>
-      </c>
-      <c r="B205" s="4"/>
-      <c r="C205" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D205" s="5">
-        <v>6</v>
-      </c>
-      <c r="E205" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F205" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A206" s="3">
-        <v>205</v>
-      </c>
-      <c r="B206" s="4"/>
-      <c r="C206" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="D206" s="5">
-        <v>2</v>
-      </c>
-      <c r="E206" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F206" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A207" s="3">
-        <v>206</v>
-      </c>
-      <c r="B207" s="4"/>
-      <c r="C207" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="D207" s="5">
-        <v>2</v>
-      </c>
-      <c r="E207" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F207" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="3">
-        <v>207</v>
-      </c>
-      <c r="B208" s="4"/>
-      <c r="C208" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="D208" s="5">
-        <v>4</v>
-      </c>
-      <c r="E208" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F208" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="3">
-        <v>208</v>
-      </c>
-      <c r="B209" s="4"/>
-      <c r="C209" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D209" s="5">
-        <v>25</v>
-      </c>
-      <c r="E209" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F209" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="3">
-        <v>209</v>
-      </c>
-      <c r="B210" s="4"/>
-      <c r="C210" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D210" s="5">
-        <v>30</v>
-      </c>
-      <c r="E210" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F210" s="4" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AD3BCB-6882-40CB-BE56-C90C1CB4DE3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{673FD8E4-332E-4635-8F56-8C8C65B1E925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="224">
   <si>
     <t>№ п/п</t>
   </si>
@@ -96,108 +96,108 @@
     <t>Ремонт двери 1900х1000мм(уст.ка вент. решеток, установка цепи и фиксатора, покраска)</t>
   </si>
   <si>
+    <t>ЛГУП-7654</t>
+  </si>
+  <si>
+    <t>мм</t>
+  </si>
+  <si>
+    <t>Комплект кабельной проходки МКС</t>
+  </si>
+  <si>
+    <t>компл</t>
+  </si>
+  <si>
+    <t>г</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с наружной резьбой РКН-20 У2 IP54 ЗЭТА</t>
+  </si>
+  <si>
     <t>Лампа индикации ADDS D22 LED белая 220В AC/DC ЛK-22 IP55 25152DEK Dekraft</t>
   </si>
   <si>
-    <t>ЛГУП-7654</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с наружной резьбой РКН-20 У2 IP54 ЗЭТА</t>
+    <t>Извещатель пожарный тепловой взрывозащищенный 101-07е 1Ex db [ia Ga] IIC Т4 Gb Х IP66</t>
+  </si>
+  <si>
+    <t>Винт для обеспечения электрического контакта крышек ( М 5 х 8) арт.CM030508</t>
+  </si>
+  <si>
+    <t>Аварийное освещение Вега 60 с БАП 2Ex Тех 1ExmbIIC T6 Gb X, IP65</t>
+  </si>
+  <si>
+    <t>Пломба 1-6х10-АД-1М ГОСТ 18677-73</t>
   </si>
   <si>
     <t>Электроприв четвер.взры. ГЗ-ОФВ-300/28М 1х220 DN80PN63 L=452 УХЛ (исп. фл. J)</t>
   </si>
   <si>
-    <t>Аварийное освещение Вега 60 с БАП 2Ex Тех 1ExmbIIC T6 Gb X, IP65</t>
-  </si>
-  <si>
-    <t>Пломба 1-6х10-АД-1М ГОСТ 18677-73</t>
-  </si>
-  <si>
-    <t>г</t>
-  </si>
-  <si>
-    <t>Комплект кабельной проходки МКС</t>
-  </si>
-  <si>
-    <t>компл</t>
-  </si>
-  <si>
-    <t>мм</t>
-  </si>
-  <si>
-    <t>Извещатель пожарный тепловой взрывозащищенный 101-07е 1Ex db [ia Ga] IIC Т4 Gb Х IP66</t>
-  </si>
-  <si>
-    <t>Винт для обеспечения электрического контакта крышек ( М 5 х 8) арт.CM030508</t>
+    <t>Бита (вставка) Spline М 8  L=30мм</t>
+  </si>
+  <si>
+    <t>ЛГУП-7867</t>
+  </si>
+  <si>
+    <t>Ветошь /рул./</t>
+  </si>
+  <si>
+    <t>Пленка воздушно-пузырчатая 1500мм*100 пог.м 2 сл (рул)</t>
+  </si>
+  <si>
+    <t>Маркер белый Paint 4мм</t>
+  </si>
+  <si>
+    <t>Кисточка 2 см</t>
+  </si>
+  <si>
+    <t>Кисточка 5 см</t>
+  </si>
+  <si>
+    <t>Кисточка 10 см</t>
+  </si>
+  <si>
+    <t>Стрейч пленка 500мм*185м</t>
+  </si>
+  <si>
+    <t>Рулетка 3м (Force) (100)</t>
+  </si>
+  <si>
+    <t>Перчатки 4нит. 10кл. (черные) (пара)</t>
   </si>
   <si>
     <t>Рулетка  7,5м х 25мм обрезиненный корпус (3 фиксатора, зацеп с магнитом)</t>
   </si>
   <si>
-    <t>ЛГУП-7867</t>
-  </si>
-  <si>
-    <t>Бита (вставка) Spline М 8  L=30мм</t>
-  </si>
-  <si>
-    <t>Ветошь /рул./</t>
-  </si>
-  <si>
-    <t>Пленка воздушно-пузырчатая 1500мм*100 пог.м 2 сл (рул)</t>
-  </si>
-  <si>
-    <t>Маркер белый Paint 4мм</t>
-  </si>
-  <si>
-    <t>Кисточка 2 см</t>
-  </si>
-  <si>
-    <t>Кисточка 5 см</t>
-  </si>
-  <si>
-    <t>Кисточка 10 см</t>
-  </si>
-  <si>
-    <t>Стрейч пленка 500мм*185м</t>
-  </si>
-  <si>
-    <t>Рулетка 3м (Force) (100)</t>
-  </si>
-  <si>
-    <t>Перчатки 4нит. 10кл. (черные) (пара)</t>
+    <t>Паронит 3 мм</t>
+  </si>
+  <si>
+    <t>лист</t>
+  </si>
+  <si>
+    <t>НТУП-018192</t>
+  </si>
+  <si>
+    <t>Паронит 2мм</t>
+  </si>
+  <si>
+    <t>Ключи обмедненные</t>
+  </si>
+  <si>
+    <t>набор</t>
+  </si>
+  <si>
+    <t>Маркер по металлу белый</t>
+  </si>
+  <si>
+    <t>Маркер по металлу красный</t>
+  </si>
+  <si>
+    <t>Мел сварщика белый</t>
   </si>
   <si>
     <t>Маркер по металлу черный тонкий</t>
   </si>
   <si>
-    <t>НТУП-018192</t>
-  </si>
-  <si>
-    <t>Маркер по металлу белый</t>
-  </si>
-  <si>
-    <t>Маркер по металлу красный</t>
-  </si>
-  <si>
-    <t>Паронит 3 мм</t>
-  </si>
-  <si>
-    <t>лист</t>
-  </si>
-  <si>
-    <t>Паронит 2мм</t>
-  </si>
-  <si>
-    <t>Ключи обмедненные</t>
-  </si>
-  <si>
-    <t>набор</t>
-  </si>
-  <si>
-    <t>Мел сварщика белый</t>
-  </si>
-  <si>
     <t>ЛГУП-7998</t>
   </si>
   <si>
@@ -207,12 +207,6 @@
     <t>ЛГУП-8008</t>
   </si>
   <si>
-    <t>Штуцер Ш2.7038.001 (покрытие Хим.Фас)</t>
-  </si>
-  <si>
-    <t>ЛГУП-8012</t>
-  </si>
-  <si>
     <t>ЛГУП-8015</t>
   </si>
   <si>
@@ -240,43 +234,37 @@
     <t>ЛГУП-8046</t>
   </si>
   <si>
-    <t>Индустриальное масло  Gazpromneft  Industrial 40 ( И-40А ) 205л</t>
-  </si>
-  <si>
-    <t>ЛГУП-8058</t>
-  </si>
-  <si>
-    <t>Кран шаровый ДУ80 Ру 40 под приварку</t>
-  </si>
-  <si>
-    <t>НТУП-018299</t>
-  </si>
-  <si>
     <t>ЛГУП-8060</t>
   </si>
   <si>
-    <t>ЛГУП-8061</t>
-  </si>
-  <si>
-    <t>(не исп1) шт</t>
-  </si>
-  <si>
-    <t>Шайба 5Л ГОСТ 6402-70</t>
-  </si>
-  <si>
-    <t>ЛГУП-8062</t>
-  </si>
-  <si>
-    <t>Коробка соединительно-разветвительная взрывозащищенная КСРВ-2-2/0-К</t>
-  </si>
-  <si>
-    <t>Текстолит 4мм (90х60)</t>
-  </si>
-  <si>
-    <t>Саморез-шуруп острый (оцинк.) 2,2х4,5 ГОСТ 1144-80</t>
-  </si>
-  <si>
-    <t>Стойка для печатных плат (шестигр., латунь) М4, 27мм ГОСТ 20862-81</t>
+    <t>ЛГУП-8075</t>
+  </si>
+  <si>
+    <t>ЛГУП-8077</t>
+  </si>
+  <si>
+    <t>спец одежда  для специалистов ПНР (зимняя)</t>
+  </si>
+  <si>
+    <t>ЛГУП-8078</t>
+  </si>
+  <si>
+    <t>Патрубок (361)</t>
+  </si>
+  <si>
+    <t>ТЛУП-012027</t>
+  </si>
+  <si>
+    <t>Масло Лукойл 5w -40 4л</t>
+  </si>
+  <si>
+    <t>Тормозная жидкость</t>
+  </si>
+  <si>
+    <t>Масло  Лукойл -Авангард Ультра 5W40 CI-4/SL  п.синт /л/</t>
+  </si>
+  <si>
+    <t>Антифриз  felix</t>
   </si>
   <si>
     <t>Гофрокороб 395*155*155</t>
@@ -366,12 +354,12 @@
     <t>Круг D75 Ст.35 ГОСТ 1050-88</t>
   </si>
   <si>
+    <t>Круг D42 Ст.14Х17Н2 ГОСТ 5949-75</t>
+  </si>
+  <si>
     <t>Круг D75 Ст.20Х13 ГОСТ 5632-72</t>
   </si>
   <si>
-    <t>Круг D42 Ст.14Х17Н2 ГОСТ 5949-75</t>
-  </si>
-  <si>
     <t>Круг D20 Ст.20 ГОСТ 1050-88</t>
   </si>
   <si>
@@ -396,207 +384,207 @@
     <t>Газоанализатор взрывозащищенный СГОЭС (метан) 1Ex d IIC T4 Gb, IP67 Ур1. 10%, ур.2 50% НКПР</t>
   </si>
   <si>
+    <t>Коробка клеммная МТ Р407(-60+40) 2-8х20НК(А)-8х20НК(С)-2,5х31(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р403(-60+40) 2-4х20НК(А)-4х20НК(С)-2,5х20(П),1ЕхеLLCGbXT6, ip66, 160х175х55</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р402(-60+40)12-2х20НК(А)-2х20НК(С)-1,5х11(П), 1ЕхеLLCGbXT6, ip66, 110х75х55</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р307(-60+40) 2-6х20НК(А)-1х20НК(В)-6х20НК(С)-4х26(П) 1ЕхеLLCGbXT6, ip66</t>
+  </si>
+  <si>
+    <t>Консоль с опорой ML 300мм (шт)</t>
+  </si>
+  <si>
+    <t>Компрессионный блок МКС КБ 120</t>
+  </si>
+  <si>
+    <t>Кабель-канал 10453 Legrand DPL 195х65 (2м)</t>
+  </si>
+  <si>
+    <t>Крышка Угол горизонтальный CPO 90 (50х50)</t>
+  </si>
+  <si>
+    <t>Трубка для фильтра 1/4" Гейзер</t>
+  </si>
+  <si>
+    <t>Лента самоклеящаяся уплотнительная ППЭ 5х15 МКС</t>
+  </si>
+  <si>
+    <t>Заглушка 10707 Legrand DPL 65х195</t>
+  </si>
+  <si>
+    <t>Заглушка  25х25 для трубы профильной ПВД черная</t>
+  </si>
+  <si>
+    <t>Диод КД209А ТТЗ.362.008 ТУ</t>
+  </si>
+  <si>
+    <t>Держатель проводника Rd8, DEHNGRIP NIRO h20 с отв.8мм М6</t>
+  </si>
+  <si>
+    <t>Припой с канифолью ПОС 61 d=1,0мм ГОСТ 21931-76 (Sn61; Pb39)</t>
+  </si>
+  <si>
+    <t>Уплотнительный модуль МКС 40/Ø 17-34 мм</t>
+  </si>
+  <si>
+    <t>Уплотнительный модуль МКС 20/О 5-14мм</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Наконечник НВИ 2-5 вилка 1,5-2,5мм SQ0503-0005 TDM</t>
+  </si>
+  <si>
+    <t>MV-клемма проводника Rd8</t>
+  </si>
+  <si>
+    <t>Плата питания ПСМ.11.00.00.01-02</t>
+  </si>
+  <si>
+    <t>Плата печатная ПСМ.11.00.01.01-02</t>
+  </si>
+  <si>
+    <t>Пластина для заземления PTCE арт. 37501</t>
+  </si>
+  <si>
+    <t>Пластина анкерная 120</t>
+  </si>
+  <si>
+    <t>Ответная рама РВО 4.1.1</t>
+  </si>
+  <si>
+    <t>Ответная рама РВО 2.1.1</t>
+  </si>
+  <si>
+    <t>Монтажная рама РВМ 4.1.1</t>
+  </si>
+  <si>
+    <t>Монтажная рама РВМ 2.1.1</t>
+  </si>
+  <si>
+    <t>Металлический лоток, неперфорированный (50х50х3000)</t>
+  </si>
+  <si>
+    <t>Металлический лоток, неперфорированный (100х50х3000)</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 3x1,5 d7,2мм</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS- 3х2,50</t>
+  </si>
+  <si>
+    <t>Короб ПВХ 100х60</t>
+  </si>
+  <si>
+    <t>Короб ПВХ  40х25 мм</t>
+  </si>
+  <si>
+    <t>Кабель КПСЭнг(А)-FRLS 2*2*0,75</t>
+  </si>
+  <si>
+    <t>Кабель КПСЭнг(A)-FRLS 4х2х0,75</t>
+  </si>
+  <si>
+    <t>Кабель КВВГЭнг(А)-LS-ХЛ 7х1,0</t>
+  </si>
+  <si>
+    <t>Кабель КВВГЭнг(А)-LS-ХЛ 4х1,0</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
+  </si>
+  <si>
+    <t>Трубка 3.31 ТВ-40 ГОСТ 19034-82</t>
+  </si>
+  <si>
+    <t>Провод НВМ 0,35 IV 500 ГОСТ 17515-72</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-FRLS 3x1,5 d7,2мм</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d8мм</t>
+  </si>
+  <si>
+    <t>Провод желто-зеленый ПуГВнг(А)-LS 1x6,0</t>
+  </si>
+  <si>
+    <t>Короб ПВХ 40х40 мм</t>
+  </si>
+  <si>
+    <t>Провод желто-зеленый ПуГВнг(А)-LS 1x25</t>
+  </si>
+  <si>
+    <t>Провод Rd8</t>
+  </si>
+  <si>
+    <t>Металлорукав в ПВХ изоляции РЗ-ЦП-15</t>
+  </si>
+  <si>
+    <t>Аварийное освещение Вега 60 2Ex Тех  IP65</t>
+  </si>
+  <si>
     <t>Аварийное освещение DL-0128A 28 Вт IP65</t>
   </si>
   <si>
-    <t>Аварийное освещение Вега 60 2Ex Тех  IP65</t>
-  </si>
-  <si>
-    <t>Крышка Угол горизонтальный CPO 90 (50х50)</t>
-  </si>
-  <si>
-    <t>Металлический лоток, неперфорированный (100х50х3000)</t>
-  </si>
-  <si>
-    <t>Металлический лоток, неперфорированный (50х50х3000)</t>
-  </si>
-  <si>
-    <t>Монтажная рама РВМ 2.1.1</t>
-  </si>
-  <si>
-    <t>Монтажная рама РВМ 4.1.1</t>
-  </si>
-  <si>
-    <t>Ответная рама РВО 2.1.1</t>
-  </si>
-  <si>
-    <t>Ответная рама РВО 4.1.1</t>
-  </si>
-  <si>
-    <t>Пластина анкерная 120</t>
-  </si>
-  <si>
-    <t>Пластина для заземления PTCE арт. 37501</t>
-  </si>
-  <si>
-    <t>Плата печатная ПСМ.11.00.01.01-02</t>
-  </si>
-  <si>
-    <t>Плата питания ПСМ.11.00.00.01-02</t>
-  </si>
-  <si>
-    <t>Угол горизонтальный CPO 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Уплотнительный модуль МКС 20/О 5-14мм</t>
-  </si>
-  <si>
-    <t>Уплотнительный модуль МКС 40/Ø 17-34 мм</t>
-  </si>
-  <si>
-    <t>Наконечник НВИ 2-5 вилка 1,5-2,5мм SQ0503-0005 TDM</t>
-  </si>
-  <si>
-    <t>Припой с канифолью ПОС 61 d=1,0мм ГОСТ 21931-76 (Sn61; Pb39)</t>
-  </si>
-  <si>
-    <t>Держатель проводника Rd8, DEHNGRIP NIRO h20 с отв.8мм М6</t>
-  </si>
-  <si>
-    <t>Диод КД209А ТТЗ.362.008 ТУ</t>
-  </si>
-  <si>
-    <t>Заглушка  25х25 для трубы профильной ПВД черная</t>
-  </si>
-  <si>
-    <t>Заглушка 10707 Legrand DPL 65х195</t>
-  </si>
-  <si>
-    <t>Лента самоклеящаяся уплотнительная ППЭ 5х15 МКС</t>
-  </si>
-  <si>
-    <t>Трубка для фильтра 1/4" Гейзер</t>
-  </si>
-  <si>
-    <t>MV-клемма проводника Rd8</t>
-  </si>
-  <si>
-    <t>Кабель-канал 10453 Legrand DPL 195х65 (2м)</t>
-  </si>
-  <si>
-    <t>Компрессионный блок МКС КБ 120</t>
-  </si>
-  <si>
-    <t>Консоль с опорой ML 300мм (шт)</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р307(-60+40) 2-6х20НК(А)-1х20НК(В)-6х20НК(С)-4х26(П) 1ЕхеLLCGbXT6, ip66</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р402(-60+40)12-2х20НК(А)-2х20НК(С)-1,5х11(П), 1ЕхеLLCGbXT6, ip66, 110х75х55</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р403(-60+40) 2-4х20НК(А)-4х20НК(С)-2,5х20(П),1ЕхеLLCGbXT6, ip66, 160х175х55</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р407(-60+40) 2-8х20НК(А)-8х20НК(С)-2,5х31(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
-  </si>
-  <si>
-    <t>Короб ПВХ 40х40 мм</t>
-  </si>
-  <si>
-    <t>Провод желто-зеленый ПуГВнг(А)-LS 1x6,0</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d8мм</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 3x1,5 d7,2мм</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS- 3х2,50</t>
-  </si>
-  <si>
-    <t>Короб ПВХ 100х60</t>
-  </si>
-  <si>
-    <t>Короб ПВХ  40х25 мм</t>
-  </si>
-  <si>
-    <t>Кабель КПСЭнг(А)-FRLS 2*2*0,75</t>
-  </si>
-  <si>
-    <t>Кабель КПСЭнг(A)-FRLS 4х2х0,75</t>
-  </si>
-  <si>
-    <t>Кабель КВВГЭнг(А)-LS-ХЛ 7х1,0</t>
-  </si>
-  <si>
-    <t>Кабель КВВГЭнг(А)-LS-ХЛ 4х1,0</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
-  </si>
-  <si>
-    <t>Трубка 3.31 ТВ-40 ГОСТ 19034-82</t>
-  </si>
-  <si>
-    <t>Провод НВМ 0,35 IV 500 ГОСТ 17515-72</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-FRLS 3x1,5 d7,2мм</t>
-  </si>
-  <si>
-    <t>Провод желто-зеленый ПуГВнг(А)-LS 1x25</t>
-  </si>
-  <si>
-    <t>Провод Rd8</t>
-  </si>
-  <si>
-    <t>Металлорукав в ПВХ изоляции РЗ-ЦП-15</t>
+    <t>Держатель для полосы заземления К-188 У2 (цинк)</t>
+  </si>
+  <si>
+    <t>Геркон КЭМ-2</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р407(-60+40) 2-8х20НК(А)-8х20НК(С)-4х26(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
+  </si>
+  <si>
+    <t>Коробка распаячная КМ41242 IP55</t>
+  </si>
+  <si>
+    <t>Крепление для труб ПВХ с защелкой, 16 мм</t>
+  </si>
+  <si>
+    <t>Крышка (100х15х3000)</t>
+  </si>
+  <si>
+    <t>Крышка (50х15х3000)</t>
+  </si>
+  <si>
+    <t>Крышка на Угол вертикальный внешний CD 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Крышка Угол горизонтальный CPO 90 (100х50)</t>
+  </si>
+  <si>
+    <t>Профиль PSM (3000) арт. 34181</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с наружной резьбой РКН-15 (ММРн-15)</t>
+  </si>
+  <si>
+    <t>Скоба металлическая СМО 16-17 49152 КВТ</t>
+  </si>
+  <si>
+    <t>Считыватель бесконтактный для proxi-карт, Proxy-3МA IP20</t>
+  </si>
+  <si>
+    <t>Считыватель бесконтактный для proxi-карт, RD 26-REH-КМ АЯКС Ex mb IIC T5 Gb X , IP67</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (100 х 50)</t>
   </si>
   <si>
     <t>Выключатель двухклавишный IP55</t>
   </si>
   <si>
-    <t>Геркон КЭМ-2</t>
-  </si>
-  <si>
-    <t>Держатель для полосы заземления К-188 У2 (цинк)</t>
-  </si>
-  <si>
-    <t>Угол горизонтальный CPO 90 (100 х 50)</t>
-  </si>
-  <si>
-    <t>Считыватель бесконтактный для proxi-карт, RD 26-REH-КМ АЯКС Ex mb IIC T5 Gb X , IP67</t>
-  </si>
-  <si>
-    <t>Считыватель бесконтактный для proxi-карт, Proxy-3МA IP20</t>
-  </si>
-  <si>
-    <t>Скоба металлическая СМО 16-17 49152 КВТ</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с наружной резьбой РКН-15 (ММРн-15)</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
-  </si>
-  <si>
-    <t>Профиль PSM (3000) арт. 34181</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р407(-60+40) 2-8х20НК(А)-8х20НК(С)-4х26(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
-  </si>
-  <si>
-    <t>Коробка распаячная КМ41242 IP55</t>
-  </si>
-  <si>
-    <t>Крышка Угол горизонтальный CPO 90 (100х50)</t>
-  </si>
-  <si>
-    <t>Крышка на Угол вертикальный внешний CD 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Крышка (50х15х3000)</t>
-  </si>
-  <si>
-    <t>Крышка (100х15х3000)</t>
-  </si>
-  <si>
-    <t>Крепление для труб ПВХ с защелкой, 16 мм</t>
-  </si>
-  <si>
     <t>Очки защитные для токарей.О15.</t>
   </si>
   <si>
@@ -609,57 +597,57 @@
     <t>Пост аварийной сигнализации загазованности в/защ.ПАСВ1-П-75-1Ж1К-В1 (=24В, -60..+40С) 1ExsIICT6</t>
   </si>
   <si>
+    <t>Пружина НТ.3.02.00.00.002-01</t>
+  </si>
+  <si>
+    <t>Пружина №467 НТ.200.000.029.0</t>
+  </si>
+  <si>
+    <t>Пружина крышки НТ.200.004.003.0</t>
+  </si>
+  <si>
+    <t>Пружина №442 НТ.110.000.007.0</t>
+  </si>
+  <si>
     <t>Магнит МС3 ЦО 14,5/4 ТУ 3498-005-12591667-2014</t>
   </si>
   <si>
-    <t>Пружина №442 НТ.110.000.007.0</t>
-  </si>
-  <si>
-    <t>Пружина крышки НТ.200.004.003.0</t>
-  </si>
-  <si>
-    <t>Пружина №467 НТ.200.000.029.0</t>
-  </si>
-  <si>
-    <t>Пружина НТ.3.02.00.00.002-01</t>
-  </si>
-  <si>
     <t>Грунт-эмаль Дюропокс ДТМ 80 (внутрянка)</t>
   </si>
   <si>
+    <t>Легкосбрасываемое окнная конструкция 1200х1100 мм / ПВХ-профили морозост. исп, RAL 9003 белый</t>
+  </si>
+  <si>
+    <t>Задвижка ЗКС 31лс77нж Ду 15 Ру 40 МПа (соединение муфтовое Rc 1/2)</t>
+  </si>
+  <si>
+    <t>Задвижка клиновая литая ЗКЛ 50-40 УХЛ1 30С15нж, класс герм.А (ряд 2, исп.фл.3)</t>
+  </si>
+  <si>
+    <t>Задвижка клиновая литая ЗКЛ 80-40 УХЛ1 30лс15нж, класс герм.А (ряд 2, исп.фл.3)</t>
+  </si>
+  <si>
+    <t>Клапан обратный поворотный КОП 80-40 УХЛ1 19лс53нж (исп. фл. 3)</t>
+  </si>
+  <si>
     <t>Дверь левс доводчиком2000х1000мм(ВхШ) полотно RAL 9003(белый)/коробка(RAL 9003)(белый)с цепью</t>
   </si>
   <si>
-    <t>Клапан обратный поворотный КОП 80-40 УХЛ1 19лс53нж (исп. фл. 3)</t>
-  </si>
-  <si>
-    <t>Задвижка клиновая литая ЗКЛ 80-40 УХЛ1 30лс15нж, класс герм.А (ряд 2, исп.фл.3)</t>
-  </si>
-  <si>
-    <t>Легкосбрасываемое окнная конструкция 1200х1100 мм / ПВХ-профили морозост. исп, RAL 9003 белый</t>
-  </si>
-  <si>
-    <t>Задвижка клиновая литая ЗКЛ 50-40 УХЛ1 30С15нж, класс герм.А (ряд 2, исп.фл.3)</t>
-  </si>
-  <si>
-    <t>Задвижка ЗКС 31лс77нж Ду 15 Ру 40 МПа (соединение муфтовое Rc 1/2)</t>
+    <t>Гайка М16-6Н.8.20.019 ГОСТ 15523-70</t>
+  </si>
+  <si>
+    <t>Гайка М14х1,5 ГОСТ 15522-70</t>
+  </si>
+  <si>
+    <t>Гайка М10.5 019 ГОСТ 5927-70</t>
+  </si>
+  <si>
+    <t>Гайка М10-6Н ГОСТ 5927-70 (размер под ключ S=17)</t>
   </si>
   <si>
     <t>Болт М8-6gх25.58.019 ГОСТ 7798-70</t>
   </si>
   <si>
-    <t>Гайка М10-6Н ГОСТ 5927-70 (размер под ключ S=17)</t>
-  </si>
-  <si>
-    <t>Гайка М10.5 019 ГОСТ 5927-70</t>
-  </si>
-  <si>
-    <t>Гайка М14х1,5 ГОСТ 15522-70</t>
-  </si>
-  <si>
-    <t>Гайка М16-6Н.8.20.019 ГОСТ 15523-70</t>
-  </si>
-  <si>
     <t>Лист чечевица В-К-ПУ-3,0 Ст.09Г2С ГОСТ 8568-77</t>
   </si>
   <si>
@@ -684,46 +672,28 @@
     <t>Лист Б-ПР-1,0 ГОСТ 19904-74/ 4-III-Ст3кп ГОСТ 16523-89</t>
   </si>
   <si>
+    <t>Кольцо уплотнительное НТ 202.003.004.0</t>
+  </si>
+  <si>
+    <t>Кольцо А18х1,2 ГОСТ 13942-86</t>
+  </si>
+  <si>
+    <t>Кольцо 070-076-36 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 038-042-25 ГОСТ 9833-70</t>
+  </si>
+  <si>
     <t>Кольцо 035-041-36-2-4 ГОСТ 9833-73</t>
   </si>
   <si>
-    <t>Кольцо 038-042-25 ГОСТ 9833-70</t>
-  </si>
-  <si>
-    <t>Кольцо 070-076-36 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Кольцо А18х1,2 ГОСТ 13942-86</t>
-  </si>
-  <si>
-    <t>Кольцо уплотнительное НТ 202.003.004.0</t>
-  </si>
-  <si>
-    <t>Пластина WNMG 080408-GP GM3225 GESAC</t>
-  </si>
-  <si>
-    <t>Пластина CCMT09T308-GP GM3225 GESAC</t>
-  </si>
-  <si>
-    <t>Пластина SPGT060204-DG AT9030</t>
-  </si>
-  <si>
-    <t>Фреза концевая твердосплавная GE-D10.0-25L-4F-10D-75L</t>
-  </si>
-  <si>
-    <t>Пластина R390-11 T3 08M-PM 1130 SANDVIK (кратно12 для корпуса ПСМ, кратно 2 -для верх.корп.КМР)</t>
-  </si>
-  <si>
-    <t>Фреза концевая твердосплавная D5*HRC55*L100*25*4F</t>
-  </si>
-  <si>
-    <t>Винт М4х6 ГОСТ 17473-80</t>
-  </si>
-  <si>
-    <t>Болт М5х40 оцинк. ГОСТ 7805-70</t>
-  </si>
-  <si>
-    <t>Шайба 5.01.019 ГОСТ 11371-78</t>
+    <t>Державка SNR0010K11</t>
+  </si>
+  <si>
+    <t>Пластина 11IR2.00ISO BT2225</t>
+  </si>
+  <si>
+    <t>Кабель ВВГ 3*2,5</t>
   </si>
   <si>
     <t>Кольцо А75х1,7 ГОСТ 13943-86_</t>
@@ -1163,12 +1133,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F198"/>
+  <dimension ref="A1:F190"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="46.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="74.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="75" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
@@ -1218,7 +1188,7 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D3" s="5">
         <v>15</v>
@@ -1236,7 +1206,7 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D4" s="5">
         <v>9</v>
@@ -1254,7 +1224,7 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D5" s="5">
         <v>21</v>
@@ -1272,7 +1242,7 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D6" s="5">
         <v>60</v>
@@ -1290,7 +1260,7 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D7" s="5">
         <v>6</v>
@@ -1308,7 +1278,7 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D8" s="5">
         <v>0.75</v>
@@ -1326,7 +1296,7 @@
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D9" s="5">
         <v>5.4</v>
@@ -1344,7 +1314,7 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="8" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D10" s="5">
         <v>0.33</v>
@@ -1362,7 +1332,7 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D11" s="5">
         <v>0.15</v>
@@ -1380,7 +1350,7 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D12" s="5">
         <v>6.6</v>
@@ -1398,7 +1368,7 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D13" s="5">
         <v>3.6</v>
@@ -1416,7 +1386,7 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="8" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D14" s="5">
         <v>36.9</v>
@@ -1434,7 +1404,7 @@
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="8" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D15" s="5">
         <v>0.3</v>
@@ -1452,7 +1422,7 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="8" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D16" s="5">
         <v>52.05</v>
@@ -1470,7 +1440,7 @@
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="8" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D17" s="5">
         <v>90</v>
@@ -1488,7 +1458,7 @@
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="8" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D18" s="5">
         <v>47.4</v>
@@ -1506,7 +1476,7 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="8" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D19" s="5">
         <v>15.9</v>
@@ -1524,7 +1494,7 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D20" s="5">
         <v>472.8</v>
@@ -1542,7 +1512,7 @@
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="8" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D21" s="5">
         <v>112.8</v>
@@ -1578,7 +1548,7 @@
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="8" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D23" s="5">
         <v>20.7</v>
@@ -1596,7 +1566,7 @@
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="8" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D24" s="5">
         <v>22.5</v>
@@ -1614,7 +1584,7 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="8" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D25" s="5">
         <v>13.65</v>
@@ -1632,7 +1602,7 @@
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="8" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D26" s="5">
         <v>21.9</v>
@@ -1650,7 +1620,7 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="8" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D27" s="5">
         <v>6.6</v>
@@ -1668,7 +1638,7 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D28" s="5">
         <v>0.09</v>
@@ -1686,7 +1656,7 @@
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="8" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D29" s="5">
         <v>55.8</v>
@@ -1704,7 +1674,7 @@
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D30" s="5">
         <v>20.399999999999999</v>
@@ -1722,7 +1692,7 @@
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D31" s="5">
         <v>40.5</v>
@@ -1740,7 +1710,7 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D32" s="5">
         <v>33.15</v>
@@ -1758,10 +1728,10 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="8" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D33" s="5">
-        <v>20.7</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>11</v>
@@ -1776,10 +1746,10 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D34" s="5">
-        <v>38.700000000000003</v>
+        <v>20.7</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>11</v>
@@ -1794,7 +1764,7 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="8" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D35" s="5">
         <v>1.05</v>
@@ -1848,7 +1818,7 @@
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="8" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D38" s="5">
         <v>200</v>
@@ -1866,7 +1836,7 @@
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="8" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D39" s="5">
         <v>200</v>
@@ -1884,7 +1854,7 @@
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="8" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D40" s="5">
         <v>200</v>
@@ -1902,7 +1872,7 @@
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="8" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D41" s="5">
         <v>200</v>
@@ -1920,7 +1890,7 @@
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="8" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D42" s="5">
         <v>200</v>
@@ -1938,7 +1908,7 @@
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="8" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D43" s="5">
         <v>200</v>
@@ -1956,7 +1926,7 @@
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="8" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D44" s="5">
         <v>1</v>
@@ -2004,76 +1974,76 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>46</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="8" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
       <c r="D47" s="5">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>47</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="8" t="s">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="D48" s="5">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>48</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D49" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>49</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D50" s="5">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2082,16 +2052,16 @@
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D51" s="5">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2100,16 +2070,16 @@
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D52" s="5">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2118,16 +2088,16 @@
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D53" s="5">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2136,16 +2106,16 @@
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="8" t="s">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="D54" s="5">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2154,16 +2124,16 @@
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D55" s="5">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2172,16 +2142,16 @@
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D56" s="5">
-        <v>8</v>
+        <v>16.8</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2190,16 +2160,16 @@
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D57" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2208,16 +2178,16 @@
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D58" s="5">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2226,16 +2196,16 @@
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D59" s="5">
-        <v>56</v>
+        <v>192</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2244,16 +2214,16 @@
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D60" s="5">
-        <v>200</v>
+        <v>560</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2262,16 +2232,16 @@
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="8" t="s">
-        <v>134</v>
+        <v>25</v>
       </c>
       <c r="D61" s="5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2280,16 +2250,16 @@
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D62" s="5">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2298,16 +2268,16 @@
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="8" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="D63" s="5">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2316,16 +2286,16 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="8" t="s">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="D64" s="5">
-        <v>16</v>
+        <v>240</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2343,7 +2313,7 @@
         <v>7</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2355,13 +2325,13 @@
         <v>137</v>
       </c>
       <c r="D66" s="5">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2373,13 +2343,13 @@
         <v>138</v>
       </c>
       <c r="D67" s="5">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2388,16 +2358,16 @@
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="8" t="s">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="D68" s="5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2406,19 +2376,19 @@
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="8" t="s">
-        <v>140</v>
+        <v>29</v>
       </c>
       <c r="D69" s="5">
-        <v>88</v>
+        <v>153</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -2427,13 +2397,13 @@
         <v>30</v>
       </c>
       <c r="D70" s="5">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2442,16 +2412,16 @@
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="8" t="s">
-        <v>141</v>
+        <v>31</v>
       </c>
       <c r="D71" s="5">
-        <v>560</v>
+        <v>160</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2460,16 +2430,16 @@
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="8" t="s">
-        <v>142</v>
+        <v>32</v>
       </c>
       <c r="D72" s="5">
-        <v>192</v>
+        <v>6</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2478,16 +2448,16 @@
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="8" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D73" s="5">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2496,16 +2466,16 @@
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="8" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D74" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2514,16 +2484,16 @@
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="8" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D75" s="5">
-        <v>16.8</v>
+        <v>200</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2532,16 +2502,16 @@
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="8" t="s">
-        <v>146</v>
+        <v>33</v>
       </c>
       <c r="D76" s="5">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2550,16 +2520,16 @@
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="8" t="s">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c r="D77" s="5">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2568,16 +2538,16 @@
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="8" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D78" s="5">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2586,16 +2556,16 @@
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="8" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D79" s="5">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2604,88 +2574,88 @@
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="8" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D80" s="5">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
         <v>80</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="8" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D81" s="5">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>81</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="8" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D82" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
         <v>82</v>
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="8" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D83" s="5">
-        <v>10</v>
+        <v>144</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
         <v>83</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="8" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D84" s="5">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2694,16 +2664,16 @@
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="D85" s="5">
-        <v>40</v>
+        <v>149</v>
+      </c>
+      <c r="D85" s="7">
+        <v>1199</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2712,16 +2682,16 @@
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="8" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D86" s="5">
-        <v>320</v>
+        <v>56</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2730,16 +2700,16 @@
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="8" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D87" s="5">
-        <v>100.8</v>
+        <v>10</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2748,16 +2718,16 @@
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="D88" s="7">
-        <v>1199</v>
+        <v>152</v>
+      </c>
+      <c r="D88" s="5">
+        <v>30</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2766,16 +2736,16 @@
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="8" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D89" s="5">
-        <v>56</v>
+        <v>861.2</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2784,16 +2754,16 @@
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="8" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D90" s="5">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2802,16 +2772,16 @@
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="8" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D91" s="5">
-        <v>30</v>
+        <v>288</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2820,16 +2790,16 @@
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="8" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D92" s="5">
-        <v>861.2</v>
+        <v>989</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2838,16 +2808,16 @@
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="8" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D93" s="5">
-        <v>98</v>
+        <v>396.5</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2856,16 +2826,16 @@
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="8" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D94" s="5">
-        <v>288</v>
+        <v>0.6</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2874,16 +2844,16 @@
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="8" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D95" s="5">
-        <v>989</v>
+        <v>16</v>
       </c>
       <c r="E95" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2892,16 +2862,16 @@
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="8" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D96" s="5">
-        <v>396.5</v>
+        <v>274.8</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2910,16 +2880,16 @@
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="8" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D97" s="5">
-        <v>0.6</v>
+        <v>100.8</v>
       </c>
       <c r="E97" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2928,16 +2898,16 @@
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="8" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D98" s="5">
-        <v>16</v>
+        <v>320</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2946,16 +2916,16 @@
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="8" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D99" s="5">
-        <v>274.8</v>
+        <v>40</v>
       </c>
       <c r="E99" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2964,7 +2934,7 @@
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="8" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D100" s="5">
         <v>48</v>
@@ -2973,7 +2943,7 @@
         <v>10</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2982,7 +2952,7 @@
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="8" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D101" s="5">
         <v>259</v>
@@ -2991,7 +2961,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3000,7 +2970,7 @@
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="8" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D102" s="7">
         <v>1040</v>
@@ -3009,7 +2979,7 @@
         <v>10</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3018,7 +2988,7 @@
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D103" s="5">
         <v>602.20000000000005</v>
@@ -3027,25 +2997,25 @@
         <v>10</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
         <v>103</v>
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="8" t="s">
-        <v>33</v>
+        <v>167</v>
       </c>
       <c r="D104" s="5">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3054,7 +3024,7 @@
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D105" s="5">
         <v>8</v>
@@ -3063,7 +3033,7 @@
         <v>7</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3072,16 +3042,16 @@
       </c>
       <c r="B106" s="4"/>
       <c r="C106" s="8" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D106" s="5">
-        <v>112</v>
+        <v>400</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3090,34 +3060,34 @@
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="8" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D107" s="5">
-        <v>400</v>
+        <v>112</v>
       </c>
       <c r="E107" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
         <v>107</v>
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="8" t="s">
-        <v>34</v>
+        <v>171</v>
       </c>
       <c r="D108" s="5">
-        <v>160</v>
+        <v>5</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3126,34 +3096,34 @@
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="8" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D109" s="5">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E109" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
         <v>109</v>
       </c>
       <c r="B110" s="4"/>
       <c r="C110" s="8" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D110" s="5">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3162,16 +3132,16 @@
       </c>
       <c r="B111" s="4"/>
       <c r="C111" s="8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D111" s="5">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="E111" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3180,16 +3150,16 @@
       </c>
       <c r="B112" s="4"/>
       <c r="C112" s="8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D112" s="5">
-        <v>900</v>
+        <v>144</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3198,16 +3168,16 @@
       </c>
       <c r="B113" s="4"/>
       <c r="C113" s="8" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D113" s="5">
-        <v>422</v>
+        <v>32</v>
       </c>
       <c r="E113" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3216,16 +3186,16 @@
       </c>
       <c r="B114" s="4"/>
       <c r="C114" s="8" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D114" s="5">
-        <v>298</v>
+        <v>32</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3234,7 +3204,7 @@
       </c>
       <c r="B115" s="4"/>
       <c r="C115" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D115" s="5">
         <v>40</v>
@@ -3243,25 +3213,25 @@
         <v>7</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
         <v>115</v>
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="8" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D116" s="5">
-        <v>5</v>
+        <v>298</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3270,16 +3240,16 @@
       </c>
       <c r="B117" s="4"/>
       <c r="C117" s="8" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D117" s="5">
-        <v>8</v>
+        <v>422</v>
       </c>
       <c r="E117" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3288,16 +3258,16 @@
       </c>
       <c r="B118" s="4"/>
       <c r="C118" s="8" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D118" s="5">
-        <v>32</v>
+        <v>900</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3306,34 +3276,34 @@
       </c>
       <c r="B119" s="4"/>
       <c r="C119" s="8" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D119" s="5">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E119" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="3">
         <v>119</v>
       </c>
       <c r="B120" s="4"/>
       <c r="C120" s="8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D120" s="5">
-        <v>144</v>
+        <v>8</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3342,16 +3312,16 @@
       </c>
       <c r="B121" s="4"/>
       <c r="C121" s="8" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D121" s="5">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="E121" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3360,16 +3330,16 @@
       </c>
       <c r="B122" s="4"/>
       <c r="C122" s="8" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D122" s="5">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3381,10 +3351,10 @@
         <v>35</v>
       </c>
       <c r="D123" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>36</v>
@@ -3396,13 +3366,13 @@
       </c>
       <c r="B124" s="4"/>
       <c r="C124" s="8" t="s">
-        <v>190</v>
+        <v>37</v>
       </c>
       <c r="D124" s="5">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>36</v>
@@ -3414,10 +3384,10 @@
       </c>
       <c r="B125" s="4"/>
       <c r="C125" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D125" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E125" s="6" t="s">
         <v>15</v>
@@ -3432,10 +3402,10 @@
       </c>
       <c r="B126" s="4"/>
       <c r="C126" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D126" s="5">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>15</v>
@@ -3450,13 +3420,13 @@
       </c>
       <c r="B127" s="4"/>
       <c r="C127" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D127" s="5">
         <v>10</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>36</v>
@@ -3468,13 +3438,13 @@
       </c>
       <c r="B128" s="4"/>
       <c r="C128" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D128" s="5">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>36</v>
@@ -3486,10 +3456,10 @@
       </c>
       <c r="B129" s="4"/>
       <c r="C129" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D129" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E129" s="6" t="s">
         <v>7</v>
@@ -3504,7 +3474,7 @@
       </c>
       <c r="B130" s="4"/>
       <c r="C130" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D130" s="5">
         <v>20</v>
@@ -3522,10 +3492,10 @@
       </c>
       <c r="B131" s="4"/>
       <c r="C131" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D131" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E131" s="6" t="s">
         <v>7</v>
@@ -3540,10 +3510,10 @@
       </c>
       <c r="B132" s="4"/>
       <c r="C132" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D132" s="5">
-        <v>20</v>
+        <v>45</v>
+      </c>
+      <c r="D132" s="7">
+        <v>1000</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>7</v>
@@ -3558,10 +3528,10 @@
       </c>
       <c r="B133" s="4"/>
       <c r="C133" s="8" t="s">
-        <v>45</v>
+        <v>186</v>
       </c>
       <c r="D133" s="5">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E133" s="6" t="s">
         <v>7</v>
@@ -3578,8 +3548,8 @@
       <c r="C134" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D134" s="7">
-        <v>1000</v>
+      <c r="D134" s="5">
+        <v>10</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>7</v>
@@ -3597,13 +3567,13 @@
         <v>47</v>
       </c>
       <c r="D135" s="5">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3612,16 +3582,16 @@
       </c>
       <c r="B136" s="4"/>
       <c r="C136" s="8" t="s">
-        <v>191</v>
+        <v>50</v>
       </c>
       <c r="D136" s="5">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3630,16 +3600,16 @@
       </c>
       <c r="B137" s="4"/>
       <c r="C137" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D137" s="5">
+        <v>10</v>
+      </c>
+      <c r="E137" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F137" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="D137" s="5">
-        <v>20</v>
-      </c>
-      <c r="E137" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F137" s="4" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3648,16 +3618,16 @@
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="8" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D138" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3666,7 +3636,7 @@
       </c>
       <c r="B139" s="4"/>
       <c r="C139" s="8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D139" s="5">
         <v>10</v>
@@ -3675,7 +3645,7 @@
         <v>15</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3684,7 +3654,7 @@
       </c>
       <c r="B140" s="4"/>
       <c r="C140" s="8" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D140" s="5">
         <v>10</v>
@@ -3693,7 +3663,7 @@
         <v>15</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3702,16 +3672,16 @@
       </c>
       <c r="B141" s="4"/>
       <c r="C141" s="8" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D141" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E141" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3720,16 +3690,16 @@
       </c>
       <c r="B142" s="4"/>
       <c r="C142" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D142" s="5">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3738,16 +3708,16 @@
       </c>
       <c r="B143" s="4"/>
       <c r="C143" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D143" s="5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3756,16 +3726,16 @@
       </c>
       <c r="B144" s="4"/>
       <c r="C144" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D144" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3774,16 +3744,16 @@
       </c>
       <c r="B145" s="4"/>
       <c r="C145" s="8" t="s">
-        <v>56</v>
+        <v>187</v>
       </c>
       <c r="D145" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E145" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3792,7 +3762,7 @@
       </c>
       <c r="B146" s="4"/>
       <c r="C146" s="8" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D146" s="5">
         <v>2</v>
@@ -3801,7 +3771,7 @@
         <v>7</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3810,7 +3780,7 @@
       </c>
       <c r="B147" s="4"/>
       <c r="C147" s="8" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D147" s="5">
         <v>6</v>
@@ -3828,10 +3798,10 @@
       </c>
       <c r="B148" s="4"/>
       <c r="C148" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="D148" s="7">
-        <v>4000</v>
+        <v>190</v>
+      </c>
+      <c r="D148" s="5">
+        <v>100</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>7</v>
@@ -3846,7 +3816,7 @@
       </c>
       <c r="B149" s="4"/>
       <c r="C149" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D149" s="5">
         <v>100</v>
@@ -3864,7 +3834,7 @@
       </c>
       <c r="B150" s="4"/>
       <c r="C150" s="8" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D150" s="5">
         <v>200</v>
@@ -3882,7 +3852,7 @@
       </c>
       <c r="B151" s="4"/>
       <c r="C151" s="8" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D151" s="5">
         <v>100</v>
@@ -3900,10 +3870,10 @@
       </c>
       <c r="B152" s="4"/>
       <c r="C152" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="D152" s="5">
-        <v>100</v>
+        <v>194</v>
+      </c>
+      <c r="D152" s="7">
+        <v>4000</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>7</v>
@@ -3918,7 +3888,7 @@
       </c>
       <c r="B153" s="4"/>
       <c r="C153" s="8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D153" s="5">
         <v>29</v>
@@ -3936,10 +3906,10 @@
       </c>
       <c r="B154" s="4"/>
       <c r="C154" s="8" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D154" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>7</v>
@@ -3954,10 +3924,10 @@
       </c>
       <c r="B155" s="4"/>
       <c r="C155" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D155" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E155" s="6" t="s">
         <v>7</v>
@@ -3972,7 +3942,7 @@
       </c>
       <c r="B156" s="4"/>
       <c r="C156" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D156" s="5">
         <v>3</v>
@@ -3990,10 +3960,10 @@
       </c>
       <c r="B157" s="4"/>
       <c r="C157" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D157" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E157" s="6" t="s">
         <v>7</v>
@@ -4008,10 +3978,10 @@
       </c>
       <c r="B158" s="4"/>
       <c r="C158" s="8" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D158" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>7</v>
@@ -4026,10 +3996,10 @@
       </c>
       <c r="B159" s="4"/>
       <c r="C159" s="8" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D159" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E159" s="6" t="s">
         <v>7</v>
@@ -4038,22 +4008,22 @@
         <v>59</v>
       </c>
     </row>
-    <row r="160" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="3">
         <v>159</v>
       </c>
       <c r="B160" s="4"/>
       <c r="C160" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D160" s="5">
+        <v>800</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F160" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="D160" s="5">
-        <v>1</v>
-      </c>
-      <c r="E160" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F160" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4062,16 +4032,16 @@
       </c>
       <c r="B161" s="4"/>
       <c r="C161" s="8" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D161" s="5">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="E161" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4080,16 +4050,16 @@
       </c>
       <c r="B162" s="4"/>
       <c r="C162" s="8" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D162" s="5">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4098,16 +4068,16 @@
       </c>
       <c r="B163" s="4"/>
       <c r="C163" s="8" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D163" s="5">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E163" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4116,16 +4086,16 @@
       </c>
       <c r="B164" s="4"/>
       <c r="C164" s="8" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D164" s="5">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4134,13 +4104,13 @@
       </c>
       <c r="B165" s="4"/>
       <c r="C165" s="8" t="s">
-        <v>210</v>
+        <v>61</v>
       </c>
       <c r="D165" s="5">
-        <v>800</v>
+        <v>4</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F165" s="4" t="s">
         <v>62</v>
@@ -4152,16 +4122,16 @@
       </c>
       <c r="B166" s="4"/>
       <c r="C166" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D166" s="5">
-        <v>4</v>
+        <v>207</v>
+      </c>
+      <c r="D166" s="7">
+        <v>2713.44</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4170,16 +4140,16 @@
       </c>
       <c r="B167" s="4"/>
       <c r="C167" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="D167" s="7">
-        <v>2713.44</v>
+        <v>208</v>
+      </c>
+      <c r="D167" s="5">
+        <v>35.28</v>
       </c>
       <c r="E167" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4188,16 +4158,16 @@
       </c>
       <c r="B168" s="4"/>
       <c r="C168" s="8" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D168" s="5">
-        <v>35.28</v>
+        <v>66</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4206,16 +4176,16 @@
       </c>
       <c r="B169" s="4"/>
       <c r="C169" s="8" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D169" s="5">
-        <v>66</v>
+        <v>5.82</v>
       </c>
       <c r="E169" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4224,16 +4194,16 @@
       </c>
       <c r="B170" s="4"/>
       <c r="C170" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D170" s="5">
-        <v>5.82</v>
+        <v>103.74</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4242,52 +4212,52 @@
       </c>
       <c r="B171" s="4"/>
       <c r="C171" s="8" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D171" s="5">
-        <v>103.74</v>
+        <v>20.22</v>
       </c>
       <c r="E171" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="3">
         <v>171</v>
       </c>
       <c r="B172" s="4"/>
       <c r="C172" s="8" t="s">
-        <v>216</v>
+        <v>64</v>
       </c>
       <c r="D172" s="5">
-        <v>20.22</v>
+        <v>612</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="3">
         <v>172</v>
       </c>
       <c r="B173" s="4"/>
       <c r="C173" s="8" t="s">
-        <v>66</v>
+        <v>213</v>
       </c>
       <c r="D173" s="5">
-        <v>612</v>
+        <v>19.5</v>
       </c>
       <c r="E173" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F173" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="F173" s="4" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="174" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4296,16 +4266,16 @@
       </c>
       <c r="B174" s="4"/>
       <c r="C174" s="8" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D174" s="5">
-        <v>19.5</v>
+        <v>1.8</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4314,16 +4284,16 @@
       </c>
       <c r="B175" s="4"/>
       <c r="C175" s="8" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D175" s="5">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="E175" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="176" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4332,16 +4302,16 @@
       </c>
       <c r="B176" s="4"/>
       <c r="C176" s="8" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D176" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4350,16 +4320,16 @@
       </c>
       <c r="B177" s="4"/>
       <c r="C177" s="8" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D177" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E177" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="178" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4368,7 +4338,7 @@
       </c>
       <c r="B178" s="4"/>
       <c r="C178" s="8" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D178" s="5">
         <v>6</v>
@@ -4377,7 +4347,7 @@
         <v>7</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="179" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4386,16 +4356,16 @@
       </c>
       <c r="B179" s="4"/>
       <c r="C179" s="8" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D179" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E179" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="180" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4404,34 +4374,34 @@
       </c>
       <c r="B180" s="4"/>
       <c r="C180" s="8" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="D180" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="3">
         <v>180</v>
       </c>
       <c r="B181" s="4"/>
       <c r="C181" s="8" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="D181" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E181" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4440,16 +4410,16 @@
       </c>
       <c r="B182" s="4"/>
       <c r="C182" s="8" t="s">
-        <v>71</v>
+        <v>220</v>
       </c>
       <c r="D182" s="5">
         <v>1</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="183" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4458,106 +4428,106 @@
       </c>
       <c r="B183" s="4"/>
       <c r="C183" s="8" t="s">
-        <v>73</v>
+        <v>221</v>
       </c>
       <c r="D183" s="5">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="3">
         <v>183</v>
       </c>
       <c r="B184" s="4"/>
       <c r="C184" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="D184" s="5">
-        <v>2</v>
+        <v>222</v>
+      </c>
+      <c r="D184" s="7">
+        <v>200000</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="3">
         <v>184</v>
       </c>
       <c r="B185" s="4"/>
       <c r="C185" s="8" t="s">
-        <v>224</v>
+        <v>72</v>
       </c>
       <c r="D185" s="5">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="E185" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="3">
         <v>185</v>
       </c>
       <c r="B186" s="4"/>
       <c r="C186" s="8" t="s">
-        <v>225</v>
+        <v>74</v>
       </c>
       <c r="D186" s="5">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="3">
         <v>186</v>
       </c>
       <c r="B187" s="4"/>
       <c r="C187" s="8" t="s">
-        <v>226</v>
+        <v>76</v>
       </c>
       <c r="D187" s="5">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="3">
         <v>187</v>
       </c>
       <c r="B188" s="4"/>
       <c r="C188" s="8" t="s">
-        <v>227</v>
+        <v>77</v>
       </c>
       <c r="D188" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="189" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4566,178 +4536,34 @@
       </c>
       <c r="B189" s="4"/>
       <c r="C189" s="8" t="s">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="D189" s="5">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="E189" s="6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="3">
         <v>189</v>
       </c>
       <c r="B190" s="4"/>
       <c r="C190" s="8" t="s">
-        <v>229</v>
+        <v>79</v>
       </c>
       <c r="D190" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="3">
-        <v>190</v>
-      </c>
-      <c r="B191" s="4"/>
-      <c r="C191" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D191" s="5">
-        <v>36</v>
-      </c>
-      <c r="E191" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F191" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="3">
-        <v>191</v>
-      </c>
-      <c r="B192" s="4"/>
-      <c r="C192" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D192" s="5">
-        <v>18</v>
-      </c>
-      <c r="E192" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F192" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A193" s="3">
-        <v>192</v>
-      </c>
-      <c r="B193" s="4"/>
-      <c r="C193" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="D193" s="5">
-        <v>36</v>
-      </c>
-      <c r="E193" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F193" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A194" s="3">
-        <v>193</v>
-      </c>
-      <c r="B194" s="4"/>
-      <c r="C194" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D194" s="5">
-        <v>18</v>
-      </c>
-      <c r="E194" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F194" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A195" s="3">
-        <v>194</v>
-      </c>
-      <c r="B195" s="4"/>
-      <c r="C195" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D195" s="5">
-        <v>36</v>
-      </c>
-      <c r="E195" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F195" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A196" s="3">
-        <v>195</v>
-      </c>
-      <c r="B196" s="4"/>
-      <c r="C196" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D196" s="5">
-        <v>18</v>
-      </c>
-      <c r="E196" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F196" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A197" s="3">
-        <v>196</v>
-      </c>
-      <c r="B197" s="4"/>
-      <c r="C197" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="D197" s="5">
-        <v>36</v>
-      </c>
-      <c r="E197" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F197" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="3">
-        <v>197</v>
-      </c>
-      <c r="B198" s="4"/>
-      <c r="C198" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="D198" s="5">
-        <v>36</v>
-      </c>
-      <c r="E198" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F198" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{673FD8E4-332E-4635-8F56-8C8C65B1E925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A462E5-8A6E-4631-8FCE-7C5D334B5D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4110" yWindow="4110" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист_1" sheetId="1" r:id="rId1"/>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="224">
-  <si>
-    <t>№ п/п</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="218">
   <si>
     <t>Полное наименование изделия Поставщика</t>
   </si>
@@ -45,658 +42,643 @@
     <t>Примечание</t>
   </si>
   <si>
-    <t>Палитра цветов</t>
+    <t>шт.</t>
+  </si>
+  <si>
+    <t>ИИ00-000017</t>
+  </si>
+  <si>
+    <t>Мел сварщика белый</t>
   </si>
   <si>
     <t>шт</t>
   </si>
   <si>
-    <t>ЛГУП-7511</t>
-  </si>
-  <si>
-    <t>ЛГУП-7564</t>
+    <t>Ключи обмедненные</t>
+  </si>
+  <si>
+    <t>набор</t>
+  </si>
+  <si>
+    <t>Паронит 2мм</t>
+  </si>
+  <si>
+    <t>лист</t>
+  </si>
+  <si>
+    <t>Маркер по металлу белый</t>
+  </si>
+  <si>
+    <t>Маркер по металлу красный</t>
+  </si>
+  <si>
+    <t>Маркер по металлу черный тонкий</t>
+  </si>
+  <si>
+    <t>Паронит 3 мм</t>
+  </si>
+  <si>
+    <t>Кувалда 1 кг</t>
+  </si>
+  <si>
+    <t>ИИ00-000013</t>
+  </si>
+  <si>
+    <t>Ключ комбинир. 36 мм</t>
+  </si>
+  <si>
+    <t>Ключ комбинир. 30 мм</t>
+  </si>
+  <si>
+    <t>Ключ комбинир. 24 мм</t>
+  </si>
+  <si>
+    <t>Изолента</t>
+  </si>
+  <si>
+    <t>Фонарик налобный аккумуляторный</t>
+  </si>
+  <si>
+    <t>Рулетка  5м х 25мм Компакт в обрезиненном корпусе</t>
+  </si>
+  <si>
+    <t>Штангенциркуль</t>
+  </si>
+  <si>
+    <t>Дождевик-костюм темно-синий 52-54</t>
+  </si>
+  <si>
+    <t>компл</t>
+  </si>
+  <si>
+    <t>ИИ00-000014</t>
   </si>
   <si>
     <t>м</t>
   </si>
   <si>
+    <t>ИИУП-000324</t>
+  </si>
+  <si>
+    <t>ИИУП-000336</t>
+  </si>
+  <si>
+    <t>Держатель проводника Rd8</t>
+  </si>
+  <si>
+    <t>Индикатор положения поплавка ИПП00.00.000 вер.2</t>
+  </si>
+  <si>
+    <t>Ответвитель DPT T-образный горизонтальный 100х50 арт.36122 "DKC"</t>
+  </si>
+  <si>
+    <t>Извещатель пожарный пламени взрывозащищенный,Спектрон -202. В комплекте 1 кабельных ввода (15 мм)</t>
+  </si>
+  <si>
+    <t>Кабель защиты огнестойкие КПСЭнг(А)-FRHF 2х2х0,75</t>
+  </si>
+  <si>
+    <t>(не исп12) шт</t>
+  </si>
+  <si>
+    <t>Газоанализатор взрывозащищенный СГОЭС 1Ex d IIC T4 Gb, IP67</t>
+  </si>
+  <si>
+    <t>ИИУП-000340</t>
+  </si>
+  <si>
+    <t>Блок клапанный БКН 3-11</t>
+  </si>
+  <si>
+    <t>Влагомер сырой нефти ВСН-2-80-100 1Ex ib llA T6, IP67</t>
+  </si>
+  <si>
     <t>кг</t>
   </si>
   <si>
+    <t>ИИУП-000346</t>
+  </si>
+  <si>
+    <t>ИИУП-000350</t>
+  </si>
+  <si>
+    <t>Противогазы</t>
+  </si>
+  <si>
+    <t>Шапка зимняя</t>
+  </si>
+  <si>
+    <t>ИИУП-000359</t>
+  </si>
+  <si>
+    <t>зимняя спецодежда (ИТР)</t>
+  </si>
+  <si>
+    <t>Зимняя обувь</t>
+  </si>
+  <si>
+    <t>Шлагбаум "AN-Motors"</t>
+  </si>
+  <si>
+    <t>НТУП-018367</t>
+  </si>
+  <si>
+    <t>Сенсорная панель оператора Weintek MT8106iP</t>
+  </si>
+  <si>
+    <t>ИИУП-000366</t>
+  </si>
+  <si>
+    <t>ИИУП-000370</t>
+  </si>
+  <si>
+    <t>НТУП-018372</t>
+  </si>
+  <si>
+    <t>печать брошюр</t>
+  </si>
+  <si>
+    <t>Доп. услуги по обеспечению спецоснасткой</t>
+  </si>
+  <si>
+    <t>Печать</t>
+  </si>
+  <si>
+    <t>Печать с автоматической оснасткой</t>
+  </si>
+  <si>
+    <t>Печать ИПП НТ</t>
+  </si>
+  <si>
+    <t>Сэндвич-панель</t>
+  </si>
+  <si>
+    <t>ИИУП-000382</t>
+  </si>
+  <si>
+    <t>Комплект элементов</t>
+  </si>
+  <si>
+    <t>Станок</t>
+  </si>
+  <si>
+    <t>ИИУП-000384</t>
+  </si>
+  <si>
+    <t>ИИУП-000386</t>
+  </si>
+  <si>
+    <t>ИИ00-000057</t>
+  </si>
+  <si>
+    <t>Дренажный насос</t>
+  </si>
+  <si>
+    <t>ИИУП-000393</t>
+  </si>
+  <si>
+    <t>Станция биологической очистки</t>
+  </si>
+  <si>
+    <t>Труба (шт)</t>
+  </si>
+  <si>
+    <t>Монтажные работы</t>
+  </si>
+  <si>
+    <t>труба 110-L500mm</t>
+  </si>
+  <si>
+    <t>Отвод 110*45</t>
+  </si>
+  <si>
+    <t>Муфта соединительная d25</t>
+  </si>
+  <si>
+    <t>песок</t>
+  </si>
+  <si>
+    <t>м3</t>
+  </si>
+  <si>
+    <t>пог. м</t>
+  </si>
+  <si>
+    <t>Видеорегистратор</t>
+  </si>
+  <si>
+    <t>ИИУП-000394</t>
+  </si>
+  <si>
+    <t>ИИУП-000398</t>
+  </si>
+  <si>
+    <t>ИИУП-000403</t>
+  </si>
+  <si>
+    <t>ИИУП-000404</t>
+  </si>
+  <si>
+    <t>ИИУП-000405</t>
+  </si>
+  <si>
+    <t>ИИУП-000407</t>
+  </si>
+  <si>
+    <t>Тройник 110 ПНД</t>
+  </si>
+  <si>
+    <t>ИИУП-000411</t>
+  </si>
+  <si>
+    <t>Саморез с пресс шайбой 4,2х13</t>
+  </si>
+  <si>
+    <t>ИИУП-000412</t>
+  </si>
+  <si>
+    <t>Шиномонтаж</t>
+  </si>
+  <si>
+    <t>КИ00-000031</t>
+  </si>
+  <si>
+    <t>ИИУП-000417</t>
+  </si>
+  <si>
+    <t>ЛГУП-8136</t>
+  </si>
+  <si>
+    <t>ЛГУП-8137</t>
+  </si>
+  <si>
     <t>м2</t>
   </si>
   <si>
-    <t>Лист S=6 Ст.09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Ящик пластиковый396х297х280</t>
-  </si>
-  <si>
-    <t>шт.</t>
-  </si>
-  <si>
-    <t>ЛГУП-7773</t>
-  </si>
-  <si>
-    <t>Ящик 60х40х40 пластик синий</t>
-  </si>
-  <si>
-    <t>ЛГУП-7968</t>
-  </si>
-  <si>
-    <t>КИ00-000026</t>
-  </si>
-  <si>
-    <t>Ремонт двери 2000х1000мм(уст.ка вент. решеток, установка цепи и фиксатора, покраска)</t>
-  </si>
-  <si>
-    <t>ЛГУП-7982</t>
-  </si>
-  <si>
-    <t>Ремонт двери 1900х1000мм(уст.ка вент. решеток, установка цепи и фиксатора, покраска)</t>
-  </si>
-  <si>
-    <t>ЛГУП-7654</t>
-  </si>
-  <si>
-    <t>мм</t>
-  </si>
-  <si>
-    <t>Комплект кабельной проходки МКС</t>
-  </si>
-  <si>
-    <t>компл</t>
-  </si>
-  <si>
-    <t>г</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с наружной резьбой РКН-20 У2 IP54 ЗЭТА</t>
-  </si>
-  <si>
-    <t>Лампа индикации ADDS D22 LED белая 220В AC/DC ЛK-22 IP55 25152DEK Dekraft</t>
-  </si>
-  <si>
-    <t>Извещатель пожарный тепловой взрывозащищенный 101-07е 1Ex db [ia Ga] IIC Т4 Gb Х IP66</t>
-  </si>
-  <si>
-    <t>Винт для обеспечения электрического контакта крышек ( М 5 х 8) арт.CM030508</t>
+    <t>Герметик силиконовый</t>
+  </si>
+  <si>
+    <t>ИИУП-000426</t>
+  </si>
+  <si>
+    <t>Фумлента</t>
+  </si>
+  <si>
+    <t>Краскопульт с верх. бачком S900-P d=2мм в блистере  (Русский Мастер) (20)</t>
+  </si>
+  <si>
+    <t>Мешок полиэтиленовый хозяйственный 300х500</t>
+  </si>
+  <si>
+    <t>Емкость пластиковая 0,5л (дно плоское, форма емкости - квадрат или прямоугольник)</t>
+  </si>
+  <si>
+    <t>Гофрокороб 395*155*155</t>
+  </si>
+  <si>
+    <t>Лента упаковочная полипропиленовая 12х0,6мм</t>
+  </si>
+  <si>
+    <t>Пакет с защелкой 250х150</t>
+  </si>
+  <si>
+    <t>Пакет с замком (гриппер) 200*300 , 35 мкм.</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с наружной резьбой РКН-15 (ММРн-15)</t>
+  </si>
+  <si>
+    <t>Розетка Bylectrica 1-местная ОУ с заз.конт. IP54</t>
+  </si>
+  <si>
+    <t>Скоба металлическая СМО 16-17 49152 КВТ</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (100 х 50)</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Извещатель пожарный ручной взрывозащищенный ИП 535-07е 1ExdbIICT6Gb, IP67</t>
+  </si>
+  <si>
+    <t>Извещатель пожарный ручной ИПР 535-25Г IP67</t>
+  </si>
+  <si>
+    <t>Клемма WAGO 222-415, 2 клеммных зажимов, номинальное сечение проводника 0.08-2.5 мм2</t>
+  </si>
+  <si>
+    <t>Клемма WAGO 222-415, 5 клеммных зажимов, номинальное сечение проводника 0.08-2.5 мм2</t>
+  </si>
+  <si>
+    <t>Кольцевой изолир. наконечник 4-6мм2 под винт М6</t>
+  </si>
+  <si>
+    <t>Консоль с опорой ML 300мм (шт)</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р403(-60+40)12-6х20НК(А)-5х20НК(С)-2,5х21(П), 1ЕхеLLCGbXT6, ip66, 110х75х55</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р405(-60+40)2-2х20НК(А)-2х20НК(С)-2,5х10(П), 1ЕхеLLCGbXT6, ip66, 190х75х75</t>
+  </si>
+  <si>
+    <t>Коробка соединительная К-СП 08.08.08</t>
+  </si>
+  <si>
+    <t>Крепление для труб ПВХ с защелкой, 16 мм</t>
+  </si>
+  <si>
+    <t>Крышка Угол горизонтальный CPO 90 (100х50)</t>
+  </si>
+  <si>
+    <t>Светильник взрывозащищенный ДБП 09-15-001 УХЛ1 ExdllBT6G IP65</t>
+  </si>
+  <si>
+    <t>Короб клем. МТ Р407(-60+40) 2-13х20НК(А)-2х20НК(С)-4х25-2,5х40(П),1ЕхеLLCGbXT6, ip66,360х160х90</t>
+  </si>
+  <si>
+    <t>ИБП для шкафа управления</t>
   </si>
   <si>
     <t>Аварийное освещение Вега 60 с БАП 2Ex Тех 1ExmbIIC T6 Gb X, IP65</t>
   </si>
   <si>
-    <t>Пломба 1-6х10-АД-1М ГОСТ 18677-73</t>
-  </si>
-  <si>
-    <t>Электроприв четвер.взры. ГЗ-ОФВ-300/28М 1х220 DN80PN63 L=452 УХЛ (исп. фл. J)</t>
-  </si>
-  <si>
-    <t>Бита (вставка) Spline М 8  L=30мм</t>
-  </si>
-  <si>
-    <t>ЛГУП-7867</t>
-  </si>
-  <si>
-    <t>Ветошь /рул./</t>
-  </si>
-  <si>
-    <t>Пленка воздушно-пузырчатая 1500мм*100 пог.м 2 сл (рул)</t>
-  </si>
-  <si>
-    <t>Маркер белый Paint 4мм</t>
-  </si>
-  <si>
-    <t>Кисточка 2 см</t>
-  </si>
-  <si>
-    <t>Кисточка 5 см</t>
-  </si>
-  <si>
-    <t>Кисточка 10 см</t>
-  </si>
-  <si>
-    <t>Стрейч пленка 500мм*185м</t>
-  </si>
-  <si>
-    <t>Рулетка 3м (Force) (100)</t>
-  </si>
-  <si>
-    <t>Перчатки 4нит. 10кл. (черные) (пара)</t>
-  </si>
-  <si>
-    <t>Рулетка  7,5м х 25мм обрезиненный корпус (3 фиксатора, зацеп с магнитом)</t>
-  </si>
-  <si>
-    <t>Паронит 3 мм</t>
-  </si>
-  <si>
-    <t>лист</t>
-  </si>
-  <si>
-    <t>НТУП-018192</t>
-  </si>
-  <si>
-    <t>Паронит 2мм</t>
-  </si>
-  <si>
-    <t>Ключи обмедненные</t>
-  </si>
-  <si>
-    <t>набор</t>
-  </si>
-  <si>
-    <t>Маркер по металлу белый</t>
-  </si>
-  <si>
-    <t>Маркер по металлу красный</t>
-  </si>
-  <si>
-    <t>Мел сварщика белый</t>
-  </si>
-  <si>
-    <t>Маркер по металлу черный тонкий</t>
-  </si>
-  <si>
-    <t>ЛГУП-7998</t>
-  </si>
-  <si>
-    <t>ЛГУП-7915</t>
-  </si>
-  <si>
-    <t>ЛГУП-8008</t>
-  </si>
-  <si>
-    <t>ЛГУП-8015</t>
-  </si>
-  <si>
-    <t>Шестиграник 27-h12 ГОСТ 8560-78/(ст.13ХФА)</t>
-  </si>
-  <si>
-    <t>ЛГ00-000047</t>
-  </si>
-  <si>
-    <t>ЛГ00-000048</t>
-  </si>
-  <si>
-    <t>Смеси асфальтобетонные плотные мелкозернистые, тип А, марка 1</t>
-  </si>
-  <si>
-    <t>т</t>
-  </si>
-  <si>
-    <t>ЛГУП-8043</t>
-  </si>
-  <si>
-    <t>ЛГУП-8044</t>
-  </si>
-  <si>
-    <t>ЛГУП-8046</t>
-  </si>
-  <si>
-    <t>ЛГУП-8060</t>
-  </si>
-  <si>
-    <t>ЛГУП-8075</t>
-  </si>
-  <si>
-    <t>ЛГУП-8077</t>
-  </si>
-  <si>
-    <t>спец одежда  для специалистов ПНР (зимняя)</t>
-  </si>
-  <si>
-    <t>ЛГУП-8078</t>
-  </si>
-  <si>
-    <t>Патрубок (361)</t>
-  </si>
-  <si>
-    <t>ТЛУП-012027</t>
-  </si>
-  <si>
-    <t>Масло Лукойл 5w -40 4л</t>
-  </si>
-  <si>
-    <t>Тормозная жидкость</t>
-  </si>
-  <si>
-    <t>Масло  Лукойл -Авангард Ультра 5W40 CI-4/SL  п.синт /л/</t>
-  </si>
-  <si>
-    <t>Антифриз  felix</t>
-  </si>
-  <si>
-    <t>Гофрокороб 395*155*155</t>
-  </si>
-  <si>
-    <t>Проволока КО 1,0 ГОСТ 792-67</t>
-  </si>
-  <si>
-    <t>Лента упаковочная полипропиленовая 12х0,6мм</t>
-  </si>
-  <si>
-    <t>Круг D30 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Круг D24 Ст.45 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Круг D20 Ст.35 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Круг D32 Ст. 45 ГОСТ 1050-88</t>
+    <t>Коробка клеммная МТ Р407(-60+40) 2-9х20НК(А)-9х20НК(С)-2,5х34(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р407(-60+40) 2-4х20НК(А)-4х20НК(С)-2,5х10(П),1ЕхеLLCGbXT6, ip66, 190х75х75</t>
+  </si>
+  <si>
+    <t>Коробка клем МТ Р403(-60+40)2-4х20НК(А)--3х25НК(С)-2,5х20(П), 1ЕхеLLCGbXT6 ip66, 160х160х90</t>
+  </si>
+  <si>
+    <t>Светильник НПП 24-100 УХЛ1 IP65</t>
+  </si>
+  <si>
+    <t>Пост кнопочный взрывозащищенный ПВК-25-ХЛ1 управление обогревом IP65 2ExеdIIСТ6</t>
+  </si>
+  <si>
+    <t>Оповещатель светозвуковой Маяк-24К IP53</t>
+  </si>
+  <si>
+    <t>Оповещатель светозвуковой взрывозащ. ВС-07е-И 1ExdIICT6, IP66, 12-24В, -60..+70С</t>
+  </si>
+  <si>
+    <t>Обогреватель взрывозащищенный ОВЭ-4-УХЛ3 1,8 кВт, 380В IExdIIАТ3, IP54</t>
+  </si>
+  <si>
+    <t>Наконечник кабельный ТМЛ 25-8-7</t>
+  </si>
+  <si>
+    <t>Светильник взрывозащищенный ДБП 09-15-101 УХЛ1 ExdllBT6G IP65</t>
+  </si>
+  <si>
+    <t>Крышка Угол горизонтальный CPO 90 (50х50)</t>
+  </si>
+  <si>
+    <t>Извещатель пожарный дымовой ИП 212-130 IP43</t>
+  </si>
+  <si>
+    <t>Извещатель охранный точечный магнитоконтактный взрывозащ.И0102 В3 АТОН исп.21Ч СМД0000000490СМД</t>
+  </si>
+  <si>
+    <t>Извещатель магнитоконтактный Smartec ST-DM146 IP66</t>
+  </si>
+  <si>
+    <t>Выключатель двухклавишный IP55</t>
+  </si>
+  <si>
+    <t>Аварийное освещение DL-0128A 28 Вт IP65</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d8мм</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р405(-60+40)2-4х20НК(А)-4х20НК(С)-4х20(П), 1ЕхеLLCGbXT6, ip66, 190х75х75</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d7.2мм</t>
+  </si>
+  <si>
+    <t>Провод желто-зеленый ПуГВнг(А)-LS 1x6,0</t>
+  </si>
+  <si>
+    <t>Провод желто-зеленый ПуГВнг(А)-LS 1x25</t>
+  </si>
+  <si>
+    <t>Провод Rd8</t>
+  </si>
+  <si>
+    <t>Металлорукав в ПВХ изоляции РЗ-ЦП-15</t>
+  </si>
+  <si>
+    <t>Короб ПВХ 40х40 мм</t>
+  </si>
+  <si>
+    <t>Короб ПВХ 100х60</t>
+  </si>
+  <si>
+    <t>Короб ПВХ  40х25 мм</t>
+  </si>
+  <si>
+    <t>Кабель КПСЭнг(A)-FRLS 2х2х0,75 d7,1мм</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
+  </si>
+  <si>
+    <t>Кабель КВВГЭнг(А)-LS-ХЛ 4х1,0</t>
+  </si>
+  <si>
+    <t>Кабель КВВГЭнг(А)-LS-ХЛ 7х1,0</t>
+  </si>
+  <si>
+    <t>Электроконвектор с терморегулятором ЭВНБ 1кВт, 220В, 50 Гц.</t>
+  </si>
+  <si>
+    <t>Труба D820х12 ст.09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D530х12 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D89х8 ГОСТ 872-78 В 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Задвижка клиновая литая 3КЛ 80-63 ХЛ1 30лс76нж, класс герметичности "А" (Р-Р-2 исп.фл.J)</t>
+  </si>
+  <si>
+    <t>Задвижка клиновая литая ЗКЛ 80-40 УХЛ1 30лс15нж, класс герм.А (ряд 2, исп.фл.3)</t>
+  </si>
+  <si>
+    <t>Круг D23 Ст.09Г2С ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D210 Ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Круг D26 Ст.09Г2С ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D55 ст.09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Квадратный прокат 30х30 Ст.09Г2С ГОСТ 2591-2006</t>
+  </si>
+  <si>
+    <t>Круг D40 Ст.20Х13 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D370 Ст.20 ГОСТ1050-88</t>
+  </si>
+  <si>
+    <t>Днище 219х4-25 ст.20 ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Днище 377-12-16ГС ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Днище 720х12-09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Труба D25х7 ст.10Г2 ГОСТ 8733-74</t>
+  </si>
+  <si>
+    <t>Труба D38х9 Ст.09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Фланец 1-250-40 09Г2С ГОСТ 12821-80</t>
+  </si>
+  <si>
+    <t>Фланец 2-50-40 09Г2С ГОСТ 12821-80</t>
+  </si>
+  <si>
+    <t>Шпонка 6х6х20 ГОСТ 23360-78</t>
+  </si>
+  <si>
+    <t>Шплинт 2х20 ГОСТ 397</t>
+  </si>
+  <si>
+    <t>Шпилька АМ30-6gх180.60.35.III.4.019 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Гайка М8-6Н.5.ГОСТ 5915-70</t>
+  </si>
+  <si>
+    <t>Болт М20-6gх30.58 (S30) ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Болт М8-6gx12 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Гайка М8-6Н.016 ГОСТ 5915-70</t>
+  </si>
+  <si>
+    <t>Шпилька М8х350, кл.пр. 8.8, оц</t>
+  </si>
+  <si>
+    <t>Кольцо А18х1,2 ГОСТ 13942-86</t>
+  </si>
+  <si>
+    <t>Кольцо уплотнительное НТ 202.003.004.0</t>
+  </si>
+  <si>
+    <t>Корпус 2 НТ.007.001.003</t>
+  </si>
+  <si>
+    <t>Мин. вата типа "URSA" П-125</t>
+  </si>
+  <si>
+    <t>Труба D85х15 БрКМц 3-1 ГОСТ 1628-78</t>
+  </si>
+  <si>
+    <t>Труба D85х10 БрАЖ9-4 ГОСТ 1208-90</t>
+  </si>
+  <si>
+    <t>Круг D18 Ст.20Х13 ГОСТ 5949-75</t>
+  </si>
+  <si>
+    <t>Проволока D1.8 Ст.60C2А ГОСТ14963-78</t>
+  </si>
+  <si>
+    <t>Круг D90 Ст.20Х13 ГОСТ 5632-72</t>
   </si>
   <si>
     <t>Сетка полутомпаковая 008Н Л80 ГОСТ 6613-86</t>
   </si>
   <si>
-    <t>Проволока D1.8 Ст.60C2А ГОСТ14963-78</t>
-  </si>
-  <si>
-    <t>Лист Б-ПН-5 ГОСТ 19903/20-ТВ1-М1-КИ-ТО ГОСТ1577</t>
-  </si>
-  <si>
-    <t>Лист Б-ПН-5 ГОСТ 19903-74 / 2-IV-Н Ст.3кп ГОСТ 16523-97 (кг)</t>
-  </si>
-  <si>
-    <t>Лист Б-ПН-10 ГОСТ 19903-74 / 2-IV-Н Ст.3кп ГОСТ 16523-97 (кг)</t>
-  </si>
-  <si>
-    <t>Лист алюм. анод. сатин (черн/бел) 1,0</t>
-  </si>
-  <si>
-    <t>Круг D90 Ст.35 ГОСт1050-88</t>
-  </si>
-  <si>
-    <t>Круг D90 Ст.20Х13 ГОСТ 5632-72</t>
-  </si>
-  <si>
-    <t>Круг D80 Ст.45 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Круг D18 Ст.20Х13 ГОСТ 5949-75</t>
-  </si>
-  <si>
-    <t>Круг D110 Ст.12Х18Н10Т ГОСТ 5949-75</t>
-  </si>
-  <si>
-    <t>Круг D100 Ст.35 ГOСТ 1050-2013</t>
-  </si>
-  <si>
-    <t>Круг D75 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Круг D70 Ст.20Х13 ГОСТ5632-72</t>
-  </si>
-  <si>
-    <t>Круг D65 Ст.35 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Круг D65 Ст.3 ГОСТ 535-2005</t>
-  </si>
-  <si>
-    <t>Круг D60 Ст.35 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Круг D4 Ст.10 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Круг D45 Ст.45 ГОСТ 1050-2013</t>
-  </si>
-  <si>
-    <t>Круг D45 Ст.3 ГОСТ 535-2005</t>
-  </si>
-  <si>
-    <t>Круг D80 Ст.35 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Круг D75 Ст.35 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Круг D42 Ст.14Х17Н2 ГОСТ 5949-75</t>
-  </si>
-  <si>
-    <t>Круг D75 Ст.20Х13 ГОСТ 5632-72</t>
-  </si>
-  <si>
-    <t>Круг D20 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Днище 377х12-09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Днище 219х4-25 16ГС-3 ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Днище 1020х14-09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Днище 820х12-09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Днище 530х12-09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Днище 720х12-09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Газоанализатор взрывозащищенный СГОЭС (метан) 1Ex d IIC T4 Gb, IP67 Ур1. 10%, ур.2 50% НКПР</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р407(-60+40) 2-8х20НК(А)-8х20НК(С)-2,5х31(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р403(-60+40) 2-4х20НК(А)-4х20НК(С)-2,5х20(П),1ЕхеLLCGbXT6, ip66, 160х175х55</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р402(-60+40)12-2х20НК(А)-2х20НК(С)-1,5х11(П), 1ЕхеLLCGbXT6, ip66, 110х75х55</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р307(-60+40) 2-6х20НК(А)-1х20НК(В)-6х20НК(С)-4х26(П) 1ЕхеLLCGbXT6, ip66</t>
-  </si>
-  <si>
-    <t>Консоль с опорой ML 300мм (шт)</t>
-  </si>
-  <si>
-    <t>Компрессионный блок МКС КБ 120</t>
-  </si>
-  <si>
-    <t>Кабель-канал 10453 Legrand DPL 195х65 (2м)</t>
-  </si>
-  <si>
-    <t>Крышка Угол горизонтальный CPO 90 (50х50)</t>
-  </si>
-  <si>
-    <t>Трубка для фильтра 1/4" Гейзер</t>
-  </si>
-  <si>
-    <t>Лента самоклеящаяся уплотнительная ППЭ 5х15 МКС</t>
-  </si>
-  <si>
-    <t>Заглушка 10707 Legrand DPL 65х195</t>
-  </si>
-  <si>
-    <t>Заглушка  25х25 для трубы профильной ПВД черная</t>
-  </si>
-  <si>
-    <t>Диод КД209А ТТЗ.362.008 ТУ</t>
-  </si>
-  <si>
-    <t>Держатель проводника Rd8, DEHNGRIP NIRO h20 с отв.8мм М6</t>
-  </si>
-  <si>
-    <t>Припой с канифолью ПОС 61 d=1,0мм ГОСТ 21931-76 (Sn61; Pb39)</t>
-  </si>
-  <si>
-    <t>Уплотнительный модуль МКС 40/Ø 17-34 мм</t>
-  </si>
-  <si>
-    <t>Уплотнительный модуль МКС 20/О 5-14мм</t>
-  </si>
-  <si>
-    <t>Угол горизонтальный CPO 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Наконечник НВИ 2-5 вилка 1,5-2,5мм SQ0503-0005 TDM</t>
-  </si>
-  <si>
-    <t>MV-клемма проводника Rd8</t>
-  </si>
-  <si>
-    <t>Плата питания ПСМ.11.00.00.01-02</t>
-  </si>
-  <si>
-    <t>Плата печатная ПСМ.11.00.01.01-02</t>
-  </si>
-  <si>
-    <t>Пластина для заземления PTCE арт. 37501</t>
-  </si>
-  <si>
-    <t>Пластина анкерная 120</t>
-  </si>
-  <si>
-    <t>Ответная рама РВО 4.1.1</t>
-  </si>
-  <si>
-    <t>Ответная рама РВО 2.1.1</t>
-  </si>
-  <si>
-    <t>Монтажная рама РВМ 4.1.1</t>
-  </si>
-  <si>
-    <t>Монтажная рама РВМ 2.1.1</t>
-  </si>
-  <si>
-    <t>Металлический лоток, неперфорированный (50х50х3000)</t>
-  </si>
-  <si>
-    <t>Металлический лоток, неперфорированный (100х50х3000)</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 3x1,5 d7,2мм</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS- 3х2,50</t>
-  </si>
-  <si>
-    <t>Короб ПВХ 100х60</t>
-  </si>
-  <si>
-    <t>Короб ПВХ  40х25 мм</t>
-  </si>
-  <si>
-    <t>Кабель КПСЭнг(А)-FRLS 2*2*0,75</t>
-  </si>
-  <si>
-    <t>Кабель КПСЭнг(A)-FRLS 4х2х0,75</t>
-  </si>
-  <si>
-    <t>Кабель КВВГЭнг(А)-LS-ХЛ 7х1,0</t>
-  </si>
-  <si>
-    <t>Кабель КВВГЭнг(А)-LS-ХЛ 4х1,0</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
-  </si>
-  <si>
-    <t>Трубка 3.31 ТВ-40 ГОСТ 19034-82</t>
-  </si>
-  <si>
-    <t>Провод НВМ 0,35 IV 500 ГОСТ 17515-72</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-FRLS 3x1,5 d7,2мм</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d8мм</t>
-  </si>
-  <si>
-    <t>Провод желто-зеленый ПуГВнг(А)-LS 1x6,0</t>
-  </si>
-  <si>
-    <t>Короб ПВХ 40х40 мм</t>
-  </si>
-  <si>
-    <t>Провод желто-зеленый ПуГВнг(А)-LS 1x25</t>
-  </si>
-  <si>
-    <t>Провод Rd8</t>
-  </si>
-  <si>
-    <t>Металлорукав в ПВХ изоляции РЗ-ЦП-15</t>
-  </si>
-  <si>
-    <t>Аварийное освещение Вега 60 2Ex Тех  IP65</t>
-  </si>
-  <si>
-    <t>Аварийное освещение DL-0128A 28 Вт IP65</t>
-  </si>
-  <si>
-    <t>Держатель для полосы заземления К-188 У2 (цинк)</t>
-  </si>
-  <si>
-    <t>Геркон КЭМ-2</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р407(-60+40) 2-8х20НК(А)-8х20НК(С)-4х26(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
-  </si>
-  <si>
-    <t>Коробка распаячная КМ41242 IP55</t>
-  </si>
-  <si>
-    <t>Крепление для труб ПВХ с защелкой, 16 мм</t>
-  </si>
-  <si>
-    <t>Крышка (100х15х3000)</t>
-  </si>
-  <si>
-    <t>Крышка (50х15х3000)</t>
-  </si>
-  <si>
-    <t>Крышка на Угол вертикальный внешний CD 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Крышка Угол горизонтальный CPO 90 (100х50)</t>
-  </si>
-  <si>
-    <t>Профиль PSM (3000) арт. 34181</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с наружной резьбой РКН-15 (ММРн-15)</t>
-  </si>
-  <si>
-    <t>Скоба металлическая СМО 16-17 49152 КВТ</t>
-  </si>
-  <si>
-    <t>Считыватель бесконтактный для proxi-карт, Proxy-3МA IP20</t>
-  </si>
-  <si>
-    <t>Считыватель бесконтактный для proxi-карт, RD 26-REH-КМ АЯКС Ex mb IIC T5 Gb X , IP67</t>
-  </si>
-  <si>
-    <t>Угол горизонтальный CPO 90 (100 х 50)</t>
-  </si>
-  <si>
-    <t>Выключатель двухклавишный IP55</t>
-  </si>
-  <si>
-    <t>Очки защитные для токарей.О15.</t>
-  </si>
-  <si>
-    <t>Фумлента</t>
-  </si>
-  <si>
-    <t>Краскопульт с верх. бачком S900-P d=2мм в блистере  (Русский Мастер) (20)</t>
-  </si>
-  <si>
-    <t>Пост аварийной сигнализации загазованности в/защ.ПАСВ1-П-75-1Ж1К-В1 (=24В, -60..+40С) 1ExsIICT6</t>
-  </si>
-  <si>
-    <t>Пружина НТ.3.02.00.00.002-01</t>
-  </si>
-  <si>
-    <t>Пружина №467 НТ.200.000.029.0</t>
-  </si>
-  <si>
-    <t>Пружина крышки НТ.200.004.003.0</t>
-  </si>
-  <si>
-    <t>Пружина №442 НТ.110.000.007.0</t>
-  </si>
-  <si>
-    <t>Магнит МС3 ЦО 14,5/4 ТУ 3498-005-12591667-2014</t>
-  </si>
-  <si>
-    <t>Грунт-эмаль Дюропокс ДТМ 80 (внутрянка)</t>
-  </si>
-  <si>
-    <t>Легкосбрасываемое окнная конструкция 1200х1100 мм / ПВХ-профили морозост. исп, RAL 9003 белый</t>
-  </si>
-  <si>
-    <t>Задвижка ЗКС 31лс77нж Ду 15 Ру 40 МПа (соединение муфтовое Rc 1/2)</t>
-  </si>
-  <si>
-    <t>Задвижка клиновая литая ЗКЛ 50-40 УХЛ1 30С15нж, класс герм.А (ряд 2, исп.фл.3)</t>
-  </si>
-  <si>
-    <t>Задвижка клиновая литая ЗКЛ 80-40 УХЛ1 30лс15нж, класс герм.А (ряд 2, исп.фл.3)</t>
-  </si>
-  <si>
-    <t>Клапан обратный поворотный КОП 80-40 УХЛ1 19лс53нж (исп. фл. 3)</t>
-  </si>
-  <si>
-    <t>Дверь левс доводчиком2000х1000мм(ВхШ) полотно RAL 9003(белый)/коробка(RAL 9003)(белый)с цепью</t>
-  </si>
-  <si>
-    <t>Гайка М16-6Н.8.20.019 ГОСТ 15523-70</t>
-  </si>
-  <si>
-    <t>Гайка М14х1,5 ГОСТ 15522-70</t>
-  </si>
-  <si>
-    <t>Гайка М10.5 019 ГОСТ 5927-70</t>
-  </si>
-  <si>
-    <t>Гайка М10-6Н ГОСТ 5927-70 (размер под ключ S=17)</t>
-  </si>
-  <si>
-    <t>Болт М8-6gх25.58.019 ГОСТ 7798-70</t>
-  </si>
-  <si>
-    <t>Лист чечевица В-К-ПУ-3,0 Ст.09Г2С ГОСТ 8568-77</t>
-  </si>
-  <si>
-    <t>Круг D98 Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Круг D265 ст.20 ГОСТ 1050-13</t>
-  </si>
-  <si>
-    <t>Круг D26 Ст.09Г2С ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Круг D185 ГОСТ 2590-2006/ 325-09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Круг D145 Ст.35 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Лист БТ-ПН-0-3,0 ГОСТ 19904-90/ ОК360В-III-Н ГОСТ 16523-97</t>
-  </si>
-  <si>
-    <t>Лист Б-ПР-1,0 ГОСТ 19904-74/ 4-III-Ст3кп ГОСТ 16523-89</t>
-  </si>
-  <si>
-    <t>Кольцо уплотнительное НТ 202.003.004.0</t>
-  </si>
-  <si>
-    <t>Кольцо А18х1,2 ГОСТ 13942-86</t>
-  </si>
-  <si>
-    <t>Кольцо 070-076-36 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Кольцо 038-042-25 ГОСТ 9833-70</t>
-  </si>
-  <si>
-    <t>Кольцо 035-041-36-2-4 ГОСТ 9833-73</t>
-  </si>
-  <si>
-    <t>Державка SNR0010K11</t>
-  </si>
-  <si>
-    <t>Пластина 11IR2.00ISO BT2225</t>
-  </si>
-  <si>
-    <t>Кабель ВВГ 3*2,5</t>
+    <t>Круг D85 Ст.35 ГОСТ 1050-88</t>
   </si>
   <si>
     <t>Кольцо А75х1,7 ГОСТ 13943-86_</t>
+  </si>
+  <si>
+    <t>№ пп</t>
+  </si>
+  <si>
+    <t>Ветошь рул.</t>
+  </si>
+  <si>
+    <t>Пена монтажная шт</t>
+  </si>
+  <si>
+    <t>Перчатки хб (с ПВХ покрытием, 5 ниток,черные,класс 10)</t>
+  </si>
+  <si>
+    <t>Дверь правая с довод 2000х1000 мм (ВхШ) полотно RAL 9003 (белый) коробка (RAL 9003) (белый) с цепь.</t>
+  </si>
+  <si>
+    <t>Окно 1200х1100 мм  ПВХ-профили морозост. исп, RAL 7036 серый</t>
+  </si>
+  <si>
+    <t>Дверь лев с доводчиком1900х1000 мм(ВхШ) полотно RAL9003(белый)коробка (RAL 9003)(белый)с цепью</t>
+  </si>
+  <si>
+    <t>Дверь левс доводчиком2000х1000мм(ВхШ) полотно RAL 9003(белый)коробка(RAL 9003)(белый)с цепью</t>
+  </si>
+  <si>
+    <t>Пост аварийной сигнализации загазованности взащ.ПАСВ1-П-75-1Ж1К-В1 (=24В, -60..+40С) 1ExsIICT6</t>
+  </si>
+  <si>
+    <t>Труба D159х8 ГОСТ 8732-78 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба 76x8,0 ГОСТ 8732-7809Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Онлайн ИБП Штиль ST1101SL (1000 ВА  900 Вт)</t>
+  </si>
+  <si>
+    <t>Кашкороб0427340х160х60Т23ВММКК4+0мат.лам</t>
+  </si>
+  <si>
+    <t>Кашкороб0427405х225х80Т23ВММКК4+0мат.лам.</t>
+  </si>
+  <si>
+    <t>Кашкороб0203300х200х400Т23ММКК4+0мат.лам</t>
+  </si>
+  <si>
+    <t>Кашкороб0201400х400х610Т23ВММКК4+0мат.лам.</t>
+  </si>
+  <si>
+    <t>Круг D185 ГОСТ 2590-2006 325-09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Круг D27 ГОСТ 2590-2006 345-09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Труба ппропилен. 20мм*4м</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-12 ГОСТ 19903-74  Ст. 09Г2С К52 ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-4,0 ГОСТ 19903-74  Ст.3пс4 ГОСТ 14637-89</t>
   </si>
 </sst>
 </file>
@@ -1133,35 +1115,35 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F190"/>
+  <dimension ref="A1:F263"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="46.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="1" customWidth="1"/>
+    <col min="3" max="3" width="74.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1170,16 +1152,16 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="5">
+        <v>5</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="D2" s="5">
-        <v>1</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1188,16 +1170,16 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="8" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="D3" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1206,16 +1188,16 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="8" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="D4" s="5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1224,16 +1206,16 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="8" t="s">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="D5" s="5">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1242,16 +1224,16 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="8" t="s">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="D6" s="5">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1260,16 +1242,16 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="8" t="s">
-        <v>84</v>
+        <v>198</v>
       </c>
       <c r="D7" s="5">
         <v>6</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1278,16 +1260,16 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="8" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="D8" s="5">
-        <v>0.75</v>
+        <v>10</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1296,16 +1278,16 @@
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="8" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="D9" s="5">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1314,16 +1296,16 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="8" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="D10" s="5">
-        <v>0.33</v>
+        <v>10</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1332,16 +1314,16 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="8" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="D11" s="5">
-        <v>0.15</v>
+        <v>20</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1350,16 +1332,16 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="8" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="D12" s="5">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1368,16 +1350,16 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="8" t="s">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="D13" s="5">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1386,16 +1368,16 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="8" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="D14" s="5">
-        <v>36.9</v>
+        <v>3</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1404,16 +1386,16 @@
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="8" t="s">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="D15" s="5">
-        <v>0.3</v>
+        <v>15</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1422,16 +1404,16 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="8" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="D16" s="5">
-        <v>52.05</v>
+        <v>15</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1440,16 +1422,16 @@
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="8" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="D17" s="5">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1458,16 +1440,16 @@
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="8" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="D18" s="5">
-        <v>47.4</v>
+        <v>10</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1476,16 +1458,16 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="8" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="D19" s="5">
-        <v>15.9</v>
+        <v>12</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1494,16 +1476,16 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="8" t="s">
-        <v>97</v>
+        <v>198</v>
       </c>
       <c r="D20" s="5">
-        <v>472.8</v>
+        <v>10</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1512,16 +1494,16 @@
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="8" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="D21" s="5">
-        <v>112.8</v>
+        <v>60</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1530,16 +1512,16 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D22" s="5">
-        <v>28.2</v>
+        <v>60</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1548,16 +1530,16 @@
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="8" t="s">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="D23" s="5">
-        <v>20.7</v>
+        <v>40</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1566,16 +1548,16 @@
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="8" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="D24" s="5">
-        <v>22.5</v>
+        <v>5</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1584,16 +1566,16 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="8" t="s">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="D25" s="5">
-        <v>13.65</v>
+        <v>3</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1602,16 +1584,16 @@
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="8" t="s">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="D26" s="5">
-        <v>21.9</v>
+        <v>10</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1620,16 +1602,16 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D27" s="5">
-        <v>6.6</v>
+        <v>200</v>
+      </c>
+      <c r="D27" s="7">
+        <v>2000</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1638,34 +1620,34 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="8" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D28" s="5">
-        <v>0.09</v>
+        <v>14</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>28</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="8" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D29" s="5">
-        <v>55.8</v>
+        <v>1</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1674,16 +1656,16 @@
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="8" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D30" s="5">
-        <v>20.399999999999999</v>
+        <v>7</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1692,16 +1674,16 @@
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="8" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D31" s="5">
-        <v>40.5</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1710,16 +1692,16 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D32" s="5">
-        <v>33.15</v>
+        <v>7</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1728,88 +1710,88 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="8" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D33" s="5">
-        <v>38.700000000000003</v>
+        <v>7</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>33</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="8" t="s">
-        <v>110</v>
+        <v>201</v>
       </c>
       <c r="D34" s="5">
-        <v>20.7</v>
+        <v>2</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>34</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="8" t="s">
-        <v>111</v>
+        <v>202</v>
       </c>
       <c r="D35" s="5">
-        <v>1.05</v>
+        <v>6</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>35</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="8" t="s">
-        <v>14</v>
+        <v>203</v>
       </c>
       <c r="D36" s="5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>36</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="8" t="s">
-        <v>17</v>
+        <v>204</v>
       </c>
       <c r="D37" s="5">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1818,16 +1800,16 @@
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="8" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D38" s="5">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1836,16 +1818,16 @@
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="8" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D39" s="5">
-        <v>200</v>
+        <v>396</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1854,16 +1836,16 @@
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="8" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D40" s="5">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1872,16 +1854,16 @@
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="8" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D41" s="5">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1890,16 +1872,16 @@
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="8" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D42" s="5">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1908,16 +1890,16 @@
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="8" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D43" s="5">
-        <v>200</v>
+        <v>16</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1926,52 +1908,52 @@
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="8" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D44" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>44</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="8" t="s">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="D45" s="5">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>45</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="8" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D46" s="5">
-        <v>4</v>
+        <v>140</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1980,16 +1962,16 @@
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="8" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D47" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1998,88 +1980,88 @@
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="8" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D48" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>48</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="8" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D49" s="5">
-        <v>5</v>
+        <v>140</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>49</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="8" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D50" s="5">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>50</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="8" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D51" s="5">
-        <v>112</v>
+        <v>2</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>51</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="8" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D52" s="5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2088,16 +2070,16 @@
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="8" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D53" s="5">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2106,16 +2088,16 @@
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="8" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D54" s="5">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2124,16 +2106,16 @@
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="8" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D55" s="5">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2142,34 +2124,34 @@
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="8" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D56" s="5">
-        <v>16.8</v>
+        <v>10</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
         <v>56</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="8" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D57" s="5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2178,16 +2160,16 @@
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="8" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D58" s="5">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2196,16 +2178,16 @@
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="8" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D59" s="5">
-        <v>192</v>
+        <v>2</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2214,70 +2196,70 @@
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="8" t="s">
-        <v>132</v>
+        <v>33</v>
       </c>
       <c r="D60" s="5">
-        <v>560</v>
+        <v>2</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
         <v>60</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="8" t="s">
-        <v>25</v>
+        <v>127</v>
       </c>
       <c r="D61" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
         <v>61</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="8" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D62" s="5">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>62</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="8" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D63" s="5">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2286,52 +2268,52 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="8" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D64" s="5">
-        <v>240</v>
+        <v>4</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
         <v>64</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="8" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D65" s="5">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
         <v>65</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="8" t="s">
-        <v>137</v>
+        <v>205</v>
       </c>
       <c r="D66" s="5">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2340,34 +2322,34 @@
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="8" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D67" s="5">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
         <v>67</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="8" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="D68" s="5">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2376,34 +2358,34 @@
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="8" t="s">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c r="D69" s="5">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
         <v>69</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="8" t="s">
-        <v>30</v>
+        <v>135</v>
       </c>
       <c r="D70" s="5">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2412,16 +2394,16 @@
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D71" s="5">
+        <v>4</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F71" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="D71" s="5">
-        <v>160</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2430,16 +2412,16 @@
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="8" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="D72" s="5">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2448,34 +2430,34 @@
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D73" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
         <v>73</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D74" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2484,16 +2466,16 @@
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D75" s="5">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2502,16 +2484,16 @@
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="8" t="s">
-        <v>33</v>
+        <v>141</v>
       </c>
       <c r="D76" s="5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2520,16 +2502,16 @@
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="8" t="s">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="D77" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2538,34 +2520,34 @@
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="8" t="s">
-        <v>142</v>
+        <v>34</v>
       </c>
       <c r="D78" s="5">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
         <v>78</v>
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="8" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="D79" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2574,16 +2556,16 @@
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D80" s="5">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2592,34 +2574,34 @@
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="8" t="s">
-        <v>145</v>
+        <v>36</v>
       </c>
       <c r="D81" s="5">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>81</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D82" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2628,16 +2610,16 @@
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D83" s="5">
-        <v>144</v>
+        <v>14</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2646,16 +2628,16 @@
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D84" s="5">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2664,16 +2646,16 @@
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="D85" s="7">
-        <v>1199</v>
+        <v>147</v>
+      </c>
+      <c r="D85" s="5">
+        <v>12</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2682,16 +2664,16 @@
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D86" s="5">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2700,16 +2682,16 @@
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D87" s="5">
-        <v>10</v>
+        <v>260</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2718,16 +2700,16 @@
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D88" s="5">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2736,16 +2718,16 @@
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D89" s="5">
-        <v>861.2</v>
+        <v>4</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2754,16 +2736,16 @@
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D90" s="5">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2772,16 +2754,16 @@
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D91" s="5">
-        <v>288</v>
+        <v>128.80000000000001</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2790,16 +2772,16 @@
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D92" s="5">
-        <v>989</v>
+        <v>100</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2808,16 +2790,16 @@
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D93" s="5">
-        <v>396.5</v>
+        <v>330</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2826,16 +2808,16 @@
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D94" s="5">
-        <v>0.6</v>
+        <v>92</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2844,16 +2826,16 @@
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="8" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
       <c r="D95" s="5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2862,16 +2844,16 @@
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="8" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D96" s="5">
-        <v>274.8</v>
+        <v>4</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2880,16 +2862,16 @@
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="8" t="s">
-        <v>161</v>
+        <v>40</v>
       </c>
       <c r="D97" s="5">
-        <v>100.8</v>
+        <v>2</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2898,106 +2880,106 @@
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="8" t="s">
-        <v>162</v>
+        <v>41</v>
       </c>
       <c r="D98" s="5">
-        <v>320</v>
+        <v>2</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
         <v>98</v>
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="8" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D99" s="5">
-        <v>40</v>
+        <v>5.7389999999999999</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
         <v>99</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="D100" s="5">
-        <v>48</v>
+        <v>159</v>
+      </c>
+      <c r="D100" s="7">
+        <v>2912.7</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
         <v>100</v>
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="D101" s="5">
-        <v>259</v>
+        <v>206</v>
+      </c>
+      <c r="D101" s="7">
+        <v>2323.62</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
         <v>101</v>
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="8" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D102" s="7">
-        <v>1040</v>
+        <v>1438.2</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
         <v>102</v>
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="8" t="s">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="D103" s="5">
-        <v>602.20000000000005</v>
+        <v>495.19799999999998</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3006,16 +2988,16 @@
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="8" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="D104" s="5">
         <v>5</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3024,52 +3006,52 @@
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="8" t="s">
-        <v>168</v>
+        <v>45</v>
       </c>
       <c r="D105" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
         <v>105</v>
       </c>
       <c r="B106" s="4"/>
       <c r="C106" s="8" t="s">
-        <v>169</v>
+        <v>46</v>
       </c>
       <c r="D106" s="5">
-        <v>400</v>
+        <v>6</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
         <v>106</v>
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="8" t="s">
-        <v>170</v>
+        <v>48</v>
       </c>
       <c r="D107" s="5">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3078,214 +3060,214 @@
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="8" t="s">
-        <v>171</v>
+        <v>49</v>
       </c>
       <c r="D108" s="5">
+        <v>6</v>
+      </c>
+      <c r="E108" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E108" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="F108" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
         <v>108</v>
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="8" t="s">
-        <v>172</v>
+        <v>50</v>
       </c>
       <c r="D109" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
         <v>109</v>
       </c>
       <c r="B110" s="4"/>
       <c r="C110" s="8" t="s">
-        <v>173</v>
+        <v>52</v>
       </c>
       <c r="D110" s="5">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
         <v>110</v>
       </c>
       <c r="B111" s="4"/>
       <c r="C111" s="8" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="D111" s="5">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
         <v>111</v>
       </c>
       <c r="B112" s="4"/>
       <c r="C112" s="8" t="s">
-        <v>175</v>
+        <v>46</v>
       </c>
       <c r="D112" s="5">
-        <v>144</v>
+        <v>2</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
         <v>112</v>
       </c>
       <c r="B113" s="4"/>
       <c r="C113" s="8" t="s">
-        <v>176</v>
+        <v>48</v>
       </c>
       <c r="D113" s="5">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
         <v>113</v>
       </c>
       <c r="B114" s="4"/>
       <c r="C114" s="8" t="s">
-        <v>177</v>
+        <v>49</v>
       </c>
       <c r="D114" s="5">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
         <v>114</v>
       </c>
       <c r="B115" s="4"/>
       <c r="C115" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="D115" s="5">
-        <v>40</v>
+        <v>209</v>
+      </c>
+      <c r="D115" s="7">
+        <v>1000</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
         <v>115</v>
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="D116" s="5">
-        <v>298</v>
+        <v>210</v>
+      </c>
+      <c r="D116" s="7">
+        <v>1000</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
         <v>116</v>
       </c>
       <c r="B117" s="4"/>
       <c r="C117" s="8" t="s">
-        <v>180</v>
+        <v>56</v>
       </c>
       <c r="D117" s="5">
-        <v>422</v>
+        <v>1</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
         <v>117</v>
       </c>
       <c r="B118" s="4"/>
       <c r="C118" s="8" t="s">
-        <v>181</v>
+        <v>57</v>
       </c>
       <c r="D118" s="5">
-        <v>900</v>
+        <v>1</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="3">
         <v>118</v>
       </c>
       <c r="B119" s="4"/>
       <c r="C119" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="D119" s="5">
-        <v>8</v>
+        <v>211</v>
+      </c>
+      <c r="D119" s="7">
+        <v>1000</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3294,484 +3276,484 @@
       </c>
       <c r="B120" s="4"/>
       <c r="C120" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="D120" s="5">
-        <v>8</v>
+        <v>212</v>
+      </c>
+      <c r="D120" s="7">
+        <v>1000</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="3">
         <v>120</v>
       </c>
       <c r="B121" s="4"/>
       <c r="C121" s="8" t="s">
-        <v>184</v>
+        <v>58</v>
       </c>
       <c r="D121" s="5">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="3">
         <v>121</v>
       </c>
       <c r="B122" s="4"/>
       <c r="C122" s="8" t="s">
-        <v>185</v>
+        <v>59</v>
       </c>
       <c r="D122" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="3">
         <v>122</v>
       </c>
       <c r="B123" s="4"/>
       <c r="C123" s="8" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="D123" s="5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="3">
         <v>123</v>
       </c>
       <c r="B124" s="4"/>
       <c r="C124" s="8" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="D124" s="5">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="3">
         <v>124</v>
       </c>
       <c r="B125" s="4"/>
       <c r="C125" s="8" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D125" s="5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="3">
         <v>125</v>
       </c>
       <c r="B126" s="4"/>
       <c r="C126" s="8" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="D126" s="5">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="3">
         <v>126</v>
       </c>
       <c r="B127" s="4"/>
       <c r="C127" s="8" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D127" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
         <v>127</v>
       </c>
       <c r="B128" s="4"/>
       <c r="C128" s="8" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="D128" s="5">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="3">
         <v>128</v>
       </c>
       <c r="B129" s="4"/>
       <c r="C129" s="8" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D129" s="5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
         <v>129</v>
       </c>
       <c r="B130" s="4"/>
       <c r="C130" s="8" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D130" s="5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="3">
         <v>130</v>
       </c>
       <c r="B131" s="4"/>
       <c r="C131" s="8" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="D131" s="5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
         <v>131</v>
       </c>
       <c r="B132" s="4"/>
       <c r="C132" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D132" s="7">
-        <v>1000</v>
+        <v>61</v>
+      </c>
+      <c r="D132" s="5">
+        <v>1</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="3">
         <v>132</v>
       </c>
       <c r="B133" s="4"/>
       <c r="C133" s="8" t="s">
-        <v>186</v>
+        <v>61</v>
       </c>
       <c r="D133" s="5">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
         <v>133</v>
       </c>
       <c r="B134" s="4"/>
       <c r="C134" s="8" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D134" s="5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="3">
         <v>134</v>
       </c>
       <c r="B135" s="4"/>
       <c r="C135" s="8" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D135" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
         <v>135</v>
       </c>
       <c r="B136" s="4"/>
       <c r="C136" s="8" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D136" s="5">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
         <v>136</v>
       </c>
       <c r="B137" s="4"/>
       <c r="C137" s="8" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D137" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
         <v>137</v>
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="8" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="D138" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="3">
         <v>138</v>
       </c>
       <c r="B139" s="4"/>
       <c r="C139" s="8" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D139" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="3">
         <v>139</v>
       </c>
       <c r="B140" s="4"/>
       <c r="C140" s="8" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D140" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="3">
         <v>140</v>
       </c>
       <c r="B141" s="4"/>
       <c r="C141" s="8" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D141" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="3">
         <v>141</v>
       </c>
       <c r="B142" s="4"/>
       <c r="C142" s="8" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D142" s="5">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="3">
         <v>142</v>
       </c>
       <c r="B143" s="4"/>
       <c r="C143" s="8" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D143" s="5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="3">
         <v>143</v>
       </c>
       <c r="B144" s="4"/>
       <c r="C144" s="8" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D144" s="5">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="3">
         <v>144</v>
       </c>
       <c r="B145" s="4"/>
       <c r="C145" s="8" t="s">
-        <v>187</v>
+        <v>61</v>
       </c>
       <c r="D145" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="3">
         <v>145</v>
       </c>
       <c r="B146" s="4"/>
       <c r="C146" s="8" t="s">
-        <v>188</v>
+        <v>61</v>
       </c>
       <c r="D146" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3780,106 +3762,106 @@
       </c>
       <c r="B147" s="4"/>
       <c r="C147" s="8" t="s">
-        <v>189</v>
+        <v>61</v>
       </c>
       <c r="D147" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="3">
         <v>147</v>
       </c>
       <c r="B148" s="4"/>
       <c r="C148" s="8" t="s">
-        <v>190</v>
+        <v>61</v>
       </c>
       <c r="D148" s="5">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="3">
         <v>148</v>
       </c>
       <c r="B149" s="4"/>
       <c r="C149" s="8" t="s">
-        <v>191</v>
+        <v>61</v>
       </c>
       <c r="D149" s="5">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="3">
         <v>149</v>
       </c>
       <c r="B150" s="4"/>
       <c r="C150" s="8" t="s">
-        <v>192</v>
+        <v>61</v>
       </c>
       <c r="D150" s="5">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="3">
         <v>150</v>
       </c>
       <c r="B151" s="4"/>
       <c r="C151" s="8" t="s">
-        <v>193</v>
+        <v>61</v>
       </c>
       <c r="D151" s="5">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="3">
         <v>151</v>
       </c>
       <c r="B152" s="4"/>
       <c r="C152" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="D152" s="7">
-        <v>4000</v>
+        <v>61</v>
+      </c>
+      <c r="D152" s="5">
+        <v>1</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3888,16 +3870,16 @@
       </c>
       <c r="B153" s="4"/>
       <c r="C153" s="8" t="s">
-        <v>195</v>
+        <v>61</v>
       </c>
       <c r="D153" s="5">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3906,16 +3888,16 @@
       </c>
       <c r="B154" s="4"/>
       <c r="C154" s="8" t="s">
-        <v>196</v>
+        <v>61</v>
       </c>
       <c r="D154" s="5">
         <v>2</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3924,16 +3906,16 @@
       </c>
       <c r="B155" s="4"/>
       <c r="C155" s="8" t="s">
-        <v>197</v>
+        <v>61</v>
       </c>
       <c r="D155" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3942,16 +3924,16 @@
       </c>
       <c r="B156" s="4"/>
       <c r="C156" s="8" t="s">
-        <v>198</v>
+        <v>61</v>
       </c>
       <c r="D156" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3960,16 +3942,16 @@
       </c>
       <c r="B157" s="4"/>
       <c r="C157" s="8" t="s">
-        <v>199</v>
+        <v>61</v>
       </c>
       <c r="D157" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3978,16 +3960,16 @@
       </c>
       <c r="B158" s="4"/>
       <c r="C158" s="8" t="s">
-        <v>200</v>
+        <v>61</v>
       </c>
       <c r="D158" s="5">
         <v>1</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3996,16 +3978,16 @@
       </c>
       <c r="B159" s="4"/>
       <c r="C159" s="8" t="s">
-        <v>201</v>
+        <v>61</v>
       </c>
       <c r="D159" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4014,16 +3996,16 @@
       </c>
       <c r="B160" s="4"/>
       <c r="C160" s="8" t="s">
-        <v>202</v>
+        <v>61</v>
       </c>
       <c r="D160" s="5">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4032,16 +4014,16 @@
       </c>
       <c r="B161" s="4"/>
       <c r="C161" s="8" t="s">
-        <v>203</v>
+        <v>61</v>
       </c>
       <c r="D161" s="5">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4050,16 +4032,16 @@
       </c>
       <c r="B162" s="4"/>
       <c r="C162" s="8" t="s">
-        <v>204</v>
+        <v>61</v>
       </c>
       <c r="D162" s="5">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4068,16 +4050,16 @@
       </c>
       <c r="B163" s="4"/>
       <c r="C163" s="8" t="s">
-        <v>205</v>
+        <v>61</v>
       </c>
       <c r="D163" s="5">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4086,16 +4068,16 @@
       </c>
       <c r="B164" s="4"/>
       <c r="C164" s="8" t="s">
-        <v>206</v>
+        <v>61</v>
       </c>
       <c r="D164" s="5">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4107,10 +4089,10 @@
         <v>61</v>
       </c>
       <c r="D165" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F165" s="4" t="s">
         <v>62</v>
@@ -4122,16 +4104,16 @@
       </c>
       <c r="B166" s="4"/>
       <c r="C166" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="D166" s="7">
-        <v>2713.44</v>
+        <v>61</v>
+      </c>
+      <c r="D166" s="5">
+        <v>2</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4140,16 +4122,16 @@
       </c>
       <c r="B167" s="4"/>
       <c r="C167" s="8" t="s">
-        <v>208</v>
+        <v>61</v>
       </c>
       <c r="D167" s="5">
-        <v>35.28</v>
+        <v>1</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4158,16 +4140,16 @@
       </c>
       <c r="B168" s="4"/>
       <c r="C168" s="8" t="s">
-        <v>209</v>
+        <v>61</v>
       </c>
       <c r="D168" s="5">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4176,16 +4158,16 @@
       </c>
       <c r="B169" s="4"/>
       <c r="C169" s="8" t="s">
-        <v>210</v>
+        <v>61</v>
       </c>
       <c r="D169" s="5">
-        <v>5.82</v>
+        <v>4</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4194,16 +4176,16 @@
       </c>
       <c r="B170" s="4"/>
       <c r="C170" s="8" t="s">
-        <v>211</v>
+        <v>61</v>
       </c>
       <c r="D170" s="5">
-        <v>103.74</v>
+        <v>1</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4212,34 +4194,34 @@
       </c>
       <c r="B171" s="4"/>
       <c r="C171" s="8" t="s">
-        <v>212</v>
+        <v>61</v>
       </c>
       <c r="D171" s="5">
-        <v>20.22</v>
+        <v>2</v>
       </c>
       <c r="E171" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="3">
         <v>171</v>
       </c>
       <c r="B172" s="4"/>
       <c r="C172" s="8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D172" s="5">
-        <v>612</v>
+        <v>2</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4248,16 +4230,16 @@
       </c>
       <c r="B173" s="4"/>
       <c r="C173" s="8" t="s">
-        <v>213</v>
+        <v>61</v>
       </c>
       <c r="D173" s="5">
-        <v>19.5</v>
+        <v>1</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="174" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4266,16 +4248,16 @@
       </c>
       <c r="B174" s="4"/>
       <c r="C174" s="8" t="s">
-        <v>214</v>
+        <v>61</v>
       </c>
       <c r="D174" s="5">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4284,16 +4266,16 @@
       </c>
       <c r="B175" s="4"/>
       <c r="C175" s="8" t="s">
-        <v>215</v>
+        <v>61</v>
       </c>
       <c r="D175" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E175" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="176" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4302,16 +4284,16 @@
       </c>
       <c r="B176" s="4"/>
       <c r="C176" s="8" t="s">
-        <v>223</v>
+        <v>61</v>
       </c>
       <c r="D176" s="5">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4320,16 +4302,16 @@
       </c>
       <c r="B177" s="4"/>
       <c r="C177" s="8" t="s">
-        <v>216</v>
+        <v>61</v>
       </c>
       <c r="D177" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E177" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="178" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4338,16 +4320,16 @@
       </c>
       <c r="B178" s="4"/>
       <c r="C178" s="8" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="D178" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="179" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4356,16 +4338,16 @@
       </c>
       <c r="B179" s="4"/>
       <c r="C179" s="8" t="s">
-        <v>218</v>
+        <v>61</v>
       </c>
       <c r="D179" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E179" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="180" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4374,34 +4356,34 @@
       </c>
       <c r="B180" s="4"/>
       <c r="C180" s="8" t="s">
-        <v>219</v>
+        <v>61</v>
       </c>
       <c r="D180" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="3">
         <v>180</v>
       </c>
       <c r="B181" s="4"/>
       <c r="C181" s="8" t="s">
-        <v>197</v>
+        <v>61</v>
       </c>
       <c r="D181" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E181" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4410,16 +4392,16 @@
       </c>
       <c r="B182" s="4"/>
       <c r="C182" s="8" t="s">
-        <v>220</v>
+        <v>61</v>
       </c>
       <c r="D182" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="183" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4428,16 +4410,16 @@
       </c>
       <c r="B183" s="4"/>
       <c r="C183" s="8" t="s">
-        <v>221</v>
+        <v>61</v>
       </c>
       <c r="D183" s="5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="184" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4446,16 +4428,16 @@
       </c>
       <c r="B184" s="4"/>
       <c r="C184" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="D184" s="7">
-        <v>200000</v>
+        <v>61</v>
+      </c>
+      <c r="D184" s="5">
+        <v>1</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="185" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4464,16 +4446,16 @@
       </c>
       <c r="B185" s="4"/>
       <c r="C185" s="8" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D185" s="5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="186" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4482,16 +4464,16 @@
       </c>
       <c r="B186" s="4"/>
       <c r="C186" s="8" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D186" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
     </row>
     <row r="187" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4500,16 +4482,16 @@
       </c>
       <c r="B187" s="4"/>
       <c r="C187" s="8" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="D187" s="5">
         <v>2</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4518,16 +4500,16 @@
       </c>
       <c r="B188" s="4"/>
       <c r="C188" s="8" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="D188" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
     </row>
     <row r="189" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4536,16 +4518,16 @@
       </c>
       <c r="B189" s="4"/>
       <c r="C189" s="8" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="D189" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E189" s="6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
     </row>
     <row r="190" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4554,16 +4536,1330 @@
       </c>
       <c r="B190" s="4"/>
       <c r="C190" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D190" s="5">
+        <v>1</v>
+      </c>
+      <c r="E190" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F190" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="3">
+        <v>190</v>
+      </c>
+      <c r="B191" s="4"/>
+      <c r="C191" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D191" s="5">
+        <v>74</v>
+      </c>
+      <c r="E191" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A192" s="3">
+        <v>191</v>
+      </c>
+      <c r="B192" s="4"/>
+      <c r="C192" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D192" s="5">
+        <v>37</v>
+      </c>
+      <c r="E192" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F192" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A193" s="3">
+        <v>192</v>
+      </c>
+      <c r="B193" s="4"/>
+      <c r="C193" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D193" s="5">
+        <v>37</v>
+      </c>
+      <c r="E193" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F193" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A194" s="3">
+        <v>193</v>
+      </c>
+      <c r="B194" s="4"/>
+      <c r="C194" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D194" s="5">
+        <v>9</v>
+      </c>
+      <c r="E194" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F194" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A195" s="3">
+        <v>194</v>
+      </c>
+      <c r="B195" s="4"/>
+      <c r="C195" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D195" s="5">
+        <v>1</v>
+      </c>
+      <c r="E195" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F195" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A196" s="3">
+        <v>195</v>
+      </c>
+      <c r="B196" s="4"/>
+      <c r="C196" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D196" s="5">
+        <v>2</v>
+      </c>
+      <c r="E196" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A197" s="3">
+        <v>196</v>
+      </c>
+      <c r="B197" s="4"/>
+      <c r="C197" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D197" s="5">
+        <v>2</v>
+      </c>
+      <c r="E197" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F197" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A198" s="3">
+        <v>197</v>
+      </c>
+      <c r="B198" s="4"/>
+      <c r="C198" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D198" s="5">
+        <v>1</v>
+      </c>
+      <c r="E198" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F198" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A199" s="3">
+        <v>198</v>
+      </c>
+      <c r="B199" s="4"/>
+      <c r="C199" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D199" s="5">
+        <v>2</v>
+      </c>
+      <c r="E199" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F199" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A200" s="3">
+        <v>199</v>
+      </c>
+      <c r="B200" s="4"/>
+      <c r="C200" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D200" s="5">
+        <v>1</v>
+      </c>
+      <c r="E200" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F200" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A201" s="3">
+        <v>200</v>
+      </c>
+      <c r="B201" s="4"/>
+      <c r="C201" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="D201" s="5">
+        <v>4</v>
+      </c>
+      <c r="E201" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F201" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A202" s="3">
+        <v>201</v>
+      </c>
+      <c r="B202" s="4"/>
+      <c r="C202" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D202" s="5">
+        <v>13</v>
+      </c>
+      <c r="E202" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F202" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A203" s="3">
+        <v>202</v>
+      </c>
+      <c r="B203" s="4"/>
+      <c r="C203" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="D203" s="5">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E203" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F203" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A204" s="3">
+        <v>203</v>
+      </c>
+      <c r="B204" s="4"/>
+      <c r="C204" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D204" s="5">
+        <v>40.76</v>
+      </c>
+      <c r="E204" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F204" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A205" s="3">
+        <v>204</v>
+      </c>
+      <c r="B205" s="4"/>
+      <c r="C205" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="D205" s="5">
+        <v>17.29</v>
+      </c>
+      <c r="E205" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F205" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A206" s="3">
+        <v>205</v>
+      </c>
+      <c r="B206" s="4"/>
+      <c r="C206" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D206" s="5">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="E206" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F206" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A207" s="3">
+        <v>206</v>
+      </c>
+      <c r="B207" s="4"/>
+      <c r="C207" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="D207" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="E207" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F207" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A208" s="3">
+        <v>207</v>
+      </c>
+      <c r="B208" s="4"/>
+      <c r="C208" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D208" s="5">
+        <v>0.42</v>
+      </c>
+      <c r="E208" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F208" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A209" s="3">
+        <v>208</v>
+      </c>
+      <c r="B209" s="4"/>
+      <c r="C209" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D209" s="5">
+        <v>1.71</v>
+      </c>
+      <c r="E209" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F209" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A210" s="3">
+        <v>209</v>
+      </c>
+      <c r="B210" s="4"/>
+      <c r="C210" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D210" s="5">
+        <v>0.84</v>
+      </c>
+      <c r="E210" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F210" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A211" s="3">
+        <v>210</v>
+      </c>
+      <c r="B211" s="4"/>
+      <c r="C211" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D211" s="5">
+        <v>1</v>
+      </c>
+      <c r="E211" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F211" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A212" s="3">
+        <v>211</v>
+      </c>
+      <c r="B212" s="4"/>
+      <c r="C212" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D212" s="5">
+        <v>1</v>
+      </c>
+      <c r="E212" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F212" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A213" s="3">
+        <v>212</v>
+      </c>
+      <c r="B213" s="4"/>
+      <c r="C213" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D213" s="5">
+        <v>1</v>
+      </c>
+      <c r="E213" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F213" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A214" s="3">
+        <v>213</v>
+      </c>
+      <c r="B214" s="4"/>
+      <c r="C214" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D214" s="5">
+        <v>1</v>
+      </c>
+      <c r="E214" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F214" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A215" s="3">
+        <v>214</v>
+      </c>
+      <c r="B215" s="4"/>
+      <c r="C215" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D215" s="5">
+        <v>6</v>
+      </c>
+      <c r="E215" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F215" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A216" s="3">
+        <v>215</v>
+      </c>
+      <c r="B216" s="4"/>
+      <c r="C216" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D216" s="5">
+        <v>4</v>
+      </c>
+      <c r="E216" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F216" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A217" s="3">
+        <v>216</v>
+      </c>
+      <c r="B217" s="4"/>
+      <c r="C217" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D217" s="5">
+        <v>1</v>
+      </c>
+      <c r="E217" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F217" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A218" s="3">
+        <v>217</v>
+      </c>
+      <c r="B218" s="4"/>
+      <c r="C218" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D218" s="5">
+        <v>7</v>
+      </c>
+      <c r="E218" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F218" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A219" s="3">
+        <v>218</v>
+      </c>
+      <c r="B219" s="4"/>
+      <c r="C219" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="D219" s="5">
+        <v>5</v>
+      </c>
+      <c r="E219" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F219" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A220" s="3">
+        <v>219</v>
+      </c>
+      <c r="B220" s="4"/>
+      <c r="C220" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D190" s="5">
-        <v>6</v>
-      </c>
-      <c r="E190" s="6" t="s">
+      <c r="D220" s="5">
+        <v>4</v>
+      </c>
+      <c r="E220" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F220" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A221" s="3">
+        <v>220</v>
+      </c>
+      <c r="B221" s="4"/>
+      <c r="C221" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D221" s="5">
+        <v>342</v>
+      </c>
+      <c r="E221" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F221" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A222" s="3">
+        <v>221</v>
+      </c>
+      <c r="B222" s="4"/>
+      <c r="C222" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D222" s="5">
+        <v>30</v>
+      </c>
+      <c r="E222" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F222" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A223" s="3">
+        <v>222</v>
+      </c>
+      <c r="B223" s="4"/>
+      <c r="C223" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="D223" s="5">
+        <v>30</v>
+      </c>
+      <c r="E223" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F223" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A224" s="3">
+        <v>223</v>
+      </c>
+      <c r="B224" s="4"/>
+      <c r="C224" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="D224" s="5">
+        <v>30</v>
+      </c>
+      <c r="E224" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F224" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A225" s="3">
+        <v>224</v>
+      </c>
+      <c r="B225" s="4"/>
+      <c r="C225" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D225" s="5">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="E225" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F225" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A226" s="3">
+        <v>225</v>
+      </c>
+      <c r="B226" s="4"/>
+      <c r="C226" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D226" s="5">
+        <v>16.5</v>
+      </c>
+      <c r="E226" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F226" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A227" s="3">
+        <v>226</v>
+      </c>
+      <c r="B227" s="4"/>
+      <c r="C227" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="D227" s="5">
         <v>15</v>
       </c>
-      <c r="F190" s="4" t="s">
+      <c r="E227" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F227" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A228" s="3">
+        <v>227</v>
+      </c>
+      <c r="B228" s="4"/>
+      <c r="C228" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D228" s="5">
+        <v>60</v>
+      </c>
+      <c r="E228" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F228" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A229" s="3">
+        <v>228</v>
+      </c>
+      <c r="B229" s="4"/>
+      <c r="C229" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="D229" s="5">
+        <v>5</v>
+      </c>
+      <c r="E229" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F229" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A230" s="3">
+        <v>229</v>
+      </c>
+      <c r="B230" s="4"/>
+      <c r="C230" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D230" s="5">
+        <v>7</v>
+      </c>
+      <c r="E230" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F230" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A231" s="3">
+        <v>230</v>
+      </c>
+      <c r="B231" s="4"/>
+      <c r="C231" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D231" s="5">
+        <v>1</v>
+      </c>
+      <c r="E231" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F231" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A232" s="3">
+        <v>231</v>
+      </c>
+      <c r="B232" s="4"/>
+      <c r="C232" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D232" s="5">
+        <v>1</v>
+      </c>
+      <c r="E232" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F232" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A233" s="3">
+        <v>232</v>
+      </c>
+      <c r="B233" s="4"/>
+      <c r="C233" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D233" s="5">
+        <v>1</v>
+      </c>
+      <c r="E233" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F233" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A234" s="3">
+        <v>233</v>
+      </c>
+      <c r="B234" s="4"/>
+      <c r="C234" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D234" s="5">
+        <v>1</v>
+      </c>
+      <c r="E234" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F234" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A235" s="3">
+        <v>234</v>
+      </c>
+      <c r="B235" s="4"/>
+      <c r="C235" s="8" t="s">
         <v>75</v>
+      </c>
+      <c r="D235" s="5">
+        <v>1</v>
+      </c>
+      <c r="E235" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F235" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A236" s="3">
+        <v>235</v>
+      </c>
+      <c r="B236" s="4"/>
+      <c r="C236" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D236" s="5">
+        <v>1</v>
+      </c>
+      <c r="E236" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F236" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A237" s="3">
+        <v>236</v>
+      </c>
+      <c r="B237" s="4"/>
+      <c r="C237" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D237" s="5">
+        <v>10</v>
+      </c>
+      <c r="E237" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F237" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A238" s="3">
+        <v>237</v>
+      </c>
+      <c r="B238" s="4"/>
+      <c r="C238" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D238" s="5">
+        <v>4</v>
+      </c>
+      <c r="E238" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F238" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A239" s="3">
+        <v>238</v>
+      </c>
+      <c r="B239" s="4"/>
+      <c r="C239" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="D239" s="7">
+        <v>9739.2000000000007</v>
+      </c>
+      <c r="E239" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F239" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A240" s="3">
+        <v>239</v>
+      </c>
+      <c r="B240" s="4"/>
+      <c r="C240" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D240" s="5">
+        <v>795.6</v>
+      </c>
+      <c r="E240" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F240" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A241" s="3">
+        <v>240</v>
+      </c>
+      <c r="B241" s="4"/>
+      <c r="C241" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="D241" s="5">
+        <v>15</v>
+      </c>
+      <c r="E241" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F241" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A242" s="3">
+        <v>241</v>
+      </c>
+      <c r="B242" s="4"/>
+      <c r="C242" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D242" s="5">
+        <v>30</v>
+      </c>
+      <c r="E242" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F242" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A243" s="3">
+        <v>242</v>
+      </c>
+      <c r="B243" s="4"/>
+      <c r="C243" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D243" s="5">
+        <v>180</v>
+      </c>
+      <c r="E243" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F243" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A244" s="3">
+        <v>243</v>
+      </c>
+      <c r="B244" s="4"/>
+      <c r="C244" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D244" s="5">
+        <v>45</v>
+      </c>
+      <c r="E244" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F244" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A245" s="3">
+        <v>244</v>
+      </c>
+      <c r="B245" s="4"/>
+      <c r="C245" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="D245" s="5">
+        <v>30</v>
+      </c>
+      <c r="E245" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F245" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A246" s="3">
+        <v>245</v>
+      </c>
+      <c r="B246" s="4"/>
+      <c r="C246" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D246" s="5">
+        <v>144</v>
+      </c>
+      <c r="E246" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F246" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A247" s="3">
+        <v>246</v>
+      </c>
+      <c r="B247" s="4"/>
+      <c r="C247" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D247" s="5">
+        <v>540</v>
+      </c>
+      <c r="E247" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F247" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A248" s="3">
+        <v>247</v>
+      </c>
+      <c r="B248" s="4"/>
+      <c r="C248" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D248" s="5">
+        <v>576</v>
+      </c>
+      <c r="E248" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F248" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A249" s="3">
+        <v>248</v>
+      </c>
+      <c r="B249" s="4"/>
+      <c r="C249" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D249" s="5">
+        <v>18</v>
+      </c>
+      <c r="E249" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F249" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A250" s="3">
+        <v>249</v>
+      </c>
+      <c r="B250" s="4"/>
+      <c r="C250" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D250" s="5">
+        <v>1</v>
+      </c>
+      <c r="E250" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F250" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A251" s="3">
+        <v>250</v>
+      </c>
+      <c r="B251" s="4"/>
+      <c r="C251" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D251" s="5">
+        <v>40</v>
+      </c>
+      <c r="E251" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F251" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A252" s="3">
+        <v>251</v>
+      </c>
+      <c r="B252" s="4"/>
+      <c r="C252" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="D252" s="5">
+        <v>40</v>
+      </c>
+      <c r="E252" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F252" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A253" s="3">
+        <v>252</v>
+      </c>
+      <c r="B253" s="4"/>
+      <c r="C253" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D253" s="5">
+        <v>80</v>
+      </c>
+      <c r="E253" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F253" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A254" s="3">
+        <v>253</v>
+      </c>
+      <c r="B254" s="4"/>
+      <c r="C254" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D254" s="5">
+        <v>80</v>
+      </c>
+      <c r="E254" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F254" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A255" s="3">
+        <v>254</v>
+      </c>
+      <c r="B255" s="4"/>
+      <c r="C255" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="D255" s="5">
+        <v>48</v>
+      </c>
+      <c r="E255" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F255" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A256" s="3">
+        <v>255</v>
+      </c>
+      <c r="B256" s="4"/>
+      <c r="C256" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D256" s="5">
+        <v>6.23</v>
+      </c>
+      <c r="E256" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F256" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A257" s="3">
+        <v>256</v>
+      </c>
+      <c r="B257" s="4"/>
+      <c r="C257" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D257" s="5">
+        <v>1.82</v>
+      </c>
+      <c r="E257" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F257" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A258" s="3">
+        <v>257</v>
+      </c>
+      <c r="B258" s="4"/>
+      <c r="C258" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D258" s="5">
+        <v>2.73</v>
+      </c>
+      <c r="E258" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F258" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A259" s="3">
+        <v>258</v>
+      </c>
+      <c r="B259" s="4"/>
+      <c r="C259" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="D259" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E259" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F259" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A260" s="3">
+        <v>259</v>
+      </c>
+      <c r="B260" s="4"/>
+      <c r="C260" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D260" s="5">
+        <v>23.87</v>
+      </c>
+      <c r="E260" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F260" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A261" s="3">
+        <v>260</v>
+      </c>
+      <c r="B261" s="4"/>
+      <c r="C261" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D261" s="5">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="E261" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F261" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A262" s="3">
+        <v>261</v>
+      </c>
+      <c r="B262" s="4"/>
+      <c r="C262" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D262" s="5">
+        <v>20.72</v>
+      </c>
+      <c r="E262" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F262" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A263" s="3">
+        <v>262</v>
+      </c>
+      <c r="B263" s="4"/>
+      <c r="C263" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D263" s="5">
+        <v>20</v>
+      </c>
+      <c r="E263" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F263" s="4" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A462E5-8A6E-4631-8FCE-7C5D334B5D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA8C249-A3F4-4A7E-99AC-57F7F2EB1262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4110" yWindow="4110" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="259">
+  <si>
+    <t>№ п/п</t>
+  </si>
   <si>
     <t>Полное наименование изделия Поставщика</t>
   </si>
@@ -42,114 +45,129 @@
     <t>Примечание</t>
   </si>
   <si>
+    <t>Дверь правая с довод 2000х1000 мм (ВхШ) полотно RAL 9003 (белый)/ коробка (RAL 9003) (белый) с цепь.</t>
+  </si>
+  <si>
+    <t>шт</t>
+  </si>
+  <si>
+    <t>ИИУП-000324</t>
+  </si>
+  <si>
+    <t>Окно 1200х1100 мм / ПВХ-профили морозост. исп, RAL 7036 серый</t>
+  </si>
+  <si>
+    <t>Ключи обмедненные</t>
+  </si>
+  <si>
+    <t>набор</t>
+  </si>
+  <si>
+    <t>ИИ00-000017</t>
+  </si>
+  <si>
+    <t>Паронит 3 мм</t>
+  </si>
+  <si>
+    <t>лист</t>
+  </si>
+  <si>
+    <t>Паронит 2мм</t>
+  </si>
+  <si>
+    <t>Маркер по металлу белый</t>
+  </si>
+  <si>
     <t>шт.</t>
   </si>
   <si>
-    <t>ИИ00-000017</t>
+    <t>Маркер по металлу черный тонкий</t>
+  </si>
+  <si>
+    <t>Маркер по металлу красный</t>
+  </si>
+  <si>
+    <t>Ветошь /рул./</t>
   </si>
   <si>
     <t>Мел сварщика белый</t>
   </si>
   <si>
-    <t>шт</t>
-  </si>
-  <si>
-    <t>Ключи обмедненные</t>
-  </si>
-  <si>
-    <t>набор</t>
-  </si>
-  <si>
-    <t>Паронит 2мм</t>
-  </si>
-  <si>
-    <t>лист</t>
-  </si>
-  <si>
-    <t>Маркер по металлу белый</t>
-  </si>
-  <si>
-    <t>Маркер по металлу красный</t>
-  </si>
-  <si>
-    <t>Маркер по металлу черный тонкий</t>
-  </si>
-  <si>
-    <t>Паронит 3 мм</t>
+    <t>Рулетка  5м х 25мм Компакт в обрезиненном корпусе</t>
+  </si>
+  <si>
+    <t>ИИ00-000013</t>
+  </si>
+  <si>
+    <t>Ключ комбинир. 24 мм</t>
+  </si>
+  <si>
+    <t>Изолента</t>
+  </si>
+  <si>
+    <t>Фонарик налобный аккумуляторный</t>
+  </si>
+  <si>
+    <t>Пена монтажная /шт/</t>
+  </si>
+  <si>
+    <t>Штангенциркуль</t>
   </si>
   <si>
     <t>Кувалда 1 кг</t>
   </si>
   <si>
-    <t>ИИ00-000013</t>
-  </si>
-  <si>
     <t>Ключ комбинир. 36 мм</t>
   </si>
   <si>
+    <t>Перчатки х/б (с ПВХ покрытием, 5 ниток,черные,класс 10)</t>
+  </si>
+  <si>
+    <t>компл</t>
+  </si>
+  <si>
+    <t>Дождевик-костюм темно-синий 52-54</t>
+  </si>
+  <si>
     <t>Ключ комбинир. 30 мм</t>
   </si>
   <si>
-    <t>Ключ комбинир. 24 мм</t>
-  </si>
-  <si>
-    <t>Изолента</t>
-  </si>
-  <si>
-    <t>Фонарик налобный аккумуляторный</t>
-  </si>
-  <si>
-    <t>Рулетка  5м х 25мм Компакт в обрезиненном корпусе</t>
-  </si>
-  <si>
-    <t>Штангенциркуль</t>
-  </si>
-  <si>
-    <t>Дождевик-костюм темно-синий 52-54</t>
-  </si>
-  <si>
-    <t>компл</t>
+    <t>м</t>
   </si>
   <si>
     <t>ИИ00-000014</t>
   </si>
   <si>
-    <t>м</t>
-  </si>
-  <si>
-    <t>ИИУП-000324</t>
-  </si>
-  <si>
     <t>ИИУП-000336</t>
   </si>
   <si>
+    <t>Индикатор положения поплавка ИПП00.00.000 вер.2</t>
+  </si>
+  <si>
+    <t>Кабель защиты огнестойкие КПСЭнг(А)-FRHF 2х2х0,75</t>
+  </si>
+  <si>
+    <t>(не исп12) шт</t>
+  </si>
+  <si>
     <t>Держатель проводника Rd8</t>
   </si>
   <si>
-    <t>Индикатор положения поплавка ИПП00.00.000 вер.2</t>
+    <t>Извещатель пожарный пламени взрывозащищенный,Спектрон -202. В комплекте 1 кабельных ввода (15 мм)</t>
   </si>
   <si>
     <t>Ответвитель DPT T-образный горизонтальный 100х50 арт.36122 "DKC"</t>
   </si>
   <si>
-    <t>Извещатель пожарный пламени взрывозащищенный,Спектрон -202. В комплекте 1 кабельных ввода (15 мм)</t>
-  </si>
-  <si>
-    <t>Кабель защиты огнестойкие КПСЭнг(А)-FRHF 2х2х0,75</t>
-  </si>
-  <si>
-    <t>(не исп12) шт</t>
+    <t>Блок клапанный БКН 3-11</t>
+  </si>
+  <si>
+    <t>ИИУП-000340</t>
   </si>
   <si>
     <t>Газоанализатор взрывозащищенный СГОЭС 1Ex d IIC T4 Gb, IP67</t>
   </si>
   <si>
-    <t>ИИУП-000340</t>
-  </si>
-  <si>
-    <t>Блок клапанный БКН 3-11</t>
-  </si>
-  <si>
     <t>Влагомер сырой нефти ВСН-2-80-100 1Ex ib llA T6, IP67</t>
   </si>
   <si>
@@ -159,57 +177,63 @@
     <t>ИИУП-000346</t>
   </si>
   <si>
+    <t>Труба 76x8,0 ГОСТ 8732-78/09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
     <t>ИИУП-000350</t>
   </si>
   <si>
     <t>Противогазы</t>
   </si>
   <si>
+    <t>Зимняя обувь</t>
+  </si>
+  <si>
+    <t>ИИУП-000359</t>
+  </si>
+  <si>
+    <t>зимняя спецодежда (ИТР)</t>
+  </si>
+  <si>
     <t>Шапка зимняя</t>
   </si>
   <si>
-    <t>ИИУП-000359</t>
-  </si>
-  <si>
-    <t>зимняя спецодежда (ИТР)</t>
-  </si>
-  <si>
-    <t>Зимняя обувь</t>
-  </si>
-  <si>
     <t>Шлагбаум "AN-Motors"</t>
   </si>
   <si>
     <t>НТУП-018367</t>
   </si>
   <si>
-    <t>Сенсорная панель оператора Weintek MT8106iP</t>
-  </si>
-  <si>
-    <t>ИИУП-000366</t>
-  </si>
-  <si>
-    <t>ИИУП-000370</t>
+    <t>Доп. услуги по обеспечению спецоснасткой</t>
   </si>
   <si>
     <t>НТУП-018372</t>
   </si>
   <si>
+    <t>Кашкороб/0201/400х400х610/Т23В/ММ/КК/4+0/мат.лам.</t>
+  </si>
+  <si>
+    <t>Кашкороб/0203/300х200х400/Т23/ММ/КК/4+0/мат.лам</t>
+  </si>
+  <si>
     <t>печать брошюр</t>
   </si>
   <si>
-    <t>Доп. услуги по обеспечению спецоснасткой</t>
+    <t>Кашкороб/0427/405х225х80/Т23В/ММ/КК/4+0/мат.лам.</t>
+  </si>
+  <si>
+    <t>Кашкороб/0427/340х160х60/Т23В/ММ/КК/4+0/мат.лам</t>
+  </si>
+  <si>
+    <t>Печать ИПП НТ</t>
+  </si>
+  <si>
+    <t>Печать с автоматической оснасткой</t>
   </si>
   <si>
     <t>Печать</t>
   </si>
   <si>
-    <t>Печать с автоматической оснасткой</t>
-  </si>
-  <si>
-    <t>Печать ИПП НТ</t>
-  </si>
-  <si>
     <t>Сэндвич-панель</t>
   </si>
   <si>
@@ -219,130 +243,268 @@
     <t>Комплект элементов</t>
   </si>
   <si>
-    <t>Станок</t>
-  </si>
-  <si>
-    <t>ИИУП-000384</t>
-  </si>
-  <si>
     <t>ИИУП-000386</t>
   </si>
   <si>
-    <t>ИИ00-000057</t>
-  </si>
-  <si>
-    <t>Дренажный насос</t>
-  </si>
-  <si>
-    <t>ИИУП-000393</t>
-  </si>
-  <si>
-    <t>Станция биологической очистки</t>
-  </si>
-  <si>
-    <t>Труба (шт)</t>
-  </si>
-  <si>
-    <t>Монтажные работы</t>
-  </si>
-  <si>
-    <t>труба 110-L500mm</t>
-  </si>
-  <si>
-    <t>Отвод 110*45</t>
-  </si>
-  <si>
-    <t>Муфта соединительная d25</t>
+    <t>Видеорегистратор</t>
+  </si>
+  <si>
+    <t>ИИУП-000394</t>
+  </si>
+  <si>
+    <t>ИИУП-000398</t>
+  </si>
+  <si>
+    <t>ИИУП-000405</t>
+  </si>
+  <si>
+    <t>ИИУП-000411</t>
+  </si>
+  <si>
+    <t>Саморез с пресс шайбой 4,2х13</t>
+  </si>
+  <si>
+    <t>ИИУП-000412</t>
+  </si>
+  <si>
+    <t>м3</t>
+  </si>
+  <si>
+    <t>ЛГУП-8136</t>
+  </si>
+  <si>
+    <t>м2</t>
+  </si>
+  <si>
+    <t>ЛГУП-8137</t>
   </si>
   <si>
     <t>песок</t>
   </si>
   <si>
-    <t>м3</t>
-  </si>
-  <si>
-    <t>пог. м</t>
-  </si>
-  <si>
-    <t>Видеорегистратор</t>
-  </si>
-  <si>
-    <t>ИИУП-000394</t>
-  </si>
-  <si>
-    <t>ИИУП-000398</t>
-  </si>
-  <si>
-    <t>ИИУП-000403</t>
-  </si>
-  <si>
-    <t>ИИУП-000404</t>
-  </si>
-  <si>
-    <t>ИИУП-000405</t>
-  </si>
-  <si>
-    <t>ИИУП-000407</t>
-  </si>
-  <si>
-    <t>Тройник 110 ПНД</t>
-  </si>
-  <si>
-    <t>ИИУП-000411</t>
-  </si>
-  <si>
-    <t>Саморез с пресс шайбой 4,2х13</t>
-  </si>
-  <si>
-    <t>ИИУП-000412</t>
-  </si>
-  <si>
-    <t>Шиномонтаж</t>
-  </si>
-  <si>
-    <t>КИ00-000031</t>
-  </si>
-  <si>
-    <t>ИИУП-000417</t>
-  </si>
-  <si>
-    <t>ЛГУП-8136</t>
-  </si>
-  <si>
-    <t>ЛГУП-8137</t>
-  </si>
-  <si>
-    <t>м2</t>
-  </si>
-  <si>
-    <t>Герметик силиконовый</t>
-  </si>
-  <si>
-    <t>ИИУП-000426</t>
+    <t>ИИУП-000427</t>
+  </si>
+  <si>
+    <t>ИИУП-000431</t>
+  </si>
+  <si>
+    <t>ИИУП-000433</t>
+  </si>
+  <si>
+    <t>ИИУП-000434</t>
+  </si>
+  <si>
+    <t>Дефектоскоп электроисксаай</t>
+  </si>
+  <si>
+    <t>ИИУП-000436</t>
+  </si>
+  <si>
+    <t>ИИУП-000437</t>
+  </si>
+  <si>
+    <t>ИИУП-000438</t>
+  </si>
+  <si>
+    <t>ИИУП-000439</t>
+  </si>
+  <si>
+    <t>Пресс маслёнка</t>
+  </si>
+  <si>
+    <t>ИИУП-000444</t>
+  </si>
+  <si>
+    <t>Колеровачный аппарат</t>
+  </si>
+  <si>
+    <t>ИИУП-000445</t>
+  </si>
+  <si>
+    <t>Сварочный аппарат</t>
+  </si>
+  <si>
+    <t>ИИУП-000446</t>
+  </si>
+  <si>
+    <t>Роликовый вращатель</t>
+  </si>
+  <si>
+    <t>Микроволновая печь</t>
+  </si>
+  <si>
+    <t>ИИУП-000447</t>
+  </si>
+  <si>
+    <t>ЛГУП-8144</t>
+  </si>
+  <si>
+    <t>ИИУП-000454</t>
+  </si>
+  <si>
+    <t>Цилиндровый механизм с вертушкой к АГЗУ</t>
+  </si>
+  <si>
+    <t>ИИУП-000455</t>
+  </si>
+  <si>
+    <t>Текущий ремонт окон ПВХ</t>
+  </si>
+  <si>
+    <t>ИИУП-000459</t>
+  </si>
+  <si>
+    <t>ТЭНР 60А 13/1,5кВт О 220В Ф1</t>
+  </si>
+  <si>
+    <t>КИУП-000436</t>
+  </si>
+  <si>
+    <t>Фен строительный 3500Вт с регулировкой температуры (профессиональный)</t>
+  </si>
+  <si>
+    <t>ИИУП-000460</t>
+  </si>
+  <si>
+    <t>ЛГУП-8146</t>
+  </si>
+  <si>
+    <t>ИИ00-000064</t>
+  </si>
+  <si>
+    <t>Дверь лев с доводчиком1900х1000 мм(ВхШ) полотно RAL9003(белый)/коробка (RAL 9003)(белый)с цепью</t>
+  </si>
+  <si>
+    <t>Дверь левс доводчиком2000х1000мм(ВхШ) полотно RAL 9003(белый)/коробка(RAL 9003)(белый)с цепью</t>
+  </si>
+  <si>
+    <t>Краскопульт с верх. бачком S900-P d=2мм в блистере  (Русский Мастер) (20)</t>
   </si>
   <si>
     <t>Фумлента</t>
   </si>
   <si>
-    <t>Краскопульт с верх. бачком S900-P d=2мм в блистере  (Русский Мастер) (20)</t>
+    <t>Лента упаковочная полипропиленовая 12х0,6мм</t>
+  </si>
+  <si>
+    <t>Гофрокороб 395*155*155</t>
+  </si>
+  <si>
+    <t>Емкость пластиковая 0,5л (дно плоское, форма емкости - квадрат или прямоугольник)</t>
   </si>
   <si>
     <t>Мешок полиэтиленовый хозяйственный 300х500</t>
   </si>
   <si>
-    <t>Емкость пластиковая 0,5л (дно плоское, форма емкости - квадрат или прямоугольник)</t>
-  </si>
-  <si>
-    <t>Гофрокороб 395*155*155</t>
-  </si>
-  <si>
-    <t>Лента упаковочная полипропиленовая 12х0,6мм</t>
+    <t>Пакет с замком (гриппер) 200*300 , 35 мкм.</t>
   </si>
   <si>
     <t>Пакет с защелкой 250х150</t>
   </si>
   <si>
-    <t>Пакет с замком (гриппер) 200*300 , 35 мкм.</t>
+    <t>Крепление для труб ПВХ с защелкой, 16 мм</t>
+  </si>
+  <si>
+    <t>Коробка соединительная К-СП 08.08.08</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р405(-60+40)2-2х20НК(А)-2х20НК(С)-2,5х10(П), 1ЕхеLLCGbXT6, ip66, 190х75х75</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р403(-60+40)12-6х20НК(А)-5х20НК(С)-2,5х21(П), 1ЕхеLLCGbXT6, ip66, 110х75х55</t>
+  </si>
+  <si>
+    <t>Консоль с опорой ML 300мм (шт)</t>
+  </si>
+  <si>
+    <t>Кольцевой изолир. наконечник 4-6мм2 под винт М6</t>
+  </si>
+  <si>
+    <t>Клемма WAGO 222-415, 5 клеммных зажимов, номинальное сечение проводника 0.08-2.5 мм2</t>
+  </si>
+  <si>
+    <t>Клемма WAGO 222-415, 2 клеммных зажимов, номинальное сечение проводника 0.08-2.5 мм2</t>
+  </si>
+  <si>
+    <t>Извещатель пожарный ручной ИПР 535-25Г IP67</t>
+  </si>
+  <si>
+    <t>Извещатель пожарный ручной взрывозащищенный ИП 535-07е 1ExdbIICT6Gb, IP67</t>
+  </si>
+  <si>
+    <t>Крышка Угол горизонтальный CPO 90 (100х50)</t>
+  </si>
+  <si>
+    <t>Крышка Угол горизонтальный CPO 90 (50х50)</t>
+  </si>
+  <si>
+    <t>Наконечник кабельный ТМЛ 25-8-7</t>
+  </si>
+  <si>
+    <t>Извещатель пожарный дымовой ИП 212-130 IP43</t>
+  </si>
+  <si>
+    <t>Извещатель охранный точечный магнитоконтактный взрывозащ.И0102 В3 АТОН исп.21Ч СМД0000000490СМД</t>
+  </si>
+  <si>
+    <t>Извещатель магнитоконтактный Smartec ST-DM146 IP66</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (50 х 50)</t>
+  </si>
+  <si>
+    <t>Угол горизонтальный CPO 90 (100 х 50)</t>
+  </si>
+  <si>
+    <t>Скоба металлическая СМО 16-17 49152 КВТ</t>
+  </si>
+  <si>
+    <t>Короб клем. МТ Р407(-60+40) 2-13х20НК(А)-2х20НК(С)-4х25-2,5х40(П),1ЕхеLLCGbXT6, ip66,360х160х90</t>
+  </si>
+  <si>
+    <t>ИБП для шкафа управления</t>
+  </si>
+  <si>
+    <t>Аварийное освещение Вега 60 с БАП 2Ex Тех 1ExmbIIC T6 Gb X, IP65</t>
+  </si>
+  <si>
+    <t>Светильник НПП 24-100 УХЛ1 IP65</t>
+  </si>
+  <si>
+    <t>Светильник взрывозащищенный ДБП 09-15-101 УХЛ1 ExdllBT6G IP65</t>
+  </si>
+  <si>
+    <t>Светильник взрывозащищенный ДБП 09-15-001 УХЛ1 ExdllBT6G IP65</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р407(-60+40) 2-9х20НК(А)-9х20НК(С)-2,5х34(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р407(-60+40) 2-4х20НК(А)-4х20НК(С)-2,5х10(П),1ЕхеLLCGbXT6, ip66, 190х75х75</t>
+  </si>
+  <si>
+    <t>Коробка клем МТ Р403(-60+40)2-4х20НК(А)--3х25НК(С)-2,5х20(П), 1ЕхеLLCGbXT6 ip66, 160х160х90</t>
+  </si>
+  <si>
+    <t>Кабель КВВГЭнг(А)-LS-ХЛ 7х1,0</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р405(-60+40)2-4х20НК(А)-4х20НК(С)-4х20(П), 1ЕхеLLCGbXT6, ip66, 190х75х75</t>
+  </si>
+  <si>
+    <t>Обогреватель взрывозащищенный ОВЭ-4-УХЛ3 1,8 кВт, 380В IExdIIАТ3, IP54</t>
+  </si>
+  <si>
+    <t>Оповещатель светозвуковой взрывозащ. ВС-07е-И 1ExdIICT6, IP66, 12-24В, -60..+70С</t>
+  </si>
+  <si>
+    <t>Оповещатель светозвуковой Маяк-24К IP53</t>
+  </si>
+  <si>
+    <t>Пост аварийной сигнализации загазованности в/защ.ПАСВ1-П-75-1Ж1К-В1 (=24В, -60..+40С) 1ExsIICT6</t>
+  </si>
+  <si>
+    <t>Пост кнопочный взрывозащищенный ПВК-25-ХЛ1 управление обогревом IP65 2ExеdIIСТ6</t>
   </si>
   <si>
     <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
@@ -354,114 +516,30 @@
     <t>Розетка Bylectrica 1-местная ОУ с заз.конт. IP54</t>
   </si>
   <si>
-    <t>Скоба металлическая СМО 16-17 49152 КВТ</t>
-  </si>
-  <si>
-    <t>Угол горизонтальный CPO 90 (100 х 50)</t>
-  </si>
-  <si>
-    <t>Угол горизонтальный CPO 90 (50 х 50)</t>
-  </si>
-  <si>
-    <t>Извещатель пожарный ручной взрывозащищенный ИП 535-07е 1ExdbIICT6Gb, IP67</t>
-  </si>
-  <si>
-    <t>Извещатель пожарный ручной ИПР 535-25Г IP67</t>
-  </si>
-  <si>
-    <t>Клемма WAGO 222-415, 2 клеммных зажимов, номинальное сечение проводника 0.08-2.5 мм2</t>
-  </si>
-  <si>
-    <t>Клемма WAGO 222-415, 5 клеммных зажимов, номинальное сечение проводника 0.08-2.5 мм2</t>
-  </si>
-  <si>
-    <t>Кольцевой изолир. наконечник 4-6мм2 под винт М6</t>
-  </si>
-  <si>
-    <t>Консоль с опорой ML 300мм (шт)</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р403(-60+40)12-6х20НК(А)-5х20НК(С)-2,5х21(П), 1ЕхеLLCGbXT6, ip66, 110х75х55</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р405(-60+40)2-2х20НК(А)-2х20НК(С)-2,5х10(П), 1ЕхеLLCGbXT6, ip66, 190х75х75</t>
-  </si>
-  <si>
-    <t>Коробка соединительная К-СП 08.08.08</t>
-  </si>
-  <si>
-    <t>Крепление для труб ПВХ с защелкой, 16 мм</t>
-  </si>
-  <si>
-    <t>Крышка Угол горизонтальный CPO 90 (100х50)</t>
-  </si>
-  <si>
-    <t>Светильник взрывозащищенный ДБП 09-15-001 УХЛ1 ExdllBT6G IP65</t>
-  </si>
-  <si>
-    <t>Короб клем. МТ Р407(-60+40) 2-13х20НК(А)-2х20НК(С)-4х25-2,5х40(П),1ЕхеLLCGbXT6, ip66,360х160х90</t>
-  </si>
-  <si>
-    <t>ИБП для шкафа управления</t>
-  </si>
-  <si>
-    <t>Аварийное освещение Вега 60 с БАП 2Ex Тех 1ExmbIIC T6 Gb X, IP65</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р407(-60+40) 2-9х20НК(А)-9х20НК(С)-2,5х34(П),1ЕхеLLCGbXT6, ip66, 220х120х90</t>
-  </si>
-  <si>
-    <t>Коробка клеммная МТ Р407(-60+40) 2-4х20НК(А)-4х20НК(С)-2,5х10(П),1ЕхеLLCGbXT6, ip66, 190х75х75</t>
-  </si>
-  <si>
-    <t>Коробка клем МТ Р403(-60+40)2-4х20НК(А)--3х25НК(С)-2,5х20(П), 1ЕхеLLCGbXT6 ip66, 160х160х90</t>
-  </si>
-  <si>
-    <t>Светильник НПП 24-100 УХЛ1 IP65</t>
-  </si>
-  <si>
-    <t>Пост кнопочный взрывозащищенный ПВК-25-ХЛ1 управление обогревом IP65 2ExеdIIСТ6</t>
-  </si>
-  <si>
-    <t>Оповещатель светозвуковой Маяк-24К IP53</t>
-  </si>
-  <si>
-    <t>Оповещатель светозвуковой взрывозащ. ВС-07е-И 1ExdIICT6, IP66, 12-24В, -60..+70С</t>
-  </si>
-  <si>
-    <t>Обогреватель взрывозащищенный ОВЭ-4-УХЛ3 1,8 кВт, 380В IExdIIАТ3, IP54</t>
-  </si>
-  <si>
-    <t>Наконечник кабельный ТМЛ 25-8-7</t>
-  </si>
-  <si>
-    <t>Светильник взрывозащищенный ДБП 09-15-101 УХЛ1 ExdllBT6G IP65</t>
-  </si>
-  <si>
-    <t>Крышка Угол горизонтальный CPO 90 (50х50)</t>
-  </si>
-  <si>
-    <t>Извещатель пожарный дымовой ИП 212-130 IP43</t>
-  </si>
-  <si>
-    <t>Извещатель охранный точечный магнитоконтактный взрывозащ.И0102 В3 АТОН исп.21Ч СМД0000000490СМД</t>
-  </si>
-  <si>
-    <t>Извещатель магнитоконтактный Smartec ST-DM146 IP66</t>
+    <t>Аварийное освещение DL-0128A 28 Вт IP65</t>
   </si>
   <si>
     <t>Выключатель двухклавишный IP55</t>
   </si>
   <si>
-    <t>Аварийное освещение DL-0128A 28 Вт IP65</t>
+    <t>Короб ПВХ 100х60</t>
+  </si>
+  <si>
+    <t>Короб ПВХ  40х25 мм</t>
+  </si>
+  <si>
+    <t>Кабель КПСЭнг(A)-FRLS 2х2х0,75 d7,1мм</t>
+  </si>
+  <si>
+    <t>Кабель КВВГЭнг(А)-LS-ХЛ 4х1,0</t>
+  </si>
+  <si>
+    <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
   </si>
   <si>
     <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d8мм</t>
   </si>
   <si>
-    <t>Коробка клеммная МТ Р405(-60+40)2-4х20НК(А)-4х20НК(С)-4х20(П), 1ЕхеLLCGbXT6, ip66, 190х75х75</t>
-  </si>
-  <si>
     <t>Кабель ВВГнг(А)-LS-ХЛ 3x2,5 d7.2мм</t>
   </si>
   <si>
@@ -480,24 +558,6 @@
     <t>Короб ПВХ 40х40 мм</t>
   </si>
   <si>
-    <t>Короб ПВХ 100х60</t>
-  </si>
-  <si>
-    <t>Короб ПВХ  40х25 мм</t>
-  </si>
-  <si>
-    <t>Кабель КПСЭнг(A)-FRLS 2х2х0,75 d7,1мм</t>
-  </si>
-  <si>
-    <t>Кабель ВВГнг(А)-LS-ХЛ 4x1,5 d10,2мм</t>
-  </si>
-  <si>
-    <t>Кабель КВВГЭнг(А)-LS-ХЛ 4х1,0</t>
-  </si>
-  <si>
-    <t>Кабель КВВГЭнг(А)-LS-ХЛ 7х1,0</t>
-  </si>
-  <si>
     <t>Электроконвектор с терморегулятором ЭВНБ 1кВт, 220В, 50 Гц.</t>
   </si>
   <si>
@@ -507,6 +567,9 @@
     <t>Труба D530х12 09Г2С ГОСТ 8731-74</t>
   </si>
   <si>
+    <t>Труба D159х8 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
     <t>Труба D89х8 ГОСТ 872-78 В 09Г2С ГОСТ 8731-74</t>
   </si>
   <si>
@@ -516,63 +579,30 @@
     <t>Задвижка клиновая литая ЗКЛ 80-40 УХЛ1 30лс15нж, класс герм.А (ряд 2, исп.фл.3)</t>
   </si>
   <si>
-    <t>Круг D23 Ст.09Г2С ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Круг D210 Ст.09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Круг D26 Ст.09Г2С ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Круг D55 ст.09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Квадратный прокат 30х30 Ст.09Г2С ГОСТ 2591-2006</t>
-  </si>
-  <si>
-    <t>Круг D40 Ст.20Х13 ГОСТ 1050-88</t>
-  </si>
-  <si>
     <t>Круг D370 Ст.20 ГОСТ1050-88</t>
   </si>
   <si>
-    <t>Днище 219х4-25 ст.20 ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Днище 377-12-16ГС ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Днище 720х12-09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>Труба D25х7 ст.10Г2 ГОСТ 8733-74</t>
-  </si>
-  <si>
-    <t>Труба D38х9 Ст.09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
     <t>Фланец 1-250-40 09Г2С ГОСТ 12821-80</t>
   </si>
   <si>
     <t>Фланец 2-50-40 09Г2С ГОСТ 12821-80</t>
   </si>
   <si>
+    <t>Болт М20-6gх30.58 (S30) ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Гайка М8-6Н.5.ГОСТ 5915-70</t>
+  </si>
+  <si>
+    <t>Шпилька АМ30-6gх180.60.35.III.4.019 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Шплинт 2х20 ГОСТ 397</t>
+  </si>
+  <si>
     <t>Шпонка 6х6х20 ГОСТ 23360-78</t>
   </si>
   <si>
-    <t>Шплинт 2х20 ГОСТ 397</t>
-  </si>
-  <si>
-    <t>Шпилька АМ30-6gх180.60.35.III.4.019 ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Гайка М8-6Н.5.ГОСТ 5915-70</t>
-  </si>
-  <si>
-    <t>Болт М20-6gх30.58 (S30) ГОСТ 7798-70</t>
-  </si>
-  <si>
     <t>Болт М8-6gx12 ГОСТ 7798-70</t>
   </si>
   <si>
@@ -582,103 +612,196 @@
     <t>Шпилька М8х350, кл.пр. 8.8, оц</t>
   </si>
   <si>
+    <t>Мин. вата типа "URSA" П-125</t>
+  </si>
+  <si>
+    <t>Сетка полутомпаковая 008Н Л80 ГОСТ 6613-86</t>
+  </si>
+  <si>
+    <t>Труба D85х15 БрКМц 3-1 ГОСТ 1628-78</t>
+  </si>
+  <si>
+    <t>Труба D85х10 БрАЖ9-4 ГОСТ 1208-90</t>
+  </si>
+  <si>
+    <t>Проволока D1.8 Ст.60C2А ГОСТ14963-78</t>
+  </si>
+  <si>
+    <t>Круг D90 Ст.20Х13 ГОСТ 5632-72</t>
+  </si>
+  <si>
+    <t>Круг D85 Ст.35 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D18 Ст.20Х13 ГОСТ 5949-75</t>
+  </si>
+  <si>
+    <t>Проволока КО 1,0 ГОСТ 792-67</t>
+  </si>
+  <si>
+    <t>Круг D18 Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D170 Ст.35 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D145 Ст.35 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D135 Ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Шайба 10.02.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
+    <t>Винт В2.М6-6gх8.48.016 ГОСТ 17475-80</t>
+  </si>
+  <si>
+    <t>Гайка М10-6Н ГОСТ 5927-70 (размер под ключ S=17)</t>
+  </si>
+  <si>
+    <t>Кольцо уплотнительное НТ.300.000.010.0</t>
+  </si>
+  <si>
+    <t>Кольцо А20х1,2 ГОСТ 13940-86</t>
+  </si>
+  <si>
+    <t>Кольцо 100-106-36-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 080-086-36-1-6 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 070-076-36-2-4 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 068-076-46-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 055-060-30-1-6 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо уплотнительное НТ 202.003.004.0</t>
+  </si>
+  <si>
     <t>Кольцо А18х1,2 ГОСТ 13942-86</t>
   </si>
   <si>
-    <t>Кольцо уплотнительное НТ 202.003.004.0</t>
-  </si>
-  <si>
-    <t>Корпус 2 НТ.007.001.003</t>
-  </si>
-  <si>
-    <t>Мин. вата типа "URSA" П-125</t>
-  </si>
-  <si>
-    <t>Труба D85х15 БрКМц 3-1 ГОСТ 1628-78</t>
-  </si>
-  <si>
-    <t>Труба D85х10 БрАЖ9-4 ГОСТ 1208-90</t>
-  </si>
-  <si>
-    <t>Круг D18 Ст.20Х13 ГОСТ 5949-75</t>
-  </si>
-  <si>
-    <t>Проволока D1.8 Ст.60C2А ГОСТ14963-78</t>
-  </si>
-  <si>
-    <t>Круг D90 Ст.20Х13 ГОСТ 5632-72</t>
-  </si>
-  <si>
-    <t>Сетка полутомпаковая 008Н Л80 ГОСТ 6613-86</t>
-  </si>
-  <si>
-    <t>Круг D85 Ст.35 ГОСТ 1050-88</t>
+    <t>Кольцо 035-041-36-2-4 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 1А62 ГОСТ 13941-68</t>
+  </si>
+  <si>
+    <t>Кольцо 1А75 ГОСТ 13943-86</t>
+  </si>
+  <si>
+    <t>Кольцо 062-068-36-2-3 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Пружина крышки НТ.200.004.003.0</t>
+  </si>
+  <si>
+    <t>Пружина №467 НТ.200.000.029.0</t>
+  </si>
+  <si>
+    <t>Пружина ПСМНТ.001.000.013 (покупная)</t>
+  </si>
+  <si>
+    <t>Пружина ПСМНТ.001.000.012</t>
+  </si>
+  <si>
+    <t>Пружина ПСМНТ.001.000.030</t>
+  </si>
+  <si>
+    <t>Кольцо 080-085-30 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 070-076-36 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 040-048-46-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 070-080-58-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 060-065-30-1-6 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 028-032-25-1-6 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 130-140-58 ГОСТ 9833-70</t>
+  </si>
+  <si>
+    <t>Кольцо 048-054-36-2-3 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 014-018-25 ГОСТ 9833-73 (фторкаучук)</t>
+  </si>
+  <si>
+    <t>Кольцо 038-042-25 ГОСТ 9833-70</t>
+  </si>
+  <si>
+    <t>Кольцо 075-080-30-2-2 ГОСТ 9833-77</t>
+  </si>
+  <si>
+    <t>Кольцо 080-085-30-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 067-075-46-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Кольцо 080-090-58-2-2 ГОСТ 9833-73</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-4,0 ГОСТ 19903-74 / Ст.3пс4 ГОСТ 14637-89</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-12 ГОСТ 19903-74 / Ст. 09Г2С К52 ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-2,0 ГОСТ 19903-74 / ОК360В-III-Н ГОСТ 16523-97</t>
+  </si>
+  <si>
+    <t>Лист Б-ПН-6,0 ГОСТ 19903-74/ 09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Лист S=2 ГОСТ 19903-74/ Ст.09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Лист S=10 ГОСТ19903-74/Ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Лист чечевица В-К-ПН-4,0 09Г2С ГОСТ 8568-77 S=4 мм</t>
+  </si>
+  <si>
+    <t>Ручка дверная чёрная противопожарная к АГЗУ</t>
+  </si>
+  <si>
+    <t>Проушина для замка</t>
+  </si>
+  <si>
+    <t>Фреза дисковая 40*2,0*12*14Т - HSS (заказывать кратно 1 - для корпуса ПСМНТ)</t>
+  </si>
+  <si>
+    <t>Круг D80 Ст.45 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D80 Ст.35 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D75 Ст.35 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D42 Ст.14Х17Н2 ГОСТ 5949-75</t>
+  </si>
+  <si>
+    <t>Коробка клеммная МТ Р402(-60+40)12-2х20НК(А)-2х20НК(С)-1,5х11(П), 1ЕхеLLCGbXT6, ip66, 110х75х55</t>
   </si>
   <si>
     <t>Кольцо А75х1,7 ГОСТ 13943-86_</t>
-  </si>
-  <si>
-    <t>№ пп</t>
-  </si>
-  <si>
-    <t>Ветошь рул.</t>
-  </si>
-  <si>
-    <t>Пена монтажная шт</t>
-  </si>
-  <si>
-    <t>Перчатки хб (с ПВХ покрытием, 5 ниток,черные,класс 10)</t>
-  </si>
-  <si>
-    <t>Дверь правая с довод 2000х1000 мм (ВхШ) полотно RAL 9003 (белый) коробка (RAL 9003) (белый) с цепь.</t>
-  </si>
-  <si>
-    <t>Окно 1200х1100 мм  ПВХ-профили морозост. исп, RAL 7036 серый</t>
-  </si>
-  <si>
-    <t>Дверь лев с доводчиком1900х1000 мм(ВхШ) полотно RAL9003(белый)коробка (RAL 9003)(белый)с цепью</t>
-  </si>
-  <si>
-    <t>Дверь левс доводчиком2000х1000мм(ВхШ) полотно RAL 9003(белый)коробка(RAL 9003)(белый)с цепью</t>
-  </si>
-  <si>
-    <t>Пост аварийной сигнализации загазованности взащ.ПАСВ1-П-75-1Ж1К-В1 (=24В, -60..+40С) 1ExsIICT6</t>
-  </si>
-  <si>
-    <t>Труба D159х8 ГОСТ 8732-78 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба 76x8,0 ГОСТ 8732-7809Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Онлайн ИБП Штиль ST1101SL (1000 ВА  900 Вт)</t>
-  </si>
-  <si>
-    <t>Кашкороб0427340х160х60Т23ВММКК4+0мат.лам</t>
-  </si>
-  <si>
-    <t>Кашкороб0427405х225х80Т23ВММКК4+0мат.лам.</t>
-  </si>
-  <si>
-    <t>Кашкороб0203300х200х400Т23ММКК4+0мат.лам</t>
-  </si>
-  <si>
-    <t>Кашкороб0201400х400х610Т23ВММКК4+0мат.лам.</t>
-  </si>
-  <si>
-    <t>Круг D185 ГОСТ 2590-2006 325-09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Круг D27 ГОСТ 2590-2006 345-09Г2С ГОСТ 19281-2014</t>
-  </si>
-  <si>
-    <t>Труба ппропилен. 20мм*4м</t>
-  </si>
-  <si>
-    <t>Лист Б-ПН-12 ГОСТ 19903-74  Ст. 09Г2С К52 ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Лист Б-ПН-4,0 ГОСТ 19903-74  Ст.3пс4 ГОСТ 14637-89</t>
   </si>
 </sst>
 </file>
@@ -1115,107 +1238,107 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F263"/>
+  <dimension ref="A1:F288"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="46.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="74.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="74.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="17" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="8" t="s">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="D2" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="8" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="D4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="8" t="s">
-        <v>9</v>
+        <v>116</v>
       </c>
       <c r="D5" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1224,16 +1347,16 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="5">
+        <v>10</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="5">
-        <v>30</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1242,16 +1365,16 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="8" t="s">
-        <v>198</v>
+        <v>13</v>
       </c>
       <c r="D7" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1260,16 +1383,16 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="8" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="D8" s="5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1278,16 +1401,16 @@
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D9" s="5">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1296,16 +1419,16 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D10" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1314,16 +1437,16 @@
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="8" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D11" s="5">
         <v>20</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1332,16 +1455,16 @@
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1350,16 +1473,16 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D13" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E13" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1368,16 +1491,16 @@
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="5">
+        <v>10</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="5">
-        <v>3</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>5</v>
-      </c>
       <c r="F14" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1386,16 +1509,16 @@
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" s="5">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1404,16 +1527,16 @@
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="8" t="s">
-        <v>20</v>
+        <v>118</v>
       </c>
       <c r="D16" s="5">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1425,13 +1548,13 @@
         <v>21</v>
       </c>
       <c r="D17" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1443,13 +1566,13 @@
         <v>22</v>
       </c>
       <c r="D18" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1458,16 +1581,16 @@
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="5">
+        <v>15</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="D19" s="5">
-        <v>12</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1476,16 +1599,16 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="8" t="s">
-        <v>198</v>
+        <v>25</v>
       </c>
       <c r="D20" s="5">
         <v>10</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1494,16 +1617,16 @@
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="8" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D21" s="5">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1512,16 +1635,16 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="8" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D22" s="5">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1530,16 +1653,16 @@
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="8" t="s">
-        <v>199</v>
+        <v>16</v>
       </c>
       <c r="D23" s="5">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1548,16 +1671,16 @@
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D24" s="5">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1566,16 +1689,16 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D25" s="5">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1584,16 +1707,16 @@
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D26" s="5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1602,16 +1725,16 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="D27" s="7">
-        <v>2000</v>
+        <v>29</v>
+      </c>
+      <c r="D27" s="5">
+        <v>3</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1620,34 +1743,34 @@
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="8" t="s">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="D28" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>28</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D29" s="5">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="D29" s="7">
+        <v>2000</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1656,16 +1779,16 @@
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="8" t="s">
-        <v>102</v>
+        <v>33</v>
       </c>
       <c r="D30" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1674,16 +1797,16 @@
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="8" t="s">
-        <v>103</v>
+        <v>34</v>
       </c>
       <c r="D31" s="5">
-        <v>9.8000000000000007</v>
+        <v>15</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1692,16 +1815,16 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="8" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="D32" s="5">
-        <v>7</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1710,16 +1833,16 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="8" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="D33" s="5">
         <v>7</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1728,70 +1851,70 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="8" t="s">
-        <v>201</v>
+        <v>121</v>
       </c>
       <c r="D34" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>34</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="8" t="s">
-        <v>202</v>
+        <v>122</v>
       </c>
       <c r="D35" s="5">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>35</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="8" t="s">
-        <v>203</v>
+        <v>123</v>
       </c>
       <c r="D36" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>36</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="8" t="s">
-        <v>204</v>
+        <v>124</v>
       </c>
       <c r="D37" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1800,16 +1923,16 @@
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="8" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="D38" s="5">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1818,52 +1941,52 @@
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="8" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="D39" s="5">
-        <v>396</v>
+        <v>8</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>39</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="8" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="D40" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>40</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="8" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="D41" s="5">
-        <v>270</v>
+        <v>2</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1872,16 +1995,16 @@
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="8" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="D42" s="5">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1890,16 +2013,16 @@
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="8" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="D43" s="5">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1908,34 +2031,34 @@
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="8" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="D44" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>44</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="8" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="D45" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1944,16 +2067,16 @@
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="8" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
       <c r="D46" s="5">
-        <v>140</v>
+        <v>2</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1962,34 +2085,34 @@
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="8" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D47" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>47</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="8" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="D48" s="5">
         <v>8</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1998,16 +2121,16 @@
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="8" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D49" s="5">
-        <v>140</v>
+        <v>16</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2016,34 +2139,34 @@
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="8" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="D50" s="5">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>50</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="8" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="D51" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2052,16 +2175,16 @@
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="8" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D52" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2070,16 +2193,16 @@
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="8" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D53" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2088,16 +2211,16 @@
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="8" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="D54" s="5">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2106,16 +2229,16 @@
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="8" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="D55" s="5">
         <v>8</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2124,16 +2247,16 @@
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="8" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="D56" s="5">
-        <v>10</v>
+        <v>270</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2142,16 +2265,16 @@
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="8" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="D57" s="5">
         <v>2</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2160,16 +2283,16 @@
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="8" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="D58" s="5">
         <v>2</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2178,16 +2301,16 @@
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="8" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="D59" s="5">
         <v>2</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2196,88 +2319,88 @@
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="8" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D60" s="5">
         <v>2</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
         <v>60</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="8" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="D61" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
         <v>61</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="8" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="D62" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>62</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="8" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="D63" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>63</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="8" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="D64" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2286,16 +2409,16 @@
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="8" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="D65" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2304,16 +2427,16 @@
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="8" t="s">
-        <v>205</v>
+        <v>152</v>
       </c>
       <c r="D66" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2322,52 +2445,52 @@
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="8" t="s">
-        <v>132</v>
+        <v>39</v>
       </c>
       <c r="D67" s="5">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
         <v>67</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="8" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="D68" s="5">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
         <v>68</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="8" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="D69" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2376,34 +2499,34 @@
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="8" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="D70" s="5">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
         <v>70</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="8" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="D71" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2412,34 +2535,34 @@
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="8" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="D72" s="5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
         <v>72</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="8" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D73" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2448,16 +2571,16 @@
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="8" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D74" s="5">
         <v>4</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2466,16 +2589,16 @@
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D75" s="5">
         <v>140</v>
       </c>
-      <c r="D75" s="5">
-        <v>2</v>
-      </c>
       <c r="E75" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2484,16 +2607,16 @@
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="8" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="D76" s="5">
-        <v>2</v>
+        <v>396</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2502,16 +2625,16 @@
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="8" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="D77" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2520,16 +2643,16 @@
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="8" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D78" s="5">
-        <v>2</v>
+        <v>140</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2538,16 +2661,16 @@
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="8" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D79" s="5">
         <v>6</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2556,16 +2679,16 @@
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="8" t="s">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="D80" s="5">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2574,34 +2697,34 @@
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="8" t="s">
-        <v>36</v>
+        <v>163</v>
       </c>
       <c r="D81" s="5">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>81</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="8" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="D82" s="5">
         <v>2</v>
       </c>
       <c r="E82" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F82" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2610,16 +2733,16 @@
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="8" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="D83" s="5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2628,16 +2751,16 @@
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="8" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="D84" s="5">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2646,16 +2769,16 @@
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="8" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="D85" s="5">
-        <v>12</v>
+        <v>128.80000000000001</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2664,16 +2787,16 @@
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="8" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="D86" s="5">
-        <v>70</v>
+        <v>330</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2682,16 +2805,16 @@
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="8" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="D87" s="5">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2700,16 +2823,16 @@
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="8" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="D88" s="5">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2718,16 +2841,16 @@
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="8" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="D89" s="5">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2736,16 +2859,16 @@
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="8" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="D90" s="5">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2754,16 +2877,16 @@
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="8" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="D91" s="5">
-        <v>128.80000000000001</v>
+        <v>12</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2772,16 +2895,16 @@
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="8" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="D92" s="5">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2790,16 +2913,16 @@
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="8" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="D93" s="5">
-        <v>330</v>
+        <v>260</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2808,16 +2931,16 @@
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="8" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="D94" s="5">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2826,16 +2949,16 @@
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="8" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D95" s="5">
         <v>2</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2844,16 +2967,16 @@
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="8" t="s">
-        <v>157</v>
+        <v>46</v>
       </c>
       <c r="D96" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2862,16 +2985,16 @@
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="8" t="s">
-        <v>40</v>
+        <v>177</v>
       </c>
       <c r="D97" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2880,16 +3003,16 @@
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="8" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D98" s="5">
         <v>2</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2898,16 +3021,16 @@
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="8" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="D99" s="5">
         <v>5.7389999999999999</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2916,16 +3039,16 @@
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="8" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="D100" s="7">
         <v>2912.7</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2934,16 +3057,16 @@
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="8" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="D101" s="7">
         <v>2323.62</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2952,16 +3075,16 @@
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="8" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="D102" s="7">
         <v>1438.2</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2970,16 +3093,16 @@
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="8" t="s">
-        <v>207</v>
+        <v>50</v>
       </c>
       <c r="D103" s="5">
         <v>495.19799999999998</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2988,16 +3111,16 @@
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="8" t="s">
-        <v>198</v>
+        <v>20</v>
       </c>
       <c r="D104" s="5">
         <v>5</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3006,16 +3129,16 @@
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="8" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D105" s="5">
         <v>2</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3024,16 +3147,16 @@
       </c>
       <c r="B106" s="4"/>
       <c r="C106" s="8" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D106" s="5">
         <v>6</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3042,16 +3165,16 @@
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="8" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D107" s="5">
         <v>6</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3060,16 +3183,16 @@
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="8" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D108" s="5">
         <v>6</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3078,16 +3201,16 @@
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="8" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D109" s="5">
         <v>1</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3096,16 +3219,16 @@
       </c>
       <c r="B110" s="4"/>
       <c r="C110" s="8" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D110" s="5">
         <v>1</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3114,16 +3237,16 @@
       </c>
       <c r="B111" s="4"/>
       <c r="C111" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="D111" s="5">
-        <v>1</v>
+        <v>61</v>
+      </c>
+      <c r="D111" s="7">
+        <v>1000</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3132,16 +3255,16 @@
       </c>
       <c r="B112" s="4"/>
       <c r="C112" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D112" s="5">
-        <v>2</v>
+        <v>62</v>
+      </c>
+      <c r="D112" s="7">
+        <v>1000</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3150,16 +3273,16 @@
       </c>
       <c r="B113" s="4"/>
       <c r="C113" s="8" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="D113" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3168,16 +3291,16 @@
       </c>
       <c r="B114" s="4"/>
       <c r="C114" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D114" s="5">
-        <v>2</v>
+        <v>64</v>
+      </c>
+      <c r="D114" s="7">
+        <v>1000</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3186,16 +3309,16 @@
       </c>
       <c r="B115" s="4"/>
       <c r="C115" s="8" t="s">
-        <v>209</v>
+        <v>65</v>
       </c>
       <c r="D115" s="7">
         <v>1000</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3204,16 +3327,16 @@
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="D116" s="7">
-        <v>1000</v>
+        <v>66</v>
+      </c>
+      <c r="D116" s="5">
+        <v>1</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3222,16 +3345,16 @@
       </c>
       <c r="B117" s="4"/>
       <c r="C117" s="8" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D117" s="5">
         <v>1</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3240,16 +3363,16 @@
       </c>
       <c r="B118" s="4"/>
       <c r="C118" s="8" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D118" s="5">
         <v>1</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3258,16 +3381,16 @@
       </c>
       <c r="B119" s="4"/>
       <c r="C119" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="D119" s="7">
-        <v>1000</v>
+        <v>69</v>
+      </c>
+      <c r="D119" s="5">
+        <v>6</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3276,16 +3399,16 @@
       </c>
       <c r="B120" s="4"/>
       <c r="C120" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="D120" s="7">
-        <v>1000</v>
+        <v>69</v>
+      </c>
+      <c r="D120" s="5">
+        <v>1</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3294,16 +3417,16 @@
       </c>
       <c r="B121" s="4"/>
       <c r="C121" s="8" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D121" s="5">
         <v>1</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3312,16 +3435,16 @@
       </c>
       <c r="B122" s="4"/>
       <c r="C122" s="8" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="D122" s="5">
         <v>1</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3330,16 +3453,16 @@
       </c>
       <c r="B123" s="4"/>
       <c r="C123" s="8" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D123" s="5">
         <v>1</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3348,16 +3471,16 @@
       </c>
       <c r="B124" s="4"/>
       <c r="C124" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D124" s="5">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3366,16 +3489,16 @@
       </c>
       <c r="B125" s="4"/>
       <c r="C125" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D125" s="5">
         <v>3</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3384,16 +3507,16 @@
       </c>
       <c r="B126" s="4"/>
       <c r="C126" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D126" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3402,16 +3525,16 @@
       </c>
       <c r="B127" s="4"/>
       <c r="C127" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D127" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3420,16 +3543,16 @@
       </c>
       <c r="B128" s="4"/>
       <c r="C128" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D128" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3438,16 +3561,16 @@
       </c>
       <c r="B129" s="4"/>
       <c r="C129" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D129" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3456,16 +3579,16 @@
       </c>
       <c r="B130" s="4"/>
       <c r="C130" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D130" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3474,16 +3597,16 @@
       </c>
       <c r="B131" s="4"/>
       <c r="C131" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D131" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3492,16 +3615,16 @@
       </c>
       <c r="B132" s="4"/>
       <c r="C132" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D132" s="5">
         <v>1</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3510,16 +3633,16 @@
       </c>
       <c r="B133" s="4"/>
       <c r="C133" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D133" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3528,16 +3651,16 @@
       </c>
       <c r="B134" s="4"/>
       <c r="C134" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D134" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3546,16 +3669,16 @@
       </c>
       <c r="B135" s="4"/>
       <c r="C135" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D135" s="5">
         <v>1</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3564,16 +3687,16 @@
       </c>
       <c r="B136" s="4"/>
       <c r="C136" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D136" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3582,16 +3705,16 @@
       </c>
       <c r="B137" s="4"/>
       <c r="C137" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D137" s="5">
         <v>1</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3600,16 +3723,16 @@
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D138" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3618,16 +3741,16 @@
       </c>
       <c r="B139" s="4"/>
       <c r="C139" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D139" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3636,16 +3759,16 @@
       </c>
       <c r="B140" s="4"/>
       <c r="C140" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D140" s="5">
         <v>1</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3654,16 +3777,16 @@
       </c>
       <c r="B141" s="4"/>
       <c r="C141" s="8" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="D141" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3672,16 +3795,16 @@
       </c>
       <c r="B142" s="4"/>
       <c r="C142" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D142" s="5">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3690,16 +3813,16 @@
       </c>
       <c r="B143" s="4"/>
       <c r="C143" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D143" s="5">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3708,16 +3831,16 @@
       </c>
       <c r="B144" s="4"/>
       <c r="C144" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D144" s="5">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3726,16 +3849,16 @@
       </c>
       <c r="B145" s="4"/>
       <c r="C145" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D145" s="5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3744,16 +3867,16 @@
       </c>
       <c r="B146" s="4"/>
       <c r="C146" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D146" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3762,16 +3885,16 @@
       </c>
       <c r="B147" s="4"/>
       <c r="C147" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D147" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3780,16 +3903,16 @@
       </c>
       <c r="B148" s="4"/>
       <c r="C148" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D148" s="5">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3798,16 +3921,16 @@
       </c>
       <c r="B149" s="4"/>
       <c r="C149" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D149" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3816,16 +3939,16 @@
       </c>
       <c r="B150" s="4"/>
       <c r="C150" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D150" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3834,16 +3957,16 @@
       </c>
       <c r="B151" s="4"/>
       <c r="C151" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D151" s="5">
         <v>2</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3852,16 +3975,16 @@
       </c>
       <c r="B152" s="4"/>
       <c r="C152" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D152" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3870,16 +3993,16 @@
       </c>
       <c r="B153" s="4"/>
       <c r="C153" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D153" s="5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3888,16 +4011,16 @@
       </c>
       <c r="B154" s="4"/>
       <c r="C154" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D154" s="5">
         <v>2</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3906,16 +4029,16 @@
       </c>
       <c r="B155" s="4"/>
       <c r="C155" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D155" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3924,16 +4047,16 @@
       </c>
       <c r="B156" s="4"/>
       <c r="C156" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D156" s="5">
         <v>1</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3942,16 +4065,16 @@
       </c>
       <c r="B157" s="4"/>
       <c r="C157" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D157" s="5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3960,16 +4083,16 @@
       </c>
       <c r="B158" s="4"/>
       <c r="C158" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D158" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3978,16 +4101,16 @@
       </c>
       <c r="B159" s="4"/>
       <c r="C159" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D159" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3996,16 +4119,16 @@
       </c>
       <c r="B160" s="4"/>
       <c r="C160" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D160" s="5">
         <v>1</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4014,16 +4137,16 @@
       </c>
       <c r="B161" s="4"/>
       <c r="C161" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D161" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4032,16 +4155,16 @@
       </c>
       <c r="B162" s="4"/>
       <c r="C162" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D162" s="5">
         <v>1</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4050,16 +4173,16 @@
       </c>
       <c r="B163" s="4"/>
       <c r="C163" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D163" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4068,16 +4191,16 @@
       </c>
       <c r="B164" s="4"/>
       <c r="C164" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D164" s="5">
         <v>1</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4086,16 +4209,16 @@
       </c>
       <c r="B165" s="4"/>
       <c r="C165" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D165" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4104,16 +4227,16 @@
       </c>
       <c r="B166" s="4"/>
       <c r="C166" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D166" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4122,16 +4245,16 @@
       </c>
       <c r="B167" s="4"/>
       <c r="C167" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D167" s="5">
         <v>1</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4140,16 +4263,16 @@
       </c>
       <c r="B168" s="4"/>
       <c r="C168" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D168" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4158,16 +4281,16 @@
       </c>
       <c r="B169" s="4"/>
       <c r="C169" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D169" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4176,16 +4299,16 @@
       </c>
       <c r="B170" s="4"/>
       <c r="C170" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D170" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4194,16 +4317,16 @@
       </c>
       <c r="B171" s="4"/>
       <c r="C171" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D171" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E171" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4212,16 +4335,16 @@
       </c>
       <c r="B172" s="4"/>
       <c r="C172" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D172" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4230,16 +4353,16 @@
       </c>
       <c r="B173" s="4"/>
       <c r="C173" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D173" s="5">
         <v>1</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="174" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4248,16 +4371,16 @@
       </c>
       <c r="B174" s="4"/>
       <c r="C174" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D174" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4266,16 +4389,16 @@
       </c>
       <c r="B175" s="4"/>
       <c r="C175" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D175" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E175" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="176" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4284,16 +4407,16 @@
       </c>
       <c r="B176" s="4"/>
       <c r="C176" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D176" s="5">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4302,16 +4425,16 @@
       </c>
       <c r="B177" s="4"/>
       <c r="C177" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D177" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E177" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="178" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4320,16 +4443,16 @@
       </c>
       <c r="B178" s="4"/>
       <c r="C178" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D178" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="179" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4338,16 +4461,16 @@
       </c>
       <c r="B179" s="4"/>
       <c r="C179" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D179" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E179" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="180" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4356,16 +4479,16 @@
       </c>
       <c r="B180" s="4"/>
       <c r="C180" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D180" s="5">
         <v>2</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4374,16 +4497,16 @@
       </c>
       <c r="B181" s="4"/>
       <c r="C181" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D181" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E181" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4392,16 +4515,16 @@
       </c>
       <c r="B182" s="4"/>
       <c r="C182" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D182" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="183" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4410,16 +4533,16 @@
       </c>
       <c r="B183" s="4"/>
       <c r="C183" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D183" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="184" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4428,16 +4551,16 @@
       </c>
       <c r="B184" s="4"/>
       <c r="C184" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D184" s="5">
         <v>1</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="185" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4446,16 +4569,16 @@
       </c>
       <c r="B185" s="4"/>
       <c r="C185" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D185" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="186" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4464,16 +4587,16 @@
       </c>
       <c r="B186" s="4"/>
       <c r="C186" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D186" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="187" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4482,16 +4605,16 @@
       </c>
       <c r="B187" s="4"/>
       <c r="C187" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D187" s="5">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4500,16 +4623,16 @@
       </c>
       <c r="B188" s="4"/>
       <c r="C188" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D188" s="5">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="189" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4518,16 +4641,16 @@
       </c>
       <c r="B189" s="4"/>
       <c r="C189" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D189" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E189" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="190" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4536,16 +4659,16 @@
       </c>
       <c r="B190" s="4"/>
       <c r="C190" s="8" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D190" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4554,16 +4677,16 @@
       </c>
       <c r="B191" s="4"/>
       <c r="C191" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D191" s="5">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="E191" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="192" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4572,16 +4695,16 @@
       </c>
       <c r="B192" s="4"/>
       <c r="C192" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D192" s="5">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4590,16 +4713,16 @@
       </c>
       <c r="B193" s="4"/>
       <c r="C193" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D193" s="5">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="E193" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="194" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4608,16 +4731,16 @@
       </c>
       <c r="B194" s="4"/>
       <c r="C194" s="8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D194" s="5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4626,16 +4749,16 @@
       </c>
       <c r="B195" s="4"/>
       <c r="C195" s="8" t="s">
-        <v>61</v>
+        <v>182</v>
       </c>
       <c r="D195" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E195" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="196" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4644,52 +4767,52 @@
       </c>
       <c r="B196" s="4"/>
       <c r="C196" s="8" t="s">
-        <v>61</v>
+        <v>183</v>
       </c>
       <c r="D196" s="5">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="3">
         <v>196</v>
       </c>
       <c r="B197" s="4"/>
       <c r="C197" s="8" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D197" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E197" s="6" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="3">
         <v>197</v>
       </c>
       <c r="B198" s="4"/>
       <c r="C198" s="8" t="s">
-        <v>61</v>
+        <v>184</v>
       </c>
       <c r="D198" s="5">
-        <v>1</v>
+        <v>342</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4698,16 +4821,16 @@
       </c>
       <c r="B199" s="4"/>
       <c r="C199" s="8" t="s">
-        <v>61</v>
+        <v>185</v>
       </c>
       <c r="D199" s="5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E199" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="200" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4716,16 +4839,16 @@
       </c>
       <c r="B200" s="4"/>
       <c r="C200" s="8" t="s">
-        <v>64</v>
+        <v>186</v>
       </c>
       <c r="D200" s="5">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="201" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4734,16 +4857,16 @@
       </c>
       <c r="B201" s="4"/>
       <c r="C201" s="8" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="D201" s="5">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E201" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="202" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4752,16 +4875,16 @@
       </c>
       <c r="B202" s="4"/>
       <c r="C202" s="8" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="D202" s="5">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="203" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4770,16 +4893,16 @@
       </c>
       <c r="B203" s="4"/>
       <c r="C203" s="8" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="D203" s="5">
-        <v>4.5999999999999996</v>
+        <v>180</v>
       </c>
       <c r="E203" s="6" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="F203" s="4" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
     </row>
     <row r="204" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4788,16 +4911,16 @@
       </c>
       <c r="B204" s="4"/>
       <c r="C204" s="8" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="D204" s="5">
-        <v>40.76</v>
+        <v>30</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
     </row>
     <row r="205" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4806,88 +4929,88 @@
       </c>
       <c r="B205" s="4"/>
       <c r="C205" s="8" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="D205" s="5">
-        <v>17.29</v>
+        <v>15</v>
       </c>
       <c r="E205" s="6" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="3">
         <v>205</v>
       </c>
       <c r="B206" s="4"/>
       <c r="C206" s="8" t="s">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="D206" s="5">
-        <v>0.56999999999999995</v>
+        <v>144</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="3">
         <v>206</v>
       </c>
       <c r="B207" s="4"/>
       <c r="C207" s="8" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="D207" s="5">
-        <v>0.75</v>
+        <v>540</v>
       </c>
       <c r="E207" s="6" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="3">
         <v>207</v>
       </c>
       <c r="B208" s="4"/>
       <c r="C208" s="8" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="D208" s="5">
-        <v>0.42</v>
+        <v>576</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="3">
         <v>208</v>
       </c>
       <c r="B209" s="4"/>
       <c r="C209" s="8" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="D209" s="5">
-        <v>1.71</v>
+        <v>18</v>
       </c>
       <c r="E209" s="6" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="210" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4896,142 +5019,142 @@
       </c>
       <c r="B210" s="4"/>
       <c r="C210" s="8" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="D210" s="5">
-        <v>0.84</v>
+        <v>48</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="3">
         <v>210</v>
       </c>
       <c r="B211" s="4"/>
       <c r="C211" s="8" t="s">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="D211" s="5">
-        <v>1</v>
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="E211" s="6" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="3">
         <v>211</v>
       </c>
       <c r="B212" s="4"/>
       <c r="C212" s="8" t="s">
-        <v>70</v>
+        <v>197</v>
       </c>
       <c r="D212" s="5">
-        <v>1</v>
+        <v>6.23</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="3">
         <v>212</v>
       </c>
       <c r="B213" s="4"/>
       <c r="C213" s="8" t="s">
-        <v>71</v>
+        <v>198</v>
       </c>
       <c r="D213" s="5">
-        <v>1</v>
+        <v>1.82</v>
       </c>
       <c r="E213" s="6" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="3">
         <v>213</v>
       </c>
       <c r="B214" s="4"/>
       <c r="C214" s="8" t="s">
-        <v>72</v>
+        <v>199</v>
       </c>
       <c r="D214" s="5">
-        <v>1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="3">
         <v>214</v>
       </c>
       <c r="B215" s="4"/>
       <c r="C215" s="8" t="s">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="D215" s="5">
-        <v>6</v>
+        <v>23.87</v>
       </c>
       <c r="E215" s="6" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="3">
         <v>215</v>
       </c>
       <c r="B216" s="4"/>
       <c r="C216" s="8" t="s">
-        <v>74</v>
+        <v>201</v>
       </c>
       <c r="D216" s="5">
-        <v>4</v>
+        <v>20.72</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="3">
         <v>216</v>
       </c>
       <c r="B217" s="4"/>
       <c r="C217" s="8" t="s">
-        <v>75</v>
+        <v>202</v>
       </c>
       <c r="D217" s="5">
-        <v>1</v>
+        <v>2.73</v>
       </c>
       <c r="E217" s="6" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="218" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5040,70 +5163,70 @@
       </c>
       <c r="B218" s="4"/>
       <c r="C218" s="8" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D218" s="5">
         <v>7</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="3">
         <v>218</v>
       </c>
       <c r="B219" s="4"/>
       <c r="C219" s="8" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="D219" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E219" s="6" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="3">
         <v>219</v>
       </c>
       <c r="B220" s="4"/>
       <c r="C220" s="8" t="s">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="D220" s="5">
-        <v>4</v>
+        <v>26.64</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="3">
         <v>220</v>
       </c>
       <c r="B221" s="4"/>
       <c r="C221" s="8" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="D221" s="5">
-        <v>342</v>
+        <v>0.54</v>
       </c>
       <c r="E221" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="222" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5112,16 +5235,16 @@
       </c>
       <c r="B222" s="4"/>
       <c r="C222" s="8" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="D222" s="5">
-        <v>30</v>
+        <v>95.58</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="223" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5130,16 +5253,16 @@
       </c>
       <c r="B223" s="4"/>
       <c r="C223" s="8" t="s">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="D223" s="5">
-        <v>30</v>
+        <v>30.33</v>
       </c>
       <c r="E223" s="6" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="224" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5148,16 +5271,16 @@
       </c>
       <c r="B224" s="4"/>
       <c r="C224" s="8" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="D224" s="5">
-        <v>30</v>
+        <v>32.130000000000003</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="225" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5166,16 +5289,16 @@
       </c>
       <c r="B225" s="4"/>
       <c r="C225" s="8" t="s">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="D225" s="5">
-        <v>20.399999999999999</v>
+        <v>45</v>
       </c>
       <c r="E225" s="6" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="226" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5184,16 +5307,16 @@
       </c>
       <c r="B226" s="4"/>
       <c r="C226" s="8" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="D226" s="5">
-        <v>16.5</v>
+        <v>9</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="227" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5202,34 +5325,34 @@
       </c>
       <c r="B227" s="4"/>
       <c r="C227" s="8" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="D227" s="5">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="E227" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="3">
         <v>227</v>
       </c>
       <c r="B228" s="4"/>
       <c r="C228" s="8" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="D228" s="5">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="229" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5238,16 +5361,16 @@
       </c>
       <c r="B229" s="4"/>
       <c r="C229" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="D229" s="5">
-        <v>5</v>
+        <v>211</v>
+      </c>
+      <c r="D229" s="7">
+        <v>2000</v>
       </c>
       <c r="E229" s="6" t="s">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="230" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5256,16 +5379,16 @@
       </c>
       <c r="B230" s="4"/>
       <c r="C230" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D230" s="5">
-        <v>7</v>
+        <v>212</v>
+      </c>
+      <c r="D230" s="7">
+        <v>2000</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="231" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5274,16 +5397,16 @@
       </c>
       <c r="B231" s="4"/>
       <c r="C231" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D231" s="5">
-        <v>1</v>
+        <v>213</v>
+      </c>
+      <c r="D231" s="7">
+        <v>2000</v>
       </c>
       <c r="E231" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="232" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5292,16 +5415,16 @@
       </c>
       <c r="B232" s="4"/>
       <c r="C232" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D232" s="5">
-        <v>1</v>
+        <v>214</v>
+      </c>
+      <c r="D232" s="7">
+        <v>2000</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="233" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5310,16 +5433,16 @@
       </c>
       <c r="B233" s="4"/>
       <c r="C233" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D233" s="5">
-        <v>1</v>
+        <v>215</v>
+      </c>
+      <c r="D233" s="7">
+        <v>2000</v>
       </c>
       <c r="E233" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="234" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5328,16 +5451,16 @@
       </c>
       <c r="B234" s="4"/>
       <c r="C234" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D234" s="5">
-        <v>1</v>
+        <v>216</v>
+      </c>
+      <c r="D234" s="7">
+        <v>2000</v>
       </c>
       <c r="E234" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="235" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5346,16 +5469,16 @@
       </c>
       <c r="B235" s="4"/>
       <c r="C235" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D235" s="5">
-        <v>1</v>
+        <v>217</v>
+      </c>
+      <c r="D235" s="7">
+        <v>2000</v>
       </c>
       <c r="E235" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="236" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5364,16 +5487,16 @@
       </c>
       <c r="B236" s="4"/>
       <c r="C236" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D236" s="5">
-        <v>1</v>
+        <v>218</v>
+      </c>
+      <c r="D236" s="7">
+        <v>2000</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="237" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5382,16 +5505,16 @@
       </c>
       <c r="B237" s="4"/>
       <c r="C237" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D237" s="5">
-        <v>10</v>
+        <v>258</v>
+      </c>
+      <c r="D237" s="7">
+        <v>2000</v>
       </c>
       <c r="E237" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="238" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5400,16 +5523,16 @@
       </c>
       <c r="B238" s="4"/>
       <c r="C238" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D238" s="5">
-        <v>4</v>
+        <v>219</v>
+      </c>
+      <c r="D238" s="7">
+        <v>2000</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="239" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5418,16 +5541,16 @@
       </c>
       <c r="B239" s="4"/>
       <c r="C239" s="8" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D239" s="7">
-        <v>9739.2000000000007</v>
+        <v>2000</v>
       </c>
       <c r="E239" s="6" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="240" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5436,16 +5559,16 @@
       </c>
       <c r="B240" s="4"/>
       <c r="C240" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="D240" s="5">
-        <v>795.6</v>
+        <v>221</v>
+      </c>
+      <c r="D240" s="7">
+        <v>2000</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="241" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5454,16 +5577,16 @@
       </c>
       <c r="B241" s="4"/>
       <c r="C241" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="D241" s="5">
-        <v>15</v>
+        <v>222</v>
+      </c>
+      <c r="D241" s="7">
+        <v>2000</v>
       </c>
       <c r="E241" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="242" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5472,16 +5595,16 @@
       </c>
       <c r="B242" s="4"/>
       <c r="C242" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="D242" s="5">
-        <v>30</v>
+        <v>223</v>
+      </c>
+      <c r="D242" s="7">
+        <v>2000</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="243" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5490,16 +5613,16 @@
       </c>
       <c r="B243" s="4"/>
       <c r="C243" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="D243" s="5">
-        <v>180</v>
+        <v>224</v>
+      </c>
+      <c r="D243" s="7">
+        <v>5000</v>
       </c>
       <c r="E243" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="244" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5508,16 +5631,16 @@
       </c>
       <c r="B244" s="4"/>
       <c r="C244" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="D244" s="5">
-        <v>45</v>
+        <v>225</v>
+      </c>
+      <c r="D244" s="7">
+        <v>5000</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="245" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5526,88 +5649,88 @@
       </c>
       <c r="B245" s="4"/>
       <c r="C245" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="D245" s="5">
-        <v>30</v>
+        <v>226</v>
+      </c>
+      <c r="D245" s="7">
+        <v>5000</v>
       </c>
       <c r="E245" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="3">
         <v>245</v>
       </c>
       <c r="B246" s="4"/>
       <c r="C246" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D246" s="5">
-        <v>144</v>
+        <v>227</v>
+      </c>
+      <c r="D246" s="7">
+        <v>5000</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="3">
         <v>246</v>
       </c>
       <c r="B247" s="4"/>
       <c r="C247" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="D247" s="5">
-        <v>540</v>
+        <v>228</v>
+      </c>
+      <c r="D247" s="7">
+        <v>5000</v>
       </c>
       <c r="E247" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="3">
         <v>247</v>
       </c>
       <c r="B248" s="4"/>
       <c r="C248" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="D248" s="5">
-        <v>576</v>
+        <v>229</v>
+      </c>
+      <c r="D248" s="7">
+        <v>2000</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="3">
         <v>248</v>
       </c>
       <c r="B249" s="4"/>
       <c r="C249" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="D249" s="5">
-        <v>18</v>
+        <v>230</v>
+      </c>
+      <c r="D249" s="7">
+        <v>2000</v>
       </c>
       <c r="E249" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="250" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5616,88 +5739,88 @@
       </c>
       <c r="B250" s="4"/>
       <c r="C250" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D250" s="5">
-        <v>1</v>
+        <v>231</v>
+      </c>
+      <c r="D250" s="7">
+        <v>2000</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F250" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="251" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="3">
         <v>250</v>
       </c>
       <c r="B251" s="4"/>
       <c r="C251" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="D251" s="5">
-        <v>40</v>
+        <v>232</v>
+      </c>
+      <c r="D251" s="7">
+        <v>1300</v>
       </c>
       <c r="E251" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="3">
         <v>251</v>
       </c>
       <c r="B252" s="4"/>
       <c r="C252" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="D252" s="5">
-        <v>40</v>
+        <v>233</v>
+      </c>
+      <c r="D252" s="7">
+        <v>2000</v>
       </c>
       <c r="E252" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="3">
         <v>252</v>
       </c>
       <c r="B253" s="4"/>
       <c r="C253" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D253" s="5">
-        <v>80</v>
+        <v>234</v>
+      </c>
+      <c r="D253" s="7">
+        <v>2000</v>
       </c>
       <c r="E253" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="3">
         <v>253</v>
       </c>
       <c r="B254" s="4"/>
       <c r="C254" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="D254" s="5">
-        <v>80</v>
+        <v>235</v>
+      </c>
+      <c r="D254" s="7">
+        <v>2000</v>
       </c>
       <c r="E254" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="255" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5706,16 +5829,16 @@
       </c>
       <c r="B255" s="4"/>
       <c r="C255" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="D255" s="5">
-        <v>48</v>
+        <v>236</v>
+      </c>
+      <c r="D255" s="7">
+        <v>1500</v>
       </c>
       <c r="E255" s="6" t="s">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="F255" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="256" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5724,16 +5847,16 @@
       </c>
       <c r="B256" s="4"/>
       <c r="C256" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="D256" s="5">
-        <v>6.23</v>
+        <v>237</v>
+      </c>
+      <c r="D256" s="7">
+        <v>2000</v>
       </c>
       <c r="E256" s="6" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="257" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5742,16 +5865,16 @@
       </c>
       <c r="B257" s="4"/>
       <c r="C257" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="D257" s="5">
-        <v>1.82</v>
+        <v>238</v>
+      </c>
+      <c r="D257" s="7">
+        <v>2000</v>
       </c>
       <c r="E257" s="6" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="258" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5760,16 +5883,16 @@
       </c>
       <c r="B258" s="4"/>
       <c r="C258" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="D258" s="5">
-        <v>2.73</v>
+        <v>239</v>
+      </c>
+      <c r="D258" s="7">
+        <v>2000</v>
       </c>
       <c r="E258" s="6" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="F258" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="259" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5778,16 +5901,16 @@
       </c>
       <c r="B259" s="4"/>
       <c r="C259" s="8" t="s">
-        <v>192</v>
+        <v>240</v>
       </c>
       <c r="D259" s="5">
-        <v>7.0000000000000007E-2</v>
+        <v>800</v>
       </c>
       <c r="E259" s="6" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="260" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5796,16 +5919,16 @@
       </c>
       <c r="B260" s="4"/>
       <c r="C260" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="D260" s="5">
-        <v>23.87</v>
+        <v>241</v>
+      </c>
+      <c r="D260" s="7">
+        <v>2000</v>
       </c>
       <c r="E260" s="6" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="261" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5814,16 +5937,16 @@
       </c>
       <c r="B261" s="4"/>
       <c r="C261" s="8" t="s">
-        <v>194</v>
+        <v>242</v>
       </c>
       <c r="D261" s="5">
-        <v>8.4000000000000005E-2</v>
+        <v>600</v>
       </c>
       <c r="E261" s="6" t="s">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="262" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5832,16 +5955,16 @@
       </c>
       <c r="B262" s="4"/>
       <c r="C262" s="8" t="s">
-        <v>195</v>
+        <v>243</v>
       </c>
       <c r="D262" s="5">
-        <v>20.72</v>
+        <v>795.6</v>
       </c>
       <c r="E262" s="6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F262" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="263" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5850,16 +5973,466 @@
       </c>
       <c r="B263" s="4"/>
       <c r="C263" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D263" s="7">
+        <v>9739.2000000000007</v>
+      </c>
+      <c r="E263" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F263" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A264" s="3">
+        <v>263</v>
+      </c>
+      <c r="B264" s="4"/>
+      <c r="C264" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="D264" s="5">
+        <v>9</v>
+      </c>
+      <c r="E264" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F264" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A265" s="3">
+        <v>264</v>
+      </c>
+      <c r="B265" s="4"/>
+      <c r="C265" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="D265" s="5">
+        <v>565.5</v>
+      </c>
+      <c r="E265" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F265" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A266" s="3">
+        <v>265</v>
+      </c>
+      <c r="B266" s="4"/>
+      <c r="C266" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="D266" s="7">
+        <v>1404</v>
+      </c>
+      <c r="E266" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F266" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A267" s="3">
+        <v>266</v>
+      </c>
+      <c r="B267" s="4"/>
+      <c r="C267" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="D267" s="7">
+        <v>1739.7</v>
+      </c>
+      <c r="E267" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F267" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A268" s="3">
+        <v>267</v>
+      </c>
+      <c r="B268" s="4"/>
+      <c r="C268" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D268" s="5">
+        <v>30</v>
+      </c>
+      <c r="E268" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F268" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A269" s="3">
+        <v>268</v>
+      </c>
+      <c r="B269" s="4"/>
+      <c r="C269" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D263" s="5">
+      <c r="D269" s="5">
+        <v>1</v>
+      </c>
+      <c r="E269" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F269" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A270" s="3">
+        <v>269</v>
+      </c>
+      <c r="B270" s="4"/>
+      <c r="C270" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D270" s="5">
+        <v>1</v>
+      </c>
+      <c r="E270" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F270" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A271" s="3">
+        <v>270</v>
+      </c>
+      <c r="B271" s="4"/>
+      <c r="C271" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D271" s="5">
+        <v>1</v>
+      </c>
+      <c r="E271" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F271" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A272" s="3">
+        <v>271</v>
+      </c>
+      <c r="B272" s="4"/>
+      <c r="C272" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D272" s="5">
+        <v>1</v>
+      </c>
+      <c r="E272" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F272" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A273" s="3">
+        <v>272</v>
+      </c>
+      <c r="B273" s="4"/>
+      <c r="C273" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D273" s="5">
+        <v>1</v>
+      </c>
+      <c r="E273" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F273" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A274" s="3">
+        <v>273</v>
+      </c>
+      <c r="B274" s="4"/>
+      <c r="C274" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D274" s="5">
+        <v>1</v>
+      </c>
+      <c r="E274" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F274" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A275" s="3">
+        <v>274</v>
+      </c>
+      <c r="B275" s="4"/>
+      <c r="C275" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="D275" s="5">
+        <v>421.45</v>
+      </c>
+      <c r="E275" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F275" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A276" s="3">
+        <v>275</v>
+      </c>
+      <c r="B276" s="4"/>
+      <c r="C276" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="D276" s="5">
+        <v>18</v>
+      </c>
+      <c r="E276" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F276" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A277" s="3">
+        <v>276</v>
+      </c>
+      <c r="B277" s="4"/>
+      <c r="C277" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D277" s="5">
+        <v>18</v>
+      </c>
+      <c r="E277" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F277" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A278" s="3">
+        <v>277</v>
+      </c>
+      <c r="B278" s="4"/>
+      <c r="C278" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="D278" s="5">
+        <v>36</v>
+      </c>
+      <c r="E278" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F278" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A279" s="3">
+        <v>278</v>
+      </c>
+      <c r="B279" s="4"/>
+      <c r="C279" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D279" s="5">
         <v>20</v>
       </c>
-      <c r="E263" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F263" s="4" t="s">
-        <v>97</v>
+      <c r="E279" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F279" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A280" s="3">
+        <v>279</v>
+      </c>
+      <c r="B280" s="4"/>
+      <c r="C280" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D280" s="5">
+        <v>1</v>
+      </c>
+      <c r="E280" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F280" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A281" s="3">
+        <v>280</v>
+      </c>
+      <c r="B281" s="4"/>
+      <c r="C281" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D281" s="5">
+        <v>2E-3</v>
+      </c>
+      <c r="E281" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F281" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A282" s="3">
+        <v>281</v>
+      </c>
+      <c r="B282" s="4"/>
+      <c r="C282" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D282" s="5">
+        <v>1</v>
+      </c>
+      <c r="E282" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F282" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A283" s="3">
+        <v>282</v>
+      </c>
+      <c r="B283" s="4"/>
+      <c r="C283" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D283" s="5">
+        <v>90</v>
+      </c>
+      <c r="E283" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F283" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A284" s="3">
+        <v>283</v>
+      </c>
+      <c r="B284" s="4"/>
+      <c r="C284" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="D284" s="5">
+        <v>47.4</v>
+      </c>
+      <c r="E284" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F284" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A285" s="3">
+        <v>284</v>
+      </c>
+      <c r="B285" s="4"/>
+      <c r="C285" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="D285" s="5">
+        <v>40.5</v>
+      </c>
+      <c r="E285" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F285" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A286" s="3">
+        <v>285</v>
+      </c>
+      <c r="B286" s="4"/>
+      <c r="C286" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="D286" s="5">
+        <v>33.15</v>
+      </c>
+      <c r="E286" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F286" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A287" s="3">
+        <v>286</v>
+      </c>
+      <c r="B287" s="4"/>
+      <c r="C287" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D287" s="5">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="E287" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F287" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A288" s="3">
+        <v>287</v>
+      </c>
+      <c r="B288" s="4"/>
+      <c r="C288" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="D288" s="5">
+        <v>6</v>
+      </c>
+      <c r="E288" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F288" s="4" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356C1355-6F79-4D95-BA63-D663EFE1D5B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0C5A70-BF0C-43FA-8CC1-29801BCBDF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4110" yWindow="4110" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="232">
   <si>
     <t>№ п/п</t>
   </si>
@@ -45,6 +45,9 @@
     <t>Примечание</t>
   </si>
   <si>
+    <t>Дверь правая с довод 2000х1000 мм (ВхШ) полотно RAL 9003 (белый)/ коробка (RAL 9003) (белый) с цепь.</t>
+  </si>
+  <si>
     <t>шт</t>
   </si>
   <si>
@@ -54,18 +57,15 @@
     <t>Окно 1200х1100 мм / ПВХ-профили морозост. исп, RAL 7036 серый</t>
   </si>
   <si>
-    <t>Дверь правая с довод 2000х1000 мм (ВхШ) полотно RAL 9003 (белый)/ коробка (RAL 9003) (белый) с цепь.</t>
+    <t>кг</t>
+  </si>
+  <si>
+    <t>ИИУП-000346</t>
   </si>
   <si>
     <t>Труба 76x8,0 ГОСТ 8732-78/09Г2С ГОСТ 8731-74</t>
   </si>
   <si>
-    <t>кг</t>
-  </si>
-  <si>
-    <t>ИИУП-000346</t>
-  </si>
-  <si>
     <t>Шлагбаум "AN-Motors"</t>
   </si>
   <si>
@@ -105,9 +105,6 @@
     <t>ИИУП-000434</t>
   </si>
   <si>
-    <t>ИИУП-000438</t>
-  </si>
-  <si>
     <t>Колеровачный аппарат</t>
   </si>
   <si>
@@ -123,72 +120,75 @@
     <t>Сварочный аппарат</t>
   </si>
   <si>
+    <t>Печать с автоматической оснасткой</t>
+  </si>
+  <si>
+    <t>НТУП-018372</t>
+  </si>
+  <si>
     <t>Печать</t>
   </si>
   <si>
-    <t>НТУП-018372</t>
-  </si>
-  <si>
-    <t>Печать с автоматической оснасткой</t>
-  </si>
-  <si>
     <t>Печать ИПП НТ</t>
   </si>
   <si>
+    <t>Кашкороб/0201/400х400х610/Т23В/ММ/КК/4+0/мат.лам.</t>
+  </si>
+  <si>
+    <t>(не исп) шт</t>
+  </si>
+  <si>
+    <t>Кашкороб/0203/300х200х400/Т23/ММ/КК/4+0/мат.лам</t>
+  </si>
+  <si>
+    <t>печать брошюр</t>
+  </si>
+  <si>
+    <t>Кашкороб/0427/405х225х80/Т23В/ММ/КК/4+0/мат.лам.</t>
+  </si>
+  <si>
     <t>Кашкороб/0427/340х160х60/Т23В/ММ/КК/4+0/мат.лам</t>
   </si>
   <si>
-    <t>(не исп) шт</t>
-  </si>
-  <si>
-    <t>Кашкороб/0427/405х225х80/Т23В/ММ/КК/4+0/мат.лам.</t>
-  </si>
-  <si>
     <t>Доп. услуги по обеспечению спецоснасткой</t>
   </si>
   <si>
-    <t>Кашкороб/0201/400х400х610/Т23В/ММ/КК/4+0/мат.лам.</t>
-  </si>
-  <si>
-    <t>Кашкороб/0203/300х200х400/Т23/ММ/КК/4+0/мат.лам</t>
-  </si>
-  <si>
-    <t>печать брошюр</t>
+    <t>Пена монтажная /шт/</t>
+  </si>
+  <si>
+    <t>ИИ00-000013</t>
+  </si>
+  <si>
+    <t>Маркер по металлу черный тонкий</t>
+  </si>
+  <si>
+    <t>Маркер по металлу белый</t>
+  </si>
+  <si>
+    <t>Ветошь /рул./</t>
+  </si>
+  <si>
+    <t>Фонарик налобный аккумуляторный</t>
+  </si>
+  <si>
+    <t>Изолента</t>
+  </si>
+  <si>
+    <t>Ключ комбинир. 24 мм</t>
+  </si>
+  <si>
+    <t>Ключ комбинир. 30 мм</t>
+  </si>
+  <si>
+    <t>Ключ комбинир. 36 мм</t>
+  </si>
+  <si>
+    <t>Кувалда 1 кг</t>
   </si>
   <si>
     <t>Штангенциркуль</t>
   </si>
   <si>
-    <t>ИИ00-000013</t>
-  </si>
-  <si>
-    <t>Кувалда 1 кг</t>
-  </si>
-  <si>
-    <t>Ключ комбинир. 36 мм</t>
-  </si>
-  <si>
-    <t>Ключ комбинир. 30 мм</t>
-  </si>
-  <si>
-    <t>Пена монтажная /шт/</t>
-  </si>
-  <si>
-    <t>Маркер по металлу черный тонкий</t>
-  </si>
-  <si>
-    <t>Ключ комбинир. 24 мм</t>
-  </si>
-  <si>
-    <t>Изолента</t>
-  </si>
-  <si>
-    <t>Фонарик налобный аккумуляторный</t>
-  </si>
-  <si>
-    <t>Маркер по металлу белый</t>
-  </si>
-  <si>
     <t>Дождевик-костюм темно-синий 52-54</t>
   </si>
   <si>
@@ -201,15 +201,6 @@
     <t>Рулетка  5м х 25мм Компакт в обрезиненном корпусе</t>
   </si>
   <si>
-    <t>Ветошь /рул./</t>
-  </si>
-  <si>
-    <t>Станок</t>
-  </si>
-  <si>
-    <t>ИИУП-000467</t>
-  </si>
-  <si>
     <t>ИИ00-000065</t>
   </si>
   <si>
@@ -219,207 +210,303 @@
     <t>ИИУП-000472</t>
   </si>
   <si>
+    <t>Вентиль игольчатый ВИ-160</t>
+  </si>
+  <si>
+    <t>НТУП-018427</t>
+  </si>
+  <si>
+    <t>Клапан магниторегулируемый КМР-2М-Ех в сборе НТ.293.000.000 (Тройник ТР)</t>
+  </si>
+  <si>
+    <t>Счетчик-расходомер вихревой ЭРВИП.НТ 80/65Ф с датчиком давления 018М</t>
+  </si>
+  <si>
+    <t>Знак безопасности F11</t>
+  </si>
+  <si>
+    <t>Знак безопасности F10</t>
+  </si>
+  <si>
+    <t>Заглушка кабельного ввода М22 взрывозащищенная EXD</t>
+  </si>
+  <si>
+    <t>Термоусадочная трубка 30/15 черная</t>
+  </si>
+  <si>
+    <t>Извещатель пожарный</t>
+  </si>
+  <si>
+    <t>Извещатель пожарный тепловой взрывозащищенный 101-07е 1Ex db [ia Ga] IIC Т4 Gb Х IP66</t>
+  </si>
+  <si>
+    <t>Термопреобразователь</t>
+  </si>
+  <si>
+    <t>Преобразователь избыточного давления Метран 75G,взрывозащита 0Ex ia IIC T4 Ga X,IP66,4-20+HART</t>
+  </si>
+  <si>
+    <t>Газоанализатор СГОЭС-2 с калибровкой на метан (порог1-10%, порог2-40%)</t>
+  </si>
+  <si>
+    <t>Металлорукав в ПВХ-оболочке РЗ-ЦП-15 ( ДУ20 изолированный, оц.сталь)</t>
+  </si>
+  <si>
+    <t>м</t>
+  </si>
+  <si>
+    <t>Кабель кввгэнг(А)-LS 4*1</t>
+  </si>
+  <si>
+    <t>Кабель КВВГЭнг(А)-LS 7*1</t>
+  </si>
+  <si>
     <t>Кабель КПСЭнг(А)-FRlS 2х2х0.75 для ОПС</t>
   </si>
   <si>
-    <t>м</t>
-  </si>
-  <si>
-    <t>НТУП-018427</t>
+    <t>Кабель КПСЭнг (А) FRLS 1*2*0.75</t>
   </si>
   <si>
     <t>Труба гофрированная ПВХ 20</t>
   </si>
   <si>
-    <t>Кабель КПСЭнг (А) FRLS 1*2*0.75</t>
-  </si>
-  <si>
-    <t>Металлорукав в ПВХ-оболочке РЗ-ЦП-15 ( ДУ20 изолированный, оц.сталь)</t>
-  </si>
-  <si>
-    <t>Кабель кввгэнг(А)-LS 4*1</t>
-  </si>
-  <si>
-    <t>Клапан магниторегулируемый КМР-2М-Ех в сборе НТ.293.000.000 (Тройник ТР)</t>
-  </si>
-  <si>
-    <t>Счетчик-расходомер вихревой ЭРВИП.НТ 80/65Ф с датчиком давления 018М</t>
-  </si>
-  <si>
-    <t>Знак безопасности F11</t>
-  </si>
-  <si>
-    <t>Знак безопасности F10</t>
-  </si>
-  <si>
-    <t>Заглушка кабельного ввода М22 взрывозащищенная EXD</t>
-  </si>
-  <si>
-    <t>Термоусадочная трубка 30/15 черная</t>
-  </si>
-  <si>
-    <t>Извещатель пожарный</t>
-  </si>
-  <si>
-    <t>Кабель КВВГЭнг(А)-LS 7*1</t>
-  </si>
-  <si>
-    <t>Термопреобразователь</t>
-  </si>
-  <si>
-    <t>Преобразователь избыточного давления Метран 75G,взрывозащита 0Ex ia IIC T4 Ga X,IP66,4-20+HART</t>
-  </si>
-  <si>
-    <t>Газоанализатор СГОЭС-2 с калибровкой на метан (порог1-10%, порог2-40%)</t>
-  </si>
-  <si>
-    <t>Вентиль игольчатый ВИ-160</t>
-  </si>
-  <si>
-    <t>Извещатель пожарный тепловой взрывозащищенный 101-07е 1Ex db [ia Ga] IIC Т4 Gb Х IP66</t>
-  </si>
-  <si>
-    <t>ИИУП-000484</t>
+    <t>ИИ00-000017</t>
+  </si>
+  <si>
+    <t>Маркер по металлу красный</t>
+  </si>
+  <si>
+    <t>Мел сварщика белый</t>
+  </si>
+  <si>
+    <t>Паронит 2мм</t>
+  </si>
+  <si>
+    <t>лист</t>
   </si>
   <si>
     <t>Паронит 3 мм</t>
   </si>
   <si>
-    <t>лист</t>
-  </si>
-  <si>
-    <t>ИИ00-000017</t>
-  </si>
-  <si>
     <t>Ключи обмедненные</t>
   </si>
   <si>
     <t>набор</t>
   </si>
   <si>
-    <t>Паронит 2мм</t>
-  </si>
-  <si>
-    <t>Маркер по металлу красный</t>
-  </si>
-  <si>
-    <t>Мел сварщика белый</t>
-  </si>
-  <si>
-    <t>Пломба пластиковая номерная 220мм</t>
-  </si>
-  <si>
-    <t>ИИУП-000486</t>
-  </si>
-  <si>
     <t>Погрузчик ПЛ-0.4</t>
   </si>
   <si>
     <t>ИИУП-000489</t>
   </si>
   <si>
-    <t>Углошлифовальная машина Makita 9069  2000Bт 6600 об/мин 230мм</t>
-  </si>
-  <si>
-    <t>ИИУП-000493</t>
-  </si>
-  <si>
-    <t>Угольник столярный 40см</t>
-  </si>
-  <si>
-    <t>Рулетка  7,5м х 25мм обрезиненный корпус</t>
-  </si>
-  <si>
-    <t>Рулетка измерительная 10 м</t>
-  </si>
-  <si>
-    <t>Очки защитные JL-D015 (прозрачные)</t>
-  </si>
-  <si>
-    <t>Наушники защитные</t>
-  </si>
-  <si>
-    <t>Прожектор светодиодный 100W LED FL5 ECON</t>
-  </si>
-  <si>
-    <t>Перчатки 5нит. 10кл. (черные) (пара)</t>
-  </si>
-  <si>
-    <t>Угловая шлифмашина Makita GA5030R, ф125мм, 720Вт, 11000об\м</t>
-  </si>
-  <si>
-    <t>Прямошлифовальная машина Makita GD 0602</t>
-  </si>
-  <si>
-    <t>Угольник стальной</t>
-  </si>
-  <si>
-    <t>Уровень магнитный</t>
-  </si>
-  <si>
-    <t>Краги сварщика спилковые</t>
-  </si>
-  <si>
-    <t>Удлинитель силовой 3-розетки, 20-метров</t>
-  </si>
-  <si>
-    <t>Молоток шлакоотбойный</t>
-  </si>
-  <si>
-    <t>Удлинитель 380В 10м</t>
-  </si>
-  <si>
-    <t>Рулетка  3м х 16мм обрезиненный корпус (3 фиксатора, зацеп с магнитом)</t>
+    <t>ИИУП-000499</t>
+  </si>
+  <si>
+    <t>Сапоги зимние</t>
+  </si>
+  <si>
+    <t>пар</t>
+  </si>
+  <si>
+    <t>НТУП-018437</t>
+  </si>
+  <si>
+    <t>Шапка трикотажная зимняя</t>
+  </si>
+  <si>
+    <t>Костюм утепленный Метель</t>
+  </si>
+  <si>
+    <t>ИИУП-000501</t>
+  </si>
+  <si>
+    <t>Доска обрезная 30*150*6м (м3)</t>
+  </si>
+  <si>
+    <t>м3</t>
+  </si>
+  <si>
+    <t>КИУП-000452</t>
+  </si>
+  <si>
+    <t>ИИУП-000502</t>
+  </si>
+  <si>
+    <t>Ботинки кожаные с защитным подноском. Размер 42</t>
+  </si>
+  <si>
+    <t>НТУП-018438</t>
+  </si>
+  <si>
+    <t>спец одежда летняя</t>
+  </si>
+  <si>
+    <t>зимняя спецодежда (ИТР)</t>
+  </si>
+  <si>
+    <t>Каска защитная СОМ3-55 FavoriT белая</t>
+  </si>
+  <si>
+    <t>Каска защитная СОМ3-55 FavoriT оранжевая</t>
+  </si>
+  <si>
+    <t>Ботинки кожаные с защитным подноском. Размер 46</t>
+  </si>
+  <si>
+    <t>Ботинки кожаные с защитным подноском. Размер 41</t>
+  </si>
+  <si>
+    <t>Ботинки кожаные с защитным подноском. Размер 44</t>
+  </si>
+  <si>
+    <t>Ботинки кожаные с защитным подноском. Размер 40</t>
+  </si>
+  <si>
+    <t>Ботинки кожаные с защитным подноском. Размер 45</t>
+  </si>
+  <si>
+    <t>Ботинки кожаные с защитным подноском. Размер 39</t>
+  </si>
+  <si>
+    <t>Ботинки кожаные с защитным подноском. Размер 36</t>
+  </si>
+  <si>
+    <t>Ботинки кожаные с защитным подноском. Размер 38</t>
+  </si>
+  <si>
+    <t>Ботинки кожаные с защитным подноском. Размер 43</t>
+  </si>
+  <si>
+    <t>Карман инструментального магазина, пластиковый TSG-607-00 (ВТ-40)</t>
+  </si>
+  <si>
+    <t>ИИУП-000503</t>
+  </si>
+  <si>
+    <t>ИИУП-000504</t>
+  </si>
+  <si>
+    <t>ИИУП-000505</t>
+  </si>
+  <si>
+    <t>Труба D89х12 Ст.09Г2 ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Труба D720х18 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-73</t>
+  </si>
+  <si>
+    <t>Труба D720х12 09Г2С ГОСТ 10705-80</t>
+  </si>
+  <si>
+    <t>ИИУП-000506</t>
+  </si>
+  <si>
+    <t>Днище 720х18-09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>ИИУП-000507</t>
+  </si>
+  <si>
+    <t>л (дм3)</t>
+  </si>
+  <si>
+    <t>Фланец х-150-63 ГОСТ 12821 (заготовка-поковка Ст.09Г2С гр.IV КП195 ГОСТ 8479-70)</t>
+  </si>
+  <si>
+    <t>ИИУП-000511</t>
+  </si>
+  <si>
+    <t>Фланец</t>
+  </si>
+  <si>
+    <t>Фланец 7-100-63 ГОСТ 12821 (заготовка-поковка Ст.09Г2С гр.IV КП195 ГОСТ 8479-70)</t>
+  </si>
+  <si>
+    <t>ИИУП-000513</t>
+  </si>
+  <si>
+    <t>ИИУП-000514</t>
+  </si>
+  <si>
+    <t>Лист S=0.5*300*600 Алюминий аннодированный матовый 2033-1 (черн/бел)</t>
+  </si>
+  <si>
+    <t>Хомут 60-В Ст.3сп-Ц9.хр. ГОСТ 24137-80 (оц)</t>
+  </si>
+  <si>
+    <t>ИИУП-000515</t>
+  </si>
+  <si>
+    <t>Хомут 90-В Ст.3сп-Ц9.хр. ГОСТ 24137-80</t>
+  </si>
+  <si>
+    <t>Хомут 110-Ст3сп-Ц9.хр ГОСТ 24137-80</t>
+  </si>
+  <si>
+    <t>ИИУП-000517</t>
+  </si>
+  <si>
+    <t>Отвод</t>
+  </si>
+  <si>
+    <t>Отвод 60-57х5-09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>ИИУП-000520</t>
+  </si>
+  <si>
+    <t>ЛГУП-8173</t>
+  </si>
+  <si>
+    <t>Дверь лев с доводчиком1900х1000 мм(ВхШ) полотно RAL9003(белый)/коробка (RAL 9003)(белый)с цепью</t>
   </si>
   <si>
     <t>Дверь левс доводчиком2000х1000мм(ВхШ) полотно RAL 9003(белый)/коробка(RAL 9003)(белый)с цепью</t>
   </si>
   <si>
-    <t>Дверь лев с доводчиком1900х1000 мм(ВхШ) полотно RAL9003(белый)/коробка (RAL 9003)(белый)с цепью</t>
+    <t>Труба D820х12 ст.09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D89х8 ГОСТ 872-78 В 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D159х8 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
   </si>
   <si>
     <t>Труба D530х12 09Г2С ГОСТ 8731-74</t>
   </si>
   <si>
-    <t>Труба D159х8 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D89х8 ГОСТ 872-78 В 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D820х12 ст.09Г2С ГОСТ 8731-74</t>
+    <t>Задвижка клиновая литая ЗКЛ 80-40 УХЛ1 30лс15нж, класс герм.А (ряд 2, исп.фл.3)</t>
   </si>
   <si>
     <t>Задвижка клиновая литая 3КЛ 80-63 ХЛ1 30лс76нж, класс герметичности "А" (Р-Р-2 исп.фл.J)</t>
   </si>
   <si>
-    <t>Задвижка клиновая литая ЗКЛ 80-40 УХЛ1 30лс15нж, класс герм.А (ряд 2, исп.фл.3)</t>
-  </si>
-  <si>
     <t>Круг D370 Ст.20 ГОСТ1050-88</t>
   </si>
   <si>
+    <t>Фланец 2-50-40 09Г2С ГОСТ 12821-80</t>
+  </si>
+  <si>
     <t>Фланец 1-250-40 09Г2С ГОСТ 12821-80</t>
   </si>
   <si>
-    <t>Фланец 2-50-40 09Г2С ГОСТ 12821-80</t>
+    <t>Шпонка 6х6х20 ГОСТ 23360-78</t>
+  </si>
+  <si>
+    <t>Шплинт 2х20 ГОСТ 397</t>
+  </si>
+  <si>
+    <t>Шпилька АМ30-6gх180.60.35.III.4.019 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Гайка М8-6Н.5.ГОСТ 5915-70</t>
   </si>
   <si>
     <t>Болт М20-6gх30.58 (S30) ГОСТ 7798-70</t>
   </si>
   <si>
-    <t>Гайка М8-6Н.5.ГОСТ 5915-70</t>
-  </si>
-  <si>
-    <t>Шпилька АМ30-6gх180.60.35.III.4.019 ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Шплинт 2х20 ГОСТ 397</t>
-  </si>
-  <si>
-    <t>Шпонка 6х6х20 ГОСТ 23360-78</t>
-  </si>
-  <si>
     <t>Шпилька М8х350, кл.пр. 8.8, оц</t>
   </si>
   <si>
@@ -432,58 +519,208 @@
     <t>Гайка М10-6Н ГОСТ 5927-70 (размер под ключ S=17)</t>
   </si>
   <si>
+    <t>Шайба 10.02.019 ГОСТ 11371-78</t>
+  </si>
+  <si>
     <t>Винт В2.М6-6gх8.48.016 ГОСТ 17475-80</t>
   </si>
   <si>
-    <t>Шайба 10.02.019 ГОСТ 11371-78</t>
-  </si>
-  <si>
-    <t>Лист Б-ПН-12 ГОСТ 19903-74 / Ст. 09Г2С К52 ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Лист Б-ПН-4,0 ГОСТ 19903-74 / Ст.3пс4 ГОСТ 14637-89</t>
-  </si>
-  <si>
     <t>Блок электронный BP15C</t>
   </si>
   <si>
+    <t>Пост кнопочный взрывозащищенный ПВК-25 (вентилятор)</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
+  </si>
+  <si>
+    <t>Резьбовой крепежный элемент с наружной резьбой РКН-15 (ММРн-15)</t>
+  </si>
+  <si>
+    <t>Извещатель пожарный ручной ИПР 535-25Г IP67</t>
+  </si>
+  <si>
+    <t>Извещатель пожарный ручной взрывозащищенный ИП 535-07е 1ExdbIICT6Gb, IP67</t>
+  </si>
+  <si>
+    <t>Оповещатель светозвуковой взрывозащ. ВС-07е-И 1ExdIICT6, IP66, 12-24В, -60..+70С</t>
+  </si>
+  <si>
+    <t>Преобразователь избыточного давления Метран 150TG 3(0...6,0)МПа 2G 2 1 A M5 IM К17</t>
+  </si>
+  <si>
+    <t>Пост аварийной сигнализации загазованности в/защ.ПАСВ1-П-75-1Ж1К-В1 (=24В, -60..+40С) 1ExsIICT6</t>
+  </si>
+  <si>
     <t>Металлорукав в ПВХ изоляции РЗ-ЦП-15</t>
   </si>
   <si>
     <t>Трубка ПВХ гибкая, гофрированная 16 мм</t>
   </si>
   <si>
-    <t>Пост кнопочный взрывозащищенный ПВК-25 (вентилятор)</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с внутренней резьбой Ркв-15</t>
-  </si>
-  <si>
-    <t>Резьбовой крепежный элемент с наружной резьбой РКН-15 (ММРн-15)</t>
-  </si>
-  <si>
-    <t>Извещатель пожарный ручной ИПР 535-25Г IP67</t>
-  </si>
-  <si>
-    <t>Оповещатель светозвуковой взрывозащ. ВС-07е-И 1ExdIICT6, IP66, 12-24В, -60..+70С</t>
-  </si>
-  <si>
-    <t>Извещатель пожарный ручной взрывозащищенный ИП 535-07е 1ExdbIICT6Gb, IP67</t>
-  </si>
-  <si>
-    <t>Преобразователь избыточного давления Метран 150TG 3(0...6,0)МПа 2G 2 1 A M5 IM К17</t>
-  </si>
-  <si>
-    <t>Пост аварийной сигнализации загазованности в/защ.ПАСВ1-П-75-1Ж1К-В1 (=24В, -60..+40С) 1ExsIICT6</t>
-  </si>
-  <si>
     <t>Фумлента</t>
   </si>
   <si>
     <t>Краскопульт с верх. бачком S900-P d=2мм в блистере  (Русский Мастер) (20)</t>
   </si>
   <si>
+    <t>Панель стеновая ПТСМ 2450х1000х80 RAL 1021 (желт) снаружи/ RAL 9003 (белый) внутри</t>
+  </si>
+  <si>
+    <t>Шпилька А1М36-6gx220.09Г2С (оцинк.) ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Гайка М16-6Н.8.20.019 ГОСТ 15523-70</t>
+  </si>
+  <si>
+    <t>Гайка АМ36-6Н.20lll.019 ГОСТ 9064-75</t>
+  </si>
+  <si>
+    <t>Труба D25х7 ст.10Г2 ГОСТ 8733-74</t>
+  </si>
+  <si>
+    <t>Труба D219х4 ГОСТ 8734-75/ Ст.В20 ГОСТ 8733-74</t>
+  </si>
+  <si>
+    <t>Швеллер №20У ГОСТ 8240-97/ 325-09Г2С ГОСТ 19281-2014</t>
+  </si>
+  <si>
+    <t>Труба D377х12 ст.09Г2С-К50 ГОСТ 8731-78</t>
+  </si>
+  <si>
+    <t>Труба D89х6 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D68х12 ст.265-09Г2С-4 ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Труба D38х9 Ст.09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Днище 720х12-09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Днище 377-12-16ГС ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Днище 219х4-25 ст.20 ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Днище 377х12-09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Крышка НТ.ЕС.040.001.003 А (Заглушка 2-450-4,0-092ГС АТК 24.200.02-90)</t>
+  </si>
+  <si>
+    <t>Скотч широкий</t>
+  </si>
+  <si>
+    <t>Растворитель Р-4 ГОСТ 7827-74</t>
+  </si>
+  <si>
+    <t>Фланец х-80-63 ГОСТ 12821 (заготовка-поковка Ст.09Г2С гр.IV КП195 ГОСТ 8479-70)</t>
+  </si>
+  <si>
+    <t>Фланец х-50-63 ГОСТ 12821 (заготовка-поковка Ст.09Г2С  гр.IV КП195 ГОСТ 8479-70)</t>
+  </si>
+  <si>
+    <t>Фланец 80-40-11-1-E-09Г2С ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 50-16-11-1-Е-09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 3-450-40 09Г2С ГОСТ 12815-80 (из поковки гр.IV КП 245 ГОСТ 8479-70)</t>
+  </si>
+  <si>
+    <t>Заглушка 159х10 ст.09Г2С ГОСТ 17379-01</t>
+  </si>
+  <si>
+    <t>Заглушка 4-250-6,3-13ХФА АТК 24.200.02.90</t>
+  </si>
+  <si>
+    <t>Отвод 45-89х8-09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Отвод 90-159х10-09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Отвод 90-57х6 09Г2С ГОСТ 17375-01</t>
+  </si>
+  <si>
+    <t>Отвод 90-89х8 Ст.09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Тройник 159х10 ст.09Г2С ГОСТ 17376-01</t>
+  </si>
+  <si>
+    <t>Тройник 89х8 ст.09Г2С ГОСТ 17376-2001</t>
+  </si>
+  <si>
+    <t>Переход 89х8-57х5 ст.09Г2С ГОСТ 17378-2001</t>
+  </si>
+  <si>
+    <t>Круг D240 ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Круг D450 Ст.09Г2С ГОСТ 2590-2006</t>
+  </si>
+  <si>
+    <t>Лист S=10 ГОСТ19903-74/Ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Лист S=2 ОК360В-4-III-Ст.3кп ГОСТ 16523-97</t>
+  </si>
+  <si>
+    <t>Лист S=3,0 ГОСТ 19903-74/09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Лист ромб. О-ПН-4,0 Ст.09Г2С ГОСТ 8568-77</t>
+  </si>
+  <si>
+    <t>Круг D165 09Г2С-8-ТО ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Круг D10 ГОСТ 2590-2006/ Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Переход 159х8-108х8 ст.09Г2С ГОСТ 17378-01</t>
+  </si>
+  <si>
+    <t>Тройник 89х6 ст.09Г2С ГОСТ 17376-2001</t>
+  </si>
+  <si>
+    <t>Тройник 159х8 09Г2С ГОСТ 17376-2001</t>
+  </si>
+  <si>
+    <t>Тройник 57х5 09Г2С ГОСТ 17376-2001</t>
+  </si>
+  <si>
+    <t>Переход 89х8-76х8 ст. 09Г2С ГОСТ 17378-01</t>
+  </si>
+  <si>
+    <t>Переход К-89х6-57х6-09Г2С ГОСТ 17378</t>
+  </si>
+  <si>
+    <t>Отвод 90-108х8 ст.09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Отвод 45-57х6 09Г2С ГОСТ 17375-01</t>
+  </si>
+  <si>
+    <t>Отвод 90-89х6-09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Отвод 60-89х6-09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Отвод 45-89х6-09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
     <t>MV-клемма проводника Rd8</t>
+  </si>
+  <si>
+    <t>Пленка термоусадочная Magnapak белая (ширина 9,8 м, толщина 190 мкм)</t>
   </si>
 </sst>
 </file>
@@ -920,12 +1157,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F201"/>
+  <dimension ref="A1:F268"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="46.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="74.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="74.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
@@ -957,16 +1194,16 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="8" t="s">
-        <v>115</v>
+        <v>6</v>
       </c>
       <c r="D2" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -975,16 +1212,16 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="8" t="s">
-        <v>116</v>
+        <v>9</v>
       </c>
       <c r="D3" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -993,16 +1230,16 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="D4" s="5">
-        <v>6</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1011,16 +1248,16 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="8" t="s">
-        <v>9</v>
+        <v>145</v>
       </c>
       <c r="D5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1029,16 +1266,16 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="5">
+        <v>5.7389999999999999</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="5">
-        <v>495.19799999999998</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1047,16 +1284,16 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="D7" s="7">
-        <v>2912.7</v>
+        <v>12</v>
+      </c>
+      <c r="D7" s="5">
+        <v>495.19799999999998</v>
       </c>
       <c r="E7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1065,16 +1302,16 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="8" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="D8" s="7">
-        <v>2323.62</v>
+        <v>1438.2</v>
       </c>
       <c r="E8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1083,16 +1320,16 @@
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="8" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="D9" s="7">
-        <v>1438.2</v>
+        <v>2323.62</v>
       </c>
       <c r="E9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1101,16 +1338,16 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="D10" s="5">
-        <v>5.7389999999999999</v>
+        <v>149</v>
+      </c>
+      <c r="D10" s="7">
+        <v>2912.7</v>
       </c>
       <c r="E10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1140,10 +1377,10 @@
         <v>16</v>
       </c>
       <c r="D12" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>17</v>
@@ -1158,10 +1395,10 @@
         <v>16</v>
       </c>
       <c r="D13" s="5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>17</v>
@@ -1176,10 +1413,10 @@
         <v>16</v>
       </c>
       <c r="D14" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>17</v>
@@ -1194,10 +1431,10 @@
         <v>16</v>
       </c>
       <c r="D15" s="5">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>17</v>
@@ -1212,10 +1449,10 @@
         <v>16</v>
       </c>
       <c r="D16" s="5">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>17</v>
@@ -1230,10 +1467,10 @@
         <v>16</v>
       </c>
       <c r="D17" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>17</v>
@@ -1248,10 +1485,10 @@
         <v>16</v>
       </c>
       <c r="D18" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>17</v>
@@ -1266,10 +1503,10 @@
         <v>16</v>
       </c>
       <c r="D19" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>17</v>
@@ -1284,10 +1521,10 @@
         <v>16</v>
       </c>
       <c r="D20" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>17</v>
@@ -1302,10 +1539,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>17</v>
@@ -1320,10 +1557,10 @@
         <v>16</v>
       </c>
       <c r="D22" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>17</v>
@@ -1341,7 +1578,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>17</v>
@@ -1356,10 +1593,10 @@
         <v>16</v>
       </c>
       <c r="D24" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>17</v>
@@ -1377,7 +1614,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>17</v>
@@ -1392,10 +1629,10 @@
         <v>16</v>
       </c>
       <c r="D26" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>17</v>
@@ -1407,13 +1644,13 @@
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D27" s="5">
         <v>1</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>17</v>
@@ -1428,10 +1665,10 @@
         <v>16</v>
       </c>
       <c r="D28" s="5">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>17</v>
@@ -1446,10 +1683,10 @@
         <v>16</v>
       </c>
       <c r="D29" s="5">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>17</v>
@@ -1464,10 +1701,10 @@
         <v>16</v>
       </c>
       <c r="D30" s="5">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>17</v>
@@ -1482,10 +1719,10 @@
         <v>16</v>
       </c>
       <c r="D31" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>17</v>
@@ -1503,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>17</v>
@@ -1518,10 +1755,10 @@
         <v>16</v>
       </c>
       <c r="D33" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>17</v>
@@ -1536,10 +1773,10 @@
         <v>16</v>
       </c>
       <c r="D34" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>17</v>
@@ -1557,7 +1794,7 @@
         <v>1</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>17</v>
@@ -1575,7 +1812,7 @@
         <v>1</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>17</v>
@@ -1593,7 +1830,7 @@
         <v>6</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>17</v>
@@ -1611,7 +1848,7 @@
         <v>1</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>17</v>
@@ -1629,7 +1866,7 @@
         <v>1</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>17</v>
@@ -1644,10 +1881,10 @@
         <v>16</v>
       </c>
       <c r="D40" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>17</v>
@@ -1662,10 +1899,10 @@
         <v>16</v>
       </c>
       <c r="D41" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>17</v>
@@ -1683,7 +1920,7 @@
         <v>1</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>17</v>
@@ -1701,7 +1938,7 @@
         <v>2</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>17</v>
@@ -1716,10 +1953,10 @@
         <v>16</v>
       </c>
       <c r="D44" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>17</v>
@@ -1734,10 +1971,10 @@
         <v>16</v>
       </c>
       <c r="D45" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>17</v>
@@ -1752,10 +1989,10 @@
         <v>16</v>
       </c>
       <c r="D46" s="5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>17</v>
@@ -1770,10 +2007,10 @@
         <v>16</v>
       </c>
       <c r="D47" s="5">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>17</v>
@@ -1788,10 +2025,10 @@
         <v>16</v>
       </c>
       <c r="D48" s="5">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>17</v>
@@ -1806,10 +2043,10 @@
         <v>16</v>
       </c>
       <c r="D49" s="5">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>17</v>
@@ -1821,13 +2058,13 @@
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D50" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>17</v>
@@ -1845,7 +2082,7 @@
         <v>1</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>17</v>
@@ -1860,10 +2097,10 @@
         <v>16</v>
       </c>
       <c r="D52" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>17</v>
@@ -1878,10 +2115,10 @@
         <v>16</v>
       </c>
       <c r="D53" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>17</v>
@@ -1896,10 +2133,10 @@
         <v>16</v>
       </c>
       <c r="D54" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>17</v>
@@ -1914,10 +2151,10 @@
         <v>16</v>
       </c>
       <c r="D55" s="5">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>17</v>
@@ -1932,10 +2169,10 @@
         <v>16</v>
       </c>
       <c r="D56" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>17</v>
@@ -1950,10 +2187,10 @@
         <v>16</v>
       </c>
       <c r="D57" s="5">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>17</v>
@@ -1968,10 +2205,10 @@
         <v>16</v>
       </c>
       <c r="D58" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>17</v>
@@ -1986,10 +2223,10 @@
         <v>16</v>
       </c>
       <c r="D59" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>17</v>
@@ -2004,10 +2241,10 @@
         <v>16</v>
       </c>
       <c r="D60" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>17</v>
@@ -2022,10 +2259,10 @@
         <v>16</v>
       </c>
       <c r="D61" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>17</v>
@@ -2040,10 +2277,10 @@
         <v>16</v>
       </c>
       <c r="D62" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>17</v>
@@ -2058,10 +2295,10 @@
         <v>16</v>
       </c>
       <c r="D63" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>17</v>
@@ -2076,10 +2313,10 @@
         <v>16</v>
       </c>
       <c r="D64" s="5">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>17</v>
@@ -2097,7 +2334,7 @@
         <v>2</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>17</v>
@@ -2112,10 +2349,10 @@
         <v>16</v>
       </c>
       <c r="D66" s="5">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>17</v>
@@ -2130,10 +2367,10 @@
         <v>16</v>
       </c>
       <c r="D67" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>17</v>
@@ -2148,10 +2385,10 @@
         <v>16</v>
       </c>
       <c r="D68" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>17</v>
@@ -2166,10 +2403,10 @@
         <v>16</v>
       </c>
       <c r="D69" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>17</v>
@@ -2184,10 +2421,10 @@
         <v>16</v>
       </c>
       <c r="D70" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>17</v>
@@ -2202,10 +2439,10 @@
         <v>16</v>
       </c>
       <c r="D71" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>17</v>
@@ -2220,10 +2457,10 @@
         <v>16</v>
       </c>
       <c r="D72" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>17</v>
@@ -2241,7 +2478,7 @@
         <v>1</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>17</v>
@@ -2259,7 +2496,7 @@
         <v>1</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>17</v>
@@ -2274,10 +2511,10 @@
         <v>16</v>
       </c>
       <c r="D75" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>17</v>
@@ -2292,10 +2529,10 @@
         <v>16</v>
       </c>
       <c r="D76" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>17</v>
@@ -2313,7 +2550,7 @@
         <v>2</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>17</v>
@@ -2331,7 +2568,7 @@
         <v>2</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>17</v>
@@ -2346,10 +2583,10 @@
         <v>16</v>
       </c>
       <c r="D79" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>17</v>
@@ -2364,10 +2601,10 @@
         <v>16</v>
       </c>
       <c r="D80" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>17</v>
@@ -2382,10 +2619,10 @@
         <v>16</v>
       </c>
       <c r="D81" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>17</v>
@@ -2400,10 +2637,10 @@
         <v>16</v>
       </c>
       <c r="D82" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>17</v>
@@ -2418,10 +2655,10 @@
         <v>16</v>
       </c>
       <c r="D83" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>17</v>
@@ -2436,10 +2673,10 @@
         <v>16</v>
       </c>
       <c r="D84" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>17</v>
@@ -2454,10 +2691,10 @@
         <v>16</v>
       </c>
       <c r="D85" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>17</v>
@@ -2472,10 +2709,10 @@
         <v>16</v>
       </c>
       <c r="D86" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>17</v>
@@ -2493,7 +2730,7 @@
         <v>1</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>17</v>
@@ -2505,13 +2742,13 @@
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="8" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="D88" s="5">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>19</v>
@@ -2523,13 +2760,13 @@
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="8" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="D89" s="5">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>19</v>
@@ -2541,13 +2778,13 @@
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="8" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="D90" s="5">
         <v>342</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>20</v>
@@ -2559,13 +2796,13 @@
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="8" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="D91" s="5">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>21</v>
@@ -2577,13 +2814,13 @@
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="8" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="D92" s="5">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>21</v>
@@ -2595,13 +2832,13 @@
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="8" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="D93" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>22</v>
@@ -2613,13 +2850,13 @@
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="8" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="D94" s="5">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>22</v>
@@ -2631,13 +2868,13 @@
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="8" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="D95" s="5">
         <v>180</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>22</v>
@@ -2649,13 +2886,13 @@
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="8" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="D96" s="5">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>22</v>
@@ -2667,13 +2904,13 @@
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="8" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="D97" s="5">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>22</v>
@@ -2685,13 +2922,13 @@
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="8" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="D98" s="5">
         <v>18</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F98" s="4" t="s">
         <v>23</v>
@@ -2703,13 +2940,13 @@
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="8" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="D99" s="5">
         <v>576</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>23</v>
@@ -2721,13 +2958,13 @@
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="8" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="D100" s="5">
         <v>540</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>23</v>
@@ -2745,7 +2982,7 @@
         <v>144</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>23</v>
@@ -2757,13 +2994,13 @@
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="8" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="D102" s="5">
         <v>36</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>25</v>
@@ -2775,13 +3012,13 @@
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="8" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="D103" s="5">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>25</v>
@@ -2793,13 +3030,13 @@
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="8" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="D104" s="5">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>25</v>
@@ -2811,16 +3048,16 @@
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="D105" s="7">
-        <v>9739.2000000000007</v>
+        <v>26</v>
+      </c>
+      <c r="D105" s="5">
+        <v>1</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2829,16 +3066,16 @@
       </c>
       <c r="B106" s="4"/>
       <c r="C106" s="8" t="s">
-        <v>138</v>
+        <v>28</v>
       </c>
       <c r="D106" s="5">
-        <v>795.6</v>
+        <v>1</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2847,16 +3084,16 @@
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D107" s="5">
         <v>1</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2865,16 +3102,16 @@
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D108" s="5">
         <v>1</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2883,19 +3120,19 @@
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D109" s="5">
         <v>1</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -2907,28 +3144,28 @@
         <v>1</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
         <v>110</v>
       </c>
       <c r="B111" s="4"/>
       <c r="C111" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D111" s="5">
         <v>1</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2937,7 +3174,7 @@
       </c>
       <c r="B112" s="4"/>
       <c r="C112" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D112" s="5">
         <v>1</v>
@@ -2946,43 +3183,43 @@
         <v>14</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
         <v>112</v>
       </c>
       <c r="B113" s="4"/>
       <c r="C113" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D113" s="5">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="D113" s="7">
+        <v>1000</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
         <v>113</v>
       </c>
       <c r="B114" s="4"/>
       <c r="C114" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D114" s="5">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="D114" s="7">
+        <v>1000</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2991,16 +3228,16 @@
       </c>
       <c r="B115" s="4"/>
       <c r="C115" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D115" s="5">
+        <v>1</v>
+      </c>
+      <c r="E115" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D115" s="7">
-        <v>1000</v>
-      </c>
-      <c r="E115" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="F115" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3009,16 +3246,16 @@
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D116" s="7">
         <v>1000</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3027,16 +3264,16 @@
       </c>
       <c r="B117" s="4"/>
       <c r="C117" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D117" s="5">
-        <v>1</v>
+        <v>40</v>
+      </c>
+      <c r="D117" s="7">
+        <v>1000</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3045,52 +3282,52 @@
       </c>
       <c r="B118" s="4"/>
       <c r="C118" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D118" s="7">
-        <v>1000</v>
+        <v>41</v>
+      </c>
+      <c r="D118" s="5">
+        <v>1</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="3">
         <v>118</v>
       </c>
       <c r="B119" s="4"/>
       <c r="C119" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D119" s="7">
-        <v>1000</v>
+        <v>42</v>
+      </c>
+      <c r="D119" s="5">
+        <v>40</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="3">
         <v>119</v>
       </c>
       <c r="B120" s="4"/>
       <c r="C120" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D120" s="5">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3099,16 +3336,16 @@
       </c>
       <c r="B121" s="4"/>
       <c r="C121" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D121" s="5">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="E121" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3117,16 +3354,16 @@
       </c>
       <c r="B122" s="4"/>
       <c r="C122" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D122" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3135,16 +3372,16 @@
       </c>
       <c r="B123" s="4"/>
       <c r="C123" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D123" s="5">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E123" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3153,16 +3390,16 @@
       </c>
       <c r="B124" s="4"/>
       <c r="C124" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D124" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3171,16 +3408,16 @@
       </c>
       <c r="B125" s="4"/>
       <c r="C125" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D125" s="5">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E125" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3189,16 +3426,16 @@
       </c>
       <c r="B126" s="4"/>
       <c r="C126" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D126" s="5">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3207,7 +3444,7 @@
       </c>
       <c r="B127" s="4"/>
       <c r="C127" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D127" s="5">
         <v>15</v>
@@ -3216,7 +3453,7 @@
         <v>14</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3225,16 +3462,16 @@
       </c>
       <c r="B128" s="4"/>
       <c r="C128" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D128" s="5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3243,16 +3480,16 @@
       </c>
       <c r="B129" s="4"/>
       <c r="C129" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D129" s="5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E129" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3261,16 +3498,16 @@
       </c>
       <c r="B130" s="4"/>
       <c r="C130" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D130" s="5">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3279,16 +3516,16 @@
       </c>
       <c r="B131" s="4"/>
       <c r="C131" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D131" s="5">
-        <v>10</v>
+        <v>56</v>
+      </c>
+      <c r="D131" s="7">
+        <v>2000</v>
       </c>
       <c r="E131" s="6" t="s">
         <v>55</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3297,16 +3534,16 @@
       </c>
       <c r="B132" s="4"/>
       <c r="C132" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D132" s="7">
-        <v>2000</v>
+        <v>57</v>
+      </c>
+      <c r="D132" s="5">
+        <v>5</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3315,70 +3552,70 @@
       </c>
       <c r="B133" s="4"/>
       <c r="C133" s="8" t="s">
-        <v>57</v>
+        <v>166</v>
       </c>
       <c r="D133" s="5">
-        <v>5</v>
+        <v>196</v>
       </c>
       <c r="E133" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
         <v>133</v>
       </c>
       <c r="B134" s="4"/>
       <c r="C134" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D134" s="5">
-        <v>10</v>
+        <v>800</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="3">
         <v>134</v>
       </c>
       <c r="B135" s="4"/>
       <c r="C135" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D135" s="5">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
         <v>135</v>
       </c>
       <c r="B136" s="4"/>
       <c r="C136" s="8" t="s">
-        <v>139</v>
+        <v>63</v>
       </c>
       <c r="D136" s="5">
-        <v>196</v>
+        <v>7</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3387,16 +3624,16 @@
       </c>
       <c r="B137" s="4"/>
       <c r="C137" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D137" s="5">
+        <v>7</v>
+      </c>
+      <c r="E137" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F137" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="D137" s="5">
-        <v>800</v>
-      </c>
-      <c r="E137" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F137" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3405,16 +3642,16 @@
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D138" s="7">
-        <v>1350000</v>
+        <v>65</v>
+      </c>
+      <c r="D138" s="5">
+        <v>115</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3423,16 +3660,16 @@
       </c>
       <c r="B139" s="4"/>
       <c r="C139" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D139" s="5">
-        <v>675</v>
+        <v>115</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3441,16 +3678,16 @@
       </c>
       <c r="B140" s="4"/>
       <c r="C140" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D140" s="7">
-        <v>2700000</v>
+        <v>67</v>
+      </c>
+      <c r="D140" s="5">
+        <v>270</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3459,16 +3696,16 @@
       </c>
       <c r="B141" s="4"/>
       <c r="C141" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="D141" s="7">
-        <v>2350</v>
+        <v>167</v>
+      </c>
+      <c r="D141" s="5">
+        <v>27</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3477,16 +3714,16 @@
       </c>
       <c r="B142" s="4"/>
       <c r="C142" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="D142" s="7">
-        <v>1350</v>
+        <v>168</v>
+      </c>
+      <c r="D142" s="5">
+        <v>135</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3495,16 +3732,16 @@
       </c>
       <c r="B143" s="4"/>
       <c r="C143" s="8" t="s">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="D143" s="5">
-        <v>405</v>
+        <v>270</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3513,16 +3750,16 @@
       </c>
       <c r="B144" s="4"/>
       <c r="C144" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D144" s="7">
-        <v>1350000</v>
+        <v>68</v>
+      </c>
+      <c r="D144" s="5">
+        <v>135</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3531,16 +3768,16 @@
       </c>
       <c r="B145" s="4"/>
       <c r="C145" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D145" s="5">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3549,16 +3786,16 @@
       </c>
       <c r="B146" s="4"/>
       <c r="C146" s="8" t="s">
-        <v>72</v>
+        <v>170</v>
       </c>
       <c r="D146" s="5">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3567,16 +3804,16 @@
       </c>
       <c r="B147" s="4"/>
       <c r="C147" s="8" t="s">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="D147" s="5">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3585,16 +3822,16 @@
       </c>
       <c r="B148" s="4"/>
       <c r="C148" s="8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D148" s="5">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3603,16 +3840,16 @@
       </c>
       <c r="B149" s="4"/>
       <c r="C149" s="8" t="s">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="D149" s="5">
-        <v>270</v>
+        <v>88</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3621,16 +3858,16 @@
       </c>
       <c r="B150" s="4"/>
       <c r="C150" s="8" t="s">
-        <v>142</v>
+        <v>71</v>
       </c>
       <c r="D150" s="5">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3639,16 +3876,16 @@
       </c>
       <c r="B151" s="4"/>
       <c r="C151" s="8" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
       <c r="D151" s="5">
-        <v>135</v>
+        <v>27</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3657,16 +3894,16 @@
       </c>
       <c r="B152" s="4"/>
       <c r="C152" s="8" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="D152" s="5">
-        <v>270</v>
+        <v>54</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3675,16 +3912,16 @@
       </c>
       <c r="B153" s="4"/>
       <c r="C153" s="8" t="s">
-        <v>76</v>
+        <v>174</v>
       </c>
       <c r="D153" s="5">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3693,16 +3930,16 @@
       </c>
       <c r="B154" s="4"/>
       <c r="C154" s="8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D154" s="5">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3711,16 +3948,16 @@
       </c>
       <c r="B155" s="4"/>
       <c r="C155" s="8" t="s">
-        <v>145</v>
+        <v>74</v>
       </c>
       <c r="D155" s="5">
-        <v>27</v>
+        <v>405</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3729,16 +3966,16 @@
       </c>
       <c r="B156" s="4"/>
       <c r="C156" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D156" s="7">
-        <v>1350</v>
+        <v>1350000</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3747,16 +3984,16 @@
       </c>
       <c r="B157" s="4"/>
       <c r="C157" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D157" s="5">
-        <v>54</v>
+        <v>77</v>
+      </c>
+      <c r="D157" s="7">
+        <v>1350</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3765,16 +4002,16 @@
       </c>
       <c r="B158" s="4"/>
       <c r="C158" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="D158" s="5">
-        <v>88</v>
+        <v>78</v>
+      </c>
+      <c r="D158" s="7">
+        <v>1350000</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3783,16 +4020,16 @@
       </c>
       <c r="B159" s="4"/>
       <c r="C159" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="D159" s="5">
-        <v>88</v>
+        <v>79</v>
+      </c>
+      <c r="D159" s="7">
+        <v>2700000</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3801,16 +4038,16 @@
       </c>
       <c r="B160" s="4"/>
       <c r="C160" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D160" s="5">
-        <v>27</v>
+        <v>175</v>
+      </c>
+      <c r="D160" s="7">
+        <v>2350</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3819,16 +4056,16 @@
       </c>
       <c r="B161" s="4"/>
       <c r="C161" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="D161" s="5">
-        <v>54</v>
+        <v>176</v>
+      </c>
+      <c r="D161" s="7">
+        <v>1350</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3837,106 +4074,106 @@
       </c>
       <c r="B162" s="4"/>
       <c r="C162" s="8" t="s">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="D162" s="5">
-        <v>61</v>
+        <v>675</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="3">
         <v>162</v>
       </c>
       <c r="B163" s="4"/>
       <c r="C163" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D163" s="5">
+        <v>6</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F163" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D163" s="5">
-        <v>61</v>
-      </c>
-      <c r="E163" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F163" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="164" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="3">
         <v>163</v>
       </c>
       <c r="B164" s="4"/>
       <c r="C164" s="8" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="D164" s="5">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="3">
         <v>164</v>
       </c>
       <c r="B165" s="4"/>
       <c r="C165" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D165" s="5">
-        <v>129</v>
+        <v>10</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="3">
         <v>165</v>
       </c>
       <c r="B166" s="4"/>
       <c r="C166" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D166" s="7">
-        <v>2323.62</v>
+        <v>45</v>
+      </c>
+      <c r="D166" s="5">
+        <v>10</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="3">
         <v>166</v>
       </c>
       <c r="B167" s="4"/>
       <c r="C167" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="D167" s="7">
-        <v>1438.2</v>
+        <v>45</v>
+      </c>
+      <c r="D167" s="5">
+        <v>20</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3945,16 +4182,16 @@
       </c>
       <c r="B168" s="4"/>
       <c r="C168" s="8" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="D168" s="5">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3963,16 +4200,16 @@
       </c>
       <c r="B169" s="4"/>
       <c r="C169" s="8" t="s">
-        <v>88</v>
+        <v>177</v>
       </c>
       <c r="D169" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3981,16 +4218,16 @@
       </c>
       <c r="B170" s="4"/>
       <c r="C170" s="8" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D170" s="5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3999,16 +4236,16 @@
       </c>
       <c r="B171" s="4"/>
       <c r="C171" s="8" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="D171" s="5">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E171" s="6" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4017,16 +4254,16 @@
       </c>
       <c r="B172" s="4"/>
       <c r="C172" s="8" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="D172" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4035,16 +4272,16 @@
       </c>
       <c r="B173" s="4"/>
       <c r="C173" s="8" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D173" s="5">
         <v>10</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="174" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4053,79 +4290,79 @@
       </c>
       <c r="B174" s="4"/>
       <c r="C174" s="8" t="s">
-        <v>53</v>
+        <v>178</v>
       </c>
       <c r="D174" s="5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="3">
         <v>174</v>
       </c>
       <c r="B175" s="4"/>
       <c r="C175" s="8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D175" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E175" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="3">
         <v>175</v>
       </c>
       <c r="B176" s="4"/>
       <c r="C176" s="8" t="s">
-        <v>53</v>
+        <v>179</v>
       </c>
       <c r="D176" s="5">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="3">
         <v>176</v>
       </c>
       <c r="B177" s="4"/>
       <c r="C177" s="8" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="D177" s="5">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E177" s="6" t="s">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="3">
         <v>177</v>
       </c>
       <c r="B178" s="4"/>
       <c r="C178" s="8" t="s">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="D178" s="5">
         <v>5</v>
@@ -4134,61 +4371,61 @@
         <v>14</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="3">
         <v>178</v>
       </c>
       <c r="B179" s="4"/>
       <c r="C179" s="8" t="s">
-        <v>151</v>
+        <v>96</v>
       </c>
       <c r="D179" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E179" s="6" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="3">
         <v>179</v>
       </c>
       <c r="B180" s="4"/>
       <c r="C180" s="8" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="D180" s="5">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="3">
         <v>180</v>
       </c>
       <c r="B181" s="4"/>
       <c r="C181" s="8" t="s">
-        <v>152</v>
+        <v>98</v>
       </c>
       <c r="D181" s="5">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="E181" s="6" t="s">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4197,16 +4434,16 @@
       </c>
       <c r="B182" s="4"/>
       <c r="C182" s="8" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="D182" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="183" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4215,16 +4452,16 @@
       </c>
       <c r="B183" s="4"/>
       <c r="C183" s="8" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D183" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="184" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4233,16 +4470,16 @@
       </c>
       <c r="B184" s="4"/>
       <c r="C184" s="8" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D184" s="5">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="185" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4251,16 +4488,16 @@
       </c>
       <c r="B185" s="4"/>
       <c r="C185" s="8" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D185" s="5">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E185" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="186" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4269,16 +4506,16 @@
       </c>
       <c r="B186" s="4"/>
       <c r="C186" s="8" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D186" s="5">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="187" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4287,16 +4524,16 @@
       </c>
       <c r="B187" s="4"/>
       <c r="C187" s="8" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D187" s="5">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E187" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4305,16 +4542,16 @@
       </c>
       <c r="B188" s="4"/>
       <c r="C188" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D188" s="5">
+        <v>1</v>
+      </c>
+      <c r="E188" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F188" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="D188" s="5">
-        <v>10</v>
-      </c>
-      <c r="E188" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F188" s="4" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="189" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4323,16 +4560,16 @@
       </c>
       <c r="B189" s="4"/>
       <c r="C189" s="8" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D189" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E189" s="6" t="s">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="190" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4341,16 +4578,16 @@
       </c>
       <c r="B190" s="4"/>
       <c r="C190" s="8" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D190" s="5">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4359,16 +4596,16 @@
       </c>
       <c r="B191" s="4"/>
       <c r="C191" s="8" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D191" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E191" s="6" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="192" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4377,16 +4614,16 @@
       </c>
       <c r="B192" s="4"/>
       <c r="C192" s="8" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D192" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4395,16 +4632,16 @@
       </c>
       <c r="B193" s="4"/>
       <c r="C193" s="8" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D193" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E193" s="6" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="194" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4413,16 +4650,16 @@
       </c>
       <c r="B194" s="4"/>
       <c r="C194" s="8" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D194" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4431,16 +4668,16 @@
       </c>
       <c r="B195" s="4"/>
       <c r="C195" s="8" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D195" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E195" s="6" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="196" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4449,16 +4686,16 @@
       </c>
       <c r="B196" s="4"/>
       <c r="C196" s="8" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D196" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="197" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4467,16 +4704,16 @@
       </c>
       <c r="B197" s="4"/>
       <c r="C197" s="8" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D197" s="5">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E197" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="198" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4485,16 +4722,16 @@
       </c>
       <c r="B198" s="4"/>
       <c r="C198" s="8" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
       <c r="D198" s="5">
-        <v>10</v>
+        <v>225</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4503,16 +4740,16 @@
       </c>
       <c r="B199" s="4"/>
       <c r="C199" s="8" t="s">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="D199" s="5">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="E199" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
     </row>
     <row r="200" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4521,16 +4758,16 @@
       </c>
       <c r="B200" s="4"/>
       <c r="C200" s="8" t="s">
-        <v>113</v>
+        <v>181</v>
       </c>
       <c r="D200" s="5">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
     </row>
     <row r="201" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4539,16 +4776,1222 @@
       </c>
       <c r="B201" s="4"/>
       <c r="C201" s="8" t="s">
-        <v>114</v>
+        <v>182</v>
       </c>
       <c r="D201" s="5">
-        <v>5</v>
+        <v>720</v>
       </c>
       <c r="E201" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F201" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A202" s="3">
+        <v>201</v>
+      </c>
+      <c r="B202" s="4"/>
+      <c r="C202" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D202" s="5">
+        <v>24.48</v>
+      </c>
+      <c r="E202" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F202" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A203" s="3">
+        <v>202</v>
+      </c>
+      <c r="B203" s="4"/>
+      <c r="C203" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D203" s="5">
+        <v>114.3</v>
+      </c>
+      <c r="E203" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F203" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A204" s="3">
+        <v>203</v>
+      </c>
+      <c r="B204" s="4"/>
+      <c r="C204" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D204" s="5">
+        <v>57.42</v>
+      </c>
+      <c r="E204" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F204" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A205" s="3">
+        <v>204</v>
+      </c>
+      <c r="B205" s="4"/>
+      <c r="C205" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="D205" s="7">
+        <v>16888.560000000001</v>
+      </c>
+      <c r="E205" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F205" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A206" s="3">
+        <v>205</v>
+      </c>
+      <c r="B206" s="4"/>
+      <c r="C206" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D206" s="7">
+        <v>2630.59</v>
+      </c>
+      <c r="E206" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F206" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A207" s="3">
+        <v>206</v>
+      </c>
+      <c r="B207" s="4"/>
+      <c r="C207" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D207" s="7">
+        <v>2997</v>
+      </c>
+      <c r="E207" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F207" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A208" s="3">
+        <v>207</v>
+      </c>
+      <c r="B208" s="4"/>
+      <c r="C208" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D208" s="5">
+        <v>761.65</v>
+      </c>
+      <c r="E208" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F208" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A209" s="3">
+        <v>208</v>
+      </c>
+      <c r="B209" s="4"/>
+      <c r="C209" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D209" s="7">
+        <v>5422.6</v>
+      </c>
+      <c r="E209" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F209" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A210" s="3">
+        <v>209</v>
+      </c>
+      <c r="B210" s="4"/>
+      <c r="C210" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D210" s="7">
+        <v>3809</v>
+      </c>
+      <c r="E210" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F210" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A211" s="3">
+        <v>210</v>
+      </c>
+      <c r="B211" s="4"/>
+      <c r="C211" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="D211" s="5">
+        <v>68.58</v>
+      </c>
+      <c r="E211" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F211" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A212" s="3">
+        <v>211</v>
+      </c>
+      <c r="B212" s="4"/>
+      <c r="C212" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D212" s="5">
+        <v>19.8</v>
+      </c>
+      <c r="E212" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F212" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A213" s="3">
+        <v>212</v>
+      </c>
+      <c r="B213" s="4"/>
+      <c r="C213" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D213" s="5">
+        <v>36</v>
+      </c>
+      <c r="E213" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F213" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A214" s="3">
+        <v>213</v>
+      </c>
+      <c r="B214" s="4"/>
+      <c r="C214" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D214" s="5">
+        <v>36</v>
+      </c>
+      <c r="E214" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F214" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A215" s="3">
+        <v>214</v>
+      </c>
+      <c r="B215" s="4"/>
+      <c r="C215" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="D215" s="5">
+        <v>36</v>
+      </c>
+      <c r="E215" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F215" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A216" s="3">
+        <v>215</v>
+      </c>
+      <c r="B216" s="4"/>
+      <c r="C216" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D216" s="5">
+        <v>12</v>
+      </c>
+      <c r="E216" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F216" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A217" s="3">
+        <v>216</v>
+      </c>
+      <c r="B217" s="4"/>
+      <c r="C217" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D217" s="5">
+        <v>12</v>
+      </c>
+      <c r="E217" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F217" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A218" s="3">
+        <v>217</v>
+      </c>
+      <c r="B218" s="4"/>
+      <c r="C218" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D218" s="5">
+        <v>18</v>
+      </c>
+      <c r="E218" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F218" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A219" s="3">
+        <v>218</v>
+      </c>
+      <c r="B219" s="4"/>
+      <c r="C219" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D219" s="5">
+        <v>18</v>
+      </c>
+      <c r="E219" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F219" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A220" s="3">
+        <v>219</v>
+      </c>
+      <c r="B220" s="4"/>
+      <c r="C220" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D220" s="5">
+        <v>27</v>
+      </c>
+      <c r="E220" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F220" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A221" s="3">
+        <v>220</v>
+      </c>
+      <c r="B221" s="4"/>
+      <c r="C221" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D221" s="5">
+        <v>60</v>
+      </c>
+      <c r="E221" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F221" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A222" s="3">
+        <v>221</v>
+      </c>
+      <c r="B222" s="4"/>
+      <c r="C222" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D222" s="5">
+        <v>636</v>
+      </c>
+      <c r="E222" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F222" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A223" s="3">
+        <v>222</v>
+      </c>
+      <c r="B223" s="4"/>
+      <c r="C223" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D223" s="5">
+        <v>168</v>
+      </c>
+      <c r="E223" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F223" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A224" s="3">
+        <v>223</v>
+      </c>
+      <c r="B224" s="4"/>
+      <c r="C224" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D224" s="5">
         <v>6</v>
       </c>
-      <c r="F201" s="4" t="s">
-        <v>98</v>
+      <c r="E224" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F224" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A225" s="3">
+        <v>224</v>
+      </c>
+      <c r="B225" s="4"/>
+      <c r="C225" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D225" s="7">
+        <v>1158</v>
+      </c>
+      <c r="E225" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F225" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A226" s="3">
+        <v>225</v>
+      </c>
+      <c r="B226" s="4"/>
+      <c r="C226" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D226" s="5">
+        <v>60</v>
+      </c>
+      <c r="E226" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F226" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A227" s="3">
+        <v>226</v>
+      </c>
+      <c r="B227" s="4"/>
+      <c r="C227" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D227" s="5">
+        <v>18</v>
+      </c>
+      <c r="E227" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F227" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A228" s="3">
+        <v>227</v>
+      </c>
+      <c r="B228" s="4"/>
+      <c r="C228" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D228" s="5">
+        <v>72</v>
+      </c>
+      <c r="E228" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F228" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A229" s="3">
+        <v>228</v>
+      </c>
+      <c r="B229" s="4"/>
+      <c r="C229" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D229" s="5">
+        <v>18</v>
+      </c>
+      <c r="E229" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F229" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A230" s="3">
+        <v>229</v>
+      </c>
+      <c r="B230" s="4"/>
+      <c r="C230" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D230" s="5">
+        <v>24</v>
+      </c>
+      <c r="E230" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F230" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A231" s="3">
+        <v>230</v>
+      </c>
+      <c r="B231" s="4"/>
+      <c r="C231" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D231" s="5">
+        <v>12</v>
+      </c>
+      <c r="E231" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F231" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A232" s="3">
+        <v>231</v>
+      </c>
+      <c r="B232" s="4"/>
+      <c r="C232" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D232" s="5">
+        <v>6</v>
+      </c>
+      <c r="E232" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F232" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A233" s="3">
+        <v>232</v>
+      </c>
+      <c r="B233" s="4"/>
+      <c r="C233" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D233" s="5">
+        <v>60</v>
+      </c>
+      <c r="E233" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F233" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A234" s="3">
+        <v>233</v>
+      </c>
+      <c r="B234" s="4"/>
+      <c r="C234" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D234" s="5">
+        <v>6</v>
+      </c>
+      <c r="E234" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F234" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A235" s="3">
+        <v>234</v>
+      </c>
+      <c r="B235" s="4"/>
+      <c r="C235" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D235" s="5">
+        <v>48</v>
+      </c>
+      <c r="E235" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F235" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A236" s="3">
+        <v>235</v>
+      </c>
+      <c r="B236" s="4"/>
+      <c r="C236" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="D236" s="5">
+        <v>84</v>
+      </c>
+      <c r="E236" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F236" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A237" s="3">
+        <v>236</v>
+      </c>
+      <c r="B237" s="4"/>
+      <c r="C237" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D237" s="5">
+        <v>12</v>
+      </c>
+      <c r="E237" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F237" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A238" s="3">
+        <v>237</v>
+      </c>
+      <c r="B238" s="4"/>
+      <c r="C238" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="D238" s="5">
+        <v>90</v>
+      </c>
+      <c r="E238" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F238" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A239" s="3">
+        <v>238</v>
+      </c>
+      <c r="B239" s="4"/>
+      <c r="C239" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="D239" s="5">
+        <v>6</v>
+      </c>
+      <c r="E239" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F239" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A240" s="3">
+        <v>239</v>
+      </c>
+      <c r="B240" s="4"/>
+      <c r="C240" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="D240" s="5">
+        <v>594.17999999999995</v>
+      </c>
+      <c r="E240" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F240" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A241" s="3">
+        <v>240</v>
+      </c>
+      <c r="B241" s="4"/>
+      <c r="C241" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="D241" s="5">
+        <v>754.4</v>
+      </c>
+      <c r="E241" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F241" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A242" s="3">
+        <v>241</v>
+      </c>
+      <c r="B242" s="4"/>
+      <c r="C242" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="D242" s="7">
+        <v>1808.82</v>
+      </c>
+      <c r="E242" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F242" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A243" s="3">
+        <v>242</v>
+      </c>
+      <c r="B243" s="4"/>
+      <c r="C243" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D243" s="5">
+        <v>9</v>
+      </c>
+      <c r="E243" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F243" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A244" s="3">
+        <v>243</v>
+      </c>
+      <c r="B244" s="4"/>
+      <c r="C244" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="D244" s="7">
+        <v>14270.1</v>
+      </c>
+      <c r="E244" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F244" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A245" s="3">
+        <v>244</v>
+      </c>
+      <c r="B245" s="4"/>
+      <c r="C245" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="D245" s="7">
+        <v>16848</v>
+      </c>
+      <c r="E245" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F245" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A246" s="3">
+        <v>245</v>
+      </c>
+      <c r="B246" s="4"/>
+      <c r="C246" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D246" s="5">
+        <v>165.06</v>
+      </c>
+      <c r="E246" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F246" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A247" s="3">
+        <v>246</v>
+      </c>
+      <c r="B247" s="4"/>
+      <c r="C247" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="D247" s="5">
+        <v>9</v>
+      </c>
+      <c r="E247" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F247" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A248" s="3">
+        <v>247</v>
+      </c>
+      <c r="B248" s="4"/>
+      <c r="C248" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D248" s="5">
+        <v>0.63</v>
+      </c>
+      <c r="E248" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F248" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A249" s="3">
+        <v>248</v>
+      </c>
+      <c r="B249" s="4"/>
+      <c r="C249" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D249" s="5">
+        <v>10</v>
+      </c>
+      <c r="E249" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F249" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A250" s="3">
+        <v>249</v>
+      </c>
+      <c r="B250" s="4"/>
+      <c r="C250" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D250" s="5">
+        <v>2</v>
+      </c>
+      <c r="E250" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F250" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A251" s="3">
+        <v>250</v>
+      </c>
+      <c r="B251" s="4"/>
+      <c r="C251" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D251" s="5">
+        <v>4</v>
+      </c>
+      <c r="E251" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F251" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A252" s="3">
+        <v>251</v>
+      </c>
+      <c r="B252" s="4"/>
+      <c r="C252" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="D252" s="5">
+        <v>60</v>
+      </c>
+      <c r="E252" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F252" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A253" s="3">
+        <v>252</v>
+      </c>
+      <c r="B253" s="4"/>
+      <c r="C253" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="D253" s="5">
+        <v>850</v>
+      </c>
+      <c r="E253" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F253" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A254" s="3">
+        <v>253</v>
+      </c>
+      <c r="B254" s="4"/>
+      <c r="C254" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="D254" s="5">
+        <v>240</v>
+      </c>
+      <c r="E254" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F254" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A255" s="3">
+        <v>254</v>
+      </c>
+      <c r="B255" s="4"/>
+      <c r="C255" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="D255" s="5">
+        <v>100</v>
+      </c>
+      <c r="E255" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F255" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A256" s="3">
+        <v>255</v>
+      </c>
+      <c r="B256" s="4"/>
+      <c r="C256" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="D256" s="5">
+        <v>800</v>
+      </c>
+      <c r="E256" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F256" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A257" s="3">
+        <v>256</v>
+      </c>
+      <c r="B257" s="4"/>
+      <c r="C257" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="D257" s="5">
+        <v>240</v>
+      </c>
+      <c r="E257" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F257" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A258" s="3">
+        <v>257</v>
+      </c>
+      <c r="B258" s="4"/>
+      <c r="C258" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="D258" s="5">
+        <v>240</v>
+      </c>
+      <c r="E258" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F258" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A259" s="3">
+        <v>258</v>
+      </c>
+      <c r="B259" s="4"/>
+      <c r="C259" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D259" s="5">
+        <v>240</v>
+      </c>
+      <c r="E259" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F259" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A260" s="3">
+        <v>259</v>
+      </c>
+      <c r="B260" s="4"/>
+      <c r="C260" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D260" s="5">
+        <v>250</v>
+      </c>
+      <c r="E260" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F260" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A261" s="3">
+        <v>260</v>
+      </c>
+      <c r="B261" s="4"/>
+      <c r="C261" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="D261" s="5">
+        <v>250</v>
+      </c>
+      <c r="E261" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F261" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A262" s="3">
+        <v>261</v>
+      </c>
+      <c r="B262" s="4"/>
+      <c r="C262" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D262" s="5">
+        <v>420</v>
+      </c>
+      <c r="E262" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F262" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A263" s="3">
+        <v>262</v>
+      </c>
+      <c r="B263" s="4"/>
+      <c r="C263" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="D263" s="5">
+        <v>600</v>
+      </c>
+      <c r="E263" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F263" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A264" s="3">
+        <v>263</v>
+      </c>
+      <c r="B264" s="4"/>
+      <c r="C264" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D264" s="5">
+        <v>250</v>
+      </c>
+      <c r="E264" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F264" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A265" s="3">
+        <v>264</v>
+      </c>
+      <c r="B265" s="4"/>
+      <c r="C265" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="D265" s="5">
+        <v>500</v>
+      </c>
+      <c r="E265" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F265" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A266" s="3">
+        <v>265</v>
+      </c>
+      <c r="B266" s="4"/>
+      <c r="C266" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="D266" s="5">
+        <v>500</v>
+      </c>
+      <c r="E266" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F266" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A267" s="3">
+        <v>266</v>
+      </c>
+      <c r="B267" s="4"/>
+      <c r="C267" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="D267" s="5">
+        <v>36</v>
+      </c>
+      <c r="E267" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F267" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A268" s="3">
+        <v>267</v>
+      </c>
+      <c r="B268" s="4"/>
+      <c r="C268" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="D268" s="5">
+        <v>132</v>
+      </c>
+      <c r="E268" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F268" s="4" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/public/procurement.xlsx
+++ b/public/procurement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lka\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0C5A70-BF0C-43FA-8CC1-29801BCBDF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A098BB-37BF-4A49-942C-5396FC70E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4110" yWindow="4110" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="219">
   <si>
     <t>№ п/п</t>
   </si>
@@ -72,7 +72,7 @@
     <t>шт.</t>
   </si>
   <si>
-    <t>НТУП-018367</t>
+    <t>ИИ00-000067</t>
   </si>
   <si>
     <t>Сэндвич-панель</t>
@@ -96,12 +96,12 @@
     <t>ИИУП-000411</t>
   </si>
   <si>
+    <t>Саморез с пресс шайбой 4,2х13</t>
+  </si>
+  <si>
     <t>ИИУП-000412</t>
   </si>
   <si>
-    <t>Саморез с пресс шайбой 4,2х13</t>
-  </si>
-  <si>
     <t>ИИУП-000434</t>
   </si>
   <si>
@@ -111,33 +111,84 @@
     <t>ИИУП-000445</t>
   </si>
   <si>
+    <t>Сварочный аппарат</t>
+  </si>
+  <si>
+    <t>ИИУП-000446</t>
+  </si>
+  <si>
     <t>Роликовый вращатель</t>
   </si>
   <si>
-    <t>ИИУП-000446</t>
-  </si>
-  <si>
-    <t>Сварочный аппарат</t>
+    <t>Рулетка  5м х 25мм Компакт в обрезиненном корпусе</t>
+  </si>
+  <si>
+    <t>ИИ00-000013</t>
+  </si>
+  <si>
+    <t>Маркер по металлу черный тонкий</t>
+  </si>
+  <si>
+    <t>Пена монтажная /шт/</t>
+  </si>
+  <si>
+    <t>Штангенциркуль</t>
+  </si>
+  <si>
+    <t>Кувалда 1 кг</t>
+  </si>
+  <si>
+    <t>Ключ комбинир. 36 мм</t>
+  </si>
+  <si>
+    <t>Ключ комбинир. 30 мм</t>
+  </si>
+  <si>
+    <t>Ключ комбинир. 24 мм</t>
+  </si>
+  <si>
+    <t>Изолента</t>
+  </si>
+  <si>
+    <t>Фонарик налобный аккумуляторный</t>
+  </si>
+  <si>
+    <t>Ветошь /рул./</t>
+  </si>
+  <si>
+    <t>Маркер по металлу белый</t>
+  </si>
+  <si>
+    <t>Дождевик-костюм темно-синий 52-54</t>
+  </si>
+  <si>
+    <t>компл</t>
+  </si>
+  <si>
+    <t>Перчатки х/б (с ПВХ покрытием, 5 ниток,черные,класс 10)</t>
+  </si>
+  <si>
+    <t>Печать ИПП НТ</t>
+  </si>
+  <si>
+    <t>НТУП-018372</t>
   </si>
   <si>
     <t>Печать с автоматической оснасткой</t>
   </si>
   <si>
-    <t>НТУП-018372</t>
-  </si>
-  <si>
     <t>Печать</t>
   </si>
   <si>
-    <t>Печать ИПП НТ</t>
+    <t>Доп. услуги по обеспечению спецоснасткой</t>
+  </si>
+  <si>
+    <t>(не исп) шт</t>
   </si>
   <si>
     <t>Кашкороб/0201/400х400х610/Т23В/ММ/КК/4+0/мат.лам.</t>
   </si>
   <si>
-    <t>(не исп) шт</t>
-  </si>
-  <si>
     <t>Кашкороб/0203/300х200х400/Т23/ММ/КК/4+0/мат.лам</t>
   </si>
   <si>
@@ -150,57 +201,6 @@
     <t>Кашкороб/0427/340х160х60/Т23В/ММ/КК/4+0/мат.лам</t>
   </si>
   <si>
-    <t>Доп. услуги по обеспечению спецоснасткой</t>
-  </si>
-  <si>
-    <t>Пена монтажная /шт/</t>
-  </si>
-  <si>
-    <t>ИИ00-000013</t>
-  </si>
-  <si>
-    <t>Маркер по металлу черный тонкий</t>
-  </si>
-  <si>
-    <t>Маркер по металлу белый</t>
-  </si>
-  <si>
-    <t>Ветошь /рул./</t>
-  </si>
-  <si>
-    <t>Фонарик налобный аккумуляторный</t>
-  </si>
-  <si>
-    <t>Изолента</t>
-  </si>
-  <si>
-    <t>Ключ комбинир. 24 мм</t>
-  </si>
-  <si>
-    <t>Ключ комбинир. 30 мм</t>
-  </si>
-  <si>
-    <t>Ключ комбинир. 36 мм</t>
-  </si>
-  <si>
-    <t>Кувалда 1 кг</t>
-  </si>
-  <si>
-    <t>Штангенциркуль</t>
-  </si>
-  <si>
-    <t>Дождевик-костюм темно-синий 52-54</t>
-  </si>
-  <si>
-    <t>компл</t>
-  </si>
-  <si>
-    <t>Перчатки х/б (с ПВХ покрытием, 5 ниток,черные,класс 10)</t>
-  </si>
-  <si>
-    <t>Рулетка  5м х 25мм Компакт в обрезиненном корпусе</t>
-  </si>
-  <si>
     <t>ИИ00-000065</t>
   </si>
   <si>
@@ -210,90 +210,90 @@
     <t>ИИУП-000472</t>
   </si>
   <si>
+    <t>Клапан магниторегулируемый КМР-2М-Ех в сборе НТ.293.000.000 (Тройник ТР)</t>
+  </si>
+  <si>
+    <t>НТУП-018427</t>
+  </si>
+  <si>
+    <t>Счетчик-расходомер вихревой ЭРВИП.НТ 80/65Ф с датчиком давления 018М</t>
+  </si>
+  <si>
+    <t>Знак безопасности F11</t>
+  </si>
+  <si>
+    <t>Знак безопасности F10</t>
+  </si>
+  <si>
+    <t>Заглушка кабельного ввода М22 взрывозащищенная EXD</t>
+  </si>
+  <si>
+    <t>Термоусадочная трубка 30/15 черная</t>
+  </si>
+  <si>
+    <t>Извещатель пожарный</t>
+  </si>
+  <si>
+    <t>Извещатель пожарный тепловой взрывозащищенный 101-07е 1Ex db [ia Ga] IIC Т4 Gb Х IP66</t>
+  </si>
+  <si>
+    <t>Термопреобразователь</t>
+  </si>
+  <si>
+    <t>Преобразователь избыточного давления Метран 75G,взрывозащита 0Ex ia IIC T4 Ga X,IP66,4-20+HART</t>
+  </si>
+  <si>
+    <t>Газоанализатор СГОЭС-2 с калибровкой на метан (порог1-10%, порог2-40%)</t>
+  </si>
+  <si>
     <t>Вентиль игольчатый ВИ-160</t>
   </si>
   <si>
-    <t>НТУП-018427</t>
-  </si>
-  <si>
-    <t>Клапан магниторегулируемый КМР-2М-Ех в сборе НТ.293.000.000 (Тройник ТР)</t>
-  </si>
-  <si>
-    <t>Счетчик-расходомер вихревой ЭРВИП.НТ 80/65Ф с датчиком давления 018М</t>
-  </si>
-  <si>
-    <t>Знак безопасности F11</t>
-  </si>
-  <si>
-    <t>Знак безопасности F10</t>
-  </si>
-  <si>
-    <t>Заглушка кабельного ввода М22 взрывозащищенная EXD</t>
-  </si>
-  <si>
-    <t>Термоусадочная трубка 30/15 черная</t>
-  </si>
-  <si>
-    <t>Извещатель пожарный</t>
-  </si>
-  <si>
-    <t>Извещатель пожарный тепловой взрывозащищенный 101-07е 1Ex db [ia Ga] IIC Т4 Gb Х IP66</t>
-  </si>
-  <si>
-    <t>Термопреобразователь</t>
-  </si>
-  <si>
-    <t>Преобразователь избыточного давления Метран 75G,взрывозащита 0Ex ia IIC T4 Ga X,IP66,4-20+HART</t>
-  </si>
-  <si>
-    <t>Газоанализатор СГОЭС-2 с калибровкой на метан (порог1-10%, порог2-40%)</t>
+    <t>Кабель КПСЭнг (А) FRLS 1*2*0.75</t>
+  </si>
+  <si>
+    <t>м</t>
+  </si>
+  <si>
+    <t>Кабель КПСЭнг(А)-FRlS 2х2х0.75 для ОПС</t>
+  </si>
+  <si>
+    <t>Кабель КВВГЭнг(А)-LS 7*1</t>
+  </si>
+  <si>
+    <t>Кабель кввгэнг(А)-LS 4*1</t>
   </si>
   <si>
     <t>Металлорукав в ПВХ-оболочке РЗ-ЦП-15 ( ДУ20 изолированный, оц.сталь)</t>
   </si>
   <si>
-    <t>м</t>
-  </si>
-  <si>
-    <t>Кабель кввгэнг(А)-LS 4*1</t>
-  </si>
-  <si>
-    <t>Кабель КВВГЭнг(А)-LS 7*1</t>
-  </si>
-  <si>
-    <t>Кабель КПСЭнг(А)-FRlS 2х2х0.75 для ОПС</t>
-  </si>
-  <si>
-    <t>Кабель КПСЭнг (А) FRLS 1*2*0.75</t>
-  </si>
-  <si>
     <t>Труба гофрированная ПВХ 20</t>
   </si>
   <si>
+    <t>Паронит 2мм</t>
+  </si>
+  <si>
+    <t>лист</t>
+  </si>
+  <si>
     <t>ИИ00-000017</t>
   </si>
   <si>
     <t>Маркер по металлу красный</t>
   </si>
   <si>
+    <t>Паронит 3 мм</t>
+  </si>
+  <si>
+    <t>Ключи обмедненные</t>
+  </si>
+  <si>
+    <t>набор</t>
+  </si>
+  <si>
     <t>Мел сварщика белый</t>
   </si>
   <si>
-    <t>Паронит 2мм</t>
-  </si>
-  <si>
-    <t>лист</t>
-  </si>
-  <si>
-    <t>Паронит 3 мм</t>
-  </si>
-  <si>
-    <t>Ключи обмедненные</t>
-  </si>
-  <si>
-    <t>набор</t>
-  </si>
-  <si>
     <t>Погрузчик ПЛ-0.4</t>
   </si>
   <si>
@@ -303,63 +303,105 @@
     <t>ИИУП-000499</t>
   </si>
   <si>
-    <t>Сапоги зимние</t>
+    <t>ИИУП-000502</t>
+  </si>
+  <si>
+    <t>Карман инструментального магазина, пластиковый TSG-607-00 (ВТ-40)</t>
+  </si>
+  <si>
+    <t>ИИУП-000503</t>
+  </si>
+  <si>
+    <t>ИИУП-000505</t>
+  </si>
+  <si>
+    <t>Труба D720х12 09Г2С ГОСТ 10705-80</t>
+  </si>
+  <si>
+    <t>Труба D89х12 Ст.09Г2 ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Труба D720х18 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-73</t>
+  </si>
+  <si>
+    <t>ИИУП-000506</t>
+  </si>
+  <si>
+    <t>Днище 720х18-09Г2С ГОСТ 6533-78</t>
+  </si>
+  <si>
+    <t>Фланец 7-100-63 ГОСТ 12821 (заготовка-поковка Ст.09Г2С гр.IV КП195 ГОСТ 8479-70)</t>
+  </si>
+  <si>
+    <t>ИИУП-000511</t>
+  </si>
+  <si>
+    <t>Фланец х-150-63 ГОСТ 12821 (заготовка-поковка Ст.09Г2С гр.IV КП195 ГОСТ 8479-70)</t>
+  </si>
+  <si>
+    <t>Фланец</t>
+  </si>
+  <si>
+    <t>ИИУП-000514</t>
+  </si>
+  <si>
+    <t>Лист S=0.5*300*600 Алюминий аннодированный матовый 2033-1 (черн/бел)</t>
+  </si>
+  <si>
+    <t>Хомут 60-В Ст.3сп-Ц9.хр. ГОСТ 24137-80 (оц)</t>
+  </si>
+  <si>
+    <t>ИИУП-000515</t>
+  </si>
+  <si>
+    <t>Хомут 90-В Ст.3сп-Ц9.хр. ГОСТ 24137-80</t>
+  </si>
+  <si>
+    <t>Хомут 110-Ст3сп-Ц9.хр ГОСТ 24137-80</t>
+  </si>
+  <si>
+    <t>ИИУП-000517</t>
+  </si>
+  <si>
+    <t>Отвод</t>
+  </si>
+  <si>
+    <t>Отвод 60-57х5-09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>ИИУП-000520</t>
+  </si>
+  <si>
+    <t>Каска защитная СОМ3-55 FavoriT белая</t>
+  </si>
+  <si>
+    <t>НТУП-018438</t>
+  </si>
+  <si>
+    <t>Каска защитная СОМ3-55 FavoriT оранжевая</t>
+  </si>
+  <si>
+    <t>Ботинки кожаные с защитным подноском. Размер 44</t>
+  </si>
+  <si>
+    <t>зимняя спецодежда (ИТР)</t>
+  </si>
+  <si>
+    <t>спец одежда летняя</t>
+  </si>
+  <si>
+    <t>Ботинки кожаные с защитным подноском. Размер 42</t>
   </si>
   <si>
     <t>пар</t>
   </si>
   <si>
-    <t>НТУП-018437</t>
-  </si>
-  <si>
-    <t>Шапка трикотажная зимняя</t>
-  </si>
-  <si>
-    <t>Костюм утепленный Метель</t>
-  </si>
-  <si>
-    <t>ИИУП-000501</t>
-  </si>
-  <si>
-    <t>Доска обрезная 30*150*6м (м3)</t>
-  </si>
-  <si>
-    <t>м3</t>
-  </si>
-  <si>
-    <t>КИУП-000452</t>
-  </si>
-  <si>
-    <t>ИИУП-000502</t>
-  </si>
-  <si>
-    <t>Ботинки кожаные с защитным подноском. Размер 42</t>
-  </si>
-  <si>
-    <t>НТУП-018438</t>
-  </si>
-  <si>
-    <t>спец одежда летняя</t>
-  </si>
-  <si>
-    <t>зимняя спецодежда (ИТР)</t>
-  </si>
-  <si>
-    <t>Каска защитная СОМ3-55 FavoriT белая</t>
-  </si>
-  <si>
-    <t>Каска защитная СОМ3-55 FavoriT оранжевая</t>
-  </si>
-  <si>
     <t>Ботинки кожаные с защитным подноском. Размер 46</t>
   </si>
   <si>
     <t>Ботинки кожаные с защитным подноском. Размер 41</t>
   </si>
   <si>
-    <t>Ботинки кожаные с защитным подноском. Размер 44</t>
-  </si>
-  <si>
     <t>Ботинки кожаные с защитным подноском. Размер 40</t>
   </si>
   <si>
@@ -369,94 +411,40 @@
     <t>Ботинки кожаные с защитным подноском. Размер 39</t>
   </si>
   <si>
+    <t>Ботинки кожаные с защитным подноском. Размер 43</t>
+  </si>
+  <si>
     <t>Ботинки кожаные с защитным подноском. Размер 36</t>
   </si>
   <si>
     <t>Ботинки кожаные с защитным подноском. Размер 38</t>
   </si>
   <si>
-    <t>Ботинки кожаные с защитным подноском. Размер 43</t>
-  </si>
-  <si>
-    <t>Карман инструментального магазина, пластиковый TSG-607-00 (ВТ-40)</t>
-  </si>
-  <si>
-    <t>ИИУП-000503</t>
-  </si>
-  <si>
-    <t>ИИУП-000504</t>
-  </si>
-  <si>
-    <t>ИИУП-000505</t>
-  </si>
-  <si>
-    <t>Труба D89х12 Ст.09Г2 ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Труба D720х18 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-73</t>
-  </si>
-  <si>
-    <t>Труба D720х12 09Г2С ГОСТ 10705-80</t>
-  </si>
-  <si>
-    <t>ИИУП-000506</t>
-  </si>
-  <si>
-    <t>Днище 720х18-09Г2С ГОСТ 6533-78</t>
-  </si>
-  <si>
-    <t>ИИУП-000507</t>
-  </si>
-  <si>
-    <t>л (дм3)</t>
-  </si>
-  <si>
-    <t>Фланец х-150-63 ГОСТ 12821 (заготовка-поковка Ст.09Г2С гр.IV КП195 ГОСТ 8479-70)</t>
-  </si>
-  <si>
-    <t>ИИУП-000511</t>
-  </si>
-  <si>
-    <t>Фланец</t>
-  </si>
-  <si>
-    <t>Фланец 7-100-63 ГОСТ 12821 (заготовка-поковка Ст.09Г2С гр.IV КП195 ГОСТ 8479-70)</t>
-  </si>
-  <si>
-    <t>ИИУП-000513</t>
-  </si>
-  <si>
-    <t>ИИУП-000514</t>
-  </si>
-  <si>
-    <t>Лист S=0.5*300*600 Алюминий аннодированный матовый 2033-1 (черн/бел)</t>
-  </si>
-  <si>
-    <t>Хомут 60-В Ст.3сп-Ц9.хр. ГОСТ 24137-80 (оц)</t>
-  </si>
-  <si>
-    <t>ИИУП-000515</t>
-  </si>
-  <si>
-    <t>Хомут 90-В Ст.3сп-Ц9.хр. ГОСТ 24137-80</t>
-  </si>
-  <si>
-    <t>Хомут 110-Ст3сп-Ц9.хр ГОСТ 24137-80</t>
-  </si>
-  <si>
-    <t>ИИУП-000517</t>
-  </si>
-  <si>
-    <t>Отвод</t>
-  </si>
-  <si>
-    <t>Отвод 60-57х5-09Г2С ГОСТ 17375-2001</t>
-  </si>
-  <si>
-    <t>ИИУП-000520</t>
-  </si>
-  <si>
-    <t>ЛГУП-8173</t>
+    <t>Клапан предохранительный СППК4 ду80 ру40 переделка с автоматического на ручной</t>
+  </si>
+  <si>
+    <t>ЛГУП-8174</t>
+  </si>
+  <si>
+    <t>Шпилька 1-М30-8gx160.09Г2С.019 ОСТ 26-2040-96</t>
+  </si>
+  <si>
+    <t>ИИУП-000523</t>
+  </si>
+  <si>
+    <t>Гайка М20.7Н.09Г2С.019 ОСТ 26-2041-91</t>
+  </si>
+  <si>
+    <t>Шпилька 1-М20-8gx110.09Г2С.019 ОСТ 26-2040-96</t>
+  </si>
+  <si>
+    <t>Шпилька 1-М20-8gx120.09Г2С.019 ОСТ 26-2040-96</t>
+  </si>
+  <si>
+    <t>ИИУП-000526</t>
+  </si>
+  <si>
+    <t>ТЛУП-012402</t>
   </si>
   <si>
     <t>Дверь лев с доводчиком1900х1000 мм(ВхШ) полотно RAL9003(белый)/коробка (RAL 9003)(белый)с цепью</t>
@@ -477,34 +465,37 @@
     <t>Труба D530х12 09Г2С ГОСТ 8731-74</t>
   </si>
   <si>
+    <t>Задвижка клиновая литая 3КЛ 80-63 ХЛ1 30лс76нж, класс герметичности "А" (Р-Р-2 исп.фл.J)</t>
+  </si>
+  <si>
     <t>Задвижка клиновая литая ЗКЛ 80-40 УХЛ1 30лс15нж, класс герм.А (ряд 2, исп.фл.3)</t>
   </si>
   <si>
-    <t>Задвижка клиновая литая 3КЛ 80-63 ХЛ1 30лс76нж, класс герметичности "А" (Р-Р-2 исп.фл.J)</t>
-  </si>
-  <si>
     <t>Круг D370 Ст.20 ГОСТ1050-88</t>
   </si>
   <si>
+    <t>Фланец 1-250-40 09Г2С ГОСТ 12821-80</t>
+  </si>
+  <si>
     <t>Фланец 2-50-40 09Г2С ГОСТ 12821-80</t>
   </si>
   <si>
-    <t>Фланец 1-250-40 09Г2С ГОСТ 12821-80</t>
+    <t>Болт М20-6gх30.58 (S30) ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Гайка М8-6Н.5.ГОСТ 5915-70</t>
+  </si>
+  <si>
+    <t>Шпилька АМ30-6gх180.60.35.III.4.019 ГОСТ 9066-75</t>
+  </si>
+  <si>
+    <t>Шплинт 2х20 ГОСТ 397</t>
   </si>
   <si>
     <t>Шпонка 6х6х20 ГОСТ 23360-78</t>
   </si>
   <si>
-    <t>Шплинт 2х20 ГОСТ 397</t>
-  </si>
-  <si>
-    <t>Шпилька АМ30-6gх180.60.35.III.4.019 ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Гайка М8-6Н.5.ГОСТ 5915-70</t>
-  </si>
-  <si>
-    <t>Болт М20-6gх30.58 (S30) ГОСТ 7798-70</t>
+    <t>Болт М8-6gx12 ГОСТ 7798-70</t>
   </si>
   <si>
     <t>Шпилька М8х350, кл.пр. 8.8, оц</t>
@@ -513,9 +504,6 @@
     <t>Гайка М8-6Н.016 ГОСТ 5915-70</t>
   </si>
   <si>
-    <t>Болт М8-6gx12 ГОСТ 7798-70</t>
-  </si>
-  <si>
     <t>Гайка М10-6Н ГОСТ 5927-70 (размер под ключ S=17)</t>
   </si>
   <si>
@@ -567,36 +555,27 @@
     <t>Панель стеновая ПТСМ 2450х1000х80 RAL 1021 (желт) снаружи/ RAL 9003 (белый) внутри</t>
   </si>
   <si>
-    <t>Шпилька А1М36-6gx220.09Г2С (оцинк.) ГОСТ 9066-75</t>
-  </si>
-  <si>
-    <t>Гайка М16-6Н.8.20.019 ГОСТ 15523-70</t>
-  </si>
-  <si>
-    <t>Гайка АМ36-6Н.20lll.019 ГОСТ 9064-75</t>
+    <t>Труба D219х4 ГОСТ 8734-75/ Ст.В20 ГОСТ 8733-74</t>
   </si>
   <si>
     <t>Труба D25х7 ст.10Г2 ГОСТ 8733-74</t>
   </si>
   <si>
-    <t>Труба D219х4 ГОСТ 8734-75/ Ст.В20 ГОСТ 8733-74</t>
+    <t>Труба D38х9 Ст.09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D68х12 ст.265-09Г2С-4 ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Труба D89х6 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
+  </si>
+  <si>
+    <t>Труба D377х12 ст.09Г2С-К50 ГОСТ 8731-78</t>
   </si>
   <si>
     <t>Швеллер №20У ГОСТ 8240-97/ 325-09Г2С ГОСТ 19281-2014</t>
   </si>
   <si>
-    <t>Труба D377х12 ст.09Г2С-К50 ГОСТ 8731-78</t>
-  </si>
-  <si>
-    <t>Труба D89х6 ГОСТ 8732-78/ 09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
-    <t>Труба D68х12 ст.265-09Г2С-4 ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Труба D38х9 Ст.09Г2С ГОСТ 8731-74</t>
-  </si>
-  <si>
     <t>Днище 720х12-09Г2С ГОСТ 6533-78</t>
   </si>
   <si>
@@ -609,108 +588,78 @@
     <t>Днище 377х12-09Г2С ГОСТ 6533-78</t>
   </si>
   <si>
-    <t>Крышка НТ.ЕС.040.001.003 А (Заглушка 2-450-4,0-092ГС АТК 24.200.02-90)</t>
-  </si>
-  <si>
-    <t>Скотч широкий</t>
-  </si>
-  <si>
-    <t>Растворитель Р-4 ГОСТ 7827-74</t>
+    <t>Фланец 3-450-40 09Г2С ГОСТ 12815-80 (из поковки гр.IV КП 245 ГОСТ 8479-70)</t>
+  </si>
+  <si>
+    <t>Фланец 50-16-11-1-Е-09Г2С-IV ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец 80-40-11-1-E-09Г2С ГОСТ 33259-2015</t>
+  </si>
+  <si>
+    <t>Фланец х-50-63 ГОСТ 12821 (заготовка-поковка Ст.09Г2С  гр.IV КП195 ГОСТ 8479-70)</t>
   </si>
   <si>
     <t>Фланец х-80-63 ГОСТ 12821 (заготовка-поковка Ст.09Г2С гр.IV КП195 ГОСТ 8479-70)</t>
   </si>
   <si>
-    <t>Фланец х-50-63 ГОСТ 12821 (заготовка-поковка Ст.09Г2С  гр.IV КП195 ГОСТ 8479-70)</t>
-  </si>
-  <si>
-    <t>Фланец 80-40-11-1-E-09Г2С ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Фланец 50-16-11-1-Е-09Г2С-IV ГОСТ 33259-2015</t>
-  </si>
-  <si>
-    <t>Фланец 3-450-40 09Г2С ГОСТ 12815-80 (из поковки гр.IV КП 245 ГОСТ 8479-70)</t>
-  </si>
-  <si>
-    <t>Заглушка 159х10 ст.09Г2С ГОСТ 17379-01</t>
-  </si>
-  <si>
-    <t>Заглушка 4-250-6,3-13ХФА АТК 24.200.02.90</t>
-  </si>
-  <si>
-    <t>Отвод 45-89х8-09Г2С ГОСТ 17375-2001</t>
+    <t>Круг D165 09Г2С-8-ТО ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Круг D10 ГОСТ 2590-2006/ Ст.20 ГОСТ 1050-88</t>
+  </si>
+  <si>
+    <t>Круг D240 ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Круг D450 Ст.09Г2С ГОСТ 2590-2006</t>
+  </si>
+  <si>
+    <t>Лист S=10 ГОСТ19903-74/Ст.09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Лист S=2 ОК360В-4-III-Ст.3кп ГОСТ 16523-97</t>
+  </si>
+  <si>
+    <t>Лист S=3,0 ГОСТ 19903-74/09Г2С ГОСТ 19281-89</t>
+  </si>
+  <si>
+    <t>Лист ромб. О-ПН-4,0 Ст.09Г2С ГОСТ 8568-77</t>
+  </si>
+  <si>
+    <t>Тройник 57х5 09Г2С ГОСТ 17376-2001</t>
+  </si>
+  <si>
+    <t>Тройник 159х8 09Г2С ГОСТ 17376-2001</t>
+  </si>
+  <si>
+    <t>Тройник 89х6 ст.09Г2С ГОСТ 17376-2001</t>
+  </si>
+  <si>
+    <t>Переход 159х8-108х8 ст.09Г2С ГОСТ 17378-01</t>
+  </si>
+  <si>
+    <t>Переход 89х8-76х8 ст. 09Г2С ГОСТ 17378-01</t>
+  </si>
+  <si>
+    <t>Переход К-89х6-57х6-09Г2С ГОСТ 17378</t>
+  </si>
+  <si>
+    <t>Отвод 90-108х8 ст.09Г2С ГОСТ 17375-2001</t>
+  </si>
+  <si>
+    <t>Отвод 45-57х6 09Г2С ГОСТ 17375-01</t>
+  </si>
+  <si>
+    <t>Отвод 90-57х6 09Г2С ГОСТ 17375-01</t>
+  </si>
+  <si>
+    <t>Отвод 90-89х6-09Г2С ГОСТ 17375-2001</t>
   </si>
   <si>
     <t>Отвод 90-159х10-09Г2С ГОСТ 17375-2001</t>
   </si>
   <si>
-    <t>Отвод 90-57х6 09Г2С ГОСТ 17375-01</t>
-  </si>
-  <si>
-    <t>Отвод 90-89х8 Ст.09Г2С ГОСТ 17375-2001</t>
-  </si>
-  <si>
-    <t>Тройник 159х10 ст.09Г2С ГОСТ 17376-01</t>
-  </si>
-  <si>
-    <t>Тройник 89х8 ст.09Г2С ГОСТ 17376-2001</t>
-  </si>
-  <si>
-    <t>Переход 89х8-57х5 ст.09Г2С ГОСТ 17378-2001</t>
-  </si>
-  <si>
-    <t>Круг D240 ст.09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Круг D450 Ст.09Г2С ГОСТ 2590-2006</t>
-  </si>
-  <si>
-    <t>Лист S=10 ГОСТ19903-74/Ст.09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Лист S=2 ОК360В-4-III-Ст.3кп ГОСТ 16523-97</t>
-  </si>
-  <si>
-    <t>Лист S=3,0 ГОСТ 19903-74/09Г2С ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Лист ромб. О-ПН-4,0 Ст.09Г2С ГОСТ 8568-77</t>
-  </si>
-  <si>
-    <t>Круг D165 09Г2С-8-ТО ГОСТ 19281-89</t>
-  </si>
-  <si>
-    <t>Круг D10 ГОСТ 2590-2006/ Ст.20 ГОСТ 1050-88</t>
-  </si>
-  <si>
-    <t>Переход 159х8-108х8 ст.09Г2С ГОСТ 17378-01</t>
-  </si>
-  <si>
-    <t>Тройник 89х6 ст.09Г2С ГОСТ 17376-2001</t>
-  </si>
-  <si>
-    <t>Тройник 159х8 09Г2С ГОСТ 17376-2001</t>
-  </si>
-  <si>
-    <t>Тройник 57х5 09Г2С ГОСТ 17376-2001</t>
-  </si>
-  <si>
-    <t>Переход 89х8-76х8 ст. 09Г2С ГОСТ 17378-01</t>
-  </si>
-  <si>
-    <t>Переход К-89х6-57х6-09Г2С ГОСТ 17378</t>
-  </si>
-  <si>
-    <t>Отвод 90-108х8 ст.09Г2С ГОСТ 17375-2001</t>
-  </si>
-  <si>
-    <t>Отвод 45-57х6 09Г2С ГОСТ 17375-01</t>
-  </si>
-  <si>
-    <t>Отвод 90-89х6-09Г2С ГОСТ 17375-2001</t>
-  </si>
-  <si>
     <t>Отвод 60-89х6-09Г2С ГОСТ 17375-2001</t>
   </si>
   <si>
@@ -718,6 +667,18 @@
   </si>
   <si>
     <t>MV-клемма проводника Rd8</t>
+  </si>
+  <si>
+    <t>Гайка М30.7Н.09Г2С.019 ОСТ 26-2041-96</t>
+  </si>
+  <si>
+    <t>Лента упаковочная полипропиленовая 12х0,6мм</t>
+  </si>
+  <si>
+    <t>Стропа Magnapack</t>
+  </si>
+  <si>
+    <t>Скотч защитный термоусадочный Magnapak цвет белый, 5 см</t>
   </si>
   <si>
     <t>Пленка термоусадочная Magnapak белая (ширина 9,8 м, толщина 190 мкм)</t>
@@ -1157,7 +1118,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F268"/>
+  <dimension ref="A1:F257"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" style="1" customWidth="1"/>
@@ -1230,7 +1191,7 @@
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="8" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D4" s="5">
         <v>1</v>
@@ -1248,7 +1209,7 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="8" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
@@ -1266,7 +1227,7 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D6" s="5">
         <v>5.7389999999999999</v>
@@ -1302,7 +1263,7 @@
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D8" s="7">
         <v>1438.2</v>
@@ -1320,7 +1281,7 @@
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D9" s="7">
         <v>2323.62</v>
@@ -1338,7 +1299,7 @@
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D10" s="7">
         <v>2912.7</v>
@@ -1377,7 +1338,7 @@
         <v>16</v>
       </c>
       <c r="D12" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>7</v>
@@ -1413,7 +1374,7 @@
         <v>16</v>
       </c>
       <c r="D14" s="5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>7</v>
@@ -1431,7 +1392,7 @@
         <v>16</v>
       </c>
       <c r="D15" s="5">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>7</v>
@@ -1449,7 +1410,7 @@
         <v>16</v>
       </c>
       <c r="D16" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>7</v>
@@ -1467,7 +1428,7 @@
         <v>16</v>
       </c>
       <c r="D17" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>7</v>
@@ -1485,7 +1446,7 @@
         <v>16</v>
       </c>
       <c r="D18" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>7</v>
@@ -1503,7 +1464,7 @@
         <v>16</v>
       </c>
       <c r="D19" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>7</v>
@@ -1521,7 +1482,7 @@
         <v>16</v>
       </c>
       <c r="D20" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>7</v>
@@ -1539,7 +1500,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>7</v>
@@ -1557,7 +1518,7 @@
         <v>16</v>
       </c>
       <c r="D22" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>7</v>
@@ -1629,7 +1590,7 @@
         <v>16</v>
       </c>
       <c r="D26" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>7</v>
@@ -1647,7 +1608,7 @@
         <v>16</v>
       </c>
       <c r="D27" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>7</v>
@@ -1665,7 +1626,7 @@
         <v>16</v>
       </c>
       <c r="D28" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>7</v>
@@ -1719,7 +1680,7 @@
         <v>16</v>
       </c>
       <c r="D31" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>7</v>
@@ -1755,7 +1716,7 @@
         <v>16</v>
       </c>
       <c r="D33" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>7</v>
@@ -1773,7 +1734,7 @@
         <v>16</v>
       </c>
       <c r="D34" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>7</v>
@@ -1827,7 +1788,7 @@
         <v>16</v>
       </c>
       <c r="D37" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>7</v>
@@ -1881,7 +1842,7 @@
         <v>16</v>
       </c>
       <c r="D40" s="5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>7</v>
@@ -1899,7 +1860,7 @@
         <v>16</v>
       </c>
       <c r="D41" s="5">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>7</v>
@@ -1917,7 +1878,7 @@
         <v>16</v>
       </c>
       <c r="D42" s="5">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>7</v>
@@ -1935,7 +1896,7 @@
         <v>16</v>
       </c>
       <c r="D43" s="5">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>7</v>
@@ -1950,7 +1911,7 @@
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D44" s="5">
         <v>1</v>
@@ -1989,7 +1950,7 @@
         <v>16</v>
       </c>
       <c r="D46" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>7</v>
@@ -2007,7 +1968,7 @@
         <v>16</v>
       </c>
       <c r="D47" s="5">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>7</v>
@@ -2025,7 +1986,7 @@
         <v>16</v>
       </c>
       <c r="D48" s="5">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>7</v>
@@ -2043,7 +2004,7 @@
         <v>16</v>
       </c>
       <c r="D49" s="5">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>7</v>
@@ -2058,7 +2019,7 @@
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D50" s="5">
         <v>1</v>
@@ -2079,7 +2040,7 @@
         <v>16</v>
       </c>
       <c r="D51" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>7</v>
@@ -2097,7 +2058,7 @@
         <v>16</v>
       </c>
       <c r="D52" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>7</v>
@@ -2115,7 +2076,7 @@
         <v>16</v>
       </c>
       <c r="D53" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>7</v>
@@ -2151,7 +2112,7 @@
         <v>16</v>
       </c>
       <c r="D55" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>7</v>
@@ -2169,7 +2130,7 @@
         <v>16</v>
       </c>
       <c r="D56" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>7</v>
@@ -2187,7 +2148,7 @@
         <v>16</v>
       </c>
       <c r="D57" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>7</v>
@@ -2205,7 +2166,7 @@
         <v>16</v>
       </c>
       <c r="D58" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>7</v>
@@ -2241,7 +2202,7 @@
         <v>16</v>
       </c>
       <c r="D60" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>7</v>
@@ -2259,7 +2220,7 @@
         <v>16</v>
       </c>
       <c r="D61" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>7</v>
@@ -2277,7 +2238,7 @@
         <v>16</v>
       </c>
       <c r="D62" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>7</v>
@@ -2295,7 +2256,7 @@
         <v>16</v>
       </c>
       <c r="D63" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>7</v>
@@ -2313,7 +2274,7 @@
         <v>16</v>
       </c>
       <c r="D64" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>7</v>
@@ -2331,7 +2292,7 @@
         <v>16</v>
       </c>
       <c r="D65" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>7</v>
@@ -2349,7 +2310,7 @@
         <v>16</v>
       </c>
       <c r="D66" s="5">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>7</v>
@@ -2367,7 +2328,7 @@
         <v>16</v>
       </c>
       <c r="D67" s="5">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>7</v>
@@ -2385,7 +2346,7 @@
         <v>16</v>
       </c>
       <c r="D68" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>7</v>
@@ -2403,7 +2364,7 @@
         <v>16</v>
       </c>
       <c r="D69" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>7</v>
@@ -2439,7 +2400,7 @@
         <v>16</v>
       </c>
       <c r="D71" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>7</v>
@@ -2475,7 +2436,7 @@
         <v>16</v>
       </c>
       <c r="D73" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>7</v>
@@ -2511,7 +2472,7 @@
         <v>16</v>
       </c>
       <c r="D75" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>7</v>
@@ -2529,7 +2490,7 @@
         <v>16</v>
       </c>
       <c r="D76" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>7</v>
@@ -2547,7 +2508,7 @@
         <v>16</v>
       </c>
       <c r="D77" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>7</v>
@@ -2565,7 +2526,7 @@
         <v>16</v>
       </c>
       <c r="D78" s="5">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>7</v>
@@ -2583,7 +2544,7 @@
         <v>16</v>
       </c>
       <c r="D79" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>7</v>
@@ -2601,7 +2562,7 @@
         <v>16</v>
       </c>
       <c r="D80" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>7</v>
@@ -2637,7 +2598,7 @@
         <v>16</v>
       </c>
       <c r="D82" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>7</v>
@@ -2655,7 +2616,7 @@
         <v>16</v>
       </c>
       <c r="D83" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>7</v>
@@ -2709,7 +2670,7 @@
         <v>16</v>
       </c>
       <c r="D86" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>7</v>
@@ -2727,7 +2688,7 @@
         <v>16</v>
       </c>
       <c r="D87" s="5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>7</v>
@@ -2742,10 +2703,10 @@
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D88" s="5">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>7</v>
@@ -2760,10 +2721,10 @@
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="8" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D89" s="5">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>7</v>
@@ -2778,7 +2739,7 @@
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="8" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D90" s="5">
         <v>342</v>
@@ -2796,10 +2757,10 @@
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D91" s="5">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>7</v>
@@ -2814,10 +2775,10 @@
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D92" s="5">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>7</v>
@@ -2832,10 +2793,10 @@
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D93" s="5">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>7</v>
@@ -2850,10 +2811,10 @@
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D94" s="5">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>7</v>
@@ -2868,7 +2829,7 @@
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D95" s="5">
         <v>180</v>
@@ -2886,10 +2847,10 @@
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="8" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D96" s="5">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>7</v>
@@ -2904,10 +2865,10 @@
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="8" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D97" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E97" s="6" t="s">
         <v>7</v>
@@ -2922,16 +2883,16 @@
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="8" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="D98" s="5">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2940,16 +2901,16 @@
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D99" s="5">
-        <v>576</v>
+        <v>540</v>
       </c>
       <c r="E99" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2958,16 +2919,16 @@
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="8" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D100" s="5">
-        <v>540</v>
+        <v>18</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2976,16 +2937,16 @@
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D101" s="5">
+        <v>576</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F101" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="D101" s="5">
-        <v>144</v>
-      </c>
-      <c r="E101" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F101" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2994,7 +2955,7 @@
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="8" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D102" s="5">
         <v>36</v>
@@ -3012,7 +2973,7 @@
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="8" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D103" s="5">
         <v>45</v>
@@ -3030,7 +2991,7 @@
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="8" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D104" s="5">
         <v>9</v>
@@ -3084,7 +3045,7 @@
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D107" s="5">
         <v>1</v>
@@ -3120,7 +3081,7 @@
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D109" s="5">
         <v>1</v>
@@ -3141,7 +3102,7 @@
         <v>31</v>
       </c>
       <c r="D110" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>14</v>
@@ -3159,7 +3120,7 @@
         <v>33</v>
       </c>
       <c r="D111" s="5">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="E111" s="6" t="s">
         <v>14</v>
@@ -3177,7 +3138,7 @@
         <v>34</v>
       </c>
       <c r="D112" s="5">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>14</v>
@@ -3186,7 +3147,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -3194,101 +3155,101 @@
       <c r="C113" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D113" s="7">
-        <v>1000</v>
+      <c r="D113" s="5">
+        <v>3</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
         <v>113</v>
       </c>
       <c r="B114" s="4"/>
       <c r="C114" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D114" s="7">
-        <v>1000</v>
+        <v>36</v>
+      </c>
+      <c r="D114" s="5">
+        <v>3</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
         <v>114</v>
       </c>
       <c r="B115" s="4"/>
       <c r="C115" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D115" s="5">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
         <v>115</v>
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D116" s="7">
-        <v>1000</v>
+        <v>38</v>
+      </c>
+      <c r="D116" s="5">
+        <v>15</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F116" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
         <v>116</v>
       </c>
       <c r="B117" s="4"/>
       <c r="C117" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D117" s="7">
-        <v>1000</v>
+        <v>39</v>
+      </c>
+      <c r="D117" s="5">
+        <v>15</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
         <v>117</v>
       </c>
       <c r="B118" s="4"/>
       <c r="C118" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D118" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>32</v>
@@ -3300,16 +3261,16 @@
       </c>
       <c r="B119" s="4"/>
       <c r="C119" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D119" s="5">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E119" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3318,16 +3279,16 @@
       </c>
       <c r="B120" s="4"/>
       <c r="C120" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D120" s="5">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3336,7 +3297,7 @@
       </c>
       <c r="B121" s="4"/>
       <c r="C121" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D121" s="5">
         <v>60</v>
@@ -3345,7 +3306,7 @@
         <v>14</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3354,16 +3315,16 @@
       </c>
       <c r="B122" s="4"/>
       <c r="C122" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D122" s="5">
         <v>10</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3372,16 +3333,16 @@
       </c>
       <c r="B123" s="4"/>
       <c r="C123" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D123" s="5">
-        <v>12</v>
+        <v>46</v>
+      </c>
+      <c r="D123" s="7">
+        <v>2000</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3390,16 +3351,16 @@
       </c>
       <c r="B124" s="4"/>
       <c r="C124" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D124" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3411,13 +3372,13 @@
         <v>49</v>
       </c>
       <c r="D125" s="5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E125" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3429,16 +3390,16 @@
         <v>50</v>
       </c>
       <c r="D126" s="5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="3">
         <v>126</v>
       </c>
@@ -3447,70 +3408,70 @@
         <v>51</v>
       </c>
       <c r="D127" s="5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
         <v>127</v>
       </c>
       <c r="B128" s="4"/>
       <c r="C128" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D128" s="7">
+        <v>1000</v>
+      </c>
+      <c r="E128" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D128" s="5">
-        <v>3</v>
-      </c>
-      <c r="E128" s="6" t="s">
-        <v>14</v>
-      </c>
       <c r="F128" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="3">
         <v>128</v>
       </c>
       <c r="B129" s="4"/>
       <c r="C129" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D129" s="5">
-        <v>3</v>
+        <v>54</v>
+      </c>
+      <c r="D129" s="7">
+        <v>1000</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
         <v>129</v>
       </c>
       <c r="B130" s="4"/>
       <c r="C130" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D130" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="3">
         <v>130</v>
       </c>
@@ -3519,16 +3480,16 @@
         <v>56</v>
       </c>
       <c r="D131" s="7">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
         <v>131</v>
       </c>
@@ -3536,14 +3497,14 @@
       <c r="C132" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D132" s="5">
-        <v>5</v>
+      <c r="D132" s="7">
+        <v>1000</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3552,7 +3513,7 @@
       </c>
       <c r="B133" s="4"/>
       <c r="C133" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D133" s="5">
         <v>196</v>
@@ -3591,7 +3552,7 @@
         <v>61</v>
       </c>
       <c r="D135" s="5">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="E135" s="6" t="s">
         <v>7</v>
@@ -3627,7 +3588,7 @@
         <v>64</v>
       </c>
       <c r="D137" s="5">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="E137" s="6" t="s">
         <v>7</v>
@@ -3663,7 +3624,7 @@
         <v>66</v>
       </c>
       <c r="D139" s="5">
-        <v>115</v>
+        <v>270</v>
       </c>
       <c r="E139" s="6" t="s">
         <v>7</v>
@@ -3678,10 +3639,10 @@
       </c>
       <c r="B140" s="4"/>
       <c r="C140" s="8" t="s">
-        <v>67</v>
+        <v>163</v>
       </c>
       <c r="D140" s="5">
-        <v>270</v>
+        <v>27</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>7</v>
@@ -3696,10 +3657,10 @@
       </c>
       <c r="B141" s="4"/>
       <c r="C141" s="8" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D141" s="5">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="E141" s="6" t="s">
         <v>7</v>
@@ -3714,10 +3675,10 @@
       </c>
       <c r="B142" s="4"/>
       <c r="C142" s="8" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D142" s="5">
-        <v>135</v>
+        <v>270</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>7</v>
@@ -3732,10 +3693,10 @@
       </c>
       <c r="B143" s="4"/>
       <c r="C143" s="8" t="s">
-        <v>169</v>
+        <v>67</v>
       </c>
       <c r="D143" s="5">
-        <v>270</v>
+        <v>135</v>
       </c>
       <c r="E143" s="6" t="s">
         <v>7</v>
@@ -3753,7 +3714,7 @@
         <v>68</v>
       </c>
       <c r="D144" s="5">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>7</v>
@@ -3768,10 +3729,10 @@
       </c>
       <c r="B145" s="4"/>
       <c r="C145" s="8" t="s">
-        <v>69</v>
+        <v>166</v>
       </c>
       <c r="D145" s="5">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="E145" s="6" t="s">
         <v>7</v>
@@ -3786,10 +3747,10 @@
       </c>
       <c r="B146" s="4"/>
       <c r="C146" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D146" s="5">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>7</v>
@@ -3804,10 +3765,10 @@
       </c>
       <c r="B147" s="4"/>
       <c r="C147" s="8" t="s">
-        <v>171</v>
+        <v>69</v>
       </c>
       <c r="D147" s="5">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="E147" s="6" t="s">
         <v>7</v>
@@ -3822,10 +3783,10 @@
       </c>
       <c r="B148" s="4"/>
       <c r="C148" s="8" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="D148" s="5">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>7</v>
@@ -3840,10 +3801,10 @@
       </c>
       <c r="B149" s="4"/>
       <c r="C149" s="8" t="s">
-        <v>172</v>
+        <v>70</v>
       </c>
       <c r="D149" s="5">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="E149" s="6" t="s">
         <v>7</v>
@@ -3861,7 +3822,7 @@
         <v>71</v>
       </c>
       <c r="D150" s="5">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>7</v>
@@ -3876,10 +3837,10 @@
       </c>
       <c r="B151" s="4"/>
       <c r="C151" s="8" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="D151" s="5">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="E151" s="6" t="s">
         <v>7</v>
@@ -3894,10 +3855,10 @@
       </c>
       <c r="B152" s="4"/>
       <c r="C152" s="8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D152" s="5">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>7</v>
@@ -3912,7 +3873,7 @@
       </c>
       <c r="B153" s="4"/>
       <c r="C153" s="8" t="s">
-        <v>174</v>
+        <v>72</v>
       </c>
       <c r="D153" s="5">
         <v>61</v>
@@ -3933,7 +3894,7 @@
         <v>73</v>
       </c>
       <c r="D154" s="5">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>7</v>
@@ -3950,8 +3911,8 @@
       <c r="C155" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D155" s="5">
-        <v>405</v>
+      <c r="D155" s="7">
+        <v>2700000</v>
       </c>
       <c r="E155" s="6" t="s">
         <v>75</v>
@@ -3966,10 +3927,10 @@
       </c>
       <c r="B156" s="4"/>
       <c r="C156" s="8" t="s">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="D156" s="7">
-        <v>1350000</v>
+        <v>2350</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>75</v>
@@ -3984,10 +3945,10 @@
       </c>
       <c r="B157" s="4"/>
       <c r="C157" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D157" s="7">
-        <v>1350</v>
+        <v>1350000</v>
       </c>
       <c r="E157" s="6" t="s">
         <v>75</v>
@@ -4002,10 +3963,10 @@
       </c>
       <c r="B158" s="4"/>
       <c r="C158" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D158" s="7">
-        <v>1350000</v>
+        <v>1350</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>75</v>
@@ -4020,10 +3981,10 @@
       </c>
       <c r="B159" s="4"/>
       <c r="C159" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D159" s="7">
-        <v>2700000</v>
+        <v>1350000</v>
       </c>
       <c r="E159" s="6" t="s">
         <v>75</v>
@@ -4038,10 +3999,10 @@
       </c>
       <c r="B160" s="4"/>
       <c r="C160" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="D160" s="7">
-        <v>2350</v>
+        <v>79</v>
+      </c>
+      <c r="D160" s="5">
+        <v>405</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>75</v>
@@ -4056,10 +4017,10 @@
       </c>
       <c r="B161" s="4"/>
       <c r="C161" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="D161" s="7">
-        <v>1350</v>
+        <v>80</v>
+      </c>
+      <c r="D161" s="5">
+        <v>675</v>
       </c>
       <c r="E161" s="6" t="s">
         <v>75</v>
@@ -4074,10 +4035,10 @@
       </c>
       <c r="B162" s="4"/>
       <c r="C162" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D162" s="5">
-        <v>675</v>
+        <v>172</v>
+      </c>
+      <c r="D162" s="7">
+        <v>1350</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>75</v>
@@ -4092,16 +4053,16 @@
       </c>
       <c r="B163" s="4"/>
       <c r="C163" s="8" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="D163" s="5">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4110,16 +4071,16 @@
       </c>
       <c r="B164" s="4"/>
       <c r="C164" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D164" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4128,7 +4089,7 @@
       </c>
       <c r="B165" s="4"/>
       <c r="C165" s="8" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="D165" s="5">
         <v>10</v>
@@ -4137,7 +4098,7 @@
         <v>14</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4146,7 +4107,7 @@
       </c>
       <c r="B166" s="4"/>
       <c r="C166" s="8" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D166" s="5">
         <v>10</v>
@@ -4155,7 +4116,7 @@
         <v>14</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4164,16 +4125,16 @@
       </c>
       <c r="B167" s="4"/>
       <c r="C167" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D167" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E167" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4182,7 +4143,7 @@
       </c>
       <c r="B168" s="4"/>
       <c r="C168" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D168" s="5">
         <v>20</v>
@@ -4191,7 +4152,7 @@
         <v>14</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4200,16 +4161,16 @@
       </c>
       <c r="B169" s="4"/>
       <c r="C169" s="8" t="s">
-        <v>177</v>
+        <v>33</v>
       </c>
       <c r="D169" s="5">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E169" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4218,16 +4179,16 @@
       </c>
       <c r="B170" s="4"/>
       <c r="C170" s="8" t="s">
-        <v>83</v>
+        <v>173</v>
       </c>
       <c r="D170" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4236,16 +4197,16 @@
       </c>
       <c r="B171" s="4"/>
       <c r="C171" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D171" s="5">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E171" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4257,13 +4218,13 @@
         <v>86</v>
       </c>
       <c r="D172" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4272,16 +4233,16 @@
       </c>
       <c r="B173" s="4"/>
       <c r="C173" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D173" s="5">
         <v>10</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="174" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4290,7 +4251,7 @@
       </c>
       <c r="B174" s="4"/>
       <c r="C174" s="8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D174" s="5">
         <v>2</v>
@@ -4299,7 +4260,7 @@
         <v>7</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4326,7 +4287,7 @@
       </c>
       <c r="B176" s="4"/>
       <c r="C176" s="8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D176" s="5">
         <v>2</v>
@@ -4344,16 +4305,16 @@
       </c>
       <c r="B177" s="4"/>
       <c r="C177" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D177" s="5">
+        <v>2</v>
+      </c>
+      <c r="E177" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F177" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="D177" s="5">
-        <v>5</v>
-      </c>
-      <c r="E177" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F177" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="178" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4362,13 +4323,13 @@
       </c>
       <c r="B178" s="4"/>
       <c r="C178" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D178" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F178" s="4" t="s">
         <v>94</v>
@@ -4380,16 +4341,16 @@
       </c>
       <c r="B179" s="4"/>
       <c r="C179" s="8" t="s">
-        <v>96</v>
+        <v>176</v>
       </c>
       <c r="D179" s="5">
-        <v>5</v>
+        <v>114.3</v>
       </c>
       <c r="E179" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="180" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4398,16 +4359,16 @@
       </c>
       <c r="B180" s="4"/>
       <c r="C180" s="8" t="s">
-        <v>33</v>
+        <v>177</v>
       </c>
       <c r="D180" s="5">
-        <v>1</v>
+        <v>24.48</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4416,16 +4377,16 @@
       </c>
       <c r="B181" s="4"/>
       <c r="C181" s="8" t="s">
-        <v>98</v>
+        <v>178</v>
       </c>
       <c r="D181" s="5">
-        <v>7</v>
+        <v>19.8</v>
       </c>
       <c r="E181" s="6" t="s">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4434,16 +4395,16 @@
       </c>
       <c r="B182" s="4"/>
       <c r="C182" s="8" t="s">
-        <v>46</v>
+        <v>179</v>
       </c>
       <c r="D182" s="5">
-        <v>2</v>
+        <v>68.58</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="183" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4452,16 +4413,16 @@
       </c>
       <c r="B183" s="4"/>
       <c r="C183" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="D183" s="5">
+        <v>180</v>
+      </c>
+      <c r="D183" s="7">
+        <v>3809</v>
+      </c>
+      <c r="E183" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E183" s="6" t="s">
-        <v>93</v>
-      </c>
       <c r="F183" s="4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="184" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4470,16 +4431,16 @@
       </c>
       <c r="B184" s="4"/>
       <c r="C184" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="D184" s="5">
-        <v>45</v>
+        <v>180</v>
+      </c>
+      <c r="D184" s="7">
+        <v>5422.6</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="185" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4488,16 +4449,16 @@
       </c>
       <c r="B185" s="4"/>
       <c r="C185" s="8" t="s">
-        <v>105</v>
+        <v>181</v>
       </c>
       <c r="D185" s="5">
-        <v>23</v>
+        <v>761.65</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="186" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4506,16 +4467,16 @@
       </c>
       <c r="B186" s="4"/>
       <c r="C186" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D186" s="5">
-        <v>23</v>
+        <v>96</v>
+      </c>
+      <c r="D186" s="7">
+        <v>2997</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="187" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4524,16 +4485,16 @@
       </c>
       <c r="B187" s="4"/>
       <c r="C187" s="8" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D187" s="5">
-        <v>22</v>
+        <v>57.42</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4542,16 +4503,16 @@
       </c>
       <c r="B188" s="4"/>
       <c r="C188" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D188" s="5">
-        <v>1</v>
+        <v>182</v>
+      </c>
+      <c r="D188" s="7">
+        <v>16888.560000000001</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="189" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4560,16 +4521,16 @@
       </c>
       <c r="B189" s="4"/>
       <c r="C189" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D189" s="5">
-        <v>6</v>
+        <v>98</v>
+      </c>
+      <c r="D189" s="7">
+        <v>2630.59</v>
       </c>
       <c r="E189" s="6" t="s">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="190" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4578,16 +4539,16 @@
       </c>
       <c r="B190" s="4"/>
       <c r="C190" s="8" t="s">
-        <v>110</v>
+        <v>183</v>
       </c>
       <c r="D190" s="5">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4596,16 +4557,16 @@
       </c>
       <c r="B191" s="4"/>
       <c r="C191" s="8" t="s">
-        <v>111</v>
+        <v>184</v>
       </c>
       <c r="D191" s="5">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="E191" s="6" t="s">
-        <v>93</v>
+        <v>7</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="192" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4614,16 +4575,16 @@
       </c>
       <c r="B192" s="4"/>
       <c r="C192" s="8" t="s">
-        <v>112</v>
+        <v>185</v>
       </c>
       <c r="D192" s="5">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>93</v>
+        <v>7</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4632,16 +4593,16 @@
       </c>
       <c r="B193" s="4"/>
       <c r="C193" s="8" t="s">
-        <v>113</v>
+        <v>186</v>
       </c>
       <c r="D193" s="5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E193" s="6" t="s">
-        <v>93</v>
+        <v>7</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="194" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4650,160 +4611,160 @@
       </c>
       <c r="B194" s="4"/>
       <c r="C194" s="8" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="D194" s="5">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="3">
         <v>194</v>
       </c>
       <c r="B195" s="4"/>
       <c r="C195" s="8" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="D195" s="5">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E195" s="6" t="s">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="3">
         <v>195</v>
       </c>
       <c r="B196" s="4"/>
       <c r="C196" s="8" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D196" s="5">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="3">
         <v>196</v>
       </c>
       <c r="B197" s="4"/>
       <c r="C197" s="8" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="D197" s="5">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E197" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="3">
         <v>197</v>
       </c>
       <c r="B198" s="4"/>
       <c r="C198" s="8" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D198" s="5">
-        <v>225</v>
+        <v>72</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="3">
         <v>198</v>
       </c>
       <c r="B199" s="4"/>
       <c r="C199" s="8" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D199" s="5">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="E199" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="3">
         <v>199</v>
       </c>
       <c r="B200" s="4"/>
       <c r="C200" s="8" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="D200" s="5">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="3">
         <v>200</v>
       </c>
       <c r="B201" s="4"/>
       <c r="C201" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="D201" s="5">
-        <v>720</v>
+        <v>189</v>
+      </c>
+      <c r="D201" s="7">
+        <v>1158</v>
       </c>
       <c r="E201" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="3">
         <v>201</v>
       </c>
       <c r="B202" s="4"/>
       <c r="C202" s="8" t="s">
-        <v>183</v>
+        <v>104</v>
       </c>
       <c r="D202" s="5">
-        <v>24.48</v>
+        <v>6</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="203" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4812,16 +4773,16 @@
       </c>
       <c r="B203" s="4"/>
       <c r="C203" s="8" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D203" s="5">
-        <v>114.3</v>
+        <v>168</v>
       </c>
       <c r="E203" s="6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F203" s="4" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="204" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4830,16 +4791,16 @@
       </c>
       <c r="B204" s="4"/>
       <c r="C204" s="8" t="s">
-        <v>121</v>
+        <v>191</v>
       </c>
       <c r="D204" s="5">
-        <v>57.42</v>
+        <v>636</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="205" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4848,16 +4809,16 @@
       </c>
       <c r="B205" s="4"/>
       <c r="C205" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="D205" s="7">
-        <v>16888.560000000001</v>
+        <v>192</v>
+      </c>
+      <c r="D205" s="5">
+        <v>165.06</v>
       </c>
       <c r="E205" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="206" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4866,16 +4827,16 @@
       </c>
       <c r="B206" s="4"/>
       <c r="C206" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="D206" s="7">
-        <v>2630.59</v>
+        <v>193</v>
+      </c>
+      <c r="D206" s="5">
+        <v>9</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="207" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4884,16 +4845,16 @@
       </c>
       <c r="B207" s="4"/>
       <c r="C207" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D207" s="7">
-        <v>2997</v>
+        <v>106</v>
+      </c>
+      <c r="D207" s="5">
+        <v>0.63</v>
       </c>
       <c r="E207" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4902,16 +4863,16 @@
       </c>
       <c r="B208" s="4"/>
       <c r="C208" s="8" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="D208" s="5">
-        <v>761.65</v>
+        <v>594.17999999999995</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="209" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4920,16 +4881,16 @@
       </c>
       <c r="B209" s="4"/>
       <c r="C209" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="D209" s="7">
-        <v>5422.6</v>
+        <v>195</v>
+      </c>
+      <c r="D209" s="5">
+        <v>754.4</v>
       </c>
       <c r="E209" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="210" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4938,16 +4899,16 @@
       </c>
       <c r="B210" s="4"/>
       <c r="C210" s="8" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="D210" s="7">
-        <v>3809</v>
+        <v>1808.82</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="211" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4956,16 +4917,16 @@
       </c>
       <c r="B211" s="4"/>
       <c r="C211" s="8" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="D211" s="5">
-        <v>68.58</v>
+        <v>9</v>
       </c>
       <c r="E211" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="212" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4974,16 +4935,16 @@
       </c>
       <c r="B212" s="4"/>
       <c r="C212" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="D212" s="5">
-        <v>19.8</v>
+        <v>198</v>
+      </c>
+      <c r="D212" s="7">
+        <v>14270.1</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="213" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4992,16 +4953,16 @@
       </c>
       <c r="B213" s="4"/>
       <c r="C213" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="D213" s="5">
-        <v>36</v>
+        <v>199</v>
+      </c>
+      <c r="D213" s="7">
+        <v>16848</v>
       </c>
       <c r="E213" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
     </row>
     <row r="214" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5010,16 +4971,16 @@
       </c>
       <c r="B214" s="4"/>
       <c r="C214" s="8" t="s">
-        <v>191</v>
+        <v>107</v>
       </c>
       <c r="D214" s="5">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
     </row>
     <row r="215" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5028,16 +4989,16 @@
       </c>
       <c r="B215" s="4"/>
       <c r="C215" s="8" t="s">
-        <v>192</v>
+        <v>109</v>
       </c>
       <c r="D215" s="5">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="E215" s="6" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
     </row>
     <row r="216" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5046,16 +5007,16 @@
       </c>
       <c r="B216" s="4"/>
       <c r="C216" s="8" t="s">
-        <v>193</v>
+        <v>110</v>
       </c>
       <c r="D216" s="5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
     </row>
     <row r="217" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5064,16 +5025,16 @@
       </c>
       <c r="B217" s="4"/>
       <c r="C217" s="8" t="s">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="D217" s="5">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="E217" s="6" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="218" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5082,16 +5043,16 @@
       </c>
       <c r="B218" s="4"/>
       <c r="C218" s="8" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="D218" s="5">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="219" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5100,16 +5061,16 @@
       </c>
       <c r="B219" s="4"/>
       <c r="C219" s="8" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="D219" s="5">
-        <v>18</v>
+        <v>850</v>
       </c>
       <c r="E219" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="220" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5118,34 +5079,34 @@
       </c>
       <c r="B220" s="4"/>
       <c r="C220" s="8" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D220" s="5">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>127</v>
+        <v>7</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="3">
         <v>220</v>
       </c>
       <c r="B221" s="4"/>
       <c r="C221" s="8" t="s">
-        <v>128</v>
+        <v>204</v>
       </c>
       <c r="D221" s="5">
-        <v>60</v>
+        <v>800</v>
       </c>
       <c r="E221" s="6" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
     <row r="222" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5154,16 +5115,16 @@
       </c>
       <c r="B222" s="4"/>
       <c r="C222" s="8" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D222" s="5">
-        <v>636</v>
+        <v>240</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
     <row r="223" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5172,142 +5133,142 @@
       </c>
       <c r="B223" s="4"/>
       <c r="C223" s="8" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="D223" s="5">
-        <v>168</v>
+        <v>240</v>
       </c>
       <c r="E223" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="3">
         <v>223</v>
       </c>
       <c r="B224" s="4"/>
       <c r="C224" s="8" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="D224" s="5">
-        <v>6</v>
+        <v>240</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="3">
         <v>224</v>
       </c>
       <c r="B225" s="4"/>
       <c r="C225" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="D225" s="7">
-        <v>1158</v>
+        <v>113</v>
+      </c>
+      <c r="D225" s="5">
+        <v>250</v>
       </c>
       <c r="E225" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="3">
         <v>225</v>
       </c>
       <c r="B226" s="4"/>
       <c r="C226" s="8" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="D226" s="5">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="3">
         <v>226</v>
       </c>
       <c r="B227" s="4"/>
       <c r="C227" s="8" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="D227" s="5">
-        <v>18</v>
+        <v>420</v>
       </c>
       <c r="E227" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="3">
         <v>227</v>
       </c>
       <c r="B228" s="4"/>
       <c r="C228" s="8" t="s">
-        <v>153</v>
+        <v>209</v>
       </c>
       <c r="D228" s="5">
-        <v>72</v>
+        <v>600</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="229" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="3">
         <v>228</v>
       </c>
       <c r="B229" s="4"/>
       <c r="C229" s="8" t="s">
-        <v>154</v>
+        <v>210</v>
       </c>
       <c r="D229" s="5">
-        <v>18</v>
+        <v>250</v>
       </c>
       <c r="E229" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="3">
         <v>229</v>
       </c>
       <c r="B230" s="4"/>
       <c r="C230" s="8" t="s">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="D230" s="5">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
     <row r="231" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5316,16 +5277,16 @@
       </c>
       <c r="B231" s="4"/>
       <c r="C231" s="8" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="D231" s="5">
-        <v>12</v>
+        <v>500</v>
       </c>
       <c r="E231" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="232" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5334,268 +5295,268 @@
       </c>
       <c r="B232" s="4"/>
       <c r="C232" s="8" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="D232" s="5">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="3">
         <v>232</v>
       </c>
       <c r="B233" s="4"/>
       <c r="C233" s="8" t="s">
-        <v>204</v>
+        <v>115</v>
       </c>
       <c r="D233" s="5">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E233" s="6" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="3">
         <v>233</v>
       </c>
       <c r="B234" s="4"/>
       <c r="C234" s="8" t="s">
-        <v>205</v>
+        <v>117</v>
       </c>
       <c r="D234" s="5">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E234" s="6" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="3">
         <v>234</v>
       </c>
       <c r="B235" s="4"/>
       <c r="C235" s="8" t="s">
-        <v>206</v>
+        <v>118</v>
       </c>
       <c r="D235" s="5">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="E235" s="6" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="3">
         <v>235</v>
       </c>
       <c r="B236" s="4"/>
       <c r="C236" s="8" t="s">
-        <v>207</v>
+        <v>119</v>
       </c>
       <c r="D236" s="5">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="3">
         <v>236</v>
       </c>
       <c r="B237" s="4"/>
       <c r="C237" s="8" t="s">
-        <v>208</v>
+        <v>120</v>
       </c>
       <c r="D237" s="5">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="E237" s="6" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="238" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="3">
         <v>237</v>
       </c>
       <c r="B238" s="4"/>
       <c r="C238" s="8" t="s">
-        <v>209</v>
+        <v>121</v>
       </c>
       <c r="D238" s="5">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>7</v>
+        <v>122</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="3">
         <v>238</v>
       </c>
       <c r="B239" s="4"/>
       <c r="C239" s="8" t="s">
-        <v>210</v>
+        <v>123</v>
       </c>
       <c r="D239" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E239" s="6" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="240" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="3">
         <v>239</v>
       </c>
       <c r="B240" s="4"/>
       <c r="C240" s="8" t="s">
-        <v>211</v>
+        <v>124</v>
       </c>
       <c r="D240" s="5">
-        <v>594.17999999999995</v>
+        <v>6</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="3">
         <v>240</v>
       </c>
       <c r="B241" s="4"/>
       <c r="C241" s="8" t="s">
-        <v>212</v>
+        <v>125</v>
       </c>
       <c r="D241" s="5">
-        <v>754.4</v>
+        <v>1</v>
       </c>
       <c r="E241" s="6" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="3">
         <v>241</v>
       </c>
       <c r="B242" s="4"/>
       <c r="C242" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="D242" s="7">
-        <v>1808.82</v>
+        <v>126</v>
+      </c>
+      <c r="D242" s="5">
+        <v>1</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="3">
         <v>242</v>
       </c>
       <c r="B243" s="4"/>
       <c r="C243" s="8" t="s">
-        <v>214</v>
+        <v>127</v>
       </c>
       <c r="D243" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E243" s="6" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="3">
         <v>243</v>
       </c>
       <c r="B244" s="4"/>
       <c r="C244" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="D244" s="7">
-        <v>14270.1</v>
+        <v>128</v>
+      </c>
+      <c r="D244" s="5">
+        <v>10</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="3">
         <v>244</v>
       </c>
       <c r="B245" s="4"/>
       <c r="C245" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="D245" s="7">
-        <v>16848</v>
+        <v>129</v>
+      </c>
+      <c r="D245" s="5">
+        <v>2</v>
       </c>
       <c r="E245" s="6" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="3">
         <v>245</v>
       </c>
       <c r="B246" s="4"/>
       <c r="C246" s="8" t="s">
-        <v>217</v>
+        <v>130</v>
       </c>
       <c r="D246" s="5">
-        <v>165.06</v>
+        <v>2</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="247" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5604,16 +5565,16 @@
       </c>
       <c r="B247" s="4"/>
       <c r="C247" s="8" t="s">
-        <v>218</v>
+        <v>131</v>
       </c>
       <c r="D247" s="5">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E247" s="6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="248" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5622,19 +5583,19 @@
       </c>
       <c r="B248" s="4"/>
       <c r="C248" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D248" s="5">
+        <v>264</v>
+      </c>
+      <c r="E248" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F248" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D248" s="5">
-        <v>0.63</v>
-      </c>
-      <c r="E248" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F248" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="249" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="3">
         <v>248</v>
       </c>
@@ -5642,68 +5603,68 @@
       <c r="C249" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="D249" s="5">
-        <v>10</v>
+      <c r="D249" s="7">
+        <v>8580</v>
       </c>
       <c r="E249" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="3">
         <v>249</v>
       </c>
       <c r="B250" s="4"/>
       <c r="C250" s="8" t="s">
-        <v>137</v>
+        <v>214</v>
       </c>
       <c r="D250" s="5">
-        <v>2</v>
+        <v>528</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="3">
         <v>250</v>
       </c>
       <c r="B251" s="4"/>
       <c r="C251" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D251" s="5">
-        <v>4</v>
+        <v>330</v>
       </c>
       <c r="E251" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="3">
         <v>251</v>
       </c>
       <c r="B252" s="4"/>
       <c r="C252" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="D252" s="5">
-        <v>60</v>
+        <v>137</v>
+      </c>
+      <c r="D252" s="7">
+        <v>3960</v>
       </c>
       <c r="E252" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="253" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5712,16 +5673,16 @@
       </c>
       <c r="B253" s="4"/>
       <c r="C253" s="8" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D253" s="5">
-        <v>850</v>
+        <v>270</v>
       </c>
       <c r="E253" s="6" t="s">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="254" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5730,16 +5691,16 @@
       </c>
       <c r="B254" s="4"/>
       <c r="C254" s="8" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D254" s="5">
-        <v>240</v>
+        <v>774</v>
       </c>
       <c r="E254" s="6" t="s">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="255" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5748,16 +5709,16 @@
       </c>
       <c r="B255" s="4"/>
       <c r="C255" s="8" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D255" s="5">
-        <v>100</v>
+        <v>720</v>
       </c>
       <c r="E255" s="6" t="s">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="F255" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="256" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -5766,232 +5727,34 @@
       </c>
       <c r="B256" s="4"/>
       <c r="C256" s="8" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D256" s="5">
-        <v>800</v>
+        <v>648</v>
       </c>
       <c r="E256" s="6" t="s">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="3">
         <v>256</v>
       </c>
       <c r="B257" s="4"/>
       <c r="C257" s="8" t="s">
-        <v>224</v>
+        <v>50</v>
       </c>
       <c r="D257" s="5">
-        <v>240</v>
+        <v>1</v>
       </c>
       <c r="E257" s="6" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F257" s="4" t="s">
         <v>139</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A258" s="3">
-        <v>257</v>
-      </c>
-      <c r="B258" s="4"/>
-      <c r="C258" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="D258" s="5">
-        <v>240</v>
-      </c>
-      <c r="E258" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F258" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A259" s="3">
-        <v>258</v>
-      </c>
-      <c r="B259" s="4"/>
-      <c r="C259" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="D259" s="5">
-        <v>240</v>
-      </c>
-      <c r="E259" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F259" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A260" s="3">
-        <v>259</v>
-      </c>
-      <c r="B260" s="4"/>
-      <c r="C260" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="D260" s="5">
-        <v>250</v>
-      </c>
-      <c r="E260" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F260" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A261" s="3">
-        <v>260</v>
-      </c>
-      <c r="B261" s="4"/>
-      <c r="C261" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="D261" s="5">
-        <v>250</v>
-      </c>
-      <c r="E261" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F261" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A262" s="3">
-        <v>261</v>
-      </c>
-      <c r="B262" s="4"/>
-      <c r="C262" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="D262" s="5">
-        <v>420</v>
-      </c>
-      <c r="E262" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F262" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A263" s="3">
-        <v>262</v>
-      </c>
-      <c r="B263" s="4"/>
-      <c r="C263" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="D263" s="5">
-        <v>600</v>
-      </c>
-      <c r="E263" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F263" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A264" s="3">
-        <v>263</v>
-      </c>
-      <c r="B264" s="4"/>
-      <c r="C264" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="D264" s="5">
-        <v>250</v>
-      </c>
-      <c r="E264" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F264" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A265" s="3">
-        <v>264</v>
-      </c>
-      <c r="B265" s="4"/>
-      <c r="C265" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="D265" s="5">
-        <v>500</v>
-      </c>
-      <c r="E265" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F265" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A266" s="3">
-        <v>265</v>
-      </c>
-      <c r="B266" s="4"/>
-      <c r="C266" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="D266" s="5">
-        <v>500</v>
-      </c>
-      <c r="E266" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F266" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A267" s="3">
-        <v>266</v>
-      </c>
-      <c r="B267" s="4"/>
-      <c r="C267" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="D267" s="5">
-        <v>36</v>
-      </c>
-      <c r="E267" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F267" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A268" s="3">
-        <v>267</v>
-      </c>
-      <c r="B268" s="4"/>
-      <c r="C268" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="D268" s="5">
-        <v>132</v>
-      </c>
-      <c r="E268" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F268" s="4" t="s">
-        <v>143</v>
       </c>
     </row>
   </sheetData>
